--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB43EDB-C269-9344-AA48-45068F5A75BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBA4442-9BDC-FE45-88C5-4C3F548E37AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="10" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -129,7 +129,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -139,12 +160,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2352,6 +2382,9 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2361,15 +2394,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2377,6 +2401,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12724,7 +12754,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12764,10 +12794,8 @@
     <v>259.92</v>
     <v>121.99</v>
     <v>1.6536999999999999</v>
-    <v>-3.99</v>
-    <v>-2.6318999999999999E-2</v>
-    <v>-0.33</v>
-    <v>-2.2360000000000001E-3</v>
+    <v>1.75</v>
+    <v>1.1856E-2</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12775,36 +12803,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>153.72999999999999</v>
+    <v>150.4999</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46234.999977198437</v>
+    <v>46237.67884743047</v>
     <v>4</v>
-    <v>146.15</v>
-    <v>154990500000</v>
+    <v>142.88999999999999</v>
+    <v>156828000000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>152.96</v>
-    <v>17.545500000000001</v>
-    <v>151.6</v>
+    <v>147.04</v>
+    <v>17.286200000000001</v>
     <v>147.61000000000001</v>
-    <v>147.28</v>
+    <v>149.36000000000001</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>13811248</v>
-    <v>16447152</v>
+    <v>6911420</v>
+    <v>15604431</v>
     <v>1991</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12823,7 +12865,7 @@
     <v>US</v>
     <v>47.47</v>
     <v>Index</v>
-    <v>7</v>
+    <v>10</v>
     <v>46.82</v>
     <v>10 Y TSY YLD NDX</v>
     <v>46.84</v>
@@ -12833,13 +12875,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12873,8 +12915,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12896,7 +12936,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12906,6 +12945,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12941,7 +12985,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12952,16 +12996,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13062,19 +13103,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13155,9 +13190,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13165,9 +13197,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13659,18 +13688,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="235" t="s">
+      <c r="B2" s="236" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="236"/>
-      <c r="E2" s="235" t="s">
+      <c r="C2" s="237"/>
+      <c r="E2" s="236" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="236"/>
-      <c r="H2" s="235" t="s">
+      <c r="F2" s="237"/>
+      <c r="H2" s="236" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="236"/>
+      <c r="I2" s="237"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13685,7 +13714,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>156761.82</v>
+        <v>158620.32</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13693,7 +13722,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>121.38647913950457</v>
+        <v>121.26353957751137</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13709,7 +13738,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>163727.82</v>
+        <v>165586.32</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13717,7 +13746,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>194.59142710127779</v>
+        <v>194.52182717807352</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13726,7 +13755,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>147.61000000000001</v>
+        <v>149.36000000000001</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13748,16 +13777,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>147.28</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>16.682220046178855</v>
+        <v>16.879997195970962</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13765,7 +13794,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>161.92822244511768</v>
+        <v>161.86968320408795</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13774,14 +13803,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-3.99</v>
+        <v>1.75</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>3.5991409866569852</v>
+        <v>3.6418108377961338</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13789,23 +13818,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>168.91246885530501</v>
+        <v>168.84969917374821</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.33</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.5763694246468943E-2</v>
+        <v>4.5227496704079273E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13813,7 +13842,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.14431589225191377</v>
+        <v>0.13048807695332212</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13822,30 +13851,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.6318999999999999E-2</v>
+        <v>1.1856E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>5.9944060037084509E-2</v>
+        <v>5.9241716002102603E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.2360000000000001E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>5.9006714772768011E-2</v>
+        <v>5.8315353291432018E-2</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>413</v>
@@ -13868,7 +13897,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>2.4320845471174038E-2</v>
+        <v>2.4035886448848416E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13909,7 +13938,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>16447152</v>
+        <v>15604431</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13925,7 +13954,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-4.4436840552119133E-2</v>
+        <v>-4.3916189300336805E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13938,10 +13967,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="238" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="237"/>
+      <c r="C17" s="238"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -14014,14 +14043,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="238" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="237"/>
-      <c r="E25" s="235" t="s">
+      <c r="C25" s="238"/>
+      <c r="E25" s="236" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="236"/>
+      <c r="F25" s="237"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14030,7 +14059,7 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
@@ -14070,15 +14099,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="238" t="s">
+      <c r="B33" s="235" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="238"/>
-      <c r="D33" s="238"/>
-      <c r="E33" s="238"/>
-      <c r="F33" s="238"/>
-      <c r="G33" s="238"/>
-      <c r="H33" s="238"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14097,24 +14126,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="238"/>
-      <c r="C39" s="238"/>
-      <c r="D39" s="238"/>
-      <c r="E39" s="238"/>
-      <c r="F39" s="238"/>
-      <c r="G39" s="238"/>
-      <c r="H39" s="238"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="238" t="s">
+      <c r="B42" s="235" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="238"/>
-      <c r="D42" s="238"/>
-      <c r="E42" s="238"/>
-      <c r="F42" s="238"/>
-      <c r="G42" s="238"/>
-      <c r="H42" s="238"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14198,24 +14227,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="238"/>
-      <c r="C55" s="238"/>
-      <c r="D55" s="238"/>
-      <c r="E55" s="238"/>
-      <c r="F55" s="238"/>
-      <c r="G55" s="238"/>
-      <c r="H55" s="238"/>
+      <c r="B55" s="235"/>
+      <c r="C55" s="235"/>
+      <c r="D55" s="235"/>
+      <c r="E55" s="235"/>
+      <c r="F55" s="235"/>
+      <c r="G55" s="235"/>
+      <c r="H55" s="235"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="238" t="s">
+      <c r="B58" s="235" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="238"/>
-      <c r="D58" s="238"/>
-      <c r="E58" s="238"/>
-      <c r="F58" s="238"/>
-      <c r="G58" s="238"/>
-      <c r="H58" s="238"/>
+      <c r="C58" s="235"/>
+      <c r="D58" s="235"/>
+      <c r="E58" s="235"/>
+      <c r="F58" s="235"/>
+      <c r="G58" s="235"/>
+      <c r="H58" s="235"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14353,28 +14382,28 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="238"/>
-      <c r="C75" s="238"/>
-      <c r="D75" s="238"/>
-      <c r="E75" s="238"/>
-      <c r="F75" s="238"/>
-      <c r="G75" s="238"/>
-      <c r="H75" s="238"/>
+      <c r="B75" s="235"/>
+      <c r="C75" s="235"/>
+      <c r="D75" s="235"/>
+      <c r="E75" s="235"/>
+      <c r="F75" s="235"/>
+      <c r="G75" s="235"/>
+      <c r="H75" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B75:H75"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14444,36 +14473,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="238" t="s">
+      <c r="S2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="238" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14632,23 +14661,23 @@
         <v>27793</v>
       </c>
       <c r="H6" s="64">
-        <f>G6+G6*H16</f>
+        <f t="shared" ref="H6:L7" si="1">G6+G6*H16</f>
         <v>23624.05</v>
       </c>
       <c r="I6" s="64">
-        <f>H6+H6*I16</f>
+        <f t="shared" si="1"/>
         <v>17718.037499999999</v>
       </c>
       <c r="J6" s="64">
-        <f>I6+I6*J16</f>
+        <f t="shared" si="1"/>
         <v>19312.660874999998</v>
       </c>
       <c r="K6" s="64">
-        <f>J6+J6*K16</f>
+        <f t="shared" si="1"/>
         <v>21243.926962499998</v>
       </c>
       <c r="L6" s="64">
-        <f>K6+K6*L16</f>
+        <f t="shared" si="1"/>
         <v>24430.516006874997</v>
       </c>
       <c r="N6" s="90" t="s">
@@ -14731,23 +14760,23 @@
         <v>3957</v>
       </c>
       <c r="H7" s="64">
-        <f>G7+G7*H17</f>
+        <f t="shared" si="1"/>
         <v>6331.2</v>
       </c>
       <c r="I7" s="64">
-        <f>H7+H7*I17</f>
+        <f t="shared" si="1"/>
         <v>6964.32</v>
       </c>
       <c r="J7" s="64">
-        <f>I7+I7*J17</f>
+        <f t="shared" si="1"/>
         <v>8357.1839999999993</v>
       </c>
       <c r="K7" s="64">
-        <f>J7+J7*K17</f>
+        <f t="shared" si="1"/>
         <v>11282.198399999999</v>
       </c>
       <c r="L7" s="64">
-        <f>K7+K7*L17</f>
+        <f t="shared" si="1"/>
         <v>14666.857919999999</v>
       </c>
       <c r="N7" s="90" t="s">
@@ -14758,7 +14787,7 @@
         <v>395</v>
       </c>
       <c r="R7" s="223" t="str">
-        <f t="shared" ref="R7:R11" si="1">B7</f>
+        <f t="shared" ref="R7:R11" si="2">B7</f>
         <v>Automotive</v>
       </c>
       <c r="S7" s="88">
@@ -14800,7 +14829,7 @@
       <c r="AB7" s="64"/>
       <c r="AC7" s="64"/>
       <c r="AE7" s="64">
-        <f t="shared" ref="AE7:AE11" si="2">SUM(X7:AA7)</f>
+        <f t="shared" ref="AE7:AE11" si="3">SUM(X7:AA7)</f>
         <v>6238.2</v>
       </c>
     </row>
@@ -14838,15 +14867,15 @@
         <v>7505.0014000000001</v>
       </c>
       <c r="J8" s="64">
-        <f t="shared" ref="J8:L8" si="3">I8+I8*J18</f>
+        <f t="shared" ref="J8:L8" si="4">I8+I8*J18</f>
         <v>8030.351498</v>
       </c>
       <c r="K8" s="64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8592.4761028600005</v>
       </c>
       <c r="L8" s="64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9193.9494300602</v>
       </c>
       <c r="N8" s="90" t="s">
@@ -14857,7 +14886,7 @@
         <v>396</v>
       </c>
       <c r="R8" s="223" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>IoT</v>
       </c>
       <c r="S8" s="88">
@@ -14899,7 +14928,7 @@
       <c r="AB8" s="64"/>
       <c r="AC8" s="64"/>
       <c r="AE8" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7348.5</v>
       </c>
     </row>
@@ -14920,15 +14949,15 @@
         <v>5000</v>
       </c>
       <c r="J9" s="64">
-        <f t="shared" ref="J9:L9" si="4">I9+I9*J19</f>
+        <f t="shared" ref="J9:L9" si="5">I9+I9*J19</f>
         <v>7000</v>
       </c>
       <c r="K9" s="64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14000</v>
       </c>
       <c r="L9" s="64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>18200</v>
       </c>
       <c r="N9" s="90" t="s">
@@ -14956,7 +14985,7 @@
       <c r="AB9" s="64"/>
       <c r="AC9" s="64"/>
       <c r="AE9" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -14990,26 +15019,26 @@
         <v>36969.270000000004</v>
       </c>
       <c r="I10" s="64">
-        <f t="shared" ref="I10:L10" si="5">SUM(I6:I9)</f>
+        <f t="shared" ref="I10:L10" si="6">SUM(I6:I9)</f>
         <v>37187.358899999999</v>
       </c>
       <c r="J10" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>42700.196372999999</v>
       </c>
       <c r="K10" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>55118.60146536</v>
       </c>
       <c r="L10" s="64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>66491.323356935201</v>
       </c>
       <c r="N10" s="90"/>
       <c r="O10" s="5"/>
       <c r="Q10" s="90"/>
       <c r="R10" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>QCT</v>
       </c>
       <c r="S10" s="88">
@@ -15051,7 +15080,7 @@
       <c r="AB10" s="64"/>
       <c r="AC10" s="64"/>
       <c r="AE10" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>36589.5</v>
       </c>
     </row>
@@ -15085,19 +15114,19 @@
         <v>5247.08</v>
       </c>
       <c r="I11" s="64">
-        <f t="shared" ref="I11:L11" si="6">H11+H11*I21</f>
+        <f t="shared" ref="I11:L11" si="7">H11+H11*I21</f>
         <v>5089.6675999999998</v>
       </c>
       <c r="J11" s="64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5191.4609519999995</v>
       </c>
       <c r="K11" s="64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5347.2047805599996</v>
       </c>
       <c r="L11" s="64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5507.6209239767995</v>
       </c>
       <c r="N11" s="90" t="s">
@@ -15108,7 +15137,7 @@
         <v>397</v>
       </c>
       <c r="R11" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>QTL</v>
       </c>
       <c r="S11" s="88">
@@ -15150,7 +15179,7 @@
       <c r="AB11" s="64"/>
       <c r="AC11" s="64"/>
       <c r="AE11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5555.5599999999995</v>
       </c>
     </row>
@@ -15183,19 +15212,19 @@
         <v>42216.350000000006</v>
       </c>
       <c r="I12" s="94">
-        <f t="shared" ref="I12:L12" si="7">I10+I11</f>
+        <f t="shared" ref="I12:L12" si="8">I10+I11</f>
         <v>42277.0265</v>
       </c>
       <c r="J12" s="94">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>47891.657325</v>
       </c>
       <c r="K12" s="94">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>60465.806245920001</v>
       </c>
       <c r="L12" s="94">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>71998.944280911994</v>
       </c>
       <c r="O12" s="5"/>
@@ -15283,43 +15312,43 @@
         <v>115</v>
       </c>
       <c r="C15" s="12">
-        <f t="shared" ref="C15:L15" si="8">C5</f>
+        <f t="shared" ref="C15:L15" si="9">C5</f>
         <v>2021</v>
       </c>
       <c r="D15" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2022</v>
       </c>
       <c r="E15" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2023</v>
       </c>
       <c r="F15" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2024</v>
       </c>
       <c r="G15" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2025</v>
       </c>
       <c r="H15" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2026</v>
       </c>
       <c r="I15" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2027</v>
       </c>
       <c r="J15" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2028</v>
       </c>
       <c r="K15" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2029</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2030</v>
       </c>
       <c r="O15" s="5"/>
@@ -15328,47 +15357,47 @@
         <v>115</v>
       </c>
       <c r="S15" s="12" t="str">
-        <f t="shared" ref="S15:AC15" si="9">S5</f>
+        <f t="shared" ref="S15:AC15" si="10">S5</f>
         <v>Q4 2024</v>
       </c>
       <c r="T15" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Q1 2025</v>
       </c>
       <c r="U15" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Q2 2025</v>
       </c>
       <c r="V15" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Q3 2025</v>
       </c>
       <c r="W15" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Q4 2025</v>
       </c>
       <c r="X15" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Q1 2026</v>
       </c>
       <c r="Y15" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Q2 2026</v>
       </c>
       <c r="Z15" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Q3 2026</v>
       </c>
       <c r="AA15" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>FQ1</v>
       </c>
       <c r="AB15" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>FQ2</v>
       </c>
       <c r="AC15" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>FQ3</v>
       </c>
     </row>
@@ -15379,19 +15408,19 @@
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="95">
-        <f t="shared" ref="D16:G16" si="10">D6/C6-1</f>
+        <f t="shared" ref="D16:G16" si="11">D6/C6-1</f>
         <v>0.48704693998811655</v>
       </c>
       <c r="E16" s="95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-9.8173972110121022E-2</v>
       </c>
       <c r="F16" s="95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.1015950376606114</v>
       </c>
       <c r="G16" s="96">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.11784579495636094</v>
       </c>
       <c r="H16" s="97">
@@ -15417,31 +15446,31 @@
       </c>
       <c r="S16" s="47"/>
       <c r="T16" s="95">
-        <f>T6/S6-1</f>
+        <f t="shared" ref="T16:Z18" si="12">T6/S6-1</f>
         <v>0.24245406824146976</v>
       </c>
       <c r="U16" s="95">
-        <f>U6/T6-1</f>
+        <f t="shared" si="12"/>
         <v>-8.5159757063638764E-2</v>
       </c>
       <c r="V16" s="95">
-        <f>V6/U6-1</f>
+        <f t="shared" si="12"/>
         <v>-8.673690287198732E-2</v>
       </c>
       <c r="W16" s="95">
-        <f>W6/V6-1</f>
+        <f t="shared" si="12"/>
         <v>0.10003160556257895</v>
       </c>
       <c r="X16" s="95">
-        <f>X6/W6-1</f>
+        <f t="shared" si="12"/>
         <v>0.12397644016664278</v>
       </c>
       <c r="Y16" s="95">
-        <f>Y6/X6-1</f>
+        <f t="shared" si="12"/>
         <v>-0.23006134969325154</v>
       </c>
       <c r="Z16" s="96">
-        <f>Z6/Y6-1</f>
+        <f t="shared" si="12"/>
         <v>-0.15571049136786186</v>
       </c>
       <c r="AA16" s="97">
@@ -15457,19 +15486,19 @@
       </c>
       <c r="C17" s="47"/>
       <c r="D17" s="95">
-        <f t="shared" ref="D17:G17" si="11">D7/C7-1</f>
+        <f t="shared" ref="D17:G17" si="13">D7/C7-1</f>
         <v>0.40717948717948715</v>
       </c>
       <c r="E17" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.36443148688046656</v>
       </c>
       <c r="F17" s="95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.55448717948717952</v>
       </c>
       <c r="G17" s="96">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.35979381443298974</v>
       </c>
       <c r="H17" s="97">
@@ -15495,31 +15524,31 @@
       </c>
       <c r="S17" s="47"/>
       <c r="T17" s="95">
-        <f>T7/S7-1</f>
+        <f t="shared" si="12"/>
         <v>6.8965517241379226E-2</v>
       </c>
       <c r="U17" s="95">
-        <f>U7/T7-1</f>
+        <f t="shared" si="12"/>
         <v>-2.0811654526534662E-3</v>
       </c>
       <c r="V17" s="95">
-        <f>V7/U7-1</f>
+        <f t="shared" si="12"/>
         <v>2.6068821689259725E-2</v>
       </c>
       <c r="W17" s="95">
-        <f>W7/V7-1</f>
+        <f t="shared" si="12"/>
         <v>7.0121951219512146E-2</v>
       </c>
       <c r="X17" s="95">
-        <f>X7/W7-1</f>
+        <f t="shared" si="12"/>
         <v>4.5584045584045496E-2</v>
       </c>
       <c r="Y17" s="95">
-        <f>Y7/X7-1</f>
+        <f t="shared" si="12"/>
         <v>0.20435967302452318</v>
       </c>
       <c r="Z17" s="96">
-        <f>Z7/Y7-1</f>
+        <f t="shared" si="12"/>
         <v>0.19758672699849167</v>
       </c>
       <c r="AA17" s="97">
@@ -15573,31 +15602,31 @@
       </c>
       <c r="S18" s="47"/>
       <c r="T18" s="95">
-        <f>T8/S8-1</f>
+        <f t="shared" si="12"/>
         <v>-7.9619726678550218E-2</v>
       </c>
       <c r="U18" s="95">
-        <f>U8/T8-1</f>
+        <f t="shared" si="12"/>
         <v>2.0658489347966436E-2</v>
       </c>
       <c r="V18" s="95">
-        <f>V8/U8-1</f>
+        <f t="shared" si="12"/>
         <v>6.3251106894370634E-2</v>
       </c>
       <c r="W18" s="95">
-        <f>W8/V8-1</f>
+        <f t="shared" si="12"/>
         <v>7.4955383700178402E-2</v>
       </c>
       <c r="X18" s="95">
-        <f>X8/W8-1</f>
+        <f t="shared" si="12"/>
         <v>-6.585500830105151E-2</v>
       </c>
       <c r="Y18" s="95">
-        <f>Y8/X8-1</f>
+        <f t="shared" si="12"/>
         <v>2.2511848341232321E-2</v>
       </c>
       <c r="Z18" s="96">
-        <f>Z8/Y8-1</f>
+        <f t="shared" si="12"/>
         <v>6.0254924681344191E-2</v>
       </c>
       <c r="AA18" s="97">
@@ -15660,15 +15689,15 @@
         <v>0.39446315555720046</v>
       </c>
       <c r="E20" s="95">
-        <f t="shared" ref="E20:E21" si="12">E10/D10-1</f>
+        <f t="shared" ref="E20:E21" si="14">E10/D10-1</f>
         <v>-0.19361944953154442</v>
       </c>
       <c r="F20" s="95">
-        <f t="shared" ref="F20:F21" si="13">F10/E10-1</f>
+        <f t="shared" ref="F20:F21" si="15">F10/E10-1</f>
         <v>9.2620630636561119E-2</v>
       </c>
       <c r="G20" s="96">
-        <f t="shared" ref="G20:G21" si="14">G10/F10-1</f>
+        <f t="shared" ref="G20:G21" si="16">G10/F10-1</f>
         <v>0.15577177973249778</v>
       </c>
       <c r="H20" s="95">
@@ -15676,25 +15705,25 @@
         <v>-3.6430526233481753E-2</v>
       </c>
       <c r="I20" s="95">
-        <f t="shared" ref="I20:L20" si="15">I10/H10-1</f>
+        <f t="shared" ref="I20:L20" si="17">I10/H10-1</f>
         <v>5.8991941144630466E-3</v>
       </c>
       <c r="J20" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.14824493150547458</v>
       </c>
       <c r="K20" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.2908278215837985</v>
       </c>
       <c r="L20" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.20633182971310582</v>
       </c>
       <c r="O20" s="5"/>
       <c r="Q20" s="91"/>
       <c r="R20" s="1" t="str">
-        <f t="shared" ref="R20:R22" si="16">R10</f>
+        <f t="shared" ref="R20:R22" si="18">R10</f>
         <v>QCT</v>
       </c>
       <c r="S20" s="47"/>
@@ -15703,23 +15732,23 @@
         <v>0.16201889836367833</v>
       </c>
       <c r="U20" s="95">
-        <f t="shared" ref="U20:Y20" si="17">U10/T10-1</f>
+        <f t="shared" ref="U20:Y20" si="19">U10/T10-1</f>
         <v>-6.0987703292344264E-2</v>
       </c>
       <c r="V20" s="95">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-5.0269299820466795E-2</v>
       </c>
       <c r="W20" s="95">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>9.2071611253196961E-2</v>
       </c>
       <c r="X20" s="95">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>8.0643518989919505E-2</v>
       </c>
       <c r="Y20" s="95">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-0.14482238763780264</v>
       </c>
       <c r="Z20" s="96">
@@ -15742,15 +15771,15 @@
         <v>6.0126582278481333E-3</v>
       </c>
       <c r="E21" s="95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.16546083674111356</v>
       </c>
       <c r="F21" s="95">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>5.0131926121371961E-2</v>
       </c>
       <c r="G21" s="96">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.7946877243359971E-3</v>
       </c>
       <c r="H21" s="97">
@@ -15771,7 +15800,7 @@
       <c r="O21" s="5"/>
       <c r="Q21" s="91"/>
       <c r="R21" s="1" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>QTL</v>
       </c>
       <c r="S21" s="47"/>
@@ -15780,27 +15809,27 @@
         <v>0.51231527093596063</v>
       </c>
       <c r="U21" s="95">
-        <f t="shared" ref="U21:Z21" si="18">U11/T11-1</f>
+        <f t="shared" ref="U21:Z21" si="20">U11/T11-1</f>
         <v>-0.14071661237785016</v>
       </c>
       <c r="V21" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-7.5815011372248886E-4</v>
       </c>
       <c r="W21" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>6.9044006069802766E-2</v>
       </c>
       <c r="X21" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.12987934705464865</v>
       </c>
       <c r="Y21" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-0.13190954773869346</v>
       </c>
       <c r="Z21" s="96">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-7.5253256150506487E-2</v>
       </c>
       <c r="AA21" s="97">
@@ -15816,78 +15845,78 @@
       </c>
       <c r="C22" s="47"/>
       <c r="D22" s="103">
-        <f t="shared" ref="D22:L22" si="19">D12/C12-1</f>
+        <f t="shared" ref="D22:L22" si="21">D12/C12-1</f>
         <v>0.31680867544539115</v>
       </c>
       <c r="E22" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-0.18959276018099547</v>
       </c>
       <c r="F22" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>8.7716359575656044E-2</v>
       </c>
       <c r="G22" s="104">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.13659463066577682</v>
       </c>
       <c r="H22" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-4.6690678348839221E-2</v>
       </c>
       <c r="I22" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1.4372748946793745E-3</v>
       </c>
       <c r="J22" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.13280571719016243</v>
       </c>
       <c r="K22" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.26255405687027977</v>
       </c>
       <c r="L22" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.19073818329793957</v>
       </c>
       <c r="O22" s="5"/>
       <c r="Q22" s="91"/>
       <c r="R22" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>Total</v>
       </c>
       <c r="S22" s="47"/>
       <c r="T22" s="103">
-        <f t="shared" ref="T22:AA22" si="20">T12/S12-1</f>
+        <f t="shared" ref="T22:AA22" si="22">T12/S12-1</f>
         <v>0.13910581803982813</v>
       </c>
       <c r="U22" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-5.9131030936669826E-2</v>
       </c>
       <c r="V22" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-4.681664996812096E-2</v>
       </c>
       <c r="W22" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>7.6923076923076872E-2</v>
       </c>
       <c r="X22" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>8.7133984028394007E-2</v>
       </c>
       <c r="Y22" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-0.13491674828599409</v>
       </c>
       <c r="Z22" s="104">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-6.1515237286536517E-2</v>
       </c>
       <c r="AA22" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-2.4825575550417311E-2</v>
       </c>
       <c r="AB22" s="103"/>
@@ -15943,35 +15972,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="P2" s="238" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -17202,20 +17231,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="247"/>
       <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -18608,12 +18637,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18621,6 +18644,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18658,20 +18687,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="S2" s="249"/>
       <c r="T2" s="249"/>
       <c r="U2" s="249"/>
@@ -19680,16 +19709,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19752,10 +19781,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="235" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19772,7 +19801,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>147.61000000000001</v>
+        <v>149.36000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19781,7 +19810,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>156761.82</v>
+        <v>158620.32</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19840,10 +19869,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="238"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19851,7 +19880,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>8.8762648677436537E-2</v>
+        <v>8.7813973773813281E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19860,7 +19889,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.91123735132256345</v>
+        <v>0.91218602622618672</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19887,7 +19916,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11480086002130303</v>
+        <v>0.1148763759666438</v>
       </c>
     </row>
   </sheetData>
@@ -19932,20 +19961,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="247"/>
       <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -20138,7 +20167,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>180404.90123376483</v>
+        <v>180253.32139407666</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20192,23 +20221,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5660.2488117013108</v>
+        <v>5659.8654157938417</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3398.6899369290586</v>
+        <v>3398.2295332523991</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5325.4819719238249</v>
+        <v>5324.3998836099008</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7538.5212962715987</v>
+        <v>7536.4790223941563</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>9179.4886118357481</v>
+        <v>9176.3801781370694</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20227,14 +20256,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>104776.01021749231</v>
+        <v>104652.52499812971</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="238" t="s">
+      <c r="B13" s="235" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="238"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20250,14 +20279,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11480086002130303</v>
+        <v>0.1148763759666438</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="238" t="s">
+      <c r="B18" s="235" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="238"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20265,7 +20294,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31102.430628661539</v>
+        <v>31095.354033187366</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20274,7 +20303,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>104776.01021749231</v>
+        <v>104652.52499812971</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20283,7 +20312,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>135878.44084615386</v>
+        <v>135747.87903131708</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20310,7 +20339,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>128912.44084615386</v>
+        <v>128781.87903131708</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20328,7 +20357,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>121.38647913950457</v>
+        <v>121.26353957751137</v>
       </c>
     </row>
   </sheetData>
@@ -20371,20 +20400,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21316,10 +21345,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="238" t="s">
+      <c r="B37" s="235" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="238"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21337,7 +21366,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11480086002130303</v>
+        <v>0.1148763759666438</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21363,7 +21392,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>213622.09558155702</v>
+        <v>213548.18046311408</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21390,7 +21419,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>206656.09558155702</v>
+        <v>206582.18046311408</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21408,14 +21437,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>194.59142710127779</v>
+        <v>194.52182717807352</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="238" t="s">
+      <c r="B49" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="238"/>
+      <c r="C49" s="235"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21471,10 +21500,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="238" t="s">
+      <c r="B57" s="235" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="238"/>
+      <c r="C57" s="235"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21491,7 +21520,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11480086002130303</v>
+        <v>0.1148763759666438</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21517,7 +21546,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>178933.77223671498</v>
+        <v>178871.60356274139</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21544,7 +21573,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>171967.77223671498</v>
+        <v>171905.60356274139</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21562,7 +21591,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>161.92822244511768</v>
+        <v>161.86968320408795</v>
       </c>
     </row>
   </sheetData>
@@ -21614,10 +21643,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21626,7 +21655,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>121.38647913950457</v>
+        <v>121.26353957751137</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21635,7 +21664,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>194.59142710127779</v>
+        <v>194.52182717807352</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21653,7 +21682,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>161.92822244511768</v>
+        <v>161.86968320408795</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21662,7 +21691,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>168.91246885530501</v>
+        <v>168.84969917374821</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21671,7 +21700,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>147.61000000000001</v>
+        <v>149.36000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21680,7 +21709,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.14431589225191377</v>
+        <v>0.13048807695332212</v>
       </c>
     </row>
   </sheetData>
@@ -21736,20 +21765,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22112,10 +22141,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="238" t="s">
+      <c r="B20" s="235" t="s">
         <v>408</v>
       </c>
-      <c r="C20" s="238"/>
+      <c r="C20" s="235"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22216,20 +22245,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="247"/>
       <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -22404,7 +22433,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>188770.67115361802</v>
+        <v>188612.06222517093</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22458,23 +22487,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11317.714770118566</v>
+        <v>11316.948166799682</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>10862.886133578559</v>
+        <v>10861.414592247091</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10426.335841458667</v>
+        <v>10424.217307168145</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10007.329336064191</v>
+        <v>10004.618233119358</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9605.1615796063033</v>
+        <v>9601.9090010370783</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22493,7 +22522,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>109634.70301688547</v>
+        <v>109505.49151776759</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22509,7 +22538,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>147.61000000000001</v>
+        <v>149.36000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22518,7 +22547,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>147.51250540734452</v>
+        <v>147.37961792203708</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22557,7 +22586,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11480086002130303</v>
+        <v>0.1148763759666438</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22575,7 +22604,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>154990.5</v>
+        <v>156828</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22602,7 +22631,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>161956.5</v>
+        <v>163794</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22618,7 +22647,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>52219.427660826288</v>
+        <v>52209.107300371354</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22627,7 +22656,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>109634.70301688547</v>
+        <v>109505.49151776759</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22636,7 +22665,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>161854.13067771174</v>
+        <v>161714.59881813894</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22663,7 +22692,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>154888.13067771174</v>
+        <v>154748.59881813894</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22681,7 +22710,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>147.51250540734452</v>
+        <v>147.37961792203708</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -23128,17 +23157,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -23483,7 +23512,7 @@
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
       <c r="T7" s="22">
-        <f t="shared" ref="T7:Z7" si="2">T5-T6</f>
+        <f t="shared" ref="T7:Y7" si="2">T5-T6</f>
         <v>5777</v>
       </c>
       <c r="U7" s="22">
@@ -23789,7 +23818,7 @@
         <v>3390</v>
       </c>
       <c r="AA11" s="24">
-        <f t="shared" ref="U11:AA11" si="6">SUM(AA8:AA10)</f>
+        <f t="shared" ref="AA11" si="6">SUM(AA8:AA10)</f>
         <v>3651</v>
       </c>
       <c r="AC11" s="24">
@@ -24374,7 +24403,7 @@
         <v>1066</v>
       </c>
       <c r="AA20" s="25">
-        <f t="shared" ref="T20:AA20" si="9">AA19*AA$85</f>
+        <f t="shared" ref="AA20" si="9">AA19*AA$85</f>
         <v>1057</v>
       </c>
       <c r="AC20" s="25">
@@ -24533,7 +24562,7 @@
         <v>1072</v>
       </c>
       <c r="AA22" s="25">
-        <f t="shared" ref="T22:AA22" si="12">AA21*AA$85</f>
+        <f t="shared" ref="AA22" si="12">AA21*AA$85</f>
         <v>1069</v>
       </c>
       <c r="AC22" s="25">
@@ -24662,7 +24691,7 @@
         <v>1.8123827392120075</v>
       </c>
       <c r="AA24" s="65">
-        <f t="shared" ref="T24:AA24" si="14">AA23/AA$85</f>
+        <f t="shared" ref="AA24" si="14">AA23/AA$85</f>
         <v>1.89</v>
       </c>
       <c r="AC24" s="65">
@@ -24794,7 +24823,7 @@
         <v>1.8022388059701493</v>
       </c>
       <c r="AA26" s="66">
-        <f t="shared" ref="T26:AA26" si="16">AA25/AA$85</f>
+        <f t="shared" ref="AA26" si="16">AA25/AA$85</f>
         <v>1.87</v>
       </c>
       <c r="AB26" s="1"/>
@@ -25299,7 +25328,7 @@
         <v>29923</v>
       </c>
       <c r="U36" s="35">
-        <f t="shared" ref="U36:Z36" si="19">U37-U32</f>
+        <f t="shared" ref="U36:W36" si="19">U37-U32</f>
         <v>29510</v>
       </c>
       <c r="V36" s="35">
@@ -25315,7 +25344,7 @@
         <v>24389</v>
       </c>
       <c r="Y36" s="35">
-        <f t="shared" ref="Y36:Z36" si="20">Y37-Y32</f>
+        <f t="shared" ref="Y36" si="20">Y37-Y32</f>
         <v>28426</v>
       </c>
       <c r="Z36" s="35">
@@ -25678,7 +25707,7 @@
         <v>18376</v>
       </c>
       <c r="U42" s="35">
-        <f t="shared" ref="U42:Z42" si="23">U43-U40</f>
+        <f t="shared" ref="U42:W42" si="23">U43-U40</f>
         <v>18741</v>
       </c>
       <c r="V42" s="35">
@@ -25694,7 +25723,7 @@
         <v>19793</v>
       </c>
       <c r="Y42" s="35">
-        <f t="shared" ref="Y42:Z42" si="24">Y43-Y40</f>
+        <f t="shared" ref="Y42" si="24">Y43-Y40</f>
         <v>20139</v>
       </c>
       <c r="Z42" s="35">
@@ -27125,7 +27154,7 @@
         <v>1932</v>
       </c>
       <c r="AA69" s="64">
-        <f t="shared" ref="T69:AA69" si="30">AA5-AA6-AA11+AA13+AA14+AA16-AA17</f>
+        <f t="shared" ref="AA69" si="30">AA5-AA6-AA11+AA13+AA14+AA16-AA17</f>
         <v>2002</v>
       </c>
       <c r="AC69" s="64">
@@ -27201,7 +27230,7 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
       <c r="T70" s="40">
-        <f t="shared" ref="T70:Z70" si="32">T18-T69</f>
+        <f t="shared" ref="T70:Y70" si="32">T18-T69</f>
         <v>0</v>
       </c>
       <c r="U70" s="40">
@@ -27336,7 +27365,7 @@
         <v>0</v>
       </c>
       <c r="AA71" s="42">
-        <f t="shared" ref="T71:AA71" si="36">AA37-(AA43+AA111)</f>
+        <f t="shared" ref="AA71" si="36">AA37-(AA43+AA111)</f>
         <v>0</v>
       </c>
       <c r="AB71" s="16"/>
@@ -27461,19 +27490,19 @@
         <v>1071</v>
       </c>
       <c r="T75" s="25">
-        <f t="shared" ref="T75:U75" si="38">T74*T85</f>
+        <f t="shared" ref="T75" si="38">T74*T85</f>
         <v>1111</v>
       </c>
       <c r="U75" s="25">
-        <f t="shared" ref="U75:V75" si="39">U74*U85</f>
+        <f t="shared" ref="U75" si="39">U74*U85</f>
         <v>1106</v>
       </c>
       <c r="V75" s="25">
-        <f t="shared" ref="V75:W75" si="40">V74*V85</f>
+        <f t="shared" ref="V75" si="40">V74*V85</f>
         <v>1098</v>
       </c>
       <c r="W75" s="25">
-        <f t="shared" ref="W75:X75" si="41">W74*W85</f>
+        <f t="shared" ref="W75" si="41">W74*W85</f>
         <v>1079</v>
       </c>
       <c r="X75" s="25">
@@ -27489,7 +27518,7 @@
         <v>1054</v>
       </c>
       <c r="AA75" s="25">
-        <f t="shared" ref="Z75:AA75" si="43">AA74*AA85</f>
+        <f t="shared" ref="AA75" si="43">AA74*AA85</f>
         <v>1050</v>
       </c>
       <c r="AC75" s="24">
@@ -27590,7 +27619,7 @@
         <v>9</v>
       </c>
       <c r="T77" s="25">
-        <f t="shared" ref="T77:Z77" si="45">T76*T85</f>
+        <f t="shared" ref="T77:Y77" si="45">T76*T85</f>
         <v>14</v>
       </c>
       <c r="U77" s="25">
@@ -27661,7 +27690,7 @@
         <v>1080</v>
       </c>
       <c r="T78" s="25">
-        <f t="shared" ref="T78:Z78" si="48">T75+T77</f>
+        <f t="shared" ref="T78:Y78" si="48">T75+T77</f>
         <v>1125</v>
       </c>
       <c r="U78" s="25">
@@ -27879,19 +27908,19 @@
         <v>3.48</v>
       </c>
       <c r="T82" s="45">
-        <f t="shared" ref="T82:U82" si="52">T81/T85</f>
+        <f t="shared" ref="T82" si="52">T81/T85</f>
         <v>0.85</v>
       </c>
       <c r="U82" s="45">
-        <f t="shared" ref="U82:V82" si="53">U81/U85</f>
+        <f t="shared" ref="U82" si="53">U81/U85</f>
         <v>0.85</v>
       </c>
       <c r="V82" s="45">
-        <f t="shared" ref="V82:W82" si="54">V81/V85</f>
+        <f t="shared" ref="V82" si="54">V81/V85</f>
         <v>0.85</v>
       </c>
       <c r="W82" s="45">
-        <f t="shared" ref="W82:X82" si="55">W81/W85</f>
+        <f t="shared" ref="W82" si="55">W81/W85</f>
         <v>0.89</v>
       </c>
       <c r="X82" s="45">
@@ -27907,7 +27936,7 @@
         <v>0.89</v>
       </c>
       <c r="AA82" s="45">
-        <f t="shared" ref="Z82:AA82" si="57">AA81/AA85</f>
+        <f t="shared" ref="AA82" si="57">AA81/AA85</f>
         <v>0.92</v>
       </c>
       <c r="AC82" s="72">
@@ -28008,7 +28037,7 @@
         <v>0.13440860215053763</v>
       </c>
       <c r="AA83" s="46">
-        <f t="shared" ref="T83:AA83" si="60">IF(AND(AA15&gt;0,AA16&lt;0),-(AA16)/AA15,0)</f>
+        <f t="shared" ref="AA83" si="60">IF(AND(AA15&gt;0,AA16&lt;0),-(AA16)/AA15,0)</f>
         <v>0.18683996750609261</v>
       </c>
       <c r="AC83" s="46">
@@ -28219,7 +28248,7 @@
         <v>-0.13491674828599412</v>
       </c>
       <c r="AA89" s="48">
-        <f t="shared" ref="T89:AA93" si="69">IF(Z5=0,
+        <f t="shared" ref="AA89:AA93" si="69">IF(Z5=0,
 IF(AA5=0,0,IF(AA5&gt;0,1,-1)),
 (AA5-Z5)/ABS(Z5)
 )</f>
@@ -28595,7 +28624,7 @@
         <v>2.1699819168173599E-2</v>
       </c>
       <c r="AA94" s="50">
-        <f t="shared" ref="T94:AA95" si="78">IF(Z11=0,
+        <f t="shared" ref="AA94:AA95" si="78">IF(Z11=0,
 IF(AA11=0,0,IF(AA11&gt;0,1,-1)),
 (AA11-Z11)/ABS(Z11)
 )</f>
@@ -28779,7 +28808,7 @@
         <v>-0.37073583309839303</v>
       </c>
       <c r="AA96" s="52">
-        <f t="shared" ref="T96:AA96" si="86">IF(Z15=0,
+        <f t="shared" ref="AA96" si="86">IF(Z15=0,
 IF(AA15=0,0,IF(AA15&gt;0,1,-1)),
 (AA15-Z15)/ABS(Z15)
 )</f>
@@ -28892,7 +28921,7 @@
         <v>-0.35685752330226367</v>
       </c>
       <c r="AA97" s="52">
-        <f t="shared" ref="T97:AA97" si="94">IF(Z18=0,
+        <f t="shared" ref="AA97" si="94">IF(Z18=0,
 IF(AA18=0,0,IF(AA18&gt;0,1,-1)),
 (AA18-Z18)/ABS(Z18)
 )</f>
@@ -28980,7 +29009,7 @@
         <v>0.53769223511652042</v>
       </c>
       <c r="AA100" s="50">
-        <f t="shared" ref="T100:AA100" si="96">AA7/AA5</f>
+        <f t="shared" ref="AA100" si="96">AA7/AA5</f>
         <v>0.53051171207399217</v>
       </c>
       <c r="AC100" s="50">
@@ -29051,7 +29080,7 @@
         <v>0.21785074063590903</v>
       </c>
       <c r="AA101" s="50">
-        <f t="shared" ref="T101:AA101" si="98">AA12/AA5</f>
+        <f t="shared" ref="AA101" si="98">AA12/AA5</f>
         <v>0.16346637177038303</v>
       </c>
       <c r="AC101" s="50">
@@ -29125,7 +29154,7 @@
         <v>0.18228134729691481</v>
       </c>
       <c r="AA102" s="55">
-        <f t="shared" ref="T102:AA102" si="100">AA110/AA5</f>
+        <f t="shared" ref="AA102" si="100">AA110/AA5</f>
         <v>0.20126671358198453</v>
       </c>
       <c r="AB102" s="1"/>
@@ -29243,7 +29272,7 @@
         <v>0.13440860215053763</v>
       </c>
       <c r="AA105" s="81">
-        <f t="shared" ref="T105:AA105" si="103">IF(AND(AA83&gt;=0,AA12&gt;=0),AA83,0)</f>
+        <f t="shared" ref="AA105" si="103">IF(AND(AA83&gt;=0,AA12&gt;=0),AA83,0)</f>
         <v>0.18683996750609261</v>
       </c>
       <c r="AC105" s="81">
@@ -29314,7 +29343,7 @@
         <v>9799</v>
       </c>
       <c r="AA106" s="25">
-        <f t="shared" ref="T106:AA106" si="106">AA29+AA34</f>
+        <f t="shared" ref="AA106" si="106">AA29+AA34</f>
         <v>8304</v>
       </c>
       <c r="AC106" s="25">
@@ -29405,7 +29434,7 @@
         <v>15270</v>
       </c>
       <c r="AA107" s="25">
-        <f t="shared" ref="T107:AA107" si="108">AA39+AA41</f>
+        <f t="shared" ref="AA107" si="108">AA39+AA41</f>
         <v>15270</v>
       </c>
       <c r="AC107" s="25">
@@ -29523,7 +29552,7 @@
         <v>-533</v>
       </c>
       <c r="AA109" s="126">
-        <f t="shared" ref="T109:AA109" si="110">AA60+AA61</f>
+        <f t="shared" ref="AA109" si="110">AA60+AA61</f>
         <v>-496</v>
       </c>
       <c r="AC109" s="126">
@@ -29594,7 +29623,7 @@
         <v>1932</v>
       </c>
       <c r="AA110" s="126">
-        <f t="shared" ref="T110:AA110" si="112">AA17+AA18</f>
+        <f t="shared" ref="AA110" si="112">AA17+AA18</f>
         <v>2002</v>
       </c>
       <c r="AC110" s="126">
@@ -29665,7 +29694,7 @@
         <v>27278</v>
       </c>
       <c r="AA111" s="126">
-        <f t="shared" ref="T111:AA111" si="114">AA49+AA48</f>
+        <f t="shared" ref="AA111" si="114">AA49+AA48</f>
         <v>27658</v>
       </c>
       <c r="AC111" s="126">
@@ -29753,7 +29782,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>147.61000000000001</v>
+        <v>149.36000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29819,12 +29848,12 @@
         <v>127.11</v>
       </c>
       <c r="AA116" s="65">
-        <f t="shared" ref="T116:AA116" si="116">AA115/AA85</f>
+        <f t="shared" ref="AA116" si="116">AA115/AA85</f>
         <v>189.39</v>
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>147.61000000000001</v>
+        <v>149.36000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -30214,7 +30243,7 @@
         <v>9947</v>
       </c>
       <c r="AA130" s="25">
-        <f t="shared" ref="T130:AA130" si="126">AB5</f>
+        <f t="shared" ref="AA130" si="126">AB5</f>
         <v>0</v>
       </c>
       <c r="AC130" s="49"/>
@@ -30267,7 +30296,7 @@
         <v>MET</v>
       </c>
       <c r="AA131" s="227" t="str">
-        <f t="shared" ref="T131:AA131" si="128">IF(AA130&gt;AA129, "BEAT", IF(AA130&lt;AA128, "MISSED", "MET"))</f>
+        <f t="shared" ref="AA131" si="128">IF(AA130&gt;AA129, "BEAT", IF(AA130&lt;AA128, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="AC131" s="49"/>
@@ -30463,7 +30492,7 @@
         <v>BEAT</v>
       </c>
       <c r="AA135" s="227" t="str">
-        <f t="shared" ref="T135:AA135" si="135">IF(AA134&gt;AA133, "BEAT", IF(AA134&lt;AA132, "MISSED", "MET"))</f>
+        <f t="shared" ref="AA135" si="135">IF(AA134&gt;AA133, "BEAT", IF(AA134&lt;AA132, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="AC135" s="49"/>
@@ -30659,7 +30688,7 @@
         <v>MET</v>
       </c>
       <c r="AA139" s="227" t="str">
-        <f t="shared" ref="T139:AA139" si="142">IF(AA138&gt;AA137, "BEAT", IF(AA138&lt;AA136, "MISSED", "MET"))</f>
+        <f t="shared" ref="AA139" si="142">IF(AA138&gt;AA137, "BEAT", IF(AA138&lt;AA136, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="AC139" s="49"/>
@@ -30796,7 +30825,7 @@
         <v>36.911972827625249</v>
       </c>
       <c r="AA144" s="118">
-        <f t="shared" ref="T144:AA144" si="145">AA30/AA5*90</f>
+        <f t="shared" ref="AA144" si="145">AA30/AA5*90</f>
         <v>42.235850005026641</v>
       </c>
       <c r="AC144" s="118">
@@ -30857,7 +30886,7 @@
         <v>548.84081632653067</v>
       </c>
       <c r="AA145" s="118">
-        <f t="shared" ref="T145:AA145" si="147">AA31/AA6*365</f>
+        <f t="shared" ref="AA145" si="147">AA31/AA6*365</f>
         <v>654.88972162740902</v>
       </c>
       <c r="AC145" s="118">
@@ -30918,7 +30947,7 @@
         <v>54.60612244897959</v>
       </c>
       <c r="AA146" s="118">
-        <f t="shared" ref="T146:AA146" si="149">AA38/AA6*90</f>
+        <f t="shared" ref="AA146" si="149">AA38/AA6*90</f>
         <v>55.83083511777302</v>
       </c>
       <c r="AC146" s="118">
@@ -30951,19 +30980,19 @@
         <v>104.633876313809</v>
       </c>
       <c r="T147" s="118">
-        <f t="shared" ref="T147:U147" si="151">T144+T145-T146</f>
+        <f t="shared" ref="T147" si="151">T144+T145-T146</f>
         <v>507.28234241000445</v>
       </c>
       <c r="U147" s="118">
-        <f t="shared" ref="U147:V147" si="152">U144+U145-U146</f>
+        <f t="shared" ref="U147" si="152">U144+U145-U146</f>
         <v>428.13687454885917</v>
       </c>
       <c r="V147" s="118">
-        <f t="shared" ref="V147:W147" si="153">V144+V145-V146</f>
+        <f t="shared" ref="V147" si="153">V144+V145-V146</f>
         <v>443.21082749852809</v>
       </c>
       <c r="W147" s="118">
-        <f t="shared" ref="W147:X147" si="154">W144+W145-W146</f>
+        <f t="shared" ref="W147" si="154">W144+W145-W146</f>
         <v>485.91338620412233</v>
       </c>
       <c r="X147" s="118">
@@ -30979,7 +31008,7 @@
         <v>531.14666670517636</v>
       </c>
       <c r="AA147" s="118">
-        <f t="shared" ref="Z147:AA147" si="156">AA144+AA145-AA146</f>
+        <f t="shared" ref="AA147" si="156">AA144+AA145-AA146</f>
         <v>641.29473651466265</v>
       </c>
       <c r="AC147" s="118">
@@ -31040,7 +31069,7 @@
         <v>0.55979177359043919</v>
       </c>
       <c r="AA148" s="118">
-        <f t="shared" ref="T148:AA148" si="159">AA107/AA49</f>
+        <f t="shared" ref="AA148" si="159">AA107/AA49</f>
         <v>0.55210065803745756</v>
       </c>
       <c r="AC148" s="118">
@@ -31101,7 +31130,7 @@
         <v>0.20056455751887969</v>
       </c>
       <c r="AA149" s="179">
-        <f t="shared" ref="T149:AA149" si="161">(AA107-AA106)/AA49</f>
+        <f t="shared" ref="AA149" si="161">(AA107-AA106)/AA49</f>
         <v>0.25186202906934702</v>
       </c>
       <c r="AC149" s="179">
@@ -31162,7 +31191,7 @@
         <v>1.4483464728166273</v>
       </c>
       <c r="AA150" s="118">
-        <f t="shared" ref="T150:AA150" si="163">(AA106+AA30)/AA40</f>
+        <f t="shared" ref="AA150" si="163">(AA106+AA30)/AA40</f>
         <v>1.1365986156137737</v>
       </c>
       <c r="AC150" s="118">
@@ -31223,7 +31252,7 @@
         <v>2.3663356199447119</v>
       </c>
       <c r="AA151" s="118">
-        <f t="shared" ref="T151:AA151" si="165">AA32/AA40</f>
+        <f t="shared" ref="AA151" si="165">AA32/AA40</f>
         <v>2.0155962498904758</v>
       </c>
       <c r="AC151" s="118">
@@ -31284,7 +31313,7 @@
         <v>13.502923976608187</v>
       </c>
       <c r="AA152" s="181">
-        <f t="shared" ref="T152:AA152" si="167">IF(AA13&gt;=0,"N/A",IF(AA12&lt;=0,"N/A",AA12/-AA13))</f>
+        <f t="shared" ref="AA152" si="167">IF(AA13&gt;=0,"N/A",IF(AA12&lt;=0,"N/A",AA12/-AA13))</f>
         <v>9.1348314606741567</v>
       </c>
       <c r="AC152" s="181">
@@ -31326,7 +31355,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>16.682220046178855</v>
+        <v>16.879997195970962</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31363,7 +31392,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>3.5991409866569852</v>
+        <v>3.6418108377961338</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31424,7 +31453,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>5.6038216790801947</v>
+        <v>5.6702581531564107</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31485,7 +31514,7 @@
       </c>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>156761.82</v>
+        <v>158620.32</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31541,12 +31570,12 @@
         <v>140207.6</v>
       </c>
       <c r="AA157" s="143">
-        <f t="shared" ref="T157:AA157" si="169">AA156+AA107-AA106+AA48+AA45</f>
+        <f t="shared" ref="AA157" si="169">AA156+AA107-AA106+AA48+AA45</f>
         <v>208098.18</v>
       </c>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>163727.82</v>
+        <v>165586.32</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31583,7 +31612,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>3.7153449214849781</v>
+        <v>3.757518380684397</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31620,7 +31649,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>16.021902338780702</v>
+        <v>16.203769449065469</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31676,7 +31705,7 @@
         <v>1055</v>
       </c>
       <c r="AA160" s="64">
-        <f t="shared" ref="T160:AA160" si="171">AA59-AA54+AA109+AA65</f>
+        <f t="shared" ref="AA160" si="171">AA59-AA54+AA109+AA65</f>
         <v>-335</v>
       </c>
       <c r="AC160" s="64">
@@ -31755,7 +31784,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>21.851382771117926</v>
+        <v>22.110443267354338</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31792,7 +31821,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>16.793002012370508</v>
+        <v>16.983621995217593</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31829,7 +31858,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>4.5763694246468943E-2</v>
+        <v>4.5227496704079273E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31866,7 +31895,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.9944060037084509E-2</v>
+        <v>5.9241716002102603E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31903,7 +31932,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>2.4320845471174038E-2</v>
+        <v>2.4035886448848416E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31940,7 +31969,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>5.9006714772768011E-2</v>
+        <v>5.8315353291432018E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31977,7 +32006,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>8.3406788719345051E-2</v>
+        <v>8.2429539922753897E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32255,7 +32284,7 @@
         <v>9.2969639468690701</v>
       </c>
       <c r="AA175" s="72">
-        <f t="shared" ref="T175:AA175" si="178">AA106/AA75</f>
+        <f t="shared" ref="AA175" si="178">AA106/AA75</f>
         <v>7.9085714285714284</v>
       </c>
       <c r="AC175" s="72">
@@ -32316,7 +32345,7 @@
         <v>0.35157207023274806</v>
       </c>
       <c r="AA176" s="154">
-        <f t="shared" ref="T176:AA176" si="180">AA54/AA59</f>
+        <f t="shared" ref="AA176" si="180">AA54/AA59</f>
         <v>0.83753784056508573</v>
       </c>
       <c r="AC176" s="154">
@@ -32377,7 +32406,7 @@
         <v>8.1234078686668557E-2</v>
       </c>
       <c r="AA177" s="154">
-        <f t="shared" ref="T177:AA177" si="182">AA54/AA5</f>
+        <f t="shared" ref="AA177" si="182">AA54/AA5</f>
         <v>8.3442243892630941E-2</v>
       </c>
       <c r="AC177" s="154">
@@ -32438,7 +32467,7 @@
         <v>-5.1907020872865273</v>
       </c>
       <c r="AA178" s="72">
-        <f t="shared" ref="T178:AA178" si="184">(AA106-AA107)/AA75</f>
+        <f t="shared" ref="AA178" si="184">(AA106-AA107)/AA75</f>
         <v>-6.6342857142857143</v>
       </c>
       <c r="AC178" s="72">
@@ -32480,7 +32509,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-4.4436840552119133E-2</v>
+        <v>-4.3916189300336805E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -32536,7 +32565,7 @@
         <v>5.0287762996509104E-2</v>
       </c>
       <c r="AA180" s="154">
-        <f t="shared" ref="T180:AA180" si="186">-AA109/AA5</f>
+        <f t="shared" ref="AA180" si="186">-AA109/AA5</f>
         <v>4.9864280687644515E-2</v>
       </c>
       <c r="AC180" s="154">
@@ -32597,7 +32626,7 @@
         <v>0.21763985300122499</v>
       </c>
       <c r="AA181" s="154">
-        <f t="shared" ref="T181:AA181" si="188">-(AA109/AA59)</f>
+        <f t="shared" ref="AA181" si="188">-(AA109/AA59)</f>
         <v>0.50050454086781027</v>
       </c>
       <c r="AC181" s="154">
@@ -32658,7 +32687,7 @@
         <v>1.2905569007263922</v>
       </c>
       <c r="AA182" s="154">
-        <f t="shared" ref="T182:AA182" si="190">-AA109/AA53</f>
+        <f t="shared" ref="AA182" si="190">-AA109/AA53</f>
         <v>1.2525252525252526</v>
       </c>
       <c r="AC182" s="154">
@@ -33254,7 +33283,7 @@
         <v>-0.23006134969325154</v>
       </c>
       <c r="AA198" s="81">
-        <f t="shared" ref="T198:AA201" si="208">IF(Z190=0,
+        <f t="shared" ref="AA198:AA201" si="208">IF(Z190=0,
 IF(AA190=0,0,IF(AA190&gt;0,1,-1)),
 (AA190-Z190)/ABS(Z190)
 )</f>
@@ -33802,15 +33831,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="235" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="238"/>
-      <c r="E4" s="238" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33818,7 +33847,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>147.61000000000001</v>
+        <v>149.36000000000001</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33834,7 +33863,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>156761.82</v>
+        <v>158620.32</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33854,7 +33883,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>163727.82</v>
+        <v>165586.32</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33874,7 +33903,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>16.682220046178855</v>
+        <v>16.879997195970962</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -33894,7 +33923,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>3.5991409866569852</v>
+        <v>3.6418108377961338</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -33914,7 +33943,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5.6038216790801947</v>
+        <v>5.6702581531564107</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33934,7 +33963,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>3.7153449214849781</v>
+        <v>3.757518380684397</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33943,18 +33972,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>16.021902338780702</v>
+        <v>16.203769449065469</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="238"/>
-      <c r="E15" s="238" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="238"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34005,14 +34034,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="238" t="s">
+      <c r="B21" s="235" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="238"/>
-      <c r="E21" s="238" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="238"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34081,14 +34110,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="238" t="s">
+      <c r="B29" s="235" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="238"/>
-      <c r="E29" s="238" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="238"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34164,14 +34193,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="238" t="s">
+      <c r="B37" s="235" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="238"/>
-      <c r="E37" s="238" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="238"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34179,7 +34208,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.9944060037084509E-2</v>
+        <v>5.9241716002102603E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -34195,7 +34224,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>4.5763694246468943E-2</v>
+        <v>4.5227496704079273E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -34211,7 +34240,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>2.4320845471174038E-2</v>
+        <v>2.4035886448848416E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -34227,7 +34256,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.9006714772768011E-2</v>
+        <v>5.8315353291432018E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34236,18 +34265,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>8.3406788719345051E-2</v>
+        <v>8.2429539922753897E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="238" t="s">
+      <c r="B45" s="235" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="238"/>
-      <c r="E45" s="238" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="238"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34280,18 +34309,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-4.4436840552119133E-2</v>
+        <v>-4.3916189300336805E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="238" t="s">
+      <c r="B51" s="235" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="238"/>
-      <c r="E51" s="238" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="238"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34460,7 +34489,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>147.61000000000001</v>
+        <v>149.36000000000001</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34489,7 +34518,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>156761.82</v>
+        <v>158620.32</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34518,7 +34547,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>163727.82</v>
+        <v>165586.32</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34547,7 +34576,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>16.682220046178855</v>
+        <v>16.879997195970962</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34576,7 +34605,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>3.5991409866569852</v>
+        <v>3.6418108377961338</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34605,7 +34634,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5.6038216790801947</v>
+        <v>5.6702581531564107</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34634,7 +34663,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>3.7153449214849781</v>
+        <v>3.757518380684397</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34663,7 +34692,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>16.021902338780702</v>
+        <v>16.203769449065469</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35436,7 +35465,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.9944060037084509E-2</v>
+        <v>5.9241716002102603E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35465,7 +35494,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>4.5763694246468943E-2</v>
+        <v>4.5227496704079273E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35494,7 +35523,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>2.4320845471174038E-2</v>
+        <v>2.4035886448848416E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35523,7 +35552,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.9006714772768011E-2</v>
+        <v>5.8315353291432018E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35552,7 +35581,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>8.3406788719345051E-2</v>
+        <v>8.2429539922753897E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35788,7 +35817,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-4.4436840552119133E-2</v>
+        <v>-4.3916189300336805E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36326,14 +36355,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="239" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="240"/>
+      <c r="F3" s="241" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36400,19 +36429,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="242">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="243"/>
+      <c r="F7" s="242">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="243"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -36439,19 +36468,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="242">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="243"/>
+      <c r="F9" s="242">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="243"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -36478,19 +36507,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="242">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="243"/>
+      <c r="F11" s="242">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="243"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -36517,19 +36546,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="242">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="243"/>
+      <c r="F13" s="242">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="243"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -36556,19 +36585,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="242">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="243"/>
+      <c r="F15" s="242">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -36595,19 +36624,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="242">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="243"/>
+      <c r="F17" s="242">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="243"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36634,22 +36663,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="242">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="243"/>
+      <c r="F19" s="242">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="243"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36676,22 +36705,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="242">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="243"/>
+      <c r="F21" s="242">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="243"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36739,22 +36768,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="242">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="243"/>
+      <c r="F25" s="242">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="243"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -36781,22 +36810,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="242">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="243"/>
+      <c r="F27" s="242">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="243"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -36823,22 +36852,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="242">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="243"/>
+      <c r="F29" s="242">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="243"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36865,22 +36894,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="239">
+      <c r="C31" s="242">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="F31" s="239">
+      <c r="D31" s="243"/>
+      <c r="F31" s="242">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="240"/>
+      <c r="G31" s="243"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36907,43 +36936,25 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="239">
+      <c r="C33" s="242">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="240"/>
-      <c r="F33" s="239">
+      <c r="D33" s="243"/>
+      <c r="F33" s="242">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="240"/>
+      <c r="G33" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36954,6 +36965,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBA4442-9BDC-FE45-88C5-4C3F548E37AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67BF8BE-7673-B24C-AB82-65C44D10DE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="10" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -129,28 +129,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -160,21 +139,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2382,7 +2352,22 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2394,6 +2379,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2401,27 +2392,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12754,7 +12724,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12793,9 +12763,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6536999999999999</v>
-    <v>1.75</v>
-    <v>1.1856E-2</v>
+    <v>1.6626000000000001</v>
+    <v>0.17</v>
+    <v>1.008E-3</v>
+    <v>-0.37</v>
+    <v>-2.1930000000000001E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12803,50 +12775,36 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>150.4999</v>
+    <v>170.63</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46237.67884743047</v>
+    <v>46269.900570173435</v>
     <v>4</v>
-    <v>142.88999999999999</v>
-    <v>156828000000</v>
+    <v>167.04</v>
+    <v>177177000000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>147.04</v>
-    <v>17.286200000000001</v>
-    <v>147.61000000000001</v>
-    <v>149.36000000000001</v>
+    <v>169.98</v>
+    <v>19.509599999999999</v>
+    <v>168.57</v>
+    <v>168.74</v>
+    <v>168.37</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>6911420</v>
-    <v>15604431</v>
+    <v>8530083</v>
+    <v>9759347</v>
     <v>1991</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12858,30 +12816,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.47</v>
+    <v>48.06</v>
     <v>39.47</v>
-    <v>0.82</v>
-    <v>1.7585E-2</v>
+    <v>-0.34</v>
+    <v>-7.0889999999999998E-3</v>
     <v>US</v>
-    <v>47.47</v>
+    <v>47.68</v>
     <v>Index</v>
-    <v>10</v>
-    <v>46.82</v>
+    <v>7</v>
+    <v>47.32</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.84</v>
-    <v>46.63</v>
-    <v>47.45</v>
+    <v>47.66</v>
+    <v>47.96</v>
+    <v>47.62</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>11</v>
+    <v>8</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12915,6 +12873,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12936,6 +12896,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12945,11 +12906,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12985,7 +12941,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12996,13 +12952,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13103,13 +13062,19 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
+      <v>1</v>
+      <v>1</v>
+      <v>6</v>
     </spb>
     <spb s="5">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13190,6 +13155,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13197,6 +13165,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13688,18 +13659,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="236" t="s">
+      <c r="B2" s="241" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="237"/>
-      <c r="E2" s="236" t="s">
+      <c r="C2" s="242"/>
+      <c r="E2" s="241" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="237"/>
-      <c r="H2" s="236" t="s">
+      <c r="F2" s="242"/>
+      <c r="H2" s="241" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="237"/>
+      <c r="I2" s="242"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13714,7 +13685,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>158620.32</v>
+        <v>179201.88</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13722,7 +13693,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>121.26353957751137</v>
+        <v>119.23431706091708</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13738,7 +13709,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>165586.32</v>
+        <v>186167.88</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13746,7 +13717,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>194.52182717807352</v>
+        <v>193.35967431903734</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13755,7 +13726,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>149.36000000000001</v>
+        <v>168.74</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13770,23 +13741,23 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>197.74374673532</v>
+        <v>197.24172217952881</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="208" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>168.37</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>16.879997195970962</v>
+        <v>19.070237860525843</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13794,7 +13765,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>161.86968320408795</v>
+        <v>160.89221737946522</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13803,14 +13774,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.75</v>
+        <v>0.17</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>3.6418108377961338</v>
+        <v>4.1143489606971047</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13818,23 +13789,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>168.84969917374821</v>
+        <v>167.68198273473712</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.37</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.5227496704079273E-2</v>
+        <v>4.003306215314259E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13842,7 +13813,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>0.13048807695332212</v>
+        <v>-6.2701035039877343E-3</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13851,37 +13822,37 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.1856E-2</v>
+        <v>1.008E-3</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>5.9241716002102603E-2</v>
+        <v>5.2437730840784909E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-2.1930000000000001E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>5.8315353291432018E-2</v>
+        <v>5.1617762045799966E-2</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>413</v>
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>36.212101132364417</v>
+        <v>36.010425920321765</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13897,7 +13868,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>2.4035886448848416E-2</v>
+        <v>2.1275334834656868E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13922,7 +13893,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6536999999999999</v>
+        <v>1.6626000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13938,7 +13909,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>15604431</v>
+        <v>9759347</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13954,7 +13925,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-4.3916189300336805E-2</v>
+        <v>-3.8872360044437032E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13967,10 +13938,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="238" t="s">
+      <c r="B17" s="243" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="238"/>
+      <c r="C17" s="243"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -14043,14 +14014,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="238" t="s">
+      <c r="B25" s="243" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="238"/>
-      <c r="E25" s="236" t="s">
+      <c r="C25" s="243"/>
+      <c r="E25" s="241" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="237"/>
+      <c r="F25" s="242"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14059,12 +14030,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="5">
+      <c r="E26" s="185" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.45</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14079,7 +14050,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.7450000000000006E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14099,15 +14070,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="238" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="238"/>
+      <c r="D33" s="238"/>
+      <c r="E33" s="238"/>
+      <c r="F33" s="238"/>
+      <c r="G33" s="238"/>
+      <c r="H33" s="238"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14126,24 +14097,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="238"/>
+      <c r="C39" s="238"/>
+      <c r="D39" s="238"/>
+      <c r="E39" s="238"/>
+      <c r="F39" s="238"/>
+      <c r="G39" s="238"/>
+      <c r="H39" s="238"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="238" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="238"/>
+      <c r="D42" s="238"/>
+      <c r="E42" s="238"/>
+      <c r="F42" s="238"/>
+      <c r="G42" s="238"/>
+      <c r="H42" s="238"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14227,24 +14198,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="235"/>
-      <c r="C55" s="235"/>
-      <c r="D55" s="235"/>
-      <c r="E55" s="235"/>
-      <c r="F55" s="235"/>
-      <c r="G55" s="235"/>
-      <c r="H55" s="235"/>
+      <c r="B55" s="238"/>
+      <c r="C55" s="238"/>
+      <c r="D55" s="238"/>
+      <c r="E55" s="238"/>
+      <c r="F55" s="238"/>
+      <c r="G55" s="238"/>
+      <c r="H55" s="238"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="235" t="s">
+      <c r="B58" s="238" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="235"/>
-      <c r="D58" s="235"/>
-      <c r="E58" s="235"/>
-      <c r="F58" s="235"/>
-      <c r="G58" s="235"/>
-      <c r="H58" s="235"/>
+      <c r="C58" s="238"/>
+      <c r="D58" s="238"/>
+      <c r="E58" s="238"/>
+      <c r="F58" s="238"/>
+      <c r="G58" s="238"/>
+      <c r="H58" s="238"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14382,28 +14353,28 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="235"/>
-      <c r="C75" s="235"/>
-      <c r="D75" s="235"/>
-      <c r="E75" s="235"/>
-      <c r="F75" s="235"/>
-      <c r="G75" s="235"/>
-      <c r="H75" s="235"/>
+      <c r="B75" s="238"/>
+      <c r="C75" s="238"/>
+      <c r="D75" s="238"/>
+      <c r="E75" s="238"/>
+      <c r="F75" s="238"/>
+      <c r="G75" s="238"/>
+      <c r="H75" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14473,36 +14444,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14513,32 +14484,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="245" t="s">
+      <c r="S4" s="236" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="237"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="237"/>
+      <c r="Y4" s="237"/>
+      <c r="Z4" s="237"/>
+      <c r="AA4" s="237"/>
+      <c r="AB4" s="237"/>
+      <c r="AC4" s="237"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15279,33 +15250,33 @@
       <c r="Q13" s="91"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="244" t="s">
+      <c r="C14" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
-      <c r="H14" s="244"/>
-      <c r="I14" s="244"/>
-      <c r="J14" s="244"/>
-      <c r="K14" s="244"/>
-      <c r="L14" s="244"/>
+      <c r="D14" s="235"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="235"/>
+      <c r="G14" s="235"/>
+      <c r="H14" s="235"/>
+      <c r="I14" s="235"/>
+      <c r="J14" s="235"/>
+      <c r="K14" s="235"/>
+      <c r="L14" s="235"/>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
-      <c r="S14" s="245" t="s">
+      <c r="S14" s="236" t="s">
         <v>114</v>
       </c>
-      <c r="T14" s="246"/>
-      <c r="U14" s="246"/>
-      <c r="V14" s="246"/>
-      <c r="W14" s="246"/>
-      <c r="X14" s="246"/>
-      <c r="Y14" s="246"/>
-      <c r="Z14" s="246"/>
-      <c r="AA14" s="246"/>
-      <c r="AB14" s="246"/>
-      <c r="AC14" s="246"/>
+      <c r="T14" s="237"/>
+      <c r="U14" s="237"/>
+      <c r="V14" s="237"/>
+      <c r="W14" s="237"/>
+      <c r="X14" s="237"/>
+      <c r="Y14" s="237"/>
+      <c r="Z14" s="237"/>
+      <c r="AA14" s="237"/>
+      <c r="AB14" s="237"/>
+      <c r="AC14" s="237"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
@@ -15972,35 +15943,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="P2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="238"/>
+      <c r="R2" s="238"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16009,31 +15980,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="P4" s="246" t="s">
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
+      <c r="P4" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="237"/>
+      <c r="W4" s="237"/>
+      <c r="X4" s="237"/>
+      <c r="Y4" s="237"/>
+      <c r="Z4" s="237"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16228,32 +16199,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="235" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="235"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="246" t="s">
+      <c r="P9" s="237" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="246"/>
-      <c r="S9" s="246"/>
-      <c r="T9" s="246"/>
-      <c r="U9" s="246"/>
-      <c r="V9" s="246"/>
-      <c r="W9" s="246"/>
-      <c r="X9" s="246"/>
-      <c r="Y9" s="246"/>
-      <c r="Z9" s="246"/>
+      <c r="Q9" s="237"/>
+      <c r="R9" s="237"/>
+      <c r="S9" s="237"/>
+      <c r="T9" s="237"/>
+      <c r="U9" s="237"/>
+      <c r="V9" s="237"/>
+      <c r="W9" s="237"/>
+      <c r="X9" s="237"/>
+      <c r="Y9" s="237"/>
+      <c r="Z9" s="237"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16729,31 +16700,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="244" t="s">
+      <c r="C17" s="235" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
-      <c r="J17" s="244"/>
-      <c r="K17" s="244"/>
-      <c r="L17" s="244"/>
-      <c r="P17" s="246" t="s">
+      <c r="D17" s="235"/>
+      <c r="E17" s="235"/>
+      <c r="F17" s="235"/>
+      <c r="G17" s="235"/>
+      <c r="H17" s="235"/>
+      <c r="I17" s="235"/>
+      <c r="J17" s="235"/>
+      <c r="K17" s="235"/>
+      <c r="L17" s="235"/>
+      <c r="P17" s="237" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="246"/>
-      <c r="R17" s="246"/>
-      <c r="S17" s="246"/>
-      <c r="T17" s="246"/>
-      <c r="U17" s="246"/>
-      <c r="V17" s="246"/>
-      <c r="W17" s="246"/>
-      <c r="X17" s="246"/>
-      <c r="Y17" s="246"/>
-      <c r="Z17" s="246"/>
+      <c r="Q17" s="237"/>
+      <c r="R17" s="237"/>
+      <c r="S17" s="237"/>
+      <c r="T17" s="237"/>
+      <c r="U17" s="237"/>
+      <c r="V17" s="237"/>
+      <c r="W17" s="237"/>
+      <c r="X17" s="237"/>
+      <c r="Y17" s="237"/>
+      <c r="Z17" s="237"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17231,20 +17202,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -17262,18 +17233,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -17470,18 +17441,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="235" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="235"/>
+      <c r="E11" s="235"/>
+      <c r="F11" s="235"/>
+      <c r="G11" s="235"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="235"/>
+      <c r="K11" s="235"/>
+      <c r="L11" s="235"/>
       <c r="N11" s="91"/>
       <c r="P11" s="249"/>
       <c r="Q11" s="249"/>
@@ -17735,18 +17706,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="235" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="235"/>
+      <c r="E18" s="235"/>
+      <c r="F18" s="235"/>
+      <c r="G18" s="235"/>
+      <c r="H18" s="235"/>
+      <c r="I18" s="235"/>
+      <c r="J18" s="235"/>
+      <c r="K18" s="235"/>
+      <c r="L18" s="235"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17964,18 +17935,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="244" t="s">
+      <c r="C26" s="235" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="244"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="244"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="244"/>
+      <c r="D26" s="235"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="235"/>
+      <c r="G26" s="235"/>
+      <c r="H26" s="235"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235"/>
+      <c r="L26" s="235"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18167,18 +18138,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="244" t="s">
+      <c r="C33" s="235" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="244"/>
-      <c r="E33" s="244"/>
-      <c r="F33" s="244"/>
-      <c r="G33" s="244"/>
-      <c r="H33" s="244"/>
-      <c r="I33" s="244"/>
-      <c r="J33" s="244"/>
-      <c r="K33" s="244"/>
-      <c r="L33" s="244"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
+      <c r="I33" s="235"/>
+      <c r="J33" s="235"/>
+      <c r="K33" s="235"/>
+      <c r="L33" s="235"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18362,18 +18333,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="244" t="s">
+      <c r="C40" s="235" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="244"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
-      <c r="G40" s="244"/>
-      <c r="H40" s="244"/>
-      <c r="I40" s="244"/>
-      <c r="J40" s="244"/>
-      <c r="K40" s="244"/>
-      <c r="L40" s="244"/>
+      <c r="D40" s="235"/>
+      <c r="E40" s="235"/>
+      <c r="F40" s="235"/>
+      <c r="G40" s="235"/>
+      <c r="H40" s="235"/>
+      <c r="I40" s="235"/>
+      <c r="J40" s="235"/>
+      <c r="K40" s="235"/>
+      <c r="L40" s="235"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18637,6 +18608,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18644,12 +18621,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18687,20 +18658,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
       <c r="S2" s="249"/>
       <c r="T2" s="249"/>
       <c r="U2" s="249"/>
@@ -18718,18 +18689,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="235" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
       <c r="S4" s="249"/>
       <c r="T4" s="249"/>
       <c r="U4" s="249"/>
@@ -19103,18 +19074,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="244" t="s">
+      <c r="C13" s="235" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="244"/>
-      <c r="I13" s="244"/>
-      <c r="J13" s="244"/>
-      <c r="K13" s="244"/>
-      <c r="L13" s="244"/>
+      <c r="D13" s="235"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="235"/>
+      <c r="H13" s="235"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="235"/>
+      <c r="K13" s="235"/>
+      <c r="L13" s="235"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19207,18 +19178,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="235" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="235"/>
+      <c r="E18" s="235"/>
+      <c r="F18" s="235"/>
+      <c r="G18" s="235"/>
+      <c r="H18" s="235"/>
+      <c r="I18" s="235"/>
+      <c r="J18" s="235"/>
+      <c r="K18" s="235"/>
+      <c r="L18" s="235"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19410,18 +19381,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="244" t="s">
+      <c r="C25" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="E25" s="244"/>
-      <c r="F25" s="244"/>
-      <c r="G25" s="244"/>
-      <c r="H25" s="244"/>
-      <c r="I25" s="244"/>
-      <c r="J25" s="244"/>
-      <c r="K25" s="244"/>
-      <c r="L25" s="244"/>
+      <c r="D25" s="235"/>
+      <c r="E25" s="235"/>
+      <c r="F25" s="235"/>
+      <c r="G25" s="235"/>
+      <c r="H25" s="235"/>
+      <c r="I25" s="235"/>
+      <c r="J25" s="235"/>
+      <c r="K25" s="235"/>
+      <c r="L25" s="235"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19559,18 +19530,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="244" t="s">
+      <c r="C31" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="244"/>
-      <c r="E31" s="244"/>
-      <c r="F31" s="244"/>
-      <c r="G31" s="244"/>
-      <c r="H31" s="244"/>
-      <c r="I31" s="244"/>
-      <c r="J31" s="244"/>
-      <c r="K31" s="244"/>
-      <c r="L31" s="244"/>
+      <c r="D31" s="235"/>
+      <c r="E31" s="235"/>
+      <c r="F31" s="235"/>
+      <c r="G31" s="235"/>
+      <c r="H31" s="235"/>
+      <c r="I31" s="235"/>
+      <c r="J31" s="235"/>
+      <c r="K31" s="235"/>
+      <c r="L31" s="235"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19709,16 +19680,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19781,10 +19752,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="238"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19801,7 +19772,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>149.36000000000001</v>
+        <v>168.74</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19810,7 +19781,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>158620.32</v>
+        <v>179201.88</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19828,7 +19799,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.7450000000000006E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19837,7 +19808,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6536999999999999</v>
+        <v>1.6626000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19869,10 +19840,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="238" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="238"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19880,7 +19851,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>8.7813973773813281E-2</v>
+        <v>7.8520349574447465E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19889,7 +19860,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.91218602622618672</v>
+        <v>0.92147965042555258</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19907,7 +19878,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1218665</v>
+        <v>0.12243699999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19916,7 +19887,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1148763759666438</v>
+        <v>0.11614186653391741</v>
       </c>
     </row>
   </sheetData>
@@ -19961,20 +19932,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -19992,18 +19963,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="235" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -20167,7 +20138,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>180253.32139407666</v>
+        <v>177750.53220817546</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20221,23 +20192,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5659.8654157938417</v>
+        <v>5653.4482151578977</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3398.2295332523991</v>
+        <v>3390.528022146787</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5324.3998836099008</v>
+        <v>5306.3098683213457</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7536.4790223941563</v>
+        <v>7502.3574277044545</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>9176.3801781370694</v>
+        <v>9124.4767428496034</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20256,14 +20227,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>104652.52499812971</v>
+        <v>102615.72444251385</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="238" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="238"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20279,14 +20250,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1148763759666438</v>
+        <v>0.11614186653391741</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="238" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="238"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20294,7 +20265,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31095.354033187366</v>
+        <v>30977.120276180089</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20303,7 +20274,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>104652.52499812971</v>
+        <v>102615.72444251385</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20312,7 +20283,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>135747.87903131708</v>
+        <v>133592.84471869393</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20339,7 +20310,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>128781.87903131708</v>
+        <v>126626.84471869393</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20357,7 +20328,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>121.26353957751137</v>
+        <v>119.23431706091708</v>
       </c>
     </row>
   </sheetData>
@@ -20400,37 +20371,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="235" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20619,18 +20590,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="244" t="s">
+      <c r="C10" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="244"/>
-      <c r="E10" s="244"/>
-      <c r="F10" s="244"/>
-      <c r="G10" s="244"/>
-      <c r="H10" s="244"/>
-      <c r="I10" s="244"/>
-      <c r="J10" s="244"/>
-      <c r="K10" s="244"/>
-      <c r="L10" s="244"/>
+      <c r="D10" s="235"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="235"/>
+      <c r="L10" s="235"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20824,18 +20795,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="244" t="s">
+      <c r="C16" s="235" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="244"/>
-      <c r="E16" s="244"/>
-      <c r="F16" s="244"/>
-      <c r="G16" s="244"/>
-      <c r="H16" s="244"/>
-      <c r="I16" s="244"/>
-      <c r="J16" s="244"/>
-      <c r="K16" s="244"/>
-      <c r="L16" s="244"/>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="235"/>
+      <c r="H16" s="235"/>
+      <c r="I16" s="235"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="235"/>
+      <c r="L16" s="235"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20969,18 +20940,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="244" t="s">
+      <c r="C21" s="235" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="244"/>
-      <c r="E21" s="244"/>
-      <c r="F21" s="244"/>
-      <c r="G21" s="244"/>
-      <c r="H21" s="244"/>
-      <c r="I21" s="244"/>
-      <c r="J21" s="244"/>
-      <c r="K21" s="244"/>
-      <c r="L21" s="244"/>
+      <c r="D21" s="235"/>
+      <c r="E21" s="235"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="235"/>
+      <c r="H21" s="235"/>
+      <c r="I21" s="235"/>
+      <c r="J21" s="235"/>
+      <c r="K21" s="235"/>
+      <c r="L21" s="235"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -21064,18 +21035,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="244" t="s">
+      <c r="C26" s="235" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="244"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="244"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="244"/>
+      <c r="D26" s="235"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="235"/>
+      <c r="G26" s="235"/>
+      <c r="H26" s="235"/>
+      <c r="I26" s="235"/>
+      <c r="J26" s="235"/>
+      <c r="K26" s="235"/>
+      <c r="L26" s="235"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21345,10 +21316,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="238" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="238"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21366,7 +21337,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1148763759666438</v>
+        <v>0.11614186653391741</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21392,7 +21363,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>213548.18046311408</v>
+        <v>212313.97412681766</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21419,7 +21390,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>206582.18046311408</v>
+        <v>205347.97412681766</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21437,14 +21408,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>194.52182717807352</v>
+        <v>193.35967431903734</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="235" t="s">
+      <c r="B49" s="238" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="235"/>
+      <c r="C49" s="238"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21461,7 +21432,7 @@
       </c>
       <c r="C51" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1218665</v>
+        <v>0.12243699999999999</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21496,14 +21467,14 @@
       </c>
       <c r="C55" s="142">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>197.74374673532</v>
+        <v>197.24172217952881</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="235" t="s">
+      <c r="B57" s="238" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="235"/>
+      <c r="C57" s="238"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21520,7 +21491,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1148763759666438</v>
+        <v>0.11614186653391741</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21546,7 +21517,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>178871.60356274139</v>
+        <v>177833.53485699208</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21573,7 +21544,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>171905.60356274139</v>
+        <v>170867.53485699208</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21591,7 +21562,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>161.86968320408795</v>
+        <v>160.89221737946522</v>
       </c>
     </row>
   </sheetData>
@@ -21643,10 +21614,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="238"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21655,7 +21626,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>121.26353957751137</v>
+        <v>119.23431706091708</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21664,7 +21635,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>194.52182717807352</v>
+        <v>193.35967431903734</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21673,7 +21644,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C55</f>
-        <v>197.74374673532</v>
+        <v>197.24172217952881</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21682,7 +21653,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>161.86968320408795</v>
+        <v>160.89221737946522</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21691,7 +21662,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>168.84969917374821</v>
+        <v>167.68198273473712</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21700,7 +21671,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>149.36000000000001</v>
+        <v>168.74</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21709,7 +21680,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>0.13048807695332212</v>
+        <v>-6.2701035039877343E-3</v>
       </c>
     </row>
   </sheetData>
@@ -21765,37 +21736,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="235" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="235"/>
+      <c r="E4" s="235"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
+      <c r="H4" s="235"/>
+      <c r="I4" s="235"/>
+      <c r="J4" s="235"/>
+      <c r="K4" s="235"/>
+      <c r="L4" s="235"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21908,18 +21879,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="235" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="235"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22040,18 +22011,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="244" t="s">
+      <c r="C14" s="235" t="s">
         <v>406</v>
       </c>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
-      <c r="H14" s="244"/>
-      <c r="I14" s="244"/>
-      <c r="J14" s="244"/>
-      <c r="K14" s="244"/>
-      <c r="L14" s="244"/>
+      <c r="D14" s="235"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="235"/>
+      <c r="G14" s="235"/>
+      <c r="H14" s="235"/>
+      <c r="I14" s="235"/>
+      <c r="J14" s="235"/>
+      <c r="K14" s="235"/>
+      <c r="L14" s="235"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22141,10 +22112,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="235" t="s">
+      <c r="B20" s="238" t="s">
         <v>408</v>
       </c>
-      <c r="C20" s="235"/>
+      <c r="C20" s="238"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22179,7 +22150,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1218665</v>
+        <v>0.12243699999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22196,7 +22167,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C23/(C24-C25)</f>
-        <v>36.212101132364417</v>
+        <v>36.010425920321765</v>
       </c>
     </row>
   </sheetData>
@@ -22245,20 +22216,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
+      <c r="G3" s="239"/>
+      <c r="H3" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -22276,18 +22247,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="235" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -22433,7 +22404,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>188612.06222517093</v>
+        <v>185993.21322967499</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22487,23 +22458,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11316.948166799682</v>
+        <v>11304.116920535367</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>10861.414592247091</v>
+        <v>10836.799037504152</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10424.217307168145</v>
+        <v>10388.80031096574</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10004.618233119358</v>
+        <v>9959.322077267092</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9601.9090010370783</v>
+        <v>9547.5986899125619</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22522,7 +22493,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>109505.49151776759</v>
+        <v>107374.24006472943</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22538,7 +22509,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>149.36000000000001</v>
+        <v>168.74</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22547,7 +22518,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>147.37961792203708</v>
+        <v>145.18559723896604</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22586,7 +22557,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1148763759666438</v>
+        <v>0.11614186653391741</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22604,7 +22575,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>156828</v>
+        <v>177177</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22631,7 +22602,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>163794</v>
+        <v>184143</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22647,7 +22618,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>52209.107300371354</v>
+        <v>52036.637036184919</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22656,7 +22627,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>109505.49151776759</v>
+        <v>107374.24006472943</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22665,7 +22636,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>161714.59881813894</v>
+        <v>159410.87710091434</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22692,7 +22663,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>154748.59881813894</v>
+        <v>152444.87710091434</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22710,22 +22681,22 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>147.37961792203708</v>
+        <v>145.18559723896604</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="244" t="s">
+      <c r="C39" s="235" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="244"/>
-      <c r="E39" s="244"/>
-      <c r="F39" s="244"/>
-      <c r="G39" s="244"/>
-      <c r="H39" s="244"/>
-      <c r="I39" s="244"/>
-      <c r="J39" s="244"/>
-      <c r="K39" s="244"/>
-      <c r="L39" s="244"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
+      <c r="I39" s="235"/>
+      <c r="J39" s="235"/>
+      <c r="K39" s="235"/>
+      <c r="L39" s="235"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23157,17 +23128,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29782,7 +29753,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>149.36000000000001</v>
+        <v>168.74</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29853,7 +29824,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>149.36000000000001</v>
+        <v>168.74</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31355,7 +31326,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>16.879997195970962</v>
+        <v>19.070237860525843</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31392,7 +31363,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>3.6418108377961338</v>
+        <v>4.1143489606971047</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31453,7 +31424,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>5.6702581531564107</v>
+        <v>6.4059946489261703</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31514,7 +31485,7 @@
       </c>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>158620.32</v>
+        <v>179201.88</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31575,7 +31546,7 @@
       </c>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>165586.32</v>
+        <v>186167.88</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31612,7 +31583,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>3.757518380684397</v>
+        <v>4.2245593174185352</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31649,7 +31620,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>16.203769449065469</v>
+        <v>18.217817790390448</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31784,7 +31755,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>22.110443267354338</v>
+        <v>24.97935321996097</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31821,7 +31792,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>16.983621995217593</v>
+        <v>19.094602148118451</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31858,7 +31829,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>4.5227496704079273E-2</v>
+        <v>4.003306215314259E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31895,7 +31866,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.9241716002102603E-2</v>
+        <v>5.2437730840784909E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31932,7 +31903,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>2.4035886448848416E-2</v>
+        <v>2.1275334834656868E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31969,7 +31940,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>5.8315353291432018E-2</v>
+        <v>5.1617762045799966E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -32006,7 +31977,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>8.2429539922753897E-2</v>
+        <v>7.296240418906319E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32509,7 +32480,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-4.3916189300336805E-2</v>
+        <v>-3.8872360044437032E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33831,15 +33802,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="238"/>
+      <c r="E4" s="238" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33847,7 +33818,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>149.36000000000001</v>
+        <v>168.74</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33863,7 +33834,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>158620.32</v>
+        <v>179201.88</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33883,7 +33854,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>165586.32</v>
+        <v>186167.88</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33903,7 +33874,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>16.879997195970962</v>
+        <v>19.070237860525843</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -33923,7 +33894,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>3.6418108377961338</v>
+        <v>4.1143489606971047</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -33943,7 +33914,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5.6702581531564107</v>
+        <v>6.4059946489261703</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33963,7 +33934,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>3.757518380684397</v>
+        <v>4.2245593174185352</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33972,18 +33943,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>16.203769449065469</v>
+        <v>18.217817790390448</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="238" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="238"/>
+      <c r="E15" s="238" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34034,14 +34005,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="238" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="238"/>
+      <c r="E21" s="238" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="238"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34110,14 +34081,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="238" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="238"/>
+      <c r="E29" s="238" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="238"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34193,14 +34164,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="238" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="238"/>
+      <c r="E37" s="238" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="238"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34208,7 +34179,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.9241716002102603E-2</v>
+        <v>5.2437730840784909E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -34224,7 +34195,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>4.5227496704079273E-2</v>
+        <v>4.003306215314259E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -34240,7 +34211,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>2.4035886448848416E-2</v>
+        <v>2.1275334834656868E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -34256,7 +34227,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.8315353291432018E-2</v>
+        <v>5.1617762045799966E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34265,18 +34236,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>8.2429539922753897E-2</v>
+        <v>7.296240418906319E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="238" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="238"/>
+      <c r="E45" s="238" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="238"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34309,18 +34280,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-4.3916189300336805E-2</v>
+        <v>-3.8872360044437032E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="238" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="238"/>
+      <c r="E51" s="238" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="238"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34489,7 +34460,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>149.36000000000001</v>
+        <v>168.74</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34518,7 +34489,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>158620.32</v>
+        <v>179201.88</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34547,7 +34518,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>165586.32</v>
+        <v>186167.88</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34576,7 +34547,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>16.879997195970962</v>
+        <v>19.070237860525843</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34605,7 +34576,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>3.6418108377961338</v>
+        <v>4.1143489606971047</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34634,7 +34605,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>5.6702581531564107</v>
+        <v>6.4059946489261703</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34663,7 +34634,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>3.757518380684397</v>
+        <v>4.2245593174185352</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34692,7 +34663,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>16.203769449065469</v>
+        <v>18.217817790390448</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35465,7 +35436,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.9241716002102603E-2</v>
+        <v>5.2437730840784909E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35494,7 +35465,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>4.5227496704079273E-2</v>
+        <v>4.003306215314259E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35523,7 +35494,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>2.4035886448848416E-2</v>
+        <v>2.1275334834656868E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35552,7 +35523,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.8315353291432018E-2</v>
+        <v>5.1617762045799966E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35581,7 +35552,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>8.2429539922753897E-2</v>
+        <v>7.296240418906319E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35817,7 +35788,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-4.3916189300336805E-2</v>
+        <v>-3.8872360044437032E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36355,14 +36326,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="246" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36429,19 +36400,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="242">
+      <c r="C7" s="244">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="F7" s="242">
+      <c r="D7" s="245"/>
+      <c r="F7" s="244">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="243"/>
+      <c r="G7" s="245"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -36468,19 +36439,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="242">
+      <c r="C9" s="244">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="243"/>
-      <c r="F9" s="242">
+      <c r="D9" s="245"/>
+      <c r="F9" s="244">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="243"/>
+      <c r="G9" s="245"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -36507,19 +36478,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="242">
+      <c r="C11" s="244">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="243"/>
-      <c r="F11" s="242">
+      <c r="D11" s="245"/>
+      <c r="F11" s="244">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="243"/>
+      <c r="G11" s="245"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -36546,19 +36517,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="242">
+      <c r="C13" s="244">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="243"/>
-      <c r="F13" s="242">
+      <c r="D13" s="245"/>
+      <c r="F13" s="244">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="243"/>
+      <c r="G13" s="245"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -36585,19 +36556,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="242">
+      <c r="C15" s="244">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="243"/>
-      <c r="F15" s="242">
+      <c r="D15" s="245"/>
+      <c r="F15" s="244">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="243"/>
+      <c r="G15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -36624,19 +36595,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="242">
+      <c r="C17" s="244">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="243"/>
-      <c r="F17" s="242">
+      <c r="D17" s="245"/>
+      <c r="F17" s="244">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="243"/>
+      <c r="G17" s="245"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36663,22 +36634,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="242">
+      <c r="C19" s="244">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="243"/>
-      <c r="F19" s="242">
+      <c r="D19" s="245"/>
+      <c r="F19" s="244">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="243"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36705,22 +36676,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="242">
+      <c r="C21" s="244">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="243"/>
-      <c r="F21" s="242">
+      <c r="D21" s="245"/>
+      <c r="F21" s="244">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="243"/>
+      <c r="G21" s="245"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36768,22 +36739,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="242">
+      <c r="C25" s="244">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="243"/>
-      <c r="F25" s="242">
+      <c r="D25" s="245"/>
+      <c r="F25" s="244">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="243"/>
+      <c r="G25" s="245"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -36810,22 +36781,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="242">
+      <c r="C27" s="244">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="243"/>
-      <c r="F27" s="242">
+      <c r="D27" s="245"/>
+      <c r="F27" s="244">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="243"/>
+      <c r="G27" s="245"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -36852,22 +36823,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="242">
+      <c r="C29" s="244">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="243"/>
-      <c r="F29" s="242">
+      <c r="D29" s="245"/>
+      <c r="F29" s="244">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="243"/>
+      <c r="G29" s="245"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36894,22 +36865,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="242">
+      <c r="C31" s="244">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="243"/>
-      <c r="F31" s="242">
+      <c r="D31" s="245"/>
+      <c r="F31" s="244">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="243"/>
+      <c r="G31" s="245"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36936,25 +36907,43 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="242">
+      <c r="C33" s="244">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="243"/>
-      <c r="F33" s="242">
+      <c r="D33" s="245"/>
+      <c r="F33" s="244">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="243"/>
+      <c r="G33" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36965,24 +36954,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67BF8BE-7673-B24C-AB82-65C44D10DE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897A2651-3EA6-2742-B3C7-FD8954FDC7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2352,22 +2352,7 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2379,12 +2364,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2392,6 +2371,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12598,7 +12598,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="C12">
-            <v>4.4999999999999998E-2</v>
+            <v>4.3999999999999997E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -12763,11 +12763,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6626000000000001</v>
-    <v>0.17</v>
-    <v>1.008E-3</v>
-    <v>-0.37</v>
-    <v>-2.1930000000000001E-3</v>
+    <v>1.6526000000000001</v>
+    <v>5.09</v>
+    <v>2.8777E-2</v>
+    <v>0.09</v>
+    <v>4.9459999999999999E-4</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12775,26 +12775,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>170.63</v>
+    <v>185.46</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46269.900570173435</v>
+    <v>46276.999878946095</v>
     <v>4</v>
-    <v>167.04</v>
-    <v>177177000000</v>
+    <v>175.74</v>
+    <v>191068500000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>169.98</v>
-    <v>19.509599999999999</v>
-    <v>168.57</v>
-    <v>168.74</v>
-    <v>168.37</v>
+    <v>178.25</v>
+    <v>20.471299999999999</v>
+    <v>176.88</v>
+    <v>181.97</v>
+    <v>182.06</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>8530083</v>
-    <v>9759347</v>
+    <v>11556632</v>
+    <v>10218769</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -12816,19 +12816,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.06</v>
+    <v>48.12</v>
     <v>39.47</v>
-    <v>-0.34</v>
-    <v>-7.0889999999999998E-3</v>
+    <v>0.22</v>
+    <v>4.62E-3</v>
     <v>US</v>
-    <v>47.68</v>
+    <v>48.12</v>
     <v>Index</v>
     <v>7</v>
-    <v>47.32</v>
+    <v>47.48</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.66</v>
-    <v>47.96</v>
+    <v>47.54</v>
     <v>47.62</v>
+    <v>47.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13070,9 +13070,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13659,18 +13659,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="241" t="s">
+      <c r="B2" s="236" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="242"/>
-      <c r="E2" s="241" t="s">
+      <c r="C2" s="237"/>
+      <c r="E2" s="236" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="242"/>
-      <c r="H2" s="241" t="s">
+      <c r="F2" s="237"/>
+      <c r="H2" s="236" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="242"/>
+      <c r="I2" s="237"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>179201.88</v>
+        <v>193252.13999999998</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>119.23431706091708</v>
+        <v>121.3531887958768</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>186167.88</v>
+        <v>200218.13999999998</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13717,7 +13717,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>193.35967431903734</v>
+        <v>194.57258941523119</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>168.74</v>
+        <v>181.97</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>197.24172217952881</v>
+        <v>198.90418974577236</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13750,14 +13750,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>168.37</v>
+        <v>182.06</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>19.070237860525843</v>
+        <v>20.565433112954175</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13765,7 +13765,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>160.89221737946522</v>
+        <v>161.91237840688953</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13774,14 +13774,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.17</v>
+        <v>5.09</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>4.1143489606971047</v>
+        <v>4.4369330353090675</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13789,7 +13789,7 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>167.68198273473712</v>
+        <v>169.18558659094245</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13798,14 +13798,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.37</v>
+        <v>0.09</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>4.003306215314259E-2</v>
+        <v>3.7122486716059139E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-6.2701035039877343E-3</v>
+        <v>-7.0255610315203332E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13822,14 +13822,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.008E-3</v>
+        <v>2.8777E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>5.2437730840784909E-2</v>
+        <v>4.8625282750310743E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13838,21 +13838,21 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.1930000000000001E-3</v>
+        <v>4.9459999999999999E-4</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>5.1617762045799966E-2</v>
+        <v>4.7864929205958605E-2</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>413</v>
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>36.010425920321765</v>
+        <v>36.684620464146768</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>2.1275334834656868E-2</v>
+        <v>1.9728526680222014E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6626000000000001</v>
+        <v>1.6526000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>9759347</v>
+        <v>10218769</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.8872360044437032E-2</v>
+        <v>-3.604617263229272E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13938,10 +13938,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="243" t="s">
+      <c r="B17" s="238" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="243"/>
+      <c r="C17" s="238"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -14014,14 +14014,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="243" t="s">
+      <c r="B25" s="238" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="243"/>
-      <c r="E25" s="241" t="s">
+      <c r="C25" s="238"/>
+      <c r="E25" s="236" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="242"/>
+      <c r="F25" s="237"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.62</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14070,15 +14070,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="238" t="s">
+      <c r="B33" s="235" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="238"/>
-      <c r="D33" s="238"/>
-      <c r="E33" s="238"/>
-      <c r="F33" s="238"/>
-      <c r="G33" s="238"/>
-      <c r="H33" s="238"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="235"/>
+      <c r="H33" s="235"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14097,24 +14097,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="238"/>
-      <c r="C39" s="238"/>
-      <c r="D39" s="238"/>
-      <c r="E39" s="238"/>
-      <c r="F39" s="238"/>
-      <c r="G39" s="238"/>
-      <c r="H39" s="238"/>
+      <c r="B39" s="235"/>
+      <c r="C39" s="235"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="235"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="235"/>
+      <c r="H39" s="235"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="238" t="s">
+      <c r="B42" s="235" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="238"/>
-      <c r="D42" s="238"/>
-      <c r="E42" s="238"/>
-      <c r="F42" s="238"/>
-      <c r="G42" s="238"/>
-      <c r="H42" s="238"/>
+      <c r="C42" s="235"/>
+      <c r="D42" s="235"/>
+      <c r="E42" s="235"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="235"/>
+      <c r="H42" s="235"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14198,24 +14198,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="238"/>
-      <c r="C55" s="238"/>
-      <c r="D55" s="238"/>
-      <c r="E55" s="238"/>
-      <c r="F55" s="238"/>
-      <c r="G55" s="238"/>
-      <c r="H55" s="238"/>
+      <c r="B55" s="235"/>
+      <c r="C55" s="235"/>
+      <c r="D55" s="235"/>
+      <c r="E55" s="235"/>
+      <c r="F55" s="235"/>
+      <c r="G55" s="235"/>
+      <c r="H55" s="235"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="238" t="s">
+      <c r="B58" s="235" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="238"/>
-      <c r="D58" s="238"/>
-      <c r="E58" s="238"/>
-      <c r="F58" s="238"/>
-      <c r="G58" s="238"/>
-      <c r="H58" s="238"/>
+      <c r="C58" s="235"/>
+      <c r="D58" s="235"/>
+      <c r="E58" s="235"/>
+      <c r="F58" s="235"/>
+      <c r="G58" s="235"/>
+      <c r="H58" s="235"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14353,28 +14353,28 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="238"/>
-      <c r="C75" s="238"/>
-      <c r="D75" s="238"/>
-      <c r="E75" s="238"/>
-      <c r="F75" s="238"/>
-      <c r="G75" s="238"/>
-      <c r="H75" s="238"/>
+      <c r="B75" s="235"/>
+      <c r="C75" s="235"/>
+      <c r="D75" s="235"/>
+      <c r="E75" s="235"/>
+      <c r="F75" s="235"/>
+      <c r="G75" s="235"/>
+      <c r="H75" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B75:H75"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14444,36 +14444,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="240" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="238" t="s">
+      <c r="S2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="238" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14484,32 +14484,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="236" t="s">
+      <c r="S4" s="245" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="237"/>
-      <c r="U4" s="237"/>
-      <c r="V4" s="237"/>
-      <c r="W4" s="237"/>
-      <c r="X4" s="237"/>
-      <c r="Y4" s="237"/>
-      <c r="Z4" s="237"/>
-      <c r="AA4" s="237"/>
-      <c r="AB4" s="237"/>
-      <c r="AC4" s="237"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15250,33 +15250,33 @@
       <c r="Q13" s="91"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="235" t="s">
+      <c r="C14" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="235"/>
-      <c r="E14" s="235"/>
-      <c r="F14" s="235"/>
-      <c r="G14" s="235"/>
-      <c r="H14" s="235"/>
-      <c r="I14" s="235"/>
-      <c r="J14" s="235"/>
-      <c r="K14" s="235"/>
-      <c r="L14" s="235"/>
+      <c r="D14" s="244"/>
+      <c r="E14" s="244"/>
+      <c r="F14" s="244"/>
+      <c r="G14" s="244"/>
+      <c r="H14" s="244"/>
+      <c r="I14" s="244"/>
+      <c r="J14" s="244"/>
+      <c r="K14" s="244"/>
+      <c r="L14" s="244"/>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
-      <c r="S14" s="236" t="s">
+      <c r="S14" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="T14" s="237"/>
-      <c r="U14" s="237"/>
-      <c r="V14" s="237"/>
-      <c r="W14" s="237"/>
-      <c r="X14" s="237"/>
-      <c r="Y14" s="237"/>
-      <c r="Z14" s="237"/>
-      <c r="AA14" s="237"/>
-      <c r="AB14" s="237"/>
-      <c r="AC14" s="237"/>
+      <c r="T14" s="246"/>
+      <c r="U14" s="246"/>
+      <c r="V14" s="246"/>
+      <c r="W14" s="246"/>
+      <c r="X14" s="246"/>
+      <c r="Y14" s="246"/>
+      <c r="Z14" s="246"/>
+      <c r="AA14" s="246"/>
+      <c r="AB14" s="246"/>
+      <c r="AC14" s="246"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
@@ -15943,35 +15943,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="240" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="P2" s="238" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15980,31 +15980,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
-      <c r="P4" s="237" t="s">
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
+      <c r="P4" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="237"/>
-      <c r="R4" s="237"/>
-      <c r="S4" s="237"/>
-      <c r="T4" s="237"/>
-      <c r="U4" s="237"/>
-      <c r="V4" s="237"/>
-      <c r="W4" s="237"/>
-      <c r="X4" s="237"/>
-      <c r="Y4" s="237"/>
-      <c r="Z4" s="237"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16199,32 +16199,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="235" t="s">
+      <c r="C9" s="244" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="235"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="237" t="s">
+      <c r="P9" s="246" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="237"/>
-      <c r="R9" s="237"/>
-      <c r="S9" s="237"/>
-      <c r="T9" s="237"/>
-      <c r="U9" s="237"/>
-      <c r="V9" s="237"/>
-      <c r="W9" s="237"/>
-      <c r="X9" s="237"/>
-      <c r="Y9" s="237"/>
-      <c r="Z9" s="237"/>
+      <c r="Q9" s="246"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="246"/>
+      <c r="U9" s="246"/>
+      <c r="V9" s="246"/>
+      <c r="W9" s="246"/>
+      <c r="X9" s="246"/>
+      <c r="Y9" s="246"/>
+      <c r="Z9" s="246"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16700,31 +16700,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="235" t="s">
+      <c r="C17" s="244" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="235"/>
-      <c r="E17" s="235"/>
-      <c r="F17" s="235"/>
-      <c r="G17" s="235"/>
-      <c r="H17" s="235"/>
-      <c r="I17" s="235"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="235"/>
-      <c r="L17" s="235"/>
-      <c r="P17" s="237" t="s">
+      <c r="D17" s="244"/>
+      <c r="E17" s="244"/>
+      <c r="F17" s="244"/>
+      <c r="G17" s="244"/>
+      <c r="H17" s="244"/>
+      <c r="I17" s="244"/>
+      <c r="J17" s="244"/>
+      <c r="K17" s="244"/>
+      <c r="L17" s="244"/>
+      <c r="P17" s="246" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="237"/>
-      <c r="R17" s="237"/>
-      <c r="S17" s="237"/>
-      <c r="T17" s="237"/>
-      <c r="U17" s="237"/>
-      <c r="V17" s="237"/>
-      <c r="W17" s="237"/>
-      <c r="X17" s="237"/>
-      <c r="Y17" s="237"/>
-      <c r="Z17" s="237"/>
+      <c r="Q17" s="246"/>
+      <c r="R17" s="246"/>
+      <c r="S17" s="246"/>
+      <c r="T17" s="246"/>
+      <c r="U17" s="246"/>
+      <c r="V17" s="246"/>
+      <c r="W17" s="246"/>
+      <c r="X17" s="246"/>
+      <c r="Y17" s="246"/>
+      <c r="Z17" s="246"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17202,20 +17202,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="239"/>
-      <c r="H3" s="240" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -17233,18 +17233,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="235" t="s">
+      <c r="C5" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="235"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="235"/>
-      <c r="I5" s="235"/>
-      <c r="J5" s="235"/>
-      <c r="K5" s="235"/>
-      <c r="L5" s="235"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -17441,18 +17441,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="235" t="s">
+      <c r="C11" s="244" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="235"/>
-      <c r="E11" s="235"/>
-      <c r="F11" s="235"/>
-      <c r="G11" s="235"/>
-      <c r="H11" s="235"/>
-      <c r="I11" s="235"/>
-      <c r="J11" s="235"/>
-      <c r="K11" s="235"/>
-      <c r="L11" s="235"/>
+      <c r="D11" s="244"/>
+      <c r="E11" s="244"/>
+      <c r="F11" s="244"/>
+      <c r="G11" s="244"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="244"/>
+      <c r="J11" s="244"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
       <c r="N11" s="91"/>
       <c r="P11" s="249"/>
       <c r="Q11" s="249"/>
@@ -17706,18 +17706,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="235" t="s">
+      <c r="C18" s="244" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="235"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+      <c r="K18" s="244"/>
+      <c r="L18" s="244"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17935,18 +17935,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="235" t="s">
+      <c r="C26" s="244" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="235"/>
-      <c r="E26" s="235"/>
-      <c r="F26" s="235"/>
-      <c r="G26" s="235"/>
-      <c r="H26" s="235"/>
-      <c r="I26" s="235"/>
-      <c r="J26" s="235"/>
-      <c r="K26" s="235"/>
-      <c r="L26" s="235"/>
+      <c r="D26" s="244"/>
+      <c r="E26" s="244"/>
+      <c r="F26" s="244"/>
+      <c r="G26" s="244"/>
+      <c r="H26" s="244"/>
+      <c r="I26" s="244"/>
+      <c r="J26" s="244"/>
+      <c r="K26" s="244"/>
+      <c r="L26" s="244"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18138,18 +18138,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="235" t="s">
+      <c r="C33" s="244" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
-      <c r="I33" s="235"/>
-      <c r="J33" s="235"/>
-      <c r="K33" s="235"/>
-      <c r="L33" s="235"/>
+      <c r="D33" s="244"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="244"/>
+      <c r="G33" s="244"/>
+      <c r="H33" s="244"/>
+      <c r="I33" s="244"/>
+      <c r="J33" s="244"/>
+      <c r="K33" s="244"/>
+      <c r="L33" s="244"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18333,18 +18333,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="235" t="s">
+      <c r="C40" s="244" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="235"/>
-      <c r="E40" s="235"/>
-      <c r="F40" s="235"/>
-      <c r="G40" s="235"/>
-      <c r="H40" s="235"/>
-      <c r="I40" s="235"/>
-      <c r="J40" s="235"/>
-      <c r="K40" s="235"/>
-      <c r="L40" s="235"/>
+      <c r="D40" s="244"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="244"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="244"/>
+      <c r="L40" s="244"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18608,12 +18608,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18621,6 +18615,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18658,20 +18658,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="240" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="S2" s="249"/>
       <c r="T2" s="249"/>
       <c r="U2" s="249"/>
@@ -18689,18 +18689,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="244" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
       <c r="S4" s="249"/>
       <c r="T4" s="249"/>
       <c r="U4" s="249"/>
@@ -19074,18 +19074,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="235" t="s">
+      <c r="C13" s="244" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="235"/>
-      <c r="E13" s="235"/>
-      <c r="F13" s="235"/>
-      <c r="G13" s="235"/>
-      <c r="H13" s="235"/>
-      <c r="I13" s="235"/>
-      <c r="J13" s="235"/>
-      <c r="K13" s="235"/>
-      <c r="L13" s="235"/>
+      <c r="D13" s="244"/>
+      <c r="E13" s="244"/>
+      <c r="F13" s="244"/>
+      <c r="G13" s="244"/>
+      <c r="H13" s="244"/>
+      <c r="I13" s="244"/>
+      <c r="J13" s="244"/>
+      <c r="K13" s="244"/>
+      <c r="L13" s="244"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19178,18 +19178,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="235" t="s">
+      <c r="C18" s="244" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="235"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="235"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+      <c r="K18" s="244"/>
+      <c r="L18" s="244"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19381,18 +19381,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="235" t="s">
+      <c r="C25" s="244" t="s">
         <v>259</v>
       </c>
-      <c r="D25" s="235"/>
-      <c r="E25" s="235"/>
-      <c r="F25" s="235"/>
-      <c r="G25" s="235"/>
-      <c r="H25" s="235"/>
-      <c r="I25" s="235"/>
-      <c r="J25" s="235"/>
-      <c r="K25" s="235"/>
-      <c r="L25" s="235"/>
+      <c r="D25" s="244"/>
+      <c r="E25" s="244"/>
+      <c r="F25" s="244"/>
+      <c r="G25" s="244"/>
+      <c r="H25" s="244"/>
+      <c r="I25" s="244"/>
+      <c r="J25" s="244"/>
+      <c r="K25" s="244"/>
+      <c r="L25" s="244"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19530,18 +19530,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="235" t="s">
+      <c r="C31" s="244" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="235"/>
-      <c r="E31" s="235"/>
-      <c r="F31" s="235"/>
-      <c r="G31" s="235"/>
-      <c r="H31" s="235"/>
-      <c r="I31" s="235"/>
-      <c r="J31" s="235"/>
-      <c r="K31" s="235"/>
-      <c r="L31" s="235"/>
+      <c r="D31" s="244"/>
+      <c r="E31" s="244"/>
+      <c r="F31" s="244"/>
+      <c r="G31" s="244"/>
+      <c r="H31" s="244"/>
+      <c r="I31" s="244"/>
+      <c r="J31" s="244"/>
+      <c r="K31" s="244"/>
+      <c r="L31" s="244"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19680,16 +19680,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19752,10 +19752,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="235" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>168.74</v>
+        <v>181.97</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19781,7 +19781,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>179201.88</v>
+        <v>193252.13999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6626000000000001</v>
+        <v>1.6526000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="C11" s="135">
         <f>[1]Sheet1!$C$12</f>
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19840,10 +19840,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="235" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="238"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.8520349574447465E-2</v>
+        <v>7.3229634033105548E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92147965042555258</v>
+        <v>0.92677036596689444</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19878,7 +19878,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.12243699999999999</v>
+        <v>0.12055440000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11614186653391741</v>
+        <v>0.1148212958893286</v>
       </c>
     </row>
   </sheetData>
@@ -19932,20 +19932,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="239"/>
-      <c r="H3" s="240" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -19963,18 +19963,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="235" t="s">
+      <c r="C5" s="244" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="235"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="235"/>
-      <c r="I5" s="235"/>
-      <c r="J5" s="235"/>
-      <c r="K5" s="235"/>
-      <c r="L5" s="235"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -20138,7 +20138,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>177750.53220817546</v>
+        <v>180363.8560593852</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20192,23 +20192,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5653.4482151578977</v>
+        <v>5660.1450532799972</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3390.528022146787</v>
+        <v>3398.5653348198721</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5306.3098683213457</v>
+        <v>5325.1891119322418</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7502.3574277044545</v>
+        <v>7537.9685548020379</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>9124.4767428496034</v>
+        <v>9178.6472934058347</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20227,14 +20227,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>102615.72444251385</v>
+        <v>104742.5711529812</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="238" t="s">
+      <c r="B13" s="235" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="238"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20250,14 +20250,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11614186653391741</v>
+        <v>0.1148212958893286</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="238" t="s">
+      <c r="B18" s="235" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="238"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20265,7 +20265,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30977.120276180089</v>
+        <v>31100.515348239984</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>102615.72444251385</v>
+        <v>104742.5711529812</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>133592.84471869393</v>
+        <v>135843.08650122117</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20310,7 +20310,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>126626.84471869393</v>
+        <v>128877.08650122117</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>119.23431706091708</v>
+        <v>121.3531887958768</v>
       </c>
     </row>
   </sheetData>
@@ -20371,37 +20371,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="240" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="244" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20590,18 +20590,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="235" t="s">
+      <c r="C10" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="235"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
+      <c r="D10" s="244"/>
+      <c r="E10" s="244"/>
+      <c r="F10" s="244"/>
+      <c r="G10" s="244"/>
+      <c r="H10" s="244"/>
+      <c r="I10" s="244"/>
+      <c r="J10" s="244"/>
+      <c r="K10" s="244"/>
+      <c r="L10" s="244"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20795,18 +20795,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="235" t="s">
+      <c r="C16" s="244" t="s">
         <v>188</v>
       </c>
-      <c r="D16" s="235"/>
-      <c r="E16" s="235"/>
-      <c r="F16" s="235"/>
-      <c r="G16" s="235"/>
-      <c r="H16" s="235"/>
-      <c r="I16" s="235"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="235"/>
-      <c r="L16" s="235"/>
+      <c r="D16" s="244"/>
+      <c r="E16" s="244"/>
+      <c r="F16" s="244"/>
+      <c r="G16" s="244"/>
+      <c r="H16" s="244"/>
+      <c r="I16" s="244"/>
+      <c r="J16" s="244"/>
+      <c r="K16" s="244"/>
+      <c r="L16" s="244"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20940,18 +20940,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="235" t="s">
+      <c r="C21" s="244" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="235"/>
-      <c r="E21" s="235"/>
-      <c r="F21" s="235"/>
-      <c r="G21" s="235"/>
-      <c r="H21" s="235"/>
-      <c r="I21" s="235"/>
-      <c r="J21" s="235"/>
-      <c r="K21" s="235"/>
-      <c r="L21" s="235"/>
+      <c r="D21" s="244"/>
+      <c r="E21" s="244"/>
+      <c r="F21" s="244"/>
+      <c r="G21" s="244"/>
+      <c r="H21" s="244"/>
+      <c r="I21" s="244"/>
+      <c r="J21" s="244"/>
+      <c r="K21" s="244"/>
+      <c r="L21" s="244"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -21035,18 +21035,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="235" t="s">
+      <c r="C26" s="244" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="235"/>
-      <c r="E26" s="235"/>
-      <c r="F26" s="235"/>
-      <c r="G26" s="235"/>
-      <c r="H26" s="235"/>
-      <c r="I26" s="235"/>
-      <c r="J26" s="235"/>
-      <c r="K26" s="235"/>
-      <c r="L26" s="235"/>
+      <c r="D26" s="244"/>
+      <c r="E26" s="244"/>
+      <c r="F26" s="244"/>
+      <c r="G26" s="244"/>
+      <c r="H26" s="244"/>
+      <c r="I26" s="244"/>
+      <c r="J26" s="244"/>
+      <c r="K26" s="244"/>
+      <c r="L26" s="244"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21316,10 +21316,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="238" t="s">
+      <c r="B37" s="235" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="238"/>
+      <c r="C37" s="235"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21337,7 +21337,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11614186653391741</v>
+        <v>0.1148212958893286</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>212313.97412681766</v>
+        <v>213602.08995897553</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21390,7 +21390,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>205347.97412681766</v>
+        <v>206636.08995897553</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21408,14 +21408,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>193.35967431903734</v>
+        <v>194.57258941523119</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="238" t="s">
+      <c r="B49" s="235" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="238"/>
+      <c r="C49" s="235"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21432,7 +21432,7 @@
       </c>
       <c r="C51" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12243699999999999</v>
+        <v>0.12055440000000001</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21467,14 +21467,14 @@
       </c>
       <c r="C55" s="142">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>197.24172217952881</v>
+        <v>198.90418974577236</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="238" t="s">
+      <c r="B57" s="235" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="238"/>
+      <c r="C57" s="235"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11614186653391741</v>
+        <v>0.1148212958893286</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21517,7 +21517,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>177833.53485699208</v>
+        <v>178916.94586811669</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>170867.53485699208</v>
+        <v>171950.94586811669</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>160.89221737946522</v>
+        <v>161.91237840688953</v>
       </c>
     </row>
   </sheetData>
@@ -21614,10 +21614,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>119.23431706091708</v>
+        <v>121.3531887958768</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>193.35967431903734</v>
+        <v>194.57258941523119</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C55</f>
-        <v>197.24172217952881</v>
+        <v>198.90418974577236</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21653,7 +21653,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>160.89221737946522</v>
+        <v>161.91237840688953</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>167.68198273473712</v>
+        <v>169.18558659094245</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21671,7 +21671,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>168.74</v>
+        <v>181.97</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21680,7 +21680,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-6.2701035039877343E-3</v>
+        <v>-7.0255610315203332E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21736,37 +21736,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="240" t="s">
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="244" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="235"/>
-      <c r="I4" s="235"/>
-      <c r="J4" s="235"/>
-      <c r="K4" s="235"/>
-      <c r="L4" s="235"/>
+      <c r="D4" s="244"/>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244"/>
+      <c r="G4" s="244"/>
+      <c r="H4" s="244"/>
+      <c r="I4" s="244"/>
+      <c r="J4" s="244"/>
+      <c r="K4" s="244"/>
+      <c r="L4" s="244"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21879,18 +21879,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="235" t="s">
+      <c r="C9" s="244" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="235"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
+      <c r="H9" s="244"/>
+      <c r="I9" s="244"/>
+      <c r="J9" s="244"/>
+      <c r="K9" s="244"/>
+      <c r="L9" s="244"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22011,18 +22011,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="235" t="s">
+      <c r="C14" s="244" t="s">
         <v>406</v>
       </c>
-      <c r="D14" s="235"/>
-      <c r="E14" s="235"/>
-      <c r="F14" s="235"/>
-      <c r="G14" s="235"/>
-      <c r="H14" s="235"/>
-      <c r="I14" s="235"/>
-      <c r="J14" s="235"/>
-      <c r="K14" s="235"/>
-      <c r="L14" s="235"/>
+      <c r="D14" s="244"/>
+      <c r="E14" s="244"/>
+      <c r="F14" s="244"/>
+      <c r="G14" s="244"/>
+      <c r="H14" s="244"/>
+      <c r="I14" s="244"/>
+      <c r="J14" s="244"/>
+      <c r="K14" s="244"/>
+      <c r="L14" s="244"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22112,10 +22112,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="238" t="s">
+      <c r="B20" s="235" t="s">
         <v>408</v>
       </c>
-      <c r="C20" s="238"/>
+      <c r="C20" s="235"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22150,7 +22150,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12243699999999999</v>
+        <v>0.12055440000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C23/(C24-C25)</f>
-        <v>36.010425920321765</v>
+        <v>36.684620464146768</v>
       </c>
     </row>
   </sheetData>
@@ -22216,20 +22216,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="235" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="239"/>
-      <c r="H3" s="240" t="s">
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="247"/>
+      <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -22247,18 +22247,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="235" t="s">
+      <c r="C5" s="244" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="235"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="235"/>
-      <c r="I5" s="235"/>
-      <c r="J5" s="235"/>
-      <c r="K5" s="235"/>
-      <c r="L5" s="235"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
       <c r="R5" s="249"/>
@@ -22404,7 +22404,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>185993.21322967499</v>
+        <v>188727.72262471294</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22458,23 +22458,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11304.116920535367</v>
+        <v>11317.50730428862</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>10836.799037504152</v>
+        <v>10862.487880560715</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10388.80031096574</v>
+        <v>10425.762474269957</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9959.322077267092</v>
+        <v>10006.595575992924</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9547.5986899125619</v>
+        <v>9604.2812474003458</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22493,7 +22493,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>107374.24006472943</v>
+        <v>109599.71330980246</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>168.74</v>
+        <v>181.97</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22518,7 +22518,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>145.18559723896604</v>
+        <v>147.47652170696668</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11614186653391741</v>
+        <v>0.1148212958893286</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>177177</v>
+        <v>191068.5</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>184143</v>
+        <v>198034.5</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22618,7 +22618,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>52036.637036184919</v>
+        <v>52216.634482512556</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22627,7 +22627,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>107374.24006472943</v>
+        <v>109599.71330980246</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22636,7 +22636,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>159410.87710091434</v>
+        <v>161816.34779231501</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22663,7 +22663,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>152444.87710091434</v>
+        <v>154850.34779231501</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22681,22 +22681,22 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>145.18559723896604</v>
+        <v>147.47652170696668</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="235" t="s">
+      <c r="C39" s="244" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
-      <c r="I39" s="235"/>
-      <c r="J39" s="235"/>
-      <c r="K39" s="235"/>
-      <c r="L39" s="235"/>
+      <c r="D39" s="244"/>
+      <c r="E39" s="244"/>
+      <c r="F39" s="244"/>
+      <c r="G39" s="244"/>
+      <c r="H39" s="244"/>
+      <c r="I39" s="244"/>
+      <c r="J39" s="244"/>
+      <c r="K39" s="244"/>
+      <c r="L39" s="244"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23128,17 +23128,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>168.74</v>
+        <v>181.97</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29824,7 +29824,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>168.74</v>
+        <v>181.97</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31326,7 +31326,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>19.070237860525843</v>
+        <v>20.565433112954175</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31363,7 +31363,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.1143489606971047</v>
+        <v>4.4369330353090675</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31424,7 +31424,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.4059946489261703</v>
+        <v>6.9082543929423679</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>179201.88</v>
+        <v>193252.13999999998</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>186167.88</v>
+        <v>200218.13999999998</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31583,7 +31583,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>4.2245593174185352</v>
+        <v>4.5433906689661425</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31620,7 +31620,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>18.217817790390448</v>
+        <v>19.59273314414326</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31755,7 +31755,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>24.97935321996097</v>
+        <v>26.937850571508221</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31792,7 +31792,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>19.094602148118451</v>
+        <v>20.53568921844241</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31829,7 +31829,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>4.003306215314259E-2</v>
+        <v>3.7122486716059139E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31866,7 +31866,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.2437730840784909E-2</v>
+        <v>4.8625282750310743E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31903,7 +31903,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>2.1275334834656868E-2</v>
+        <v>1.9728526680222014E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31940,7 +31940,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>5.1617762045799966E-2</v>
+        <v>4.7864929205958605E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31977,7 +31977,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>7.296240418906319E-2</v>
+        <v>6.7657724255990134E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32480,7 +32480,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.8872360044437032E-2</v>
+        <v>-3.604617263229272E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33802,15 +33802,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="235" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="238"/>
-      <c r="E4" s="238" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33818,7 +33818,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>168.74</v>
+        <v>181.97</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33834,7 +33834,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>179201.88</v>
+        <v>193252.13999999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33854,7 +33854,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>186167.88</v>
+        <v>200218.13999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>19.070237860525843</v>
+        <v>20.565433112954175</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -33894,7 +33894,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.1143489606971047</v>
+        <v>4.4369330353090675</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>6.4059946489261703</v>
+        <v>6.9082543929423679</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33934,7 +33934,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.2245593174185352</v>
+        <v>4.5433906689661425</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33943,18 +33943,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>18.217817790390448</v>
+        <v>19.59273314414326</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="238"/>
-      <c r="E15" s="238" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="238"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34005,14 +34005,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="238" t="s">
+      <c r="B21" s="235" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="238"/>
-      <c r="E21" s="238" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="238"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34081,14 +34081,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="238" t="s">
+      <c r="B29" s="235" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="238"/>
-      <c r="E29" s="238" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="238"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34164,14 +34164,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="238" t="s">
+      <c r="B37" s="235" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="238"/>
-      <c r="E37" s="238" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="238"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34179,7 +34179,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.2437730840784909E-2</v>
+        <v>4.8625282750310743E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -34195,7 +34195,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>4.003306215314259E-2</v>
+        <v>3.7122486716059139E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -34211,7 +34211,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>2.1275334834656868E-2</v>
+        <v>1.9728526680222014E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -34227,7 +34227,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.1617762045799966E-2</v>
+        <v>4.7864929205958605E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34236,18 +34236,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>7.296240418906319E-2</v>
+        <v>6.7657724255990134E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="238" t="s">
+      <c r="B45" s="235" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="238"/>
-      <c r="E45" s="238" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="238"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34280,18 +34280,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-3.8872360044437032E-2</v>
+        <v>-3.604617263229272E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="238" t="s">
+      <c r="B51" s="235" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="238"/>
-      <c r="E51" s="238" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="238"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34460,7 +34460,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>168.74</v>
+        <v>181.97</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34489,7 +34489,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>179201.88</v>
+        <v>193252.13999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34518,7 +34518,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>186167.88</v>
+        <v>200218.13999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34547,7 +34547,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>19.070237860525843</v>
+        <v>20.565433112954175</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34576,7 +34576,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.1143489606971047</v>
+        <v>4.4369330353090675</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34605,7 +34605,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>6.4059946489261703</v>
+        <v>6.9082543929423679</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34634,7 +34634,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.2245593174185352</v>
+        <v>4.5433906689661425</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34663,7 +34663,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>18.217817790390448</v>
+        <v>19.59273314414326</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>5.2437730840784909E-2</v>
+        <v>4.8625282750310743E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35465,7 +35465,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>4.003306215314259E-2</v>
+        <v>3.7122486716059139E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35494,7 +35494,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>2.1275334834656868E-2</v>
+        <v>1.9728526680222014E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35523,7 +35523,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>5.1617762045799966E-2</v>
+        <v>4.7864929205958605E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35552,7 +35552,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>7.296240418906319E-2</v>
+        <v>6.7657724255990134E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35788,7 +35788,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-3.8872360044437032E-2</v>
+        <v>-3.604617263229272E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36326,14 +36326,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="239" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="240"/>
+      <c r="F3" s="241" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36400,19 +36400,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="242">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="243"/>
+      <c r="F7" s="242">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="243"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -36439,19 +36439,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="242">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="243"/>
+      <c r="F9" s="242">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="243"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -36478,19 +36478,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="242">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="243"/>
+      <c r="F11" s="242">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="243"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -36517,19 +36517,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="242">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="243"/>
+      <c r="F13" s="242">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="243"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -36556,19 +36556,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="242">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="243"/>
+      <c r="F15" s="242">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -36595,19 +36595,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="242">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="243"/>
+      <c r="F17" s="242">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="243"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36634,22 +36634,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="242">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="243"/>
+      <c r="F19" s="242">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="243"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36676,22 +36676,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="242">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="243"/>
+      <c r="F21" s="242">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="243"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36739,22 +36739,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="242">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="243"/>
+      <c r="F25" s="242">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="243"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -36781,22 +36781,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="242">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="243"/>
+      <c r="F27" s="242">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="243"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -36823,22 +36823,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="242">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="243"/>
+      <c r="F29" s="242">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="243"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36865,22 +36865,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="244">
+      <c r="C31" s="242">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="245"/>
-      <c r="F31" s="244">
+      <c r="D31" s="243"/>
+      <c r="F31" s="242">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="245"/>
+      <c r="G31" s="243"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36907,43 +36907,25 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="244">
+      <c r="C33" s="242">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="245"/>
-      <c r="F33" s="244">
+      <c r="D33" s="243"/>
+      <c r="F33" s="242">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="245"/>
+      <c r="G33" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36954,6 +36936,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897A2651-3EA6-2742-B3C7-FD8954FDC7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D32126-38CE-0A40-B2D4-F373815AA5F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -129,7 +129,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -139,12 +160,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2352,9 +2382,6 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2364,6 +2391,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2371,12 +2407,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12724,7 +12754,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12763,11 +12793,9 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6526000000000001</v>
-    <v>5.09</v>
-    <v>2.8777E-2</v>
-    <v>0.09</v>
-    <v>4.9459999999999999E-4</v>
+    <v>1.6614</v>
+    <v>1.41</v>
+    <v>7.2589999999999998E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12775,36 +12803,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>185.46</v>
+    <v>197.4</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46276.999878946095</v>
+    <v>46287.766350960155</v>
     <v>4</v>
-    <v>175.74</v>
-    <v>191068500000</v>
+    <v>191.66</v>
+    <v>205422000000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>178.25</v>
-    <v>20.471299999999999</v>
-    <v>176.88</v>
-    <v>181.97</v>
-    <v>182.06</v>
+    <v>192.28</v>
+    <v>22.642499999999998</v>
+    <v>194.23</v>
+    <v>195.64</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>11556632</v>
-    <v>10218769</v>
+    <v>5643160</v>
+    <v>13433436</v>
     <v>1991</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12816,30 +12858,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.12</v>
+    <v>50.16</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.62E-3</v>
+    <v>-0.35</v>
+    <v>-7.0030000000000005E-3</v>
     <v>US</v>
-    <v>48.12</v>
+    <v>49.76</v>
     <v>Index</v>
-    <v>7</v>
-    <v>47.48</v>
+    <v>10</v>
+    <v>49.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.54</v>
-    <v>47.62</v>
-    <v>47.84</v>
+    <v>49.53</v>
+    <v>49.98</v>
+    <v>49.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12873,8 +12915,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12896,7 +12936,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12906,6 +12945,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12941,7 +12985,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12952,16 +12996,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13062,19 +13103,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13155,9 +13190,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13165,9 +13197,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13659,18 +13688,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="236" t="s">
+      <c r="B2" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="237"/>
-      <c r="E2" s="236" t="s">
+      <c r="C2" s="236"/>
+      <c r="E2" s="235" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="237"/>
-      <c r="H2" s="236" t="s">
+      <c r="F2" s="236"/>
+      <c r="H2" s="235" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="237"/>
+      <c r="I2" s="236"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13685,7 +13714,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC156</f>
-        <v>193252.13999999998</v>
+        <v>207769.68</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13693,7 +13722,7 @@
       </c>
       <c r="I3" s="211">
         <f ca="1">'AVG target price'!C5</f>
-        <v>121.3531887958768</v>
+        <v>117.54643303720623</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13709,7 +13738,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC157</f>
-        <v>200218.13999999998</v>
+        <v>214735.68</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13717,7 +13746,7 @@
       </c>
       <c r="I4" s="211">
         <f ca="1">'AVG target price'!C6</f>
-        <v>194.57258941523119</v>
+        <v>192.37342913081443</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13726,7 +13755,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>181.97</v>
+        <v>195.64</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>240</v>
@@ -13741,23 +13770,23 @@
       </c>
       <c r="I5" s="211">
         <f ca="1">'AVG target price'!C7</f>
-        <v>198.90418974577236</v>
+        <v>196.98308099993119</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>182.06</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>234</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC153</f>
-        <v>20.565433112954175</v>
+        <v>22.110355191615952</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13765,7 +13794,7 @@
       </c>
       <c r="I6" s="211">
         <f ca="1">'AVG target price'!C8</f>
-        <v>161.91237840688953</v>
+        <v>160.06270432643535</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13774,14 +13803,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>5.09</v>
+        <v>1.41</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC154</f>
-        <v>4.4369330353090675</v>
+        <v>4.7702455296360169</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13789,23 +13818,23 @@
       </c>
       <c r="I7" s="212">
         <f ca="1">'AVG target price'!C9</f>
-        <v>169.18558659094245</v>
+        <v>166.7414118735968</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.09</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>262</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC164</f>
-        <v>3.7122486716059139E-2</v>
+        <v>3.4528618420166024E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13813,7 +13842,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-7.0255610315203332E-2</v>
+        <v>-0.14771308590473925</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13822,37 +13851,37 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.8777E-2</v>
+        <v>7.2589999999999998E-3</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>285</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC165</f>
-        <v>4.8625282750310743E-2</v>
+        <v>4.5227676866050122E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>4.9459999999999999E-4</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>290</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC167</f>
-        <v>4.7864929205958605E-2</v>
+        <v>4.4520451684769403E-2</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>413</v>
       </c>
       <c r="I10" s="212">
         <f ca="1">DDM!C26</f>
-        <v>36.684620464146768</v>
+        <v>35.907160016976277</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13868,7 +13897,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC166</f>
-        <v>1.9728526680222014E-2</v>
+        <v>1.8350030668574935E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13893,7 +13922,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6526000000000001</v>
+        <v>1.6614</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>96</v>
@@ -13909,7 +13938,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>10218769</v>
+        <v>13433436</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>97</v>
@@ -13925,7 +13954,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.604617263229272E-2</v>
+        <v>-3.352750988498418E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13938,10 +13967,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="238" t="s">
+      <c r="B17" s="237" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="238"/>
+      <c r="C17" s="237"/>
       <c r="E17" s="184" t="s">
         <v>293</v>
       </c>
@@ -14014,14 +14043,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="238" t="s">
+      <c r="B25" s="237" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="238"/>
-      <c r="E25" s="236" t="s">
+      <c r="C25" s="237"/>
+      <c r="E25" s="235" t="s">
         <v>338</v>
       </c>
-      <c r="F25" s="237"/>
+      <c r="F25" s="236"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14030,12 +14059,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.84</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14050,7 +14079,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14070,15 +14099,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="238" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="235"/>
-      <c r="D33" s="235"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="235"/>
-      <c r="G33" s="235"/>
-      <c r="H33" s="235"/>
+      <c r="C33" s="238"/>
+      <c r="D33" s="238"/>
+      <c r="E33" s="238"/>
+      <c r="F33" s="238"/>
+      <c r="G33" s="238"/>
+      <c r="H33" s="238"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14097,24 +14126,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="235"/>
-      <c r="C39" s="235"/>
-      <c r="D39" s="235"/>
-      <c r="E39" s="235"/>
-      <c r="F39" s="235"/>
-      <c r="G39" s="235"/>
-      <c r="H39" s="235"/>
+      <c r="B39" s="238"/>
+      <c r="C39" s="238"/>
+      <c r="D39" s="238"/>
+      <c r="E39" s="238"/>
+      <c r="F39" s="238"/>
+      <c r="G39" s="238"/>
+      <c r="H39" s="238"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="235" t="s">
+      <c r="B42" s="238" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="235"/>
-      <c r="D42" s="235"/>
-      <c r="E42" s="235"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="235"/>
-      <c r="H42" s="235"/>
+      <c r="C42" s="238"/>
+      <c r="D42" s="238"/>
+      <c r="E42" s="238"/>
+      <c r="F42" s="238"/>
+      <c r="G42" s="238"/>
+      <c r="H42" s="238"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14198,24 +14227,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="235"/>
-      <c r="C55" s="235"/>
-      <c r="D55" s="235"/>
-      <c r="E55" s="235"/>
-      <c r="F55" s="235"/>
-      <c r="G55" s="235"/>
-      <c r="H55" s="235"/>
+      <c r="B55" s="238"/>
+      <c r="C55" s="238"/>
+      <c r="D55" s="238"/>
+      <c r="E55" s="238"/>
+      <c r="F55" s="238"/>
+      <c r="G55" s="238"/>
+      <c r="H55" s="238"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="235" t="s">
+      <c r="B58" s="238" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="235"/>
-      <c r="D58" s="235"/>
-      <c r="E58" s="235"/>
-      <c r="F58" s="235"/>
-      <c r="G58" s="235"/>
-      <c r="H58" s="235"/>
+      <c r="C58" s="238"/>
+      <c r="D58" s="238"/>
+      <c r="E58" s="238"/>
+      <c r="F58" s="238"/>
+      <c r="G58" s="238"/>
+      <c r="H58" s="238"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14353,28 +14382,28 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="235"/>
-      <c r="C75" s="235"/>
-      <c r="D75" s="235"/>
-      <c r="E75" s="235"/>
-      <c r="F75" s="235"/>
-      <c r="G75" s="235"/>
-      <c r="H75" s="235"/>
+      <c r="B75" s="238"/>
+      <c r="C75" s="238"/>
+      <c r="D75" s="238"/>
+      <c r="E75" s="238"/>
+      <c r="F75" s="238"/>
+      <c r="G75" s="238"/>
+      <c r="H75" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14444,36 +14473,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15943,35 +15972,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="P2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="238"/>
+      <c r="R2" s="238"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="238"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="238"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -17202,20 +17231,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
       <c r="G3" s="247"/>
       <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -18608,6 +18637,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18615,12 +18650,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18658,20 +18687,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
       <c r="S2" s="249"/>
       <c r="T2" s="249"/>
       <c r="U2" s="249"/>
@@ -19680,16 +19709,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19752,10 +19781,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="238"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19772,7 +19801,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>181.97</v>
+        <v>195.64</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19781,7 +19810,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>193252.13999999998</v>
+        <v>207769.68</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19799,7 +19828,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19808,7 +19837,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6526000000000001</v>
+        <v>1.6614</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19840,10 +19869,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="238" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="238"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19851,7 +19880,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.3229634033105548E-2</v>
+        <v>6.8463154179561239E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19860,7 +19889,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92677036596689444</v>
+        <v>0.93153684582043872</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19878,7 +19907,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.12055440000000001</v>
+        <v>0.1227316</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19887,7 +19916,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1148212958893286</v>
+        <v>0.11722260275789491</v>
       </c>
     </row>
   </sheetData>
@@ -19932,20 +19961,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
       <c r="G3" s="247"/>
       <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -20138,7 +20167,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>180363.8560593852</v>
+        <v>175667.51315163283</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20192,23 +20221,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5660.1450532799972</v>
+        <v>5647.9793978770622</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3398.5653348198721</v>
+        <v>3383.971595265185</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5325.1891119322418</v>
+        <v>5290.9257122127256</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7537.9685548020379</v>
+        <v>7473.3701440965679</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>9178.6472934058347</v>
+        <v>9080.4295997337176</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20227,14 +20256,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>104742.5711529812</v>
+        <v>100923.63543632775</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="238" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="238"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20250,14 +20279,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1148212958893286</v>
+        <v>0.11722260275789491</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="238" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="238"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20265,7 +20294,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>31100.515348239984</v>
+        <v>30876.676449185259</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20274,7 +20303,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>104742.5711529812</v>
+        <v>100923.63543632775</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20283,7 +20312,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>135843.08650122117</v>
+        <v>131800.31188551302</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20310,7 +20339,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>128877.08650122117</v>
+        <v>124834.31188551302</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20328,7 +20357,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C24/C25</f>
-        <v>121.3531887958768</v>
+        <v>117.54643303720623</v>
       </c>
     </row>
   </sheetData>
@@ -20371,20 +20400,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21316,10 +21345,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="238" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="235"/>
+      <c r="C37" s="238"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21337,7 +21366,7 @@
       </c>
       <c r="C39" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1148212958893286</v>
+        <v>0.11722260275789491</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21363,7 +21392,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>213602.08995897553</v>
+        <v>211266.58173692491</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21390,7 +21419,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>206636.08995897553</v>
+        <v>204300.58173692491</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21408,14 +21437,14 @@
       </c>
       <c r="C47" s="142">
         <f ca="1">C45/C46</f>
-        <v>194.57258941523119</v>
+        <v>192.37342913081443</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="235" t="s">
+      <c r="B49" s="238" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="235"/>
+      <c r="C49" s="238"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21432,7 +21461,7 @@
       </c>
       <c r="C51" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12055440000000001</v>
+        <v>0.1227316</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21467,14 +21496,14 @@
       </c>
       <c r="C55" s="142">
         <f ca="1">C54/(1+C51)^5</f>
-        <v>198.90418974577236</v>
+        <v>196.98308099993119</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="235" t="s">
+      <c r="B57" s="238" t="s">
         <v>319</v>
       </c>
-      <c r="C57" s="235"/>
+      <c r="C57" s="238"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21491,7 +21520,7 @@
       </c>
       <c r="C59" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1148212958893286</v>
+        <v>0.11722260275789491</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21517,7 +21546,7 @@
       </c>
       <c r="C62" s="24">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>178916.94586811669</v>
+        <v>176952.59199467435</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21544,7 +21573,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>171950.94586811669</v>
+        <v>169986.59199467435</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21562,7 +21591,7 @@
       </c>
       <c r="C67" s="142">
         <f ca="1">C65/C66</f>
-        <v>161.91237840688953</v>
+        <v>160.06270432643535</v>
       </c>
     </row>
   </sheetData>
@@ -21614,10 +21643,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="238"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21626,7 +21655,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>121.3531887958768</v>
+        <v>117.54643303720623</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21635,7 +21664,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C47</f>
-        <v>194.57258941523119</v>
+        <v>192.37342913081443</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21644,7 +21673,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C55</f>
-        <v>198.90418974577236</v>
+        <v>196.98308099993119</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21653,7 +21682,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C67</f>
-        <v>161.91237840688953</v>
+        <v>160.06270432643535</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21662,7 +21691,7 @@
       </c>
       <c r="C9" s="142">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>169.18558659094245</v>
+        <v>166.7414118735968</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21671,7 +21700,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>181.97</v>
+        <v>195.64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21680,7 +21709,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-7.0255610315203332E-2</v>
+        <v>-0.14771308590473925</v>
       </c>
     </row>
   </sheetData>
@@ -21736,20 +21765,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
       <c r="G2" s="247"/>
       <c r="H2" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22112,10 +22141,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="235" t="s">
+      <c r="B20" s="238" t="s">
         <v>408</v>
       </c>
-      <c r="C20" s="235"/>
+      <c r="C20" s="238"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22150,7 +22179,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12055440000000001</v>
+        <v>0.1227316</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22167,7 +22196,7 @@
       </c>
       <c r="C26" s="142">
         <f ca="1">C23/(C24-C25)</f>
-        <v>36.684620464146768</v>
+        <v>35.907160016976277</v>
       </c>
     </row>
   </sheetData>
@@ -22216,20 +22245,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="238"/>
       <c r="G3" s="247"/>
       <c r="H3" s="248" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="238"/>
+      <c r="K3" s="238"/>
+      <c r="L3" s="238"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
       <c r="R3" s="249"/>
@@ -22404,7 +22433,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>188727.72262471294</v>
+        <v>183813.60002271555</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22458,23 +22487,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11317.50730428862</v>
+        <v>11293.18197470994</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>10862.487880560715</v>
+        <v>10815.843398719895</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10425.762474269957</v>
+        <v>10358.680900352478</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>10006.595575992924</v>
+        <v>9920.8416800882078</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>9604.2812474003458</v>
+        <v>9501.5089844138674</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22493,7 +22522,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>109599.71330980246</v>
+        <v>105603.6851897512</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22509,7 +22538,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>181.97</v>
+        <v>195.64</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22518,7 +22547,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>147.47652170696668</v>
+        <v>143.35975440765293</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22557,7 +22586,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1148212958893286</v>
+        <v>0.11722260275789491</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22575,7 +22604,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>191068.5</v>
+        <v>205422</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22602,7 +22631,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>198034.5</v>
+        <v>212388</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22618,7 +22647,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>52216.634482512556</v>
+        <v>51890.056938284397</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22627,7 +22656,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>109599.71330980246</v>
+        <v>105603.6851897512</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22636,7 +22665,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>161816.34779231501</v>
+        <v>157493.74212803558</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22663,7 +22692,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>154850.34779231501</v>
+        <v>150527.74212803558</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22681,7 +22710,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>147.47652170696668</v>
+        <v>143.35975440765293</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -23128,17 +23157,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29753,7 +29782,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>181.97</v>
+        <v>195.64</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29824,7 +29853,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>181.97</v>
+        <v>195.64</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31326,7 +31355,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>20.565433112954175</v>
+        <v>22.110355191615952</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31363,7 +31392,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.4369330353090675</v>
+        <v>4.7702455296360169</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31424,7 +31453,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.9082543929423679</v>
+        <v>7.4272181647262991</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31485,7 +31514,7 @@
       </c>
       <c r="AC156" s="143">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>193252.13999999998</v>
+        <v>207769.68</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31546,7 +31575,7 @@
       </c>
       <c r="AC157" s="143">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>200218.13999999998</v>
+        <v>214735.68</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31583,7 +31612,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="183">
         <f ca="1">AC157/AC5</f>
-        <v>4.5433906689661425</v>
+        <v>4.8728256331124626</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31620,7 +31649,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="183">
         <f ca="1">AC157/AC12</f>
-        <v>19.59273314414326</v>
+        <v>21.013375085624816</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31755,7 +31784,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>26.937850571508221</v>
+        <v>28.961483133537776</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31792,7 +31821,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>20.53568921844241</v>
+        <v>22.024703598739354</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31829,7 +31858,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>3.7122486716059139E-2</v>
+        <v>3.4528618420166024E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31866,7 +31895,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>4.8625282750310743E-2</v>
+        <v>4.5227676866050122E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31903,7 +31932,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">AC82/AC116</f>
-        <v>1.9728526680222014E-2</v>
+        <v>1.8350030668574935E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31940,7 +31969,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="154">
         <f ca="1">-AC63/AC156</f>
-        <v>4.7864929205958605E-2</v>
+        <v>4.4520451684769403E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31977,7 +32006,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="154">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>6.7657724255990134E-2</v>
+        <v>6.2930260084147024E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32480,7 +32509,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="154">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.604617263229272E-2</v>
+        <v>-3.352750988498418E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33802,15 +33831,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="238" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="238"/>
+      <c r="E4" s="238" t="s">
         <v>237</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33818,7 +33847,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>181.97</v>
+        <v>195.64</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33834,7 +33863,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>193252.13999999998</v>
+        <v>207769.68</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33854,7 +33883,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>200218.13999999998</v>
+        <v>214735.68</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33874,7 +33903,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>20.565433112954175</v>
+        <v>22.110355191615952</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>240</v>
@@ -33894,7 +33923,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.4369330353090675</v>
+        <v>4.7702455296360169</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>241</v>
@@ -33914,7 +33943,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>6.9082543929423679</v>
+        <v>7.4272181647262991</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33934,7 +33963,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.5433906689661425</v>
+        <v>4.8728256331124626</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33943,18 +33972,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>19.59273314414326</v>
+        <v>21.013375085624816</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="238" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="238"/>
+      <c r="E15" s="238" t="s">
         <v>243</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34005,14 +34034,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="238" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="238"/>
+      <c r="E21" s="238" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="238"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34081,14 +34110,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="238" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="238"/>
+      <c r="E29" s="238" t="s">
         <v>253</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="238"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34164,14 +34193,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="238" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="238"/>
+      <c r="E37" s="238" t="s">
         <v>268</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="238"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34179,7 +34208,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>4.8625282750310743E-2</v>
+        <v>4.5227676866050122E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>267</v>
@@ -34195,7 +34224,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC164</f>
-        <v>3.7122486716059139E-2</v>
+        <v>3.4528618420166024E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>269</v>
@@ -34211,7 +34240,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.9728526680222014E-2</v>
+        <v>1.8350030668574935E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>270</v>
@@ -34227,7 +34256,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>4.7864929205958605E-2</v>
+        <v>4.4520451684769403E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34236,18 +34265,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>6.7657724255990134E-2</v>
+        <v>6.2930260084147024E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="238" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="238"/>
+      <c r="E45" s="238" t="s">
         <v>282</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="238"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34280,18 +34309,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC179</f>
-        <v>-3.604617263229272E-2</v>
+        <v>-3.352750988498418E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="238" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="238"/>
+      <c r="E51" s="238" t="s">
         <v>300</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="238"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34460,7 +34489,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC115</f>
-        <v>181.97</v>
+        <v>195.64</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34489,7 +34518,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>193252.13999999998</v>
+        <v>207769.68</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34518,7 +34547,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC157</f>
-        <v>200218.13999999998</v>
+        <v>214735.68</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34547,7 +34576,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>20.565433112954175</v>
+        <v>22.110355191615952</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34576,7 +34605,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>4.4369330353090675</v>
+        <v>4.7702455296360169</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34605,7 +34634,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC155</f>
-        <v>6.9082543929423679</v>
+        <v>7.4272181647262991</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34634,7 +34663,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC158</f>
-        <v>4.5433906689661425</v>
+        <v>4.8728256331124626</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34663,7 +34692,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC159</f>
-        <v>19.59273314414326</v>
+        <v>21.013375085624816</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35436,7 +35465,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC165</f>
-        <v>4.8625282750310743E-2</v>
+        <v>4.5227676866050122E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35465,7 +35494,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC164</f>
-        <v>3.7122486716059139E-2</v>
+        <v>3.4528618420166024E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35494,7 +35523,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC166</f>
-        <v>1.9728526680222014E-2</v>
+        <v>1.8350030668574935E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35523,7 +35552,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC167</f>
-        <v>4.7864929205958605E-2</v>
+        <v>4.4520451684769403E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35552,7 +35581,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC168</f>
-        <v>6.7657724255990134E-2</v>
+        <v>6.2930260084147024E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35788,7 +35817,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC179</f>
-        <v>-3.604617263229272E-2</v>
+        <v>-3.352750988498418E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36326,14 +36355,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="241" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36400,19 +36429,19 @@
       <c r="B7" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="242">
+      <c r="C7" s="239">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="F7" s="242">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="243"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -36439,19 +36468,19 @@
       <c r="B9" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="242">
+      <c r="C9" s="239">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="243"/>
-      <c r="F9" s="242">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="243"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -36478,19 +36507,19 @@
       <c r="B11" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="242">
+      <c r="C11" s="239">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="243"/>
-      <c r="F11" s="242">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="243"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -36517,19 +36546,19 @@
       <c r="B13" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C13" s="242">
+      <c r="C13" s="239">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="243"/>
-      <c r="F13" s="242">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="243"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -36556,19 +36585,19 @@
       <c r="B15" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="242">
+      <c r="C15" s="239">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="243"/>
-      <c r="F15" s="242">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="243"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -36595,19 +36624,19 @@
       <c r="B17" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C17" s="242">
+      <c r="C17" s="239">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="243"/>
-      <c r="F17" s="242">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="243"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36634,22 +36663,22 @@
       <c r="B19" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="242">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="243"/>
-      <c r="F19" s="242">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="243"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36676,22 +36705,22 @@
       <c r="B21" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C21" s="242">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="243"/>
-      <c r="F21" s="242">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="243"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36739,22 +36768,22 @@
       <c r="B25" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="242">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="243"/>
-      <c r="F25" s="242">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="243"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="222" t="s">
@@ -36781,22 +36810,22 @@
       <c r="B27" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="242">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="243"/>
-      <c r="F27" s="242">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="243"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="222" t="s">
@@ -36823,22 +36852,22 @@
       <c r="B29" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="242">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="243"/>
-      <c r="F29" s="242">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="243"/>
+      <c r="G29" s="240"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36865,22 +36894,22 @@
       <c r="B31" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C31" s="242">
+      <c r="C31" s="239">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="243"/>
-      <c r="F31" s="242">
+      <c r="D31" s="240"/>
+      <c r="F31" s="239">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="243"/>
+      <c r="G31" s="240"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36907,25 +36936,43 @@
       <c r="B33" s="206" t="s">
         <v>312</v>
       </c>
-      <c r="C33" s="242">
+      <c r="C33" s="239">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="243"/>
-      <c r="F33" s="242">
+      <c r="D33" s="240"/>
+      <c r="F33" s="239">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="243"/>
+      <c r="G33" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36936,24 +36983,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660295D7-05BE-1F40-80E2-31085CA4B2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77622472-77E9-DB4F-8538-762260BDF223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -129,28 +129,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -160,21 +139,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2368,7 +2338,16 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2380,12 +2359,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2395,19 +2368,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12740,7 +12710,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12780,8 +12750,10 @@
     <v>259.92</v>
     <v>121.99</v>
     <v>1.6521999999999999</v>
-    <v>11.06</v>
-    <v>5.6933999999999998E-2</v>
+    <v>7.71</v>
+    <v>3.9689000000000002E-2</v>
+    <v>-0.33</v>
+    <v>-1.6339999999999998E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12793,46 +12765,32 @@
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.719172128905</v>
+    <v>46290.83637109922</v>
     <v>4</v>
     <v>194.53</v>
-    <v>215586000000</v>
+    <v>212068500000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>195.4</v>
-    <v>23.762799999999999</v>
+    <v>23.3751</v>
     <v>194.26</v>
-    <v>205.32</v>
+    <v>201.97</v>
+    <v>201.64</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>9950897</v>
+    <v>17531585</v>
     <v>13522451</v>
     <v>1991</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12851,7 +12809,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>10</v>
+    <v>7</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -12861,13 +12819,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>11</v>
+    <v>8</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12901,6 +12859,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12922,6 +12882,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12931,11 +12892,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12971,7 +12927,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12982,13 +12938,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13089,13 +13048,19 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
+      <v>1</v>
+      <v>1</v>
+      <v>6</v>
     </spb>
     <spb s="5">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13176,6 +13141,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13183,6 +13151,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13674,18 +13645,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="234" t="s">
+      <c r="B2" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="E2" s="234" t="s">
+      <c r="C2" s="238"/>
+      <c r="E2" s="237" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="235"/>
-      <c r="H2" s="234" t="s">
+      <c r="F2" s="238"/>
+      <c r="H2" s="237" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="235"/>
+      <c r="I2" s="238"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="181" t="s">
@@ -13700,7 +13671,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC156</f>
-        <v>218049.84</v>
+        <v>214492.13999999998</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13708,7 +13679,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>112.67991613730157</v>
+        <v>112.80190773457896</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13724,7 +13695,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC157</f>
-        <v>225015.84</v>
+        <v>221458.13999999998</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13732,7 +13703,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>209.78998595251571</v>
+        <v>214.25413667049858</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13741,7 +13712,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>205.32</v>
+        <v>201.97</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>235</v>
@@ -13763,16 +13734,16 @@
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="204" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="204" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>201.64</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>23.204345368751724</v>
+        <v>22.825743396292548</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13780,7 +13751,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>177.94774040133379</v>
+        <v>182.39983552985856</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13789,14 +13760,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>11.06</v>
+        <v>7.71</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>5.0062707633657073</v>
+        <v>4.9245884768993378</v>
       </c>
       <c r="H7" s="180" t="str">
         <f>'AVG target price'!B9</f>
@@ -13804,23 +13775,23 @@
       </c>
       <c r="I7" s="208">
         <f ca="1">'AVG target price'!C9</f>
-        <v>173.64628001685941</v>
+        <v>175.90583937780565</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.33</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC164</f>
-        <v>3.2900734987927532E-2</v>
+        <v>3.3446447035308614E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B11</f>
@@ -13828,7 +13799,7 @@
       </c>
       <c r="I8" s="209">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.15426514700536034</v>
+        <v>-0.12904966392134648</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13837,30 +13808,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>5.6933999999999998E-2</v>
+        <v>3.9689000000000002E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC165</f>
-        <v>4.3095376495587596E-2</v>
+        <v>4.3810183205793163E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-1.6339999999999998E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC167</f>
-        <v>4.2421494095111464E-2</v>
+        <v>4.3125123372819166E-2</v>
       </c>
       <c r="H10" s="180" t="s">
         <v>404</v>
@@ -13883,7 +13854,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.7484901616988117E-2</v>
+        <v>1.7774917066891122E-2</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13940,7 +13911,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC179</f>
-        <v>-3.1946824634221244E-2</v>
+        <v>-3.2476714531357656E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13953,10 +13924,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="236" t="s">
+      <c r="B17" s="239" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="236"/>
+      <c r="C17" s="239"/>
       <c r="E17" s="180" t="s">
         <v>288</v>
       </c>
@@ -14029,14 +14000,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="236" t="s">
+      <c r="B25" s="239" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="236"/>
-      <c r="E25" s="234" t="s">
+      <c r="C25" s="239"/>
+      <c r="E25" s="237" t="s">
         <v>330</v>
       </c>
-      <c r="F25" s="235"/>
+      <c r="F25" s="238"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -14045,7 +14016,7 @@
       <c r="C26" s="166">
         <v>0.21</v>
       </c>
-      <c r="E26" s="181" t="e" vm="5">
+      <c r="E26" s="181" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="215" cm="1">
@@ -14085,15 +14056,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="233" t="s">
+      <c r="B33" s="234" t="s">
         <v>325</v>
       </c>
-      <c r="C33" s="233"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
+      <c r="C33" s="234"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
+      <c r="F33" s="234"/>
+      <c r="G33" s="234"/>
+      <c r="H33" s="234"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14112,24 +14083,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="233"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="233"/>
+      <c r="B39" s="234"/>
+      <c r="C39" s="234"/>
+      <c r="D39" s="234"/>
+      <c r="E39" s="234"/>
+      <c r="F39" s="234"/>
+      <c r="G39" s="234"/>
+      <c r="H39" s="234"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="233" t="s">
+      <c r="B42" s="234" t="s">
         <v>328</v>
       </c>
-      <c r="C42" s="233"/>
-      <c r="D42" s="233"/>
-      <c r="E42" s="233"/>
-      <c r="F42" s="233"/>
-      <c r="G42" s="233"/>
-      <c r="H42" s="233"/>
+      <c r="C42" s="234"/>
+      <c r="D42" s="234"/>
+      <c r="E42" s="234"/>
+      <c r="F42" s="234"/>
+      <c r="G42" s="234"/>
+      <c r="H42" s="234"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14213,24 +14184,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="233"/>
-      <c r="C55" s="233"/>
-      <c r="D55" s="233"/>
-      <c r="E55" s="233"/>
-      <c r="F55" s="233"/>
-      <c r="G55" s="233"/>
-      <c r="H55" s="233"/>
+      <c r="B55" s="234"/>
+      <c r="C55" s="234"/>
+      <c r="D55" s="234"/>
+      <c r="E55" s="234"/>
+      <c r="F55" s="234"/>
+      <c r="G55" s="234"/>
+      <c r="H55" s="234"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="233" t="s">
+      <c r="B58" s="234" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="233"/>
-      <c r="D58" s="233"/>
-      <c r="E58" s="233"/>
-      <c r="F58" s="233"/>
-      <c r="G58" s="233"/>
-      <c r="H58" s="233"/>
+      <c r="C58" s="234"/>
+      <c r="D58" s="234"/>
+      <c r="E58" s="234"/>
+      <c r="F58" s="234"/>
+      <c r="G58" s="234"/>
+      <c r="H58" s="234"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14368,28 +14339,28 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="233"/>
-      <c r="C75" s="233"/>
-      <c r="D75" s="233"/>
-      <c r="E75" s="233"/>
-      <c r="F75" s="233"/>
-      <c r="G75" s="233"/>
-      <c r="H75" s="233"/>
+      <c r="B75" s="234"/>
+      <c r="C75" s="234"/>
+      <c r="D75" s="234"/>
+      <c r="E75" s="234"/>
+      <c r="F75" s="234"/>
+      <c r="G75" s="234"/>
+      <c r="H75" s="234"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B75:H75"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14459,36 +14430,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246" t="s">
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="236" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="233" t="s">
+      <c r="S2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233" t="s">
+      <c r="T2" s="234"/>
+      <c r="U2" s="234"/>
+      <c r="V2" s="234"/>
+      <c r="W2" s="234"/>
+      <c r="X2" s="234"/>
+      <c r="Y2" s="234"/>
+      <c r="Z2" s="234"/>
+      <c r="AA2" s="234" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
+      <c r="AB2" s="234"/>
+      <c r="AC2" s="234"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14499,32 +14470,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="233"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="243" t="s">
+      <c r="S4" s="245" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
-      <c r="AA4" s="244"/>
-      <c r="AB4" s="244"/>
-      <c r="AC4" s="244"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15265,33 +15236,33 @@
       <c r="Q13" s="91"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="242" t="s">
+      <c r="C14" s="233" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="242"/>
-      <c r="E14" s="242"/>
-      <c r="F14" s="242"/>
-      <c r="G14" s="242"/>
-      <c r="H14" s="242"/>
-      <c r="I14" s="242"/>
-      <c r="J14" s="242"/>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
+      <c r="D14" s="233"/>
+      <c r="E14" s="233"/>
+      <c r="F14" s="233"/>
+      <c r="G14" s="233"/>
+      <c r="H14" s="233"/>
+      <c r="I14" s="233"/>
+      <c r="J14" s="233"/>
+      <c r="K14" s="233"/>
+      <c r="L14" s="233"/>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
-      <c r="S14" s="243" t="s">
+      <c r="S14" s="245" t="s">
         <v>114</v>
       </c>
-      <c r="T14" s="244"/>
-      <c r="U14" s="244"/>
-      <c r="V14" s="244"/>
-      <c r="W14" s="244"/>
-      <c r="X14" s="244"/>
-      <c r="Y14" s="244"/>
-      <c r="Z14" s="244"/>
-      <c r="AA14" s="244"/>
-      <c r="AB14" s="244"/>
-      <c r="AC14" s="244"/>
+      <c r="T14" s="246"/>
+      <c r="U14" s="246"/>
+      <c r="V14" s="246"/>
+      <c r="W14" s="246"/>
+      <c r="X14" s="246"/>
+      <c r="Y14" s="246"/>
+      <c r="Z14" s="246"/>
+      <c r="AA14" s="246"/>
+      <c r="AB14" s="246"/>
+      <c r="AC14" s="246"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
@@ -15958,35 +15929,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246" t="s">
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="236" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="P2" s="233" t="s">
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
+      <c r="P2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233" t="s">
+      <c r="Q2" s="234"/>
+      <c r="R2" s="234"/>
+      <c r="S2" s="234"/>
+      <c r="T2" s="234"/>
+      <c r="U2" s="234"/>
+      <c r="V2" s="234"/>
+      <c r="W2" s="234"/>
+      <c r="X2" s="234" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
+      <c r="Y2" s="234"/>
+      <c r="Z2" s="234"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15995,31 +15966,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="P4" s="244" t="s">
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="233"/>
+      <c r="P4" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="244"/>
-      <c r="S4" s="244"/>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
+      <c r="Q4" s="246"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16214,32 +16185,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="242" t="s">
+      <c r="C9" s="233" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="242"/>
-      <c r="L9" s="242"/>
+      <c r="D9" s="233"/>
+      <c r="E9" s="233"/>
+      <c r="F9" s="233"/>
+      <c r="G9" s="233"/>
+      <c r="H9" s="233"/>
+      <c r="I9" s="233"/>
+      <c r="J9" s="233"/>
+      <c r="K9" s="233"/>
+      <c r="L9" s="233"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="244" t="s">
+      <c r="P9" s="246" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="244"/>
-      <c r="R9" s="244"/>
-      <c r="S9" s="244"/>
-      <c r="T9" s="244"/>
-      <c r="U9" s="244"/>
-      <c r="V9" s="244"/>
-      <c r="W9" s="244"/>
-      <c r="X9" s="244"/>
-      <c r="Y9" s="244"/>
-      <c r="Z9" s="244"/>
+      <c r="Q9" s="246"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="246"/>
+      <c r="U9" s="246"/>
+      <c r="V9" s="246"/>
+      <c r="W9" s="246"/>
+      <c r="X9" s="246"/>
+      <c r="Y9" s="246"/>
+      <c r="Z9" s="246"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16715,31 +16686,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="242" t="s">
+      <c r="C17" s="233" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="242"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="242"/>
-      <c r="K17" s="242"/>
-      <c r="L17" s="242"/>
-      <c r="P17" s="244" t="s">
+      <c r="D17" s="233"/>
+      <c r="E17" s="233"/>
+      <c r="F17" s="233"/>
+      <c r="G17" s="233"/>
+      <c r="H17" s="233"/>
+      <c r="I17" s="233"/>
+      <c r="J17" s="233"/>
+      <c r="K17" s="233"/>
+      <c r="L17" s="233"/>
+      <c r="P17" s="246" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="244"/>
-      <c r="R17" s="244"/>
-      <c r="S17" s="244"/>
-      <c r="T17" s="244"/>
-      <c r="U17" s="244"/>
-      <c r="V17" s="244"/>
-      <c r="W17" s="244"/>
-      <c r="X17" s="244"/>
-      <c r="Y17" s="244"/>
-      <c r="Z17" s="244"/>
+      <c r="Q17" s="246"/>
+      <c r="R17" s="246"/>
+      <c r="S17" s="246"/>
+      <c r="T17" s="246"/>
+      <c r="U17" s="246"/>
+      <c r="V17" s="246"/>
+      <c r="W17" s="246"/>
+      <c r="X17" s="246"/>
+      <c r="Y17" s="246"/>
+      <c r="Z17" s="246"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17217,20 +17188,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="245"/>
-      <c r="H3" s="246" t="s">
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
+      <c r="G3" s="235"/>
+      <c r="H3" s="236" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
       <c r="P3" s="247"/>
       <c r="Q3" s="247"/>
       <c r="R3" s="247"/>
@@ -17248,18 +17219,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="D5" s="233"/>
+      <c r="E5" s="233"/>
+      <c r="F5" s="233"/>
+      <c r="G5" s="233"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="233"/>
+      <c r="K5" s="233"/>
+      <c r="L5" s="233"/>
       <c r="P5" s="247"/>
       <c r="Q5" s="247"/>
       <c r="R5" s="247"/>
@@ -17456,18 +17427,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="242" t="s">
+      <c r="C11" s="233" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
-      <c r="F11" s="242"/>
-      <c r="G11" s="242"/>
-      <c r="H11" s="242"/>
-      <c r="I11" s="242"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
+      <c r="D11" s="233"/>
+      <c r="E11" s="233"/>
+      <c r="F11" s="233"/>
+      <c r="G11" s="233"/>
+      <c r="H11" s="233"/>
+      <c r="I11" s="233"/>
+      <c r="J11" s="233"/>
+      <c r="K11" s="233"/>
+      <c r="L11" s="233"/>
       <c r="N11" s="91"/>
       <c r="P11" s="247"/>
       <c r="Q11" s="247"/>
@@ -17721,18 +17692,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="242" t="s">
+      <c r="C18" s="233" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="242"/>
-      <c r="I18" s="242"/>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
+      <c r="D18" s="233"/>
+      <c r="E18" s="233"/>
+      <c r="F18" s="233"/>
+      <c r="G18" s="233"/>
+      <c r="H18" s="233"/>
+      <c r="I18" s="233"/>
+      <c r="J18" s="233"/>
+      <c r="K18" s="233"/>
+      <c r="L18" s="233"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17950,18 +17921,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="242" t="s">
+      <c r="C26" s="233" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="242"/>
-      <c r="E26" s="242"/>
-      <c r="F26" s="242"/>
-      <c r="G26" s="242"/>
-      <c r="H26" s="242"/>
-      <c r="I26" s="242"/>
-      <c r="J26" s="242"/>
-      <c r="K26" s="242"/>
-      <c r="L26" s="242"/>
+      <c r="D26" s="233"/>
+      <c r="E26" s="233"/>
+      <c r="F26" s="233"/>
+      <c r="G26" s="233"/>
+      <c r="H26" s="233"/>
+      <c r="I26" s="233"/>
+      <c r="J26" s="233"/>
+      <c r="K26" s="233"/>
+      <c r="L26" s="233"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18153,18 +18124,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="242" t="s">
+      <c r="C33" s="233" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="242"/>
-      <c r="E33" s="242"/>
-      <c r="F33" s="242"/>
-      <c r="G33" s="242"/>
-      <c r="H33" s="242"/>
-      <c r="I33" s="242"/>
-      <c r="J33" s="242"/>
-      <c r="K33" s="242"/>
-      <c r="L33" s="242"/>
+      <c r="D33" s="233"/>
+      <c r="E33" s="233"/>
+      <c r="F33" s="233"/>
+      <c r="G33" s="233"/>
+      <c r="H33" s="233"/>
+      <c r="I33" s="233"/>
+      <c r="J33" s="233"/>
+      <c r="K33" s="233"/>
+      <c r="L33" s="233"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18348,18 +18319,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="242" t="s">
+      <c r="C40" s="233" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="242"/>
-      <c r="E40" s="242"/>
-      <c r="F40" s="242"/>
-      <c r="G40" s="242"/>
-      <c r="H40" s="242"/>
-      <c r="I40" s="242"/>
-      <c r="J40" s="242"/>
-      <c r="K40" s="242"/>
-      <c r="L40" s="242"/>
+      <c r="D40" s="233"/>
+      <c r="E40" s="233"/>
+      <c r="F40" s="233"/>
+      <c r="G40" s="233"/>
+      <c r="H40" s="233"/>
+      <c r="I40" s="233"/>
+      <c r="J40" s="233"/>
+      <c r="K40" s="233"/>
+      <c r="L40" s="233"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18623,12 +18594,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18636,6 +18601,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18673,20 +18644,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246" t="s">
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="236" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
       <c r="S2" s="247"/>
       <c r="T2" s="247"/>
       <c r="U2" s="247"/>
@@ -18704,18 +18675,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="233" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="233"/>
       <c r="S4" s="247"/>
       <c r="T4" s="247"/>
       <c r="U4" s="247"/>
@@ -19089,18 +19060,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="242" t="s">
+      <c r="C13" s="233" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="E13" s="242"/>
-      <c r="F13" s="242"/>
-      <c r="G13" s="242"/>
-      <c r="H13" s="242"/>
-      <c r="I13" s="242"/>
-      <c r="J13" s="242"/>
-      <c r="K13" s="242"/>
-      <c r="L13" s="242"/>
+      <c r="D13" s="233"/>
+      <c r="E13" s="233"/>
+      <c r="F13" s="233"/>
+      <c r="G13" s="233"/>
+      <c r="H13" s="233"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="233"/>
+      <c r="K13" s="233"/>
+      <c r="L13" s="233"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19193,18 +19164,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="242" t="s">
+      <c r="C18" s="233" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="242"/>
-      <c r="I18" s="242"/>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
+      <c r="D18" s="233"/>
+      <c r="E18" s="233"/>
+      <c r="F18" s="233"/>
+      <c r="G18" s="233"/>
+      <c r="H18" s="233"/>
+      <c r="I18" s="233"/>
+      <c r="J18" s="233"/>
+      <c r="K18" s="233"/>
+      <c r="L18" s="233"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19396,18 +19367,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="242" t="s">
+      <c r="C25" s="233" t="s">
         <v>254</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="E25" s="242"/>
-      <c r="F25" s="242"/>
-      <c r="G25" s="242"/>
-      <c r="H25" s="242"/>
-      <c r="I25" s="242"/>
-      <c r="J25" s="242"/>
-      <c r="K25" s="242"/>
-      <c r="L25" s="242"/>
+      <c r="D25" s="233"/>
+      <c r="E25" s="233"/>
+      <c r="F25" s="233"/>
+      <c r="G25" s="233"/>
+      <c r="H25" s="233"/>
+      <c r="I25" s="233"/>
+      <c r="J25" s="233"/>
+      <c r="K25" s="233"/>
+      <c r="L25" s="233"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19545,18 +19516,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="242" t="s">
+      <c r="C31" s="233" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="E31" s="242"/>
-      <c r="F31" s="242"/>
-      <c r="G31" s="242"/>
-      <c r="H31" s="242"/>
-      <c r="I31" s="242"/>
-      <c r="J31" s="242"/>
-      <c r="K31" s="242"/>
-      <c r="L31" s="242"/>
+      <c r="D31" s="233"/>
+      <c r="E31" s="233"/>
+      <c r="F31" s="233"/>
+      <c r="G31" s="233"/>
+      <c r="H31" s="233"/>
+      <c r="I31" s="233"/>
+      <c r="J31" s="233"/>
+      <c r="K31" s="233"/>
+      <c r="L31" s="233"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19695,16 +19666,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19767,10 +19738,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="234" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="234"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19787,7 +19758,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>205.32</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19796,7 +19767,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>218049.84</v>
+        <v>214492.13999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19855,10 +19826,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="234" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="233"/>
+      <c r="C15" s="234"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19866,7 +19837,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.5446641828658891E-2</v>
+        <v>6.6460035582885851E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19875,7 +19846,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93455335817134111</v>
+        <v>0.93353996441711418</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19902,7 +19873,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.12049085429237394</v>
+        <v>0.12040602918157012</v>
       </c>
     </row>
   </sheetData>
@@ -19947,20 +19918,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="245"/>
-      <c r="H3" s="246" t="s">
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
+      <c r="G3" s="235"/>
+      <c r="H3" s="236" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
       <c r="P3" s="247"/>
       <c r="Q3" s="247"/>
       <c r="R3" s="247"/>
@@ -19978,18 +19949,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="233" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="D5" s="233"/>
+      <c r="E5" s="233"/>
+      <c r="F5" s="233"/>
+      <c r="G5" s="233"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="233"/>
+      <c r="K5" s="233"/>
+      <c r="L5" s="233"/>
       <c r="P5" s="247"/>
       <c r="Q5" s="247"/>
       <c r="R5" s="247"/>
@@ -20153,7 +20124,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>169655.1507775558</v>
+        <v>169805.99047905681</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20207,23 +20178,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5631.5053523611132</v>
+        <v>5631.9317094611861</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3364.2596255074745</v>
+        <v>3364.7690560010442</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5244.7628520762955</v>
+        <v>5245.954173601097</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7386.5574860424113</v>
+        <v>7388.7946632788935</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>8948.7707495114591</v>
+        <v>8952.1587865183792</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20242,14 +20213,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>96056.214872315526</v>
+        <v>96178.017625262262</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="233" t="s">
+      <c r="B13" s="234" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="233"/>
+      <c r="C13" s="234"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20265,14 +20236,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12049085429237394</v>
+        <v>0.12040602918157012</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="234" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="233"/>
+      <c r="C18" s="234"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20280,7 +20251,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30575.856065498752</v>
+        <v>30583.608388860597</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20289,7 +20260,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>96056.214872315526</v>
+        <v>96178.017625262262</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20298,7 +20269,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>126632.07093781428</v>
+        <v>126761.62601412286</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20325,7 +20296,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119666.07093781428</v>
+        <v>119795.62601412286</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20343,7 +20314,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C24/C25</f>
-        <v>112.67991613730157</v>
+        <v>112.80190773457896</v>
       </c>
     </row>
   </sheetData>
@@ -20386,37 +20357,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246" t="s">
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="236" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="233" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="233"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20612,23 +20583,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>5631.5053523611132</v>
+        <v>5631.9317094611861</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>3364.2596255074745</v>
+        <v>3364.7690560010442</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>5244.7628520762955</v>
+        <v>5245.954173601097</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7386.5574860424113</v>
+        <v>7388.7946632788935</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>8948.7707495114591</v>
+        <v>8952.1587865183792</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20636,18 +20607,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="242" t="s">
+      <c r="C11" s="233" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
-      <c r="F11" s="242"/>
-      <c r="G11" s="242"/>
-      <c r="H11" s="242"/>
-      <c r="I11" s="242"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
+      <c r="D11" s="233"/>
+      <c r="E11" s="233"/>
+      <c r="F11" s="233"/>
+      <c r="G11" s="233"/>
+      <c r="H11" s="233"/>
+      <c r="I11" s="233"/>
+      <c r="J11" s="233"/>
+      <c r="K11" s="233"/>
+      <c r="L11" s="233"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20841,18 +20812,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="242" t="s">
+      <c r="C17" s="233" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="242"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="242"/>
-      <c r="K17" s="242"/>
-      <c r="L17" s="242"/>
+      <c r="D17" s="233"/>
+      <c r="E17" s="233"/>
+      <c r="F17" s="233"/>
+      <c r="G17" s="233"/>
+      <c r="H17" s="233"/>
+      <c r="I17" s="233"/>
+      <c r="J17" s="233"/>
+      <c r="K17" s="233"/>
+      <c r="L17" s="233"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20986,18 +20957,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="242" t="s">
+      <c r="C22" s="233" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="242"/>
-      <c r="E22" s="242"/>
-      <c r="F22" s="242"/>
-      <c r="G22" s="242"/>
-      <c r="H22" s="242"/>
-      <c r="I22" s="242"/>
-      <c r="J22" s="242"/>
-      <c r="K22" s="242"/>
-      <c r="L22" s="242"/>
+      <c r="D22" s="233"/>
+      <c r="E22" s="233"/>
+      <c r="F22" s="233"/>
+      <c r="G22" s="233"/>
+      <c r="H22" s="233"/>
+      <c r="I22" s="233"/>
+      <c r="J22" s="233"/>
+      <c r="K22" s="233"/>
+      <c r="L22" s="233"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21081,18 +21052,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="242" t="s">
+      <c r="C27" s="233" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="E27" s="242"/>
-      <c r="F27" s="242"/>
-      <c r="G27" s="242"/>
-      <c r="H27" s="242"/>
-      <c r="I27" s="242"/>
-      <c r="J27" s="242"/>
-      <c r="K27" s="242"/>
-      <c r="L27" s="242"/>
+      <c r="D27" s="233"/>
+      <c r="E27" s="233"/>
+      <c r="F27" s="233"/>
+      <c r="G27" s="233"/>
+      <c r="H27" s="233"/>
+      <c r="I27" s="233"/>
+      <c r="J27" s="233"/>
+      <c r="K27" s="233"/>
+      <c r="L27" s="233"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21362,10 +21333,10 @@
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="233" t="s">
+      <c r="B38" s="234" t="s">
         <v>197</v>
       </c>
-      <c r="C38" s="233"/>
+      <c r="C38" s="234"/>
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -21383,7 +21354,7 @@
       </c>
       <c r="C40" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12049085429237394</v>
+        <v>0.12040602918157012</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
@@ -21408,8 +21379,8 @@
         <v>420</v>
       </c>
       <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5-G31+G32</f>
-        <v>208135.8797655844</v>
+        <f ca="1">C42/(1+C40)^5</f>
+        <v>212872.44354172729</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21418,7 +21389,7 @@
       </c>
       <c r="C44" s="108">
         <f ca="1">SUM(H9:K9)+C43</f>
-        <v>229762.96508157169</v>
+        <v>234503.8931440695</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21445,7 +21416,7 @@
       </c>
       <c r="C47" s="108">
         <f ca="1">C44+C45-C46</f>
-        <v>222796.96508157169</v>
+        <v>227537.8931440695</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -21463,14 +21434,14 @@
       </c>
       <c r="C49" s="232">
         <f ca="1">C47/C48</f>
-        <v>209.78998595251571</v>
+        <v>214.25413667049858</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="233" t="s">
+      <c r="B51" s="234" t="s">
         <v>202</v>
       </c>
-      <c r="C51" s="233"/>
+      <c r="C51" s="234"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
@@ -21526,10 +21497,10 @@
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="233" t="s">
+      <c r="B59" s="234" t="s">
         <v>314</v>
       </c>
-      <c r="C59" s="233"/>
+      <c r="C59" s="234"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
@@ -21546,7 +21517,7 @@
       </c>
       <c r="C61" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12049085429237394</v>
+        <v>0.12040602918157012</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
@@ -21571,8 +21542,8 @@
         <v>420</v>
       </c>
       <c r="C64" s="24">
-        <f ca="1">C63/(1+C61)^5-G31+G32</f>
-        <v>174319.41499022918</v>
+        <f ca="1">C63/(1+C61)^5</f>
+        <v>179043.17573036757</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -21581,7 +21552,7 @@
       </c>
       <c r="C65" s="108">
         <f ca="1">SUM(H9:K9)+C64</f>
-        <v>195946.50030621648</v>
+        <v>200674.62533270978</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21608,7 +21579,7 @@
       </c>
       <c r="C68" s="108">
         <f ca="1">C65+C66-C67</f>
-        <v>188980.50030621648</v>
+        <v>193708.62533270978</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -21626,7 +21597,7 @@
       </c>
       <c r="C70" s="232">
         <f ca="1">C68/C69</f>
-        <v>177.94774040133379</v>
+        <v>182.39983552985856</v>
       </c>
     </row>
   </sheetData>
@@ -21678,10 +21649,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="234" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="234"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21690,7 +21661,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>112.67991613730157</v>
+        <v>112.80190773457896</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21699,7 +21670,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C49</f>
-        <v>209.78998595251571</v>
+        <v>214.25413667049858</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21717,7 +21688,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C70</f>
-        <v>177.94774040133379</v>
+        <v>182.39983552985856</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21726,7 +21697,7 @@
       </c>
       <c r="C9" s="232">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>173.64628001685941</v>
+        <v>175.90583937780565</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21735,7 +21706,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>205.32</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21744,7 +21715,7 @@
       </c>
       <c r="C11" s="152">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.15426514700536034</v>
+        <v>-0.12904966392134648</v>
       </c>
     </row>
   </sheetData>
@@ -21800,37 +21771,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246" t="s">
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="236" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="233" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="233"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21943,18 +21914,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="242" t="s">
+      <c r="C9" s="233" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="242"/>
-      <c r="L9" s="242"/>
+      <c r="D9" s="233"/>
+      <c r="E9" s="233"/>
+      <c r="F9" s="233"/>
+      <c r="G9" s="233"/>
+      <c r="H9" s="233"/>
+      <c r="I9" s="233"/>
+      <c r="J9" s="233"/>
+      <c r="K9" s="233"/>
+      <c r="L9" s="233"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22075,18 +22046,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="242" t="s">
+      <c r="C14" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="D14" s="242"/>
-      <c r="E14" s="242"/>
-      <c r="F14" s="242"/>
-      <c r="G14" s="242"/>
-      <c r="H14" s="242"/>
-      <c r="I14" s="242"/>
-      <c r="J14" s="242"/>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
+      <c r="D14" s="233"/>
+      <c r="E14" s="233"/>
+      <c r="F14" s="233"/>
+      <c r="G14" s="233"/>
+      <c r="H14" s="233"/>
+      <c r="I14" s="233"/>
+      <c r="J14" s="233"/>
+      <c r="K14" s="233"/>
+      <c r="L14" s="233"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22176,10 +22147,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="233" t="s">
+      <c r="B20" s="234" t="s">
         <v>399</v>
       </c>
-      <c r="C20" s="233"/>
+      <c r="C20" s="234"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22280,20 +22251,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="234" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="245"/>
-      <c r="H3" s="246" t="s">
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
+      <c r="G3" s="235"/>
+      <c r="H3" s="236" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
       <c r="P3" s="247"/>
       <c r="Q3" s="247"/>
       <c r="R3" s="247"/>
@@ -22311,18 +22282,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="233" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="D5" s="233"/>
+      <c r="E5" s="233"/>
+      <c r="F5" s="233"/>
+      <c r="G5" s="233"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="233"/>
+      <c r="J5" s="233"/>
+      <c r="K5" s="233"/>
+      <c r="L5" s="233"/>
       <c r="P5" s="247"/>
       <c r="Q5" s="247"/>
       <c r="R5" s="247"/>
@@ -22468,7 +22439,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>265842.42802416591</v>
+        <v>266078.78744093393</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22522,23 +22493,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12207.365140577722</v>
+        <v>12208.289351152909</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12637.803788245104</v>
+        <v>12639.71745821655</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13083.419947789302</v>
+        <v>13086.391780880982</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13544.748786923572</v>
+        <v>13548.851104372157</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14022.344343679555</v>
+        <v>14027.653254019307</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22557,7 +22528,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>150516.01599734963</v>
+        <v>150706.87574687676</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22573,7 +22544,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>205.32</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22582,7 +22553,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>199.09114095672845</v>
+        <v>199.28740828144635</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22621,7 +22592,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12049085429237394</v>
+        <v>0.12040602918157012</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22639,7 +22610,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>215586</v>
+        <v>212068.5</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22666,7 +22637,7 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>222552</v>
+        <v>219034.5</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22682,7 +22653,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>65495.682007215255</v>
+        <v>65510.902948641902</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22691,7 +22662,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>150516.01599734963</v>
+        <v>150706.87574687676</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22700,7 +22671,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>216011.69800456488</v>
+        <v>216217.77869551867</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22727,7 +22698,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>209045.69800456488</v>
+        <v>209251.77869551867</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22745,21 +22716,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>199.09114095672845</v>
+        <v>199.28740828144635</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29374,7 +29345,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>205.32</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29445,7 +29416,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>205.32</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -30947,7 +30918,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>23.204345368751724</v>
+        <v>22.825743396292548</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30984,7 +30955,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>5.0062707633657073</v>
+        <v>4.9245884768993378</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31045,7 +31016,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>7.7947067756164579</v>
+        <v>7.6675283823848437</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31106,7 +31077,7 @@
       </c>
       <c r="AC156" s="141">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>218049.84</v>
+        <v>214492.13999999998</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31167,7 +31138,7 @@
       </c>
       <c r="AC157" s="141">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>225015.84</v>
+        <v>221458.13999999998</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31204,7 +31175,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="179">
         <f ca="1">AC157/AC5</f>
-        <v>5.1061051102841066</v>
+        <v>5.0253730598166468</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31241,7 +31212,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="179">
         <f ca="1">AC157/AC12</f>
-        <v>22.01936001565711</v>
+        <v>21.67121440454056</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31376,7 +31347,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>30.394457764148314</v>
+        <v>29.898541957067184</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31413,7 +31384,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>23.079104418144944</v>
+        <v>22.714203308123381</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31450,7 +31421,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>3.2900734987927532E-2</v>
+        <v>3.3446447035308614E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31487,7 +31458,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>4.3095376495587596E-2</v>
+        <v>4.3810183205793163E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31524,7 +31495,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="152">
         <f ca="1">AC82/AC116</f>
-        <v>1.7484901616988117E-2</v>
+        <v>1.7774917066891122E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31561,7 +31532,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="152">
         <f ca="1">-AC63/AC156</f>
-        <v>4.2421494095111464E-2</v>
+        <v>4.3125123372819166E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31598,7 +31569,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="152">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>5.9963355166873775E-2</v>
+        <v>6.0957944659417361E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32101,7 +32072,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="152">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.1946824634221244E-2</v>
+        <v>-3.2476714531357656E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33423,15 +33394,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="234" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="233"/>
-      <c r="E4" s="233" t="s">
+      <c r="C4" s="234"/>
+      <c r="E4" s="234" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33439,7 +33410,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>205.32</v>
+        <v>201.97</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33455,7 +33426,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>218049.84</v>
+        <v>214492.13999999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33475,7 +33446,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>225015.84</v>
+        <v>221458.13999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33495,7 +33466,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>23.204345368751724</v>
+        <v>22.825743396292548</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33515,7 +33486,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>5.0062707633657073</v>
+        <v>4.9245884768993378</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33535,7 +33506,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>7.7947067756164579</v>
+        <v>7.6675283823848437</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33555,7 +33526,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>5.1061051102841066</v>
+        <v>5.0253730598166468</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33564,18 +33535,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>22.01936001565711</v>
+        <v>21.67121440454056</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="234" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="233"/>
-      <c r="E15" s="233" t="s">
+      <c r="C15" s="234"/>
+      <c r="E15" s="234" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="233"/>
+      <c r="F15" s="234"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33626,14 +33597,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="233" t="s">
+      <c r="B21" s="234" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="233"/>
-      <c r="E21" s="233" t="s">
+      <c r="C21" s="234"/>
+      <c r="E21" s="234" t="s">
         <v>241</v>
       </c>
-      <c r="F21" s="233"/>
+      <c r="F21" s="234"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33702,14 +33673,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="233" t="s">
+      <c r="B29" s="234" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="233"/>
-      <c r="E29" s="233" t="s">
+      <c r="C29" s="234"/>
+      <c r="E29" s="234" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="233"/>
+      <c r="F29" s="234"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33785,14 +33756,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="234" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="233"/>
-      <c r="E37" s="233" t="s">
+      <c r="C37" s="234"/>
+      <c r="E37" s="234" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="233"/>
+      <c r="F37" s="234"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33800,7 +33771,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>4.3095376495587596E-2</v>
+        <v>4.3810183205793163E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33816,7 +33787,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC164</f>
-        <v>3.2900734987927532E-2</v>
+        <v>3.3446447035308614E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33832,7 +33803,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>1.7484901616988117E-2</v>
+        <v>1.7774917066891122E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33848,7 +33819,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.2421494095111464E-2</v>
+        <v>4.3125123372819166E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33857,18 +33828,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>5.9963355166873775E-2</v>
+        <v>6.0957944659417361E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="233" t="s">
+      <c r="B45" s="234" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="233"/>
-      <c r="E45" s="233" t="s">
+      <c r="C45" s="234"/>
+      <c r="E45" s="234" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="233"/>
+      <c r="F45" s="234"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33901,18 +33872,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC179</f>
-        <v>-3.1946824634221244E-2</v>
+        <v>-3.2476714531357656E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="233" t="s">
+      <c r="B51" s="234" t="s">
         <v>274</v>
       </c>
-      <c r="C51" s="233"/>
-      <c r="E51" s="233" t="s">
+      <c r="C51" s="234"/>
+      <c r="E51" s="234" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="233"/>
+      <c r="F51" s="234"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34081,7 +34052,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC115</f>
-        <v>205.32</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34110,7 +34081,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>218049.84</v>
+        <v>214492.13999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34139,7 +34110,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>225015.84</v>
+        <v>221458.13999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34168,7 +34139,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>23.204345368751724</v>
+        <v>22.825743396292548</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34197,7 +34168,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>5.0062707633657073</v>
+        <v>4.9245884768993378</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34226,7 +34197,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>7.7947067756164579</v>
+        <v>7.6675283823848437</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34255,7 +34226,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>5.1061051102841066</v>
+        <v>5.0253730598166468</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34284,7 +34255,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>22.01936001565711</v>
+        <v>21.67121440454056</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35057,7 +35028,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>4.3095376495587596E-2</v>
+        <v>4.3810183205793163E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35086,7 +35057,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC164</f>
-        <v>3.2900734987927532E-2</v>
+        <v>3.3446447035308614E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35115,7 +35086,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>1.7484901616988117E-2</v>
+        <v>1.7774917066891122E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35144,7 +35115,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.2421494095111464E-2</v>
+        <v>4.3125123372819166E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35173,7 +35144,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>5.9963355166873775E-2</v>
+        <v>6.0957944659417361E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35409,7 +35380,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.1946824634221244E-2</v>
+        <v>-3.2476714531357656E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35947,14 +35918,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="240" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="241"/>
+      <c r="F3" s="242" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="241"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36021,19 +35992,19 @@
       <c r="B7" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="237">
+      <c r="C7" s="243">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="F7" s="237">
+      <c r="D7" s="244"/>
+      <c r="F7" s="243">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="238"/>
+      <c r="G7" s="244"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36060,19 +36031,19 @@
       <c r="B9" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="237">
+      <c r="C9" s="243">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="F9" s="237">
+      <c r="D9" s="244"/>
+      <c r="F9" s="243">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="238"/>
+      <c r="G9" s="244"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36099,19 +36070,19 @@
       <c r="B11" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="237">
+      <c r="C11" s="243">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="F11" s="237">
+      <c r="D11" s="244"/>
+      <c r="F11" s="243">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="238"/>
+      <c r="G11" s="244"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36138,19 +36109,19 @@
       <c r="B13" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="237">
+      <c r="C13" s="243">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="F13" s="237">
+      <c r="D13" s="244"/>
+      <c r="F13" s="243">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="238"/>
+      <c r="G13" s="244"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36177,19 +36148,19 @@
       <c r="B15" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="237">
+      <c r="C15" s="243">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="F15" s="237">
+      <c r="D15" s="244"/>
+      <c r="F15" s="243">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="238"/>
+      <c r="G15" s="244"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36216,19 +36187,19 @@
       <c r="B17" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="237">
+      <c r="C17" s="243">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="238"/>
-      <c r="F17" s="237">
+      <c r="D17" s="244"/>
+      <c r="F17" s="243">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="238"/>
+      <c r="G17" s="244"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36255,22 +36226,22 @@
       <c r="B19" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="237">
+      <c r="C19" s="243">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="238"/>
-      <c r="F19" s="237">
+      <c r="D19" s="244"/>
+      <c r="F19" s="243">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="238"/>
+      <c r="G19" s="244"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36297,22 +36268,22 @@
       <c r="B21" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="237">
+      <c r="C21" s="243">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="F21" s="237">
+      <c r="D21" s="244"/>
+      <c r="F21" s="243">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="238"/>
+      <c r="G21" s="244"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36360,22 +36331,22 @@
       <c r="B25" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="237">
+      <c r="C25" s="243">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="F25" s="237">
+      <c r="D25" s="244"/>
+      <c r="F25" s="243">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="238"/>
+      <c r="G25" s="244"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="218" t="s">
@@ -36402,22 +36373,22 @@
       <c r="B27" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="237">
+      <c r="C27" s="243">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="238"/>
-      <c r="F27" s="237">
+      <c r="D27" s="244"/>
+      <c r="F27" s="243">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="238"/>
+      <c r="G27" s="244"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="218" t="s">
@@ -36444,22 +36415,22 @@
       <c r="B29" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="237">
+      <c r="C29" s="243">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="238"/>
-      <c r="F29" s="237">
+      <c r="D29" s="244"/>
+      <c r="F29" s="243">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="238"/>
+      <c r="G29" s="244"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36486,22 +36457,22 @@
       <c r="B31" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="237">
+      <c r="C31" s="243">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="F31" s="237">
+      <c r="D31" s="244"/>
+      <c r="F31" s="243">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="238"/>
+      <c r="G31" s="244"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36528,43 +36499,25 @@
       <c r="B33" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="237">
+      <c r="C33" s="243">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="F33" s="237">
+      <c r="D33" s="244"/>
+      <c r="F33" s="243">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="238"/>
+      <c r="G33" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36575,6 +36528,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77622472-77E9-DB4F-8538-762260BDF223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD069157-89DC-DA4E-8239-B8183EB34D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="428">
   <si>
     <t>Ticker</t>
   </si>
@@ -1423,6 +1423,18 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
   </si>
 </sst>
 </file>
@@ -2338,16 +2350,7 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2359,6 +2362,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2368,10 +2377,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2380,17 +2386,23 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12749,11 +12761,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6521999999999999</v>
+    <v>1.6571</v>
     <v>7.71</v>
     <v>3.9689000000000002E-2</v>
-    <v>-0.33</v>
-    <v>-1.6339999999999998E-3</v>
+    <v>0.73</v>
+    <v>3.614E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12765,21 +12777,21 @@
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.83637109922</v>
+    <v>46290.999975185157</v>
     <v>4</v>
     <v>194.53</v>
     <v>212068500000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>195.4</v>
-    <v>23.3751</v>
+    <v>195.03</v>
+    <v>22.482800000000001</v>
     <v>194.26</v>
     <v>201.97</v>
-    <v>201.64</v>
+    <v>202.7</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>17531585</v>
+    <v>17817795</v>
     <v>13522451</v>
     <v>1991</v>
   </rv>
@@ -12802,19 +12814,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>7</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13056,9 +13068,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13645,18 +13657,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="234" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="238"/>
-      <c r="E2" s="237" t="s">
+      <c r="C2" s="235"/>
+      <c r="E2" s="234" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="238"/>
-      <c r="H2" s="237" t="s">
+      <c r="F2" s="235"/>
+      <c r="H2" s="234" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="238"/>
+      <c r="I2" s="235"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="181" t="s">
@@ -13679,7 +13691,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>112.80190773457896</v>
+        <v>112.21256788433617</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13703,7 +13715,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>214.25413667049858</v>
+        <v>213.86678313853716</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13727,7 +13739,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>194.1674775762865</v>
+        <v>193.7881133053782</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13736,7 +13748,7 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>201.64</v>
+        <v>202.7</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>229</v>
@@ -13751,7 +13763,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>182.39983552985856</v>
+        <v>182.07087535214498</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13770,12 +13782,12 @@
         <v>4.9245884768993378</v>
       </c>
       <c r="H7" s="180" t="str">
-        <f>'AVG target price'!B9</f>
+        <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="208">
-        <f ca="1">'AVG target price'!C9</f>
-        <v>175.90583937780565</v>
+        <f ca="1">'AVG target price'!C10</f>
+        <v>181.47454823635672</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13784,7 +13796,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.33</v>
+        <v>0.73</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>257</v>
@@ -13794,12 +13806,12 @@
         <v>3.3446447035308614E-2</v>
       </c>
       <c r="H8" s="180" t="str">
-        <f>'AVG target price'!B11</f>
+        <f>'AVG target price'!B12</f>
         <v>Upside/Downside</v>
       </c>
       <c r="I8" s="209">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>-0.12904966392134648</v>
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.10147770343933889</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13824,7 +13836,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.6339999999999998E-3</v>
+        <v>3.614E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>285</v>
@@ -13838,7 +13850,7 @@
       </c>
       <c r="I10" s="208">
         <f ca="1">DDM!C26</f>
-        <v>34.810180335758574</v>
+        <v>34.66607774681772</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13879,7 +13891,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6521999999999999</v>
+        <v>1.6571</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>96</v>
@@ -13924,10 +13936,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="239" t="s">
+      <c r="B17" s="236" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="239"/>
+      <c r="C17" s="236"/>
       <c r="E17" s="180" t="s">
         <v>288</v>
       </c>
@@ -14000,14 +14012,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="239" t="s">
+      <c r="B25" s="236" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="239"/>
-      <c r="E25" s="237" t="s">
+      <c r="C25" s="236"/>
+      <c r="E25" s="234" t="s">
         <v>330</v>
       </c>
-      <c r="F25" s="238"/>
+      <c r="F25" s="235"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -14021,7 +14033,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14036,7 +14048,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14056,15 +14068,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="234" t="s">
+      <c r="B33" s="233" t="s">
         <v>325</v>
       </c>
-      <c r="C33" s="234"/>
-      <c r="D33" s="234"/>
-      <c r="E33" s="234"/>
-      <c r="F33" s="234"/>
-      <c r="G33" s="234"/>
-      <c r="H33" s="234"/>
+      <c r="C33" s="233"/>
+      <c r="D33" s="233"/>
+      <c r="E33" s="233"/>
+      <c r="F33" s="233"/>
+      <c r="G33" s="233"/>
+      <c r="H33" s="233"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14083,24 +14095,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="234"/>
-      <c r="C39" s="234"/>
-      <c r="D39" s="234"/>
-      <c r="E39" s="234"/>
-      <c r="F39" s="234"/>
-      <c r="G39" s="234"/>
-      <c r="H39" s="234"/>
+      <c r="B39" s="233"/>
+      <c r="C39" s="233"/>
+      <c r="D39" s="233"/>
+      <c r="E39" s="233"/>
+      <c r="F39" s="233"/>
+      <c r="G39" s="233"/>
+      <c r="H39" s="233"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="234" t="s">
+      <c r="B42" s="233" t="s">
         <v>328</v>
       </c>
-      <c r="C42" s="234"/>
-      <c r="D42" s="234"/>
-      <c r="E42" s="234"/>
-      <c r="F42" s="234"/>
-      <c r="G42" s="234"/>
-      <c r="H42" s="234"/>
+      <c r="C42" s="233"/>
+      <c r="D42" s="233"/>
+      <c r="E42" s="233"/>
+      <c r="F42" s="233"/>
+      <c r="G42" s="233"/>
+      <c r="H42" s="233"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14184,24 +14196,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="234"/>
-      <c r="C55" s="234"/>
-      <c r="D55" s="234"/>
-      <c r="E55" s="234"/>
-      <c r="F55" s="234"/>
-      <c r="G55" s="234"/>
-      <c r="H55" s="234"/>
+      <c r="B55" s="233"/>
+      <c r="C55" s="233"/>
+      <c r="D55" s="233"/>
+      <c r="E55" s="233"/>
+      <c r="F55" s="233"/>
+      <c r="G55" s="233"/>
+      <c r="H55" s="233"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="234" t="s">
+      <c r="B58" s="233" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="234"/>
-      <c r="D58" s="234"/>
-      <c r="E58" s="234"/>
-      <c r="F58" s="234"/>
-      <c r="G58" s="234"/>
-      <c r="H58" s="234"/>
+      <c r="C58" s="233"/>
+      <c r="D58" s="233"/>
+      <c r="E58" s="233"/>
+      <c r="F58" s="233"/>
+      <c r="G58" s="233"/>
+      <c r="H58" s="233"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14339,28 +14351,28 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="234"/>
-      <c r="C75" s="234"/>
-      <c r="D75" s="234"/>
-      <c r="E75" s="234"/>
-      <c r="F75" s="234"/>
-      <c r="G75" s="234"/>
-      <c r="H75" s="234"/>
+      <c r="B75" s="233"/>
+      <c r="C75" s="233"/>
+      <c r="D75" s="233"/>
+      <c r="E75" s="233"/>
+      <c r="F75" s="233"/>
+      <c r="G75" s="233"/>
+      <c r="H75" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14430,36 +14442,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="234" t="s">
+      <c r="S2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="234"/>
-      <c r="U2" s="234"/>
-      <c r="V2" s="234"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="234"/>
-      <c r="Y2" s="234"/>
-      <c r="Z2" s="234"/>
-      <c r="AA2" s="234" t="s">
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="234"/>
-      <c r="AC2" s="234"/>
+      <c r="AB2" s="233"/>
+      <c r="AC2" s="233"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14470,32 +14482,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="245" t="s">
+      <c r="S4" s="243" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="T4" s="244"/>
+      <c r="U4" s="244"/>
+      <c r="V4" s="244"/>
+      <c r="W4" s="244"/>
+      <c r="X4" s="244"/>
+      <c r="Y4" s="244"/>
+      <c r="Z4" s="244"/>
+      <c r="AA4" s="244"/>
+      <c r="AB4" s="244"/>
+      <c r="AC4" s="244"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15236,33 +15248,33 @@
       <c r="Q13" s="91"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="233" t="s">
+      <c r="C14" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="233"/>
-      <c r="E14" s="233"/>
-      <c r="F14" s="233"/>
-      <c r="G14" s="233"/>
-      <c r="H14" s="233"/>
-      <c r="I14" s="233"/>
-      <c r="J14" s="233"/>
-      <c r="K14" s="233"/>
-      <c r="L14" s="233"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="242"/>
+      <c r="F14" s="242"/>
+      <c r="G14" s="242"/>
+      <c r="H14" s="242"/>
+      <c r="I14" s="242"/>
+      <c r="J14" s="242"/>
+      <c r="K14" s="242"/>
+      <c r="L14" s="242"/>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
-      <c r="S14" s="245" t="s">
+      <c r="S14" s="243" t="s">
         <v>114</v>
       </c>
-      <c r="T14" s="246"/>
-      <c r="U14" s="246"/>
-      <c r="V14" s="246"/>
-      <c r="W14" s="246"/>
-      <c r="X14" s="246"/>
-      <c r="Y14" s="246"/>
-      <c r="Z14" s="246"/>
-      <c r="AA14" s="246"/>
-      <c r="AB14" s="246"/>
-      <c r="AC14" s="246"/>
+      <c r="T14" s="244"/>
+      <c r="U14" s="244"/>
+      <c r="V14" s="244"/>
+      <c r="W14" s="244"/>
+      <c r="X14" s="244"/>
+      <c r="Y14" s="244"/>
+      <c r="Z14" s="244"/>
+      <c r="AA14" s="244"/>
+      <c r="AB14" s="244"/>
+      <c r="AC14" s="244"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
@@ -15929,35 +15941,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
-      <c r="P2" s="234" t="s">
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
+      <c r="P2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="234"/>
-      <c r="R2" s="234"/>
-      <c r="S2" s="234"/>
-      <c r="T2" s="234"/>
-      <c r="U2" s="234"/>
-      <c r="V2" s="234"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="234" t="s">
+      <c r="Q2" s="233"/>
+      <c r="R2" s="233"/>
+      <c r="S2" s="233"/>
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="234"/>
-      <c r="Z2" s="234"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15966,31 +15978,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
-      <c r="P4" s="246" t="s">
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
+      <c r="P4" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
+      <c r="Q4" s="244"/>
+      <c r="R4" s="244"/>
+      <c r="S4" s="244"/>
+      <c r="T4" s="244"/>
+      <c r="U4" s="244"/>
+      <c r="V4" s="244"/>
+      <c r="W4" s="244"/>
+      <c r="X4" s="244"/>
+      <c r="Y4" s="244"/>
+      <c r="Z4" s="244"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16185,32 +16197,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="233" t="s">
+      <c r="C9" s="242" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="242"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="242"/>
+      <c r="J9" s="242"/>
+      <c r="K9" s="242"/>
+      <c r="L9" s="242"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="246" t="s">
+      <c r="P9" s="244" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="246"/>
-      <c r="S9" s="246"/>
-      <c r="T9" s="246"/>
-      <c r="U9" s="246"/>
-      <c r="V9" s="246"/>
-      <c r="W9" s="246"/>
-      <c r="X9" s="246"/>
-      <c r="Y9" s="246"/>
-      <c r="Z9" s="246"/>
+      <c r="Q9" s="244"/>
+      <c r="R9" s="244"/>
+      <c r="S9" s="244"/>
+      <c r="T9" s="244"/>
+      <c r="U9" s="244"/>
+      <c r="V9" s="244"/>
+      <c r="W9" s="244"/>
+      <c r="X9" s="244"/>
+      <c r="Y9" s="244"/>
+      <c r="Z9" s="244"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16686,31 +16698,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="233" t="s">
+      <c r="C17" s="242" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="233"/>
-      <c r="E17" s="233"/>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="233"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="233"/>
-      <c r="K17" s="233"/>
-      <c r="L17" s="233"/>
-      <c r="P17" s="246" t="s">
+      <c r="D17" s="242"/>
+      <c r="E17" s="242"/>
+      <c r="F17" s="242"/>
+      <c r="G17" s="242"/>
+      <c r="H17" s="242"/>
+      <c r="I17" s="242"/>
+      <c r="J17" s="242"/>
+      <c r="K17" s="242"/>
+      <c r="L17" s="242"/>
+      <c r="P17" s="244" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="246"/>
-      <c r="R17" s="246"/>
-      <c r="S17" s="246"/>
-      <c r="T17" s="246"/>
-      <c r="U17" s="246"/>
-      <c r="V17" s="246"/>
-      <c r="W17" s="246"/>
-      <c r="X17" s="246"/>
-      <c r="Y17" s="246"/>
-      <c r="Z17" s="246"/>
+      <c r="Q17" s="244"/>
+      <c r="R17" s="244"/>
+      <c r="S17" s="244"/>
+      <c r="T17" s="244"/>
+      <c r="U17" s="244"/>
+      <c r="V17" s="244"/>
+      <c r="W17" s="244"/>
+      <c r="X17" s="244"/>
+      <c r="Y17" s="244"/>
+      <c r="Z17" s="244"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17188,20 +17200,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="235"/>
-      <c r="H3" s="236" t="s">
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="245"/>
+      <c r="H3" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="247"/>
       <c r="Q3" s="247"/>
       <c r="R3" s="247"/>
@@ -17219,18 +17231,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
+      <c r="G5" s="242"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="242"/>
+      <c r="J5" s="242"/>
+      <c r="K5" s="242"/>
+      <c r="L5" s="242"/>
       <c r="P5" s="247"/>
       <c r="Q5" s="247"/>
       <c r="R5" s="247"/>
@@ -17427,18 +17439,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="233" t="s">
+      <c r="C11" s="242" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="233"/>
-      <c r="E11" s="233"/>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
+      <c r="H11" s="242"/>
+      <c r="I11" s="242"/>
+      <c r="J11" s="242"/>
+      <c r="K11" s="242"/>
+      <c r="L11" s="242"/>
       <c r="N11" s="91"/>
       <c r="P11" s="247"/>
       <c r="Q11" s="247"/>
@@ -17692,18 +17704,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="233" t="s">
+      <c r="C18" s="242" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
-      <c r="L18" s="233"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="242"/>
+      <c r="F18" s="242"/>
+      <c r="G18" s="242"/>
+      <c r="H18" s="242"/>
+      <c r="I18" s="242"/>
+      <c r="J18" s="242"/>
+      <c r="K18" s="242"/>
+      <c r="L18" s="242"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17921,18 +17933,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="233" t="s">
+      <c r="C26" s="242" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="233"/>
-      <c r="E26" s="233"/>
-      <c r="F26" s="233"/>
-      <c r="G26" s="233"/>
-      <c r="H26" s="233"/>
-      <c r="I26" s="233"/>
-      <c r="J26" s="233"/>
-      <c r="K26" s="233"/>
-      <c r="L26" s="233"/>
+      <c r="D26" s="242"/>
+      <c r="E26" s="242"/>
+      <c r="F26" s="242"/>
+      <c r="G26" s="242"/>
+      <c r="H26" s="242"/>
+      <c r="I26" s="242"/>
+      <c r="J26" s="242"/>
+      <c r="K26" s="242"/>
+      <c r="L26" s="242"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18124,18 +18136,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="233" t="s">
+      <c r="C33" s="242" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
-      <c r="I33" s="233"/>
-      <c r="J33" s="233"/>
-      <c r="K33" s="233"/>
-      <c r="L33" s="233"/>
+      <c r="D33" s="242"/>
+      <c r="E33" s="242"/>
+      <c r="F33" s="242"/>
+      <c r="G33" s="242"/>
+      <c r="H33" s="242"/>
+      <c r="I33" s="242"/>
+      <c r="J33" s="242"/>
+      <c r="K33" s="242"/>
+      <c r="L33" s="242"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18319,18 +18331,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="233" t="s">
+      <c r="C40" s="242" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="233"/>
-      <c r="E40" s="233"/>
-      <c r="F40" s="233"/>
-      <c r="G40" s="233"/>
-      <c r="H40" s="233"/>
-      <c r="I40" s="233"/>
-      <c r="J40" s="233"/>
-      <c r="K40" s="233"/>
-      <c r="L40" s="233"/>
+      <c r="D40" s="242"/>
+      <c r="E40" s="242"/>
+      <c r="F40" s="242"/>
+      <c r="G40" s="242"/>
+      <c r="H40" s="242"/>
+      <c r="I40" s="242"/>
+      <c r="J40" s="242"/>
+      <c r="K40" s="242"/>
+      <c r="L40" s="242"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18594,6 +18606,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18601,12 +18619,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18644,20 +18656,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="S2" s="247"/>
       <c r="T2" s="247"/>
       <c r="U2" s="247"/>
@@ -18675,18 +18687,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="242" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
       <c r="S4" s="247"/>
       <c r="T4" s="247"/>
       <c r="U4" s="247"/>
@@ -19060,18 +19072,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="233" t="s">
+      <c r="C13" s="242" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="233"/>
-      <c r="E13" s="233"/>
-      <c r="F13" s="233"/>
-      <c r="G13" s="233"/>
-      <c r="H13" s="233"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="233"/>
-      <c r="K13" s="233"/>
-      <c r="L13" s="233"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="242"/>
+      <c r="F13" s="242"/>
+      <c r="G13" s="242"/>
+      <c r="H13" s="242"/>
+      <c r="I13" s="242"/>
+      <c r="J13" s="242"/>
+      <c r="K13" s="242"/>
+      <c r="L13" s="242"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19164,18 +19176,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="233" t="s">
+      <c r="C18" s="242" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-      <c r="K18" s="233"/>
-      <c r="L18" s="233"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="242"/>
+      <c r="F18" s="242"/>
+      <c r="G18" s="242"/>
+      <c r="H18" s="242"/>
+      <c r="I18" s="242"/>
+      <c r="J18" s="242"/>
+      <c r="K18" s="242"/>
+      <c r="L18" s="242"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19367,18 +19379,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="233" t="s">
+      <c r="C25" s="242" t="s">
         <v>254</v>
       </c>
-      <c r="D25" s="233"/>
-      <c r="E25" s="233"/>
-      <c r="F25" s="233"/>
-      <c r="G25" s="233"/>
-      <c r="H25" s="233"/>
-      <c r="I25" s="233"/>
-      <c r="J25" s="233"/>
-      <c r="K25" s="233"/>
-      <c r="L25" s="233"/>
+      <c r="D25" s="242"/>
+      <c r="E25" s="242"/>
+      <c r="F25" s="242"/>
+      <c r="G25" s="242"/>
+      <c r="H25" s="242"/>
+      <c r="I25" s="242"/>
+      <c r="J25" s="242"/>
+      <c r="K25" s="242"/>
+      <c r="L25" s="242"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19516,18 +19528,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="233" t="s">
+      <c r="C31" s="242" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="233"/>
-      <c r="E31" s="233"/>
-      <c r="F31" s="233"/>
-      <c r="G31" s="233"/>
-      <c r="H31" s="233"/>
-      <c r="I31" s="233"/>
-      <c r="J31" s="233"/>
-      <c r="K31" s="233"/>
-      <c r="L31" s="233"/>
+      <c r="D31" s="242"/>
+      <c r="E31" s="242"/>
+      <c r="F31" s="242"/>
+      <c r="G31" s="242"/>
+      <c r="H31" s="242"/>
+      <c r="I31" s="242"/>
+      <c r="J31" s="242"/>
+      <c r="K31" s="242"/>
+      <c r="L31" s="242"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19666,16 +19678,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19738,10 +19750,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="233" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="234"/>
+      <c r="C4" s="233"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19785,7 +19797,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19794,7 +19806,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6521999999999999</v>
+        <v>1.6571</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19826,10 +19838,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="234" t="s">
+      <c r="B15" s="233" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="234"/>
+      <c r="C15" s="233"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19864,7 +19876,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.125969</v>
+        <v>0.12640950000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19873,7 +19885,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.12040602918157012</v>
+        <v>0.12081725353589587</v>
       </c>
     </row>
   </sheetData>
@@ -19918,20 +19930,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="235"/>
-      <c r="H3" s="236" t="s">
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="245"/>
+      <c r="H3" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="247"/>
       <c r="Q3" s="247"/>
       <c r="R3" s="247"/>
@@ -19949,18 +19961,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="242" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
+      <c r="G5" s="242"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="242"/>
+      <c r="J5" s="242"/>
+      <c r="K5" s="242"/>
+      <c r="L5" s="242"/>
       <c r="P5" s="247"/>
       <c r="Q5" s="247"/>
       <c r="R5" s="247"/>
@@ -20124,7 +20136,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>169805.99047905681</v>
+        <v>169077.22445604368</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20178,23 +20190,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5631.9317094611861</v>
+        <v>5629.8653712838222</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3364.7690560010442</v>
+        <v>3362.3004624009236</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5245.954173601097</v>
+        <v>5240.1821191978088</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7388.7946632788935</v>
+        <v>7377.9569267396473</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>8952.1587865183792</v>
+        <v>8935.7482372177874</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20213,14 +20225,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>96178.017625262262</v>
+        <v>95589.693976324997</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="234" t="s">
+      <c r="B13" s="233" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="234"/>
+      <c r="C13" s="233"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20236,14 +20248,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12040602918157012</v>
+        <v>0.12081725353589587</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="234" t="s">
+      <c r="B18" s="233" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="234"/>
+      <c r="C18" s="233"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20251,7 +20263,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30583.608388860597</v>
+        <v>30546.05311683999</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20260,7 +20272,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>96178.017625262262</v>
+        <v>95589.693976324997</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20269,7 +20281,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>126761.62601412286</v>
+        <v>126135.74709316499</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20296,7 +20308,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119795.62601412286</v>
+        <v>119169.747093165</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20314,7 +20326,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C24/C25</f>
-        <v>112.80190773457896</v>
+        <v>112.21256788433617</v>
       </c>
     </row>
   </sheetData>
@@ -20335,7 +20347,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -20357,37 +20369,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="242" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20583,23 +20595,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>5631.9317094611861</v>
+        <v>5629.8653712838222</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>3364.7690560010442</v>
+        <v>3362.3004624009236</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>5245.954173601097</v>
+        <v>5240.1821191978088</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7388.7946632788935</v>
+        <v>7377.9569267396473</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>8952.1587865183792</v>
+        <v>8935.7482372177874</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20607,18 +20619,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="233" t="s">
+      <c r="C11" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="233"/>
-      <c r="E11" s="233"/>
-      <c r="F11" s="233"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="233"/>
-      <c r="K11" s="233"/>
-      <c r="L11" s="233"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
+      <c r="H11" s="242"/>
+      <c r="I11" s="242"/>
+      <c r="J11" s="242"/>
+      <c r="K11" s="242"/>
+      <c r="L11" s="242"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20812,18 +20824,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="233" t="s">
+      <c r="C17" s="242" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="233"/>
-      <c r="E17" s="233"/>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="233"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="233"/>
-      <c r="K17" s="233"/>
-      <c r="L17" s="233"/>
+      <c r="D17" s="242"/>
+      <c r="E17" s="242"/>
+      <c r="F17" s="242"/>
+      <c r="G17" s="242"/>
+      <c r="H17" s="242"/>
+      <c r="I17" s="242"/>
+      <c r="J17" s="242"/>
+      <c r="K17" s="242"/>
+      <c r="L17" s="242"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20957,18 +20969,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="233" t="s">
+      <c r="C22" s="242" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="233"/>
-      <c r="E22" s="233"/>
-      <c r="F22" s="233"/>
-      <c r="G22" s="233"/>
-      <c r="H22" s="233"/>
-      <c r="I22" s="233"/>
-      <c r="J22" s="233"/>
-      <c r="K22" s="233"/>
-      <c r="L22" s="233"/>
+      <c r="D22" s="242"/>
+      <c r="E22" s="242"/>
+      <c r="F22" s="242"/>
+      <c r="G22" s="242"/>
+      <c r="H22" s="242"/>
+      <c r="I22" s="242"/>
+      <c r="J22" s="242"/>
+      <c r="K22" s="242"/>
+      <c r="L22" s="242"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21052,18 +21064,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="233" t="s">
+      <c r="C27" s="242" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="233"/>
-      <c r="E27" s="233"/>
-      <c r="F27" s="233"/>
-      <c r="G27" s="233"/>
-      <c r="H27" s="233"/>
-      <c r="I27" s="233"/>
-      <c r="J27" s="233"/>
-      <c r="K27" s="233"/>
-      <c r="L27" s="233"/>
+      <c r="D27" s="242"/>
+      <c r="E27" s="242"/>
+      <c r="F27" s="242"/>
+      <c r="G27" s="242"/>
+      <c r="H27" s="242"/>
+      <c r="I27" s="242"/>
+      <c r="J27" s="242"/>
+      <c r="K27" s="242"/>
+      <c r="L27" s="242"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21304,7 +21316,7 @@
         <v>20.022536942114947</v>
       </c>
       <c r="D35" s="147">
-        <f t="shared" ref="D35:G35" si="13">D33/D8</f>
+        <f t="shared" ref="D35:G36" si="13">D33/D8</f>
         <v>27.99681549890132</v>
       </c>
       <c r="E35" s="147">
@@ -21327,285 +21339,421 @@
       <c r="N35" s="91"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="C36" s="147">
+        <f>C33/C6</f>
+        <v>4.6820925936960016</v>
+      </c>
+      <c r="D36" s="147">
+        <f t="shared" ref="D36:G36" si="14">D33/D6</f>
+        <v>3.3233717194570134</v>
+      </c>
+      <c r="E36" s="147">
+        <f t="shared" si="14"/>
+        <v>3.4986510329424902</v>
+      </c>
+      <c r="F36" s="147">
+        <f t="shared" si="14"/>
+        <v>4.9684538781376721</v>
+      </c>
+      <c r="G36" s="148">
+        <f t="shared" si="14"/>
+        <v>4.3271158883569685</v>
+      </c>
+      <c r="H36" s="137"/>
+      <c r="I36" s="137"/>
+      <c r="J36" s="137"/>
+      <c r="K36" s="137"/>
+      <c r="L36" s="137"/>
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="234" t="s">
+      <c r="N38" s="91"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="233" t="s">
         <v>197</v>
       </c>
-      <c r="C38" s="234"/>
-      <c r="N38" s="91"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="233"/>
+      <c r="N39" s="91"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C39" s="64">
+      <c r="C40" s="64">
         <f>L7</f>
         <v>20879.693841464476</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C40" s="135">
+      <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12040602918157012</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+        <v>0.12081725353589587</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="C41" s="105">
+      <c r="C42" s="105">
         <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>375834.48914636055</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>375834.48914636055</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5</f>
-        <v>212872.44354172729</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+      <c r="C44" s="24">
+        <f ca="1">C43/(1+C41)^5</f>
+        <v>212482.21881350424</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="C44" s="108">
-        <f ca="1">SUM(H9:K9)+C43</f>
-        <v>234503.8931440695</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="108">
+        <f ca="1">SUM(H9:K9)+C44</f>
+        <v>234092.52369312645</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C45" s="136">
+      <c r="C46" s="136">
         <f>Statement!AC106</f>
         <v>8304</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C46" s="136">
+      <c r="C47" s="136">
         <f>Statement!AC107</f>
         <v>15270</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C47" s="108">
-        <f ca="1">C44+C45-C46</f>
-        <v>227537.8931440695</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="108">
+        <f ca="1">C45+C46-C47</f>
+        <v>227126.52369312645</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="88">
+      <c r="C49" s="88">
         <f>Statement!AC78</f>
         <v>1062</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="231" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="231" t="s">
         <v>201</v>
       </c>
-      <c r="C49" s="232">
-        <f ca="1">C47/C48</f>
-        <v>214.25413667049858</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="234" t="s">
+      <c r="C50" s="232">
+        <f ca="1">C48/C49</f>
+        <v>213.86678313853716</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="233" t="s">
         <v>202</v>
       </c>
-      <c r="C51" s="234"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="233"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C52" s="64">
+      <c r="C53" s="64">
         <f>L6</f>
         <v>71998.944280911994</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C53" s="135">
+      <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.125969</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+        <v>0.12640950000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="105">
+      <c r="C55" s="105">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>1024.4422356918749</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
         <v>351.40558331376417</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="231" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="231" t="s">
         <v>201</v>
       </c>
-      <c r="C57" s="232">
-        <f ca="1">C56/(1+C53)^5</f>
-        <v>194.1674775762865</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="234" t="s">
+      <c r="C58" s="232">
+        <f ca="1">C57/(1+C54)^5</f>
+        <v>193.7881133053782</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="233" t="s">
         <v>314</v>
       </c>
-      <c r="C59" s="234"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="233"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C60" s="64">
+      <c r="C61" s="64">
         <f>L8</f>
         <v>15805.380763756404</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C61" s="135">
+      <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12040602918157012</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+        <v>0.12081725353589587</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>345</v>
       </c>
-      <c r="C62" s="105">
+      <c r="C63" s="105">
         <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C63" s="24">
-        <f>(C60*C62)</f>
-        <v>316107.6152751281</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C64" s="24">
+        <f>(C61*C63)</f>
+        <v>316107.6152751281</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C64" s="24">
-        <f ca="1">C63/(1+C61)^5</f>
-        <v>179043.17573036757</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+      <c r="C65" s="24">
+        <f ca="1">C64/(1+C62)^5</f>
+        <v>178714.96474435576</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="C65" s="108">
-        <f ca="1">SUM(H9:K9)+C64</f>
-        <v>200674.62533270978</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="108">
+        <f ca="1">SUM(H9:K9)+C65</f>
+        <v>200325.26962397798</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C66" s="136">
+      <c r="C67" s="136">
         <f>Statement!AC106</f>
         <v>8304</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C67" s="136">
+      <c r="C68" s="136">
         <f>Statement!AC107</f>
         <v>15270</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C68" s="108">
-        <f ca="1">C65+C66-C67</f>
-        <v>193708.62533270978</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="108">
+        <f ca="1">C66+C67-C68</f>
+        <v>193359.26962397798</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C69" s="88">
+      <c r="C70" s="88">
         <f>Statement!AC78</f>
         <v>1062</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="231" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="231" t="s">
         <v>201</v>
       </c>
-      <c r="C70" s="232">
-        <f ca="1">C68/C69</f>
-        <v>182.39983552985856</v>
+      <c r="C71" s="232">
+        <f ca="1">C69/C70</f>
+        <v>182.07087535214498</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="233" t="s">
+        <v>425</v>
+      </c>
+      <c r="C73" s="233"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C74" s="64">
+        <f>L6</f>
+        <v>71998.944280911994</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C75" s="135">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.12081725353589587</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>427</v>
+      </c>
+      <c r="C76" s="105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C77" s="24">
+        <f>(C74*C76)</f>
+        <v>359994.72140455997</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C78" s="24">
+        <f ca="1">C77/(1+C75)^5</f>
+        <v>203527.02951485084</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="C79" s="108">
+        <f ca="1">SUM(H9:K9)+C78</f>
+        <v>225137.33439447306</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C80" s="136">
+        <f>Statement!AC106</f>
+        <v>8304</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C81" s="136">
+        <f>Statement!AC107</f>
+        <v>15270</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="108">
+        <f ca="1">C79+C80-C81</f>
+        <v>218171.33439447306</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C83" s="88">
+        <f>Statement!AC78</f>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="231" t="s">
+        <v>201</v>
+      </c>
+      <c r="C84" s="232">
+        <f ca="1">C82/C83</f>
+        <v>205.43440150138707</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
     <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -21622,7 +21770,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -21649,10 +21797,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="233" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="234"/>
+      <c r="C4" s="233"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21661,7 +21809,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>112.80190773457896</v>
+        <v>112.21256788433617</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21669,8 +21817,8 @@
         <v>208</v>
       </c>
       <c r="C6" s="133">
-        <f ca="1">Multiples!C49</f>
-        <v>214.25413667049858</v>
+        <f ca="1">Multiples!C50</f>
+        <v>213.86678313853716</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21678,8 +21826,8 @@
         <v>209</v>
       </c>
       <c r="C7" s="133">
-        <f ca="1">Multiples!C57</f>
-        <v>194.1674775762865</v>
+        <f ca="1">Multiples!C58</f>
+        <v>193.7881133053782</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21687,35 +21835,44 @@
         <v>315</v>
       </c>
       <c r="C8" s="133">
-        <f ca="1">Multiples!C70</f>
-        <v>182.39983552985856</v>
+        <f ca="1">Multiples!C71</f>
+        <v>182.07087535214498</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="231" t="s">
+      <c r="B9" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C9" s="133">
+        <f ca="1">Multiples!C84</f>
+        <v>205.43440150138707</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="231" t="s">
         <v>210</v>
       </c>
-      <c r="C9" s="232">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>175.90583937780565</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="232">
+        <f ca="1">AVERAGE(C5:C9)</f>
+        <v>181.47454823635672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C10" s="133">
+      <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
         <v>201.97</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C11" s="152">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>-0.12904966392134648</v>
+      <c r="C12" s="152">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>-0.10147770343933889</v>
       </c>
     </row>
   </sheetData>
@@ -21771,37 +21928,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="233" t="s">
+      <c r="C4" s="242" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21914,18 +22071,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="233" t="s">
+      <c r="C9" s="242" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="233"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="233"/>
-      <c r="G9" s="233"/>
-      <c r="H9" s="233"/>
-      <c r="I9" s="233"/>
-      <c r="J9" s="233"/>
-      <c r="K9" s="233"/>
-      <c r="L9" s="233"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="242"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="242"/>
+      <c r="J9" s="242"/>
+      <c r="K9" s="242"/>
+      <c r="L9" s="242"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22046,18 +22203,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="233" t="s">
+      <c r="C14" s="242" t="s">
         <v>397</v>
       </c>
-      <c r="D14" s="233"/>
-      <c r="E14" s="233"/>
-      <c r="F14" s="233"/>
-      <c r="G14" s="233"/>
-      <c r="H14" s="233"/>
-      <c r="I14" s="233"/>
-      <c r="J14" s="233"/>
-      <c r="K14" s="233"/>
-      <c r="L14" s="233"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="242"/>
+      <c r="F14" s="242"/>
+      <c r="G14" s="242"/>
+      <c r="H14" s="242"/>
+      <c r="I14" s="242"/>
+      <c r="J14" s="242"/>
+      <c r="K14" s="242"/>
+      <c r="L14" s="242"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22147,10 +22304,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="234" t="s">
+      <c r="B20" s="233" t="s">
         <v>399</v>
       </c>
-      <c r="C20" s="234"/>
+      <c r="C20" s="233"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22185,7 +22342,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.125969</v>
+        <v>0.12640950000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22202,7 +22359,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C23/(C24-C25)</f>
-        <v>34.810180335758574</v>
+        <v>34.66607774681772</v>
       </c>
     </row>
   </sheetData>
@@ -22251,20 +22408,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
-      <c r="G3" s="235"/>
-      <c r="H3" s="236" t="s">
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="245"/>
+      <c r="H3" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="247"/>
       <c r="Q3" s="247"/>
       <c r="R3" s="247"/>
@@ -22282,18 +22439,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="242" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
+      <c r="G5" s="242"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="242"/>
+      <c r="J5" s="242"/>
+      <c r="K5" s="242"/>
+      <c r="L5" s="242"/>
       <c r="P5" s="247"/>
       <c r="Q5" s="247"/>
       <c r="R5" s="247"/>
@@ -22439,7 +22596,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>266078.78744093393</v>
+        <v>264936.84198197559</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22493,23 +22650,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12208.289351152909</v>
+        <v>12203.810167869451</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12639.71745821655</v>
+        <v>12630.444213870394</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13086.391780880982</v>
+        <v>13071.992996064659</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13548.851104372157</v>
+        <v>13528.977919993598</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14027.653254019307</v>
+        <v>14001.938619059598</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22528,15 +22685,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>150706.87574687676</v>
+        <v>149784.99753344967</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="248" t="s">
+      <c r="B14" s="249" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="249"/>
+      <c r="C14" s="250"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22553,7 +22710,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>199.28740828144635</v>
+        <v>198.33920138124512</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22563,20 +22720,20 @@
       <c r="C17" s="156">
         <v>0.16</v>
       </c>
-      <c r="E17" s="250" t="s">
+      <c r="E17" s="248" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="248" t="s">
+      <c r="B19" s="249" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="249"/>
+      <c r="C19" s="250"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22592,7 +22749,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12040602918157012</v>
+        <v>0.12081725353589587</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22642,10 +22799,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="248" t="s">
+      <c r="B28" s="249" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="249"/>
+      <c r="C28" s="250"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22653,7 +22810,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>65510.902948641902</v>
+        <v>65437.163916857709</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22662,7 +22819,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>150706.87574687676</v>
+        <v>149784.99753344967</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22671,7 +22828,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>216217.77869551867</v>
+        <v>215222.16145030738</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22698,7 +22855,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>209251.77869551867</v>
+        <v>208256.16145030738</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22716,21 +22873,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>199.28740828144635</v>
+        <v>198.33920138124512</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33394,15 +33551,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="233" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="234"/>
-      <c r="E4" s="234" t="s">
+      <c r="C4" s="233"/>
+      <c r="E4" s="233" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33539,14 +33696,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="234" t="s">
+      <c r="B15" s="233" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="234"/>
-      <c r="E15" s="234" t="s">
+      <c r="C15" s="233"/>
+      <c r="E15" s="233" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="234"/>
+      <c r="F15" s="233"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33597,14 +33754,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="234" t="s">
+      <c r="B21" s="233" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="234"/>
-      <c r="E21" s="234" t="s">
+      <c r="C21" s="233"/>
+      <c r="E21" s="233" t="s">
         <v>241</v>
       </c>
-      <c r="F21" s="234"/>
+      <c r="F21" s="233"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33673,14 +33830,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="234" t="s">
+      <c r="B29" s="233" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="234"/>
-      <c r="E29" s="234" t="s">
+      <c r="C29" s="233"/>
+      <c r="E29" s="233" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="234"/>
+      <c r="F29" s="233"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33756,14 +33913,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="234" t="s">
+      <c r="B37" s="233" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="234"/>
-      <c r="E37" s="234" t="s">
+      <c r="C37" s="233"/>
+      <c r="E37" s="233" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="234"/>
+      <c r="F37" s="233"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33832,14 +33989,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="234" t="s">
+      <c r="B45" s="233" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="234"/>
-      <c r="E45" s="234" t="s">
+      <c r="C45" s="233"/>
+      <c r="E45" s="233" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="234"/>
+      <c r="F45" s="233"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33876,14 +34033,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="234" t="s">
+      <c r="B51" s="233" t="s">
         <v>274</v>
       </c>
-      <c r="C51" s="234"/>
-      <c r="E51" s="234" t="s">
+      <c r="C51" s="233"/>
+      <c r="E51" s="233" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="234"/>
+      <c r="F51" s="233"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -35918,14 +36075,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="F3" s="242" t="s">
+      <c r="D3" s="240"/>
+      <c r="F3" s="241" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="241"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -35992,19 +36149,19 @@
       <c r="B7" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="243">
+      <c r="C7" s="237">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="244"/>
-      <c r="F7" s="243">
+      <c r="D7" s="238"/>
+      <c r="F7" s="237">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="244"/>
+      <c r="G7" s="238"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36031,19 +36188,19 @@
       <c r="B9" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="243">
+      <c r="C9" s="237">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="F9" s="243">
+      <c r="D9" s="238"/>
+      <c r="F9" s="237">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="244"/>
+      <c r="G9" s="238"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36070,19 +36227,19 @@
       <c r="B11" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="243">
+      <c r="C11" s="237">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="F11" s="243">
+      <c r="D11" s="238"/>
+      <c r="F11" s="237">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="244"/>
+      <c r="G11" s="238"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36109,19 +36266,19 @@
       <c r="B13" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="243">
+      <c r="C13" s="237">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="F13" s="243">
+      <c r="D13" s="238"/>
+      <c r="F13" s="237">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="244"/>
+      <c r="G13" s="238"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36148,19 +36305,19 @@
       <c r="B15" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="243">
+      <c r="C15" s="237">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="244"/>
-      <c r="F15" s="243">
+      <c r="D15" s="238"/>
+      <c r="F15" s="237">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="244"/>
+      <c r="G15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36187,19 +36344,19 @@
       <c r="B17" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="243">
+      <c r="C17" s="237">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="F17" s="243">
+      <c r="D17" s="238"/>
+      <c r="F17" s="237">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="244"/>
+      <c r="G17" s="238"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36226,22 +36383,22 @@
       <c r="B19" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="243">
+      <c r="C19" s="237">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="244"/>
-      <c r="F19" s="243">
+      <c r="D19" s="238"/>
+      <c r="F19" s="237">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="244"/>
+      <c r="G19" s="238"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36268,22 +36425,22 @@
       <c r="B21" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="243">
+      <c r="C21" s="237">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="244"/>
-      <c r="F21" s="243">
+      <c r="D21" s="238"/>
+      <c r="F21" s="237">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="244"/>
+      <c r="G21" s="238"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36331,22 +36488,22 @@
       <c r="B25" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="243">
+      <c r="C25" s="237">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="F25" s="243">
+      <c r="D25" s="238"/>
+      <c r="F25" s="237">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="244"/>
+      <c r="G25" s="238"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="218" t="s">
@@ -36373,22 +36530,22 @@
       <c r="B27" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="243">
+      <c r="C27" s="237">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="244"/>
-      <c r="F27" s="243">
+      <c r="D27" s="238"/>
+      <c r="F27" s="237">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="244"/>
+      <c r="G27" s="238"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="218" t="s">
@@ -36415,22 +36572,22 @@
       <c r="B29" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="243">
+      <c r="C29" s="237">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="244"/>
-      <c r="F29" s="243">
+      <c r="D29" s="238"/>
+      <c r="F29" s="237">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="244"/>
+      <c r="G29" s="238"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36457,22 +36614,22 @@
       <c r="B31" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="243">
+      <c r="C31" s="237">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="244"/>
-      <c r="F31" s="243">
+      <c r="D31" s="238"/>
+      <c r="F31" s="237">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="244"/>
+      <c r="G31" s="238"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36499,25 +36656,43 @@
       <c r="B33" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="243">
+      <c r="C33" s="237">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="244"/>
-      <c r="F33" s="243">
+      <c r="D33" s="238"/>
+      <c r="F33" s="237">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="244"/>
+      <c r="G33" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36528,24 +36703,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD069157-89DC-DA4E-8239-B8183EB34D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E13B623-AB9F-0449-8BCE-8D6DEFE5261E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="429">
   <si>
     <t>Ticker</t>
   </si>
@@ -1435,6 +1435,9 @@
   </si>
   <si>
     <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>Reverse DCF rate</t>
   </si>
 </sst>
 </file>
@@ -2350,9 +2353,6 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2360,6 +2360,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12761,11 +12764,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6571</v>
-    <v>7.71</v>
-    <v>3.9689000000000002E-2</v>
-    <v>0.73</v>
-    <v>3.614E-3</v>
+    <v>1.6524000000000001</v>
+    <v>-3.38</v>
+    <v>-1.8029E-2</v>
+    <v>0.66379999999999995</v>
+    <v>3.6059999999999998E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12773,26 +12776,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>205.85319999999999</v>
+    <v>190.03</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.999975185157</v>
+    <v>46294.964478113281</v>
     <v>4</v>
-    <v>194.53</v>
-    <v>212068500000</v>
+    <v>182.23</v>
+    <v>193305000000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>195.03</v>
-    <v>22.482800000000001</v>
-    <v>194.26</v>
-    <v>201.97</v>
-    <v>202.7</v>
+    <v>189.48</v>
+    <v>21.306899999999999</v>
+    <v>187.48</v>
+    <v>184.1</v>
+    <v>184.7638</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>17817795</v>
-    <v>13522451</v>
+    <v>10015338</v>
+    <v>14221047</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -12814,19 +12817,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.3</v>
+    <v>52.93</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.2620000000000002E-3</v>
+    <v>0.15</v>
+    <v>2.8630000000000001E-3</v>
     <v>US</v>
-    <v>52.3</v>
+    <v>52.93</v>
     <v>Index</v>
     <v>7</v>
-    <v>51.62</v>
+    <v>52.13</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.86</v>
-    <v>51.62</v>
-    <v>51.84</v>
+    <v>52.13</v>
+    <v>52.4</v>
+    <v>52.55</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13068,9 +13071,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13657,18 +13660,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="234" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="E2" s="234" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="235"/>
-      <c r="H2" s="234" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="235"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="181" t="s">
@@ -13683,7 +13686,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC156</f>
-        <v>214492.13999999998</v>
+        <v>195514.19999999998</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13691,7 +13694,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>112.21256788433617</v>
+        <v>112.27125177067325</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13707,7 +13710,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC157</f>
-        <v>221458.13999999998</v>
+        <v>202480.19999999998</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13715,7 +13718,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>213.86678313853716</v>
+        <v>213.90546968658586</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13724,7 +13727,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>201.97</v>
+        <v>184.1</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>235</v>
@@ -13739,7 +13742,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>193.7881133053782</v>
+        <v>193.35987095916772</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13748,14 +13751,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>202.7</v>
+        <v>184.7638</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>22.825743396292548</v>
+        <v>20.80615615812971</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13763,7 +13766,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>182.07087535214498</v>
+        <v>182.10373001125001</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13772,22 +13775,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>7.71</v>
+        <v>-3.38</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>4.9245884768993378</v>
-      </c>
-      <c r="H7" s="180" t="str">
-        <f>'AVG target price'!B10</f>
-        <v>AVG price</v>
-      </c>
-      <c r="I7" s="208">
-        <f ca="1">'AVG target price'!C10</f>
-        <v>181.47454823635672</v>
+        <v>4.4888683398384313</v>
+      </c>
+      <c r="H7" s="181" t="str">
+        <f>'AVG target price'!B9</f>
+        <v>EV/Sales</v>
+      </c>
+      <c r="I7" s="207">
+        <f ca="1">'AVG target price'!C9</f>
+        <v>205.47154141288209</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13796,22 +13799,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.73</v>
+        <v>0.66379999999999995</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC164</f>
-        <v>3.3446447035308614E-2</v>
+        <v>3.6692987005547427E-2</v>
       </c>
       <c r="H8" s="180" t="str">
-        <f>'AVG target price'!B12</f>
-        <v>Upside/Downside</v>
-      </c>
-      <c r="I8" s="209">
-        <f ca="1">'AVG target price'!C12</f>
-        <v>-0.10147770343933889</v>
+        <f>'AVG target price'!B10</f>
+        <v>AVG price</v>
+      </c>
+      <c r="I8" s="208">
+        <f ca="1">'AVG target price'!C10</f>
+        <v>181.42237276811179</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13820,14 +13823,22 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.9689000000000002E-2</v>
+        <v>-1.8029E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC165</f>
-        <v>4.3810183205793163E-2</v>
+        <v>4.8062698001488574E-2</v>
+      </c>
+      <c r="H9" s="180" t="str">
+        <f>'AVG target price'!B12</f>
+        <v>Upside/Downside</v>
+      </c>
+      <c r="I9" s="209">
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-1.4544417337795814E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13836,21 +13847,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.614E-3</v>
+        <v>3.6059999999999998E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC167</f>
-        <v>4.3125123372819166E-2</v>
-      </c>
-      <c r="H10" s="180" t="s">
-        <v>404</v>
-      </c>
-      <c r="I10" s="208">
-        <f ca="1">DDM!C26</f>
-        <v>34.66607774681772</v>
+        <v>4.7311141594830457E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13866,7 +13870,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.7774917066891122E-2</v>
+        <v>1.9500271591526345E-2</v>
+      </c>
+      <c r="H11" s="180" t="s">
+        <v>404</v>
+      </c>
+      <c r="I11" s="208">
+        <f ca="1">DDM!C26</f>
+        <v>34.504433718711411</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13891,7 +13902,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6571</v>
+        <v>1.6524000000000001</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>96</v>
@@ -13900,6 +13911,13 @@
         <f>Statement!AC124</f>
         <v>0.3442403644515149</v>
       </c>
+      <c r="H13" s="180" t="s">
+        <v>428</v>
+      </c>
+      <c r="I13" s="209">
+        <f>'Reverse DCF'!C17</f>
+        <v>0.14000000000000001</v>
+      </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="182" t="s">
@@ -13907,7 +13925,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>13522451</v>
+        <v>14221047</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>97</v>
@@ -13923,7 +13941,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC179</f>
-        <v>-3.2476714531357656E-2</v>
+        <v>-3.562912565941502E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13936,10 +13954,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="236" t="s">
+      <c r="B17" s="235" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="236"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="180" t="s">
         <v>288</v>
       </c>
@@ -14012,14 +14030,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="236" t="s">
+      <c r="B25" s="235" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="236"/>
-      <c r="E25" s="234" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>330</v>
       </c>
-      <c r="F25" s="235"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -14033,7 +14051,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.84</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14048,7 +14066,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2549999999999999E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14068,15 +14086,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="233" t="s">
+      <c r="B33" s="132" t="s">
         <v>325</v>
       </c>
-      <c r="C33" s="233"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
+      <c r="C33" s="132"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14095,24 +14113,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="233"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="233"/>
+      <c r="B39" s="132"/>
+      <c r="C39" s="132"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="132"/>
+      <c r="H39" s="132"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="233" t="s">
+      <c r="B42" s="132" t="s">
         <v>328</v>
       </c>
-      <c r="C42" s="233"/>
-      <c r="D42" s="233"/>
-      <c r="E42" s="233"/>
-      <c r="F42" s="233"/>
-      <c r="G42" s="233"/>
-      <c r="H42" s="233"/>
+      <c r="C42" s="132"/>
+      <c r="D42" s="132"/>
+      <c r="E42" s="132"/>
+      <c r="F42" s="132"/>
+      <c r="G42" s="132"/>
+      <c r="H42" s="132"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14196,24 +14214,24 @@
       </c>
     </row>
     <row r="55" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="233"/>
-      <c r="C55" s="233"/>
-      <c r="D55" s="233"/>
-      <c r="E55" s="233"/>
-      <c r="F55" s="233"/>
-      <c r="G55" s="233"/>
-      <c r="H55" s="233"/>
+      <c r="B55" s="132"/>
+      <c r="C55" s="132"/>
+      <c r="D55" s="132"/>
+      <c r="E55" s="132"/>
+      <c r="F55" s="132"/>
+      <c r="G55" s="132"/>
+      <c r="H55" s="132"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="233" t="s">
+      <c r="B58" s="132" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="233"/>
-      <c r="D58" s="233"/>
-      <c r="E58" s="233"/>
-      <c r="F58" s="233"/>
-      <c r="G58" s="233"/>
-      <c r="H58" s="233"/>
+      <c r="C58" s="132"/>
+      <c r="D58" s="132"/>
+      <c r="E58" s="132"/>
+      <c r="F58" s="132"/>
+      <c r="G58" s="132"/>
+      <c r="H58" s="132"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="41" t="s">
@@ -14351,22 +14369,16 @@
       </c>
     </row>
     <row r="75" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="233"/>
-      <c r="C75" s="233"/>
-      <c r="D75" s="233"/>
-      <c r="E75" s="233"/>
-      <c r="F75" s="233"/>
-      <c r="G75" s="233"/>
-      <c r="H75" s="233"/>
+      <c r="B75" s="132"/>
+      <c r="C75" s="132"/>
+      <c r="D75" s="132"/>
+      <c r="E75" s="132"/>
+      <c r="F75" s="132"/>
+      <c r="G75" s="132"/>
+      <c r="H75" s="132"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B55:H55"/>
+  <mergeCells count="6">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
@@ -14442,36 +14454,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="236" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
       <c r="G2" s="245"/>
       <c r="H2" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="233" t="s">
+      <c r="S2" s="236" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233" t="s">
+      <c r="T2" s="236"/>
+      <c r="U2" s="236"/>
+      <c r="V2" s="236"/>
+      <c r="W2" s="236"/>
+      <c r="X2" s="236"/>
+      <c r="Y2" s="236"/>
+      <c r="Z2" s="236"/>
+      <c r="AA2" s="236" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
+      <c r="AB2" s="236"/>
+      <c r="AC2" s="236"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15941,35 +15953,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="236" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
       <c r="G2" s="245"/>
       <c r="H2" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="P2" s="233" t="s">
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
+      <c r="P2" s="236" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233" t="s">
+      <c r="Q2" s="236"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="236"/>
+      <c r="U2" s="236"/>
+      <c r="V2" s="236"/>
+      <c r="W2" s="236"/>
+      <c r="X2" s="236" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
+      <c r="Y2" s="236"/>
+      <c r="Z2" s="236"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -17200,20 +17212,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="236" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
+      <c r="F3" s="236"/>
       <c r="G3" s="245"/>
       <c r="H3" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="236"/>
+      <c r="J3" s="236"/>
+      <c r="K3" s="236"/>
+      <c r="L3" s="236"/>
       <c r="P3" s="247"/>
       <c r="Q3" s="247"/>
       <c r="R3" s="247"/>
@@ -18656,20 +18668,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="236" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
       <c r="G2" s="245"/>
       <c r="H2" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
       <c r="S2" s="247"/>
       <c r="T2" s="247"/>
       <c r="U2" s="247"/>
@@ -19750,10 +19762,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="236" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="236"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19770,7 +19782,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>201.97</v>
+        <v>184.1</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19779,7 +19791,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>214492.13999999998</v>
+        <v>195514.19999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19797,7 +19809,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2549999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19806,7 +19818,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6571</v>
+        <v>1.6524000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19838,10 +19850,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="236" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="233"/>
+      <c r="C15" s="236"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19849,7 +19861,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.6460035582885851E-2</v>
+        <v>7.2443760016168202E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19858,7 +19870,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93353996441711418</v>
+        <v>0.92755623998383185</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19876,7 +19888,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.12640950000000001</v>
+        <v>0.12690800000000002</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19885,7 +19897,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.12081725353589587</v>
+        <v>0.1207761428209515</v>
       </c>
     </row>
   </sheetData>
@@ -19930,20 +19942,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="236" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
+      <c r="F3" s="236"/>
       <c r="G3" s="245"/>
       <c r="H3" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="236"/>
+      <c r="J3" s="236"/>
+      <c r="K3" s="236"/>
+      <c r="L3" s="236"/>
       <c r="P3" s="247"/>
       <c r="Q3" s="247"/>
       <c r="R3" s="247"/>
@@ -20136,7 +20148,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>169077.22445604368</v>
+        <v>169149.79874619015</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20190,23 +20202,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5629.8653712838222</v>
+        <v>5630.0718779907465</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3362.3004624009236</v>
+        <v>3362.5471291628237</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5240.1821191978088</v>
+        <v>5240.7587790513708</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7377.9569267396473</v>
+        <v>7379.0394971529668</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>8935.7482372177874</v>
+        <v>8937.3871994294786</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20225,14 +20237,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>95589.693976324997</v>
+        <v>95648.264897667585</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="233" t="s">
+      <c r="B13" s="236" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="233"/>
+      <c r="C13" s="236"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20248,14 +20260,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12081725353589587</v>
+        <v>0.1207761428209515</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="236" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="233"/>
+      <c r="C18" s="236"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20263,7 +20275,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30546.05311683999</v>
+        <v>30549.804482787389</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20272,7 +20284,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>95589.693976324997</v>
+        <v>95648.264897667585</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20281,7 +20293,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>126135.74709316499</v>
+        <v>126198.06938045498</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20308,7 +20320,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119169.747093165</v>
+        <v>119232.06938045498</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20326,7 +20338,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C24/C25</f>
-        <v>112.21256788433617</v>
+        <v>112.27125177067325</v>
       </c>
     </row>
   </sheetData>
@@ -20369,20 +20381,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="236" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
       <c r="G2" s="245"/>
       <c r="H2" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20595,23 +20607,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>5629.8653712838222</v>
+        <v>5630.0718779907465</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>3362.3004624009236</v>
+        <v>3362.5471291628237</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>5240.1821191978088</v>
+        <v>5240.7587790513708</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7377.9569267396473</v>
+        <v>7379.0394971529668</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>8935.7482372177874</v>
+        <v>8937.3871994294786</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21316,7 +21328,7 @@
         <v>20.022536942114947</v>
       </c>
       <c r="D35" s="147">
-        <f t="shared" ref="D35:G36" si="13">D33/D8</f>
+        <f t="shared" ref="D35:G35" si="13">D33/D8</f>
         <v>27.99681549890132</v>
       </c>
       <c r="E35" s="147">
@@ -21376,10 +21388,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="233" t="s">
+      <c r="B39" s="236" t="s">
         <v>197</v>
       </c>
-      <c r="C39" s="233"/>
+      <c r="C39" s="236"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21397,7 +21409,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12081725353589587</v>
+        <v>0.1207761428209515</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21423,7 +21435,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>212482.21881350424</v>
+        <v>212521.19152379627</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21432,7 +21444,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>234092.52369312645</v>
+        <v>234133.60880715417</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21459,7 +21471,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>227126.52369312645</v>
+        <v>227167.60880715417</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21477,14 +21489,14 @@
       </c>
       <c r="C50" s="232">
         <f ca="1">C48/C49</f>
-        <v>213.86678313853716</v>
+        <v>213.90546968658586</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="233" t="s">
+      <c r="B52" s="236" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="233"/>
+      <c r="C52" s="236"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21501,7 +21513,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12640950000000001</v>
+        <v>0.12690800000000002</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21536,14 +21548,14 @@
       </c>
       <c r="C58" s="232">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>193.7881133053782</v>
+        <v>193.35987095916772</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="233" t="s">
+      <c r="B60" s="236" t="s">
         <v>314</v>
       </c>
-      <c r="C60" s="233"/>
+      <c r="C60" s="236"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21560,7 +21572,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12081725353589587</v>
+        <v>0.1207761428209515</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21586,7 +21598,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>178714.96474435576</v>
+        <v>178747.74398858959</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21595,7 +21607,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>200325.26962397798</v>
+        <v>200360.16127194749</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21622,7 +21634,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>193359.26962397798</v>
+        <v>193394.16127194749</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21640,14 +21652,14 @@
       </c>
       <c r="C71" s="232">
         <f ca="1">C69/C70</f>
-        <v>182.07087535214498</v>
+        <v>182.10373001125001</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="233" t="s">
+      <c r="B73" s="236" t="s">
         <v>425</v>
       </c>
-      <c r="C73" s="233"/>
+      <c r="C73" s="236"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21664,7 +21676,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12081725353589587</v>
+        <v>0.1207761428209515</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21690,7 +21702,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>203527.02951485084</v>
+        <v>203564.35969712288</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21699,7 +21711,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>225137.33439447306</v>
+        <v>225176.77698048079</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21726,7 +21738,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>218171.33439447306</v>
+        <v>218210.77698048079</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21744,7 +21756,7 @@
       </c>
       <c r="C84" s="232">
         <f ca="1">C82/C83</f>
-        <v>205.43440150138707</v>
+        <v>205.47154141288209</v>
       </c>
     </row>
   </sheetData>
@@ -21754,12 +21766,12 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B60:C60"/>
+    <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21797,10 +21809,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="236" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="236"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21809,7 +21821,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>112.21256788433617</v>
+        <v>112.27125177067325</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21818,7 +21830,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>213.86678313853716</v>
+        <v>213.90546968658586</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21827,7 +21839,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>193.7881133053782</v>
+        <v>193.35987095916772</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21836,7 +21848,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>182.07087535214498</v>
+        <v>182.10373001125001</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21845,7 +21857,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>205.43440150138707</v>
+        <v>205.47154141288209</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21854,7 +21866,7 @@
       </c>
       <c r="C10" s="232">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>181.47454823635672</v>
+        <v>181.42237276811179</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21863,7 +21875,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>201.97</v>
+        <v>184.1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21872,7 +21884,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.10147770343933889</v>
+        <v>-1.4544417337795814E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21928,20 +21940,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="236" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
       <c r="G2" s="245"/>
       <c r="H2" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="236"/>
+      <c r="K2" s="236"/>
+      <c r="L2" s="236"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22304,10 +22316,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="233" t="s">
+      <c r="B20" s="236" t="s">
         <v>399</v>
       </c>
-      <c r="C20" s="233"/>
+      <c r="C20" s="236"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22342,7 +22354,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12640950000000001</v>
+        <v>0.12690800000000002</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22359,7 +22371,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C23/(C24-C25)</f>
-        <v>34.66607774681772</v>
+        <v>34.504433718711411</v>
       </c>
     </row>
   </sheetData>
@@ -22408,20 +22420,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="236" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
+      <c r="F3" s="236"/>
       <c r="G3" s="245"/>
       <c r="H3" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="236"/>
+      <c r="J3" s="236"/>
+      <c r="K3" s="236"/>
+      <c r="L3" s="236"/>
       <c r="P3" s="247"/>
       <c r="Q3" s="247"/>
       <c r="R3" s="247"/>
@@ -22548,23 +22560,23 @@
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>13678.240995024877</v>
+        <v>13442.409253731346</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>15866.759554228856</v>
+        <v>15324.346549253736</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>18405.441082905472</v>
+        <v>17469.755066149261</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>21350.311656170346</v>
+        <v>19915.520775410158</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>24766.3615211576</v>
+        <v>22703.693683967584</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22596,7 +22608,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>264936.84198197559</v>
+        <v>242975.81151885833</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22650,23 +22662,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>12203.810167869451</v>
+        <v>11993.839572545956</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12630.444213870394</v>
+        <v>12199.561170429646</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13071.992996064659</v>
+        <v>12408.811361102978</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>13528.977919993598</v>
+        <v>12621.650667949027</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>14001.938619059598</v>
+        <v>12838.140652464392</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22685,7 +22697,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>149784.99753344967</v>
+        <v>137394.27984040073</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22701,7 +22713,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>201.97</v>
+        <v>184.1</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22710,7 +22722,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>198.33920138124512</v>
+        <v>183.32407929989785</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22718,7 +22730,7 @@
         <v>316</v>
       </c>
       <c r="C17" s="156">
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E17" s="248" t="s">
         <v>217</v>
@@ -22749,7 +22761,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12081725353589587</v>
+        <v>0.1207761428209515</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22767,7 +22779,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>212068.5</v>
+        <v>193305</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22794,7 +22806,7 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>219034.5</v>
+        <v>200271</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22810,7 +22822,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>65437.163916857709</v>
+        <v>62062.003424491995</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22819,7 +22831,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>149784.99753344967</v>
+        <v>137394.27984040073</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22828,7 +22840,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>215222.16145030738</v>
+        <v>199456.28326489273</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22855,7 +22867,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>208256.16145030738</v>
+        <v>192490.28326489273</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22873,7 +22885,7 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>198.33920138124512</v>
+        <v>183.32407929989785</v>
       </c>
     </row>
   </sheetData>
@@ -29502,7 +29514,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>201.97</v>
+        <v>184.1</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29573,7 +29585,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>201.97</v>
+        <v>184.1</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31075,7 +31087,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>22.825743396292548</v>
+        <v>20.80615615812971</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31112,7 +31124,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.9245884768993378</v>
+        <v>4.4888683398384313</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31173,7 +31185,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>7.6675283823848437</v>
+        <v>6.989117072817991</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31234,7 +31246,7 @@
       </c>
       <c r="AC156" s="141">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>214492.13999999998</v>
+        <v>195514.19999999998</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31295,7 +31307,7 @@
       </c>
       <c r="AC157" s="141">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>221458.13999999998</v>
+        <v>202480.19999999998</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31332,7 +31344,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="179">
         <f ca="1">AC157/AC5</f>
-        <v>5.0253730598166468</v>
+        <v>4.5947217935917211</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31369,7 +31381,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="179">
         <f ca="1">AC157/AC12</f>
-        <v>21.67121440454056</v>
+        <v>19.814091398375574</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31504,7 +31516,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>29.898541957067184</v>
+        <v>27.253164204070252</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31541,7 +31553,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>22.714203308123381</v>
+        <v>20.767700968993434</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31578,7 +31590,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>3.3446447035308614E-2</v>
+        <v>3.6692987005547427E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31615,7 +31627,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>4.3810183205793163E-2</v>
+        <v>4.8062698001488574E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31652,7 +31664,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="152">
         <f ca="1">AC82/AC116</f>
-        <v>1.7774917066891122E-2</v>
+        <v>1.9500271591526345E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31689,7 +31701,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="152">
         <f ca="1">-AC63/AC156</f>
-        <v>4.3125123372819166E-2</v>
+        <v>4.7311141594830457E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31726,7 +31738,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="152">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>6.0957944659417361E-2</v>
+        <v>6.6874937984044133E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32229,7 +32241,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="152">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.2476714531357656E-2</v>
+        <v>-3.562912565941502E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33551,15 +33563,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="236" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="233"/>
-      <c r="E4" s="233" t="s">
+      <c r="C4" s="236"/>
+      <c r="E4" s="236" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33567,7 +33579,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>201.97</v>
+        <v>184.1</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33583,7 +33595,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>214492.13999999998</v>
+        <v>195514.19999999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33603,7 +33615,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>221458.13999999998</v>
+        <v>202480.19999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33623,7 +33635,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>22.825743396292548</v>
+        <v>20.80615615812971</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33643,7 +33655,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.9245884768993378</v>
+        <v>4.4888683398384313</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33663,7 +33675,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>7.6675283823848437</v>
+        <v>6.989117072817991</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33683,7 +33695,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>5.0253730598166468</v>
+        <v>4.5947217935917211</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33692,18 +33704,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>21.67121440454056</v>
+        <v>19.814091398375574</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="233"/>
-      <c r="E15" s="233" t="s">
+      <c r="C15" s="236"/>
+      <c r="E15" s="236" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="233"/>
+      <c r="F15" s="236"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33754,14 +33766,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="233" t="s">
+      <c r="B21" s="236" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="233"/>
-      <c r="E21" s="233" t="s">
+      <c r="C21" s="236"/>
+      <c r="E21" s="236" t="s">
         <v>241</v>
       </c>
-      <c r="F21" s="233"/>
+      <c r="F21" s="236"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33830,14 +33842,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="233" t="s">
+      <c r="B29" s="236" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="233"/>
-      <c r="E29" s="233" t="s">
+      <c r="C29" s="236"/>
+      <c r="E29" s="236" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="233"/>
+      <c r="F29" s="236"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33913,14 +33925,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="236" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="233"/>
-      <c r="E37" s="233" t="s">
+      <c r="C37" s="236"/>
+      <c r="E37" s="236" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="233"/>
+      <c r="F37" s="236"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33928,7 +33940,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>4.3810183205793163E-2</v>
+        <v>4.8062698001488574E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33944,7 +33956,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC164</f>
-        <v>3.3446447035308614E-2</v>
+        <v>3.6692987005547427E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33960,7 +33972,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>1.7774917066891122E-2</v>
+        <v>1.9500271591526345E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33976,7 +33988,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.3125123372819166E-2</v>
+        <v>4.7311141594830457E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33985,18 +33997,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>6.0957944659417361E-2</v>
+        <v>6.6874937984044133E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="233" t="s">
+      <c r="B45" s="236" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="233"/>
-      <c r="E45" s="233" t="s">
+      <c r="C45" s="236"/>
+      <c r="E45" s="236" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="233"/>
+      <c r="F45" s="236"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34029,18 +34041,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC179</f>
-        <v>-3.2476714531357656E-2</v>
+        <v>-3.562912565941502E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="233" t="s">
+      <c r="B51" s="236" t="s">
         <v>274</v>
       </c>
-      <c r="C51" s="233"/>
-      <c r="E51" s="233" t="s">
+      <c r="C51" s="236"/>
+      <c r="E51" s="236" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="233"/>
+      <c r="F51" s="236"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34209,7 +34221,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC115</f>
-        <v>201.97</v>
+        <v>184.1</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34238,7 +34250,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>214492.13999999998</v>
+        <v>195514.19999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34267,7 +34279,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>221458.13999999998</v>
+        <v>202480.19999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34296,7 +34308,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>22.825743396292548</v>
+        <v>20.80615615812971</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34325,7 +34337,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.9245884768993378</v>
+        <v>4.4888683398384313</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34354,7 +34366,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>7.6675283823848437</v>
+        <v>6.989117072817991</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34383,7 +34395,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>5.0253730598166468</v>
+        <v>4.5947217935917211</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34412,7 +34424,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>21.67121440454056</v>
+        <v>19.814091398375574</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35185,7 +35197,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>4.3810183205793163E-2</v>
+        <v>4.8062698001488574E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35214,7 +35226,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC164</f>
-        <v>3.3446447035308614E-2</v>
+        <v>3.6692987005547427E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35243,7 +35255,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>1.7774917066891122E-2</v>
+        <v>1.9500271591526345E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35272,7 +35284,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.3125123372819166E-2</v>
+        <v>4.7311141594830457E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35301,7 +35313,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>6.0957944659417361E-2</v>
+        <v>6.6874937984044133E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35537,7 +35549,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.2476714531357656E-2</v>
+        <v>-3.562912565941502E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E13B623-AB9F-0449-8BCE-8D6DEFE5261E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6288DF1-C762-474E-83A9-C2E4BC6CF4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2365,12 +2365,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2378,6 +2372,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2398,14 +2398,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12764,11 +12764,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6524000000000001</v>
-    <v>-3.38</v>
-    <v>-1.8029E-2</v>
-    <v>0.66379999999999995</v>
-    <v>3.6059999999999998E-3</v>
+    <v>1.6906000000000001</v>
+    <v>-4.08</v>
+    <v>-2.2069999999999999E-2</v>
+    <v>0.68</v>
+    <v>3.761E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12776,26 +12776,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>190.03</v>
+    <v>185.48</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46294.964478113281</v>
+    <v>46300.894140635937</v>
     <v>4</v>
-    <v>182.23</v>
-    <v>193305000000</v>
+    <v>180.3</v>
+    <v>189829500000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>189.48</v>
-    <v>21.306899999999999</v>
-    <v>187.48</v>
-    <v>184.1</v>
-    <v>184.7638</v>
+    <v>185.07499999999999</v>
+    <v>21.396100000000001</v>
+    <v>184.87</v>
+    <v>180.79</v>
+    <v>181.47</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>10015338</v>
-    <v>14221047</v>
+    <v>12273142</v>
+    <v>13860225</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -12817,19 +12817,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.93</v>
+    <v>53.42</v>
     <v>39.47</v>
-    <v>0.15</v>
-    <v>2.8630000000000001E-3</v>
+    <v>0.4</v>
+    <v>7.6380000000000007E-3</v>
     <v>US</v>
-    <v>52.93</v>
+    <v>52.98</v>
     <v>Index</v>
     <v>7</v>
-    <v>52.13</v>
+    <v>51.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.13</v>
-    <v>52.4</v>
-    <v>52.55</v>
+    <v>52.16</v>
+    <v>52.37</v>
+    <v>52.77</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC156</f>
-        <v>195514.19999999998</v>
+        <v>191998.97999999998</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>112.27125177067325</v>
+        <v>109.89769708806385</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC157</f>
-        <v>202480.19999999998</v>
+        <v>198964.97999999998</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>213.90546968658586</v>
+        <v>212.32000063580659</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>184.1</v>
+        <v>180.79</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>235</v>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>193.35987095916772</v>
+        <v>191.70491241625226</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13751,14 +13751,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>184.7638</v>
+        <v>181.47</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>20.80615615812971</v>
+        <v>20.43207480623721</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>182.10373001125001</v>
+        <v>180.75724971180603</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13775,14 +13775,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-3.38</v>
+        <v>-4.08</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>4.4888683398384313</v>
+        <v>4.4081613642552417</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>205.47154141288209</v>
+        <v>203.94945298239475</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13799,14 +13799,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.66379999999999995</v>
+        <v>0.68</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC164</f>
-        <v>3.6692987005547427E-2</v>
+        <v>3.7364781833736829E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>181.42237276811179</v>
+        <v>179.72586256686469</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13823,14 +13823,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.8029E-2</v>
+        <v>-2.2069999999999999E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC165</f>
-        <v>4.8062698001488574E-2</v>
+        <v>4.8942655578704829E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-1.4544417337795814E-2</v>
+        <v>-5.8860414466248168E-3</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13847,14 +13847,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.6059999999999998E-3</v>
+        <v>3.761E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC167</f>
-        <v>4.7311141594830457E-2</v>
+        <v>4.817733927544824E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13870,14 +13870,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.9500271591526345E-2</v>
+        <v>1.985729299186902E-2</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>404</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>34.504433718711411</v>
+        <v>33.889771881632015</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6524000000000001</v>
+        <v>1.6906000000000001</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>96</v>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>14221047</v>
+        <v>13860225</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>97</v>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC179</f>
-        <v>-3.562912565941502E-2</v>
+        <v>-3.6281442745164587E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.55</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18618,12 +18618,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18631,6 +18625,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19690,16 +19690,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>184.1</v>
+        <v>180.79</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19791,7 +19791,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>195514.19999999998</v>
+        <v>191998.97999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19809,7 +19809,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6524000000000001</v>
+        <v>1.6906000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.2443760016168202E-2</v>
+        <v>7.3672384550741751E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92755623998383185</v>
+        <v>0.92632761544925823</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19888,7 +19888,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.12690800000000002</v>
+        <v>0.12884700000000002</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1207761428209515</v>
+        <v>0.1224682976008277</v>
       </c>
     </row>
   </sheetData>
@@ -20148,7 +20148,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>169149.79874619015</v>
+        <v>166213.17578765977</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20202,23 +20202,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5630.0718779907465</v>
+        <v>5621.5843749942233</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3362.5471291628237</v>
+        <v>3352.4164888166483</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5240.7587790513708</v>
+        <v>5217.0926869734749</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7379.0394971529668</v>
+        <v>7334.6435182592077</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>8937.3871994294786</v>
+        <v>8870.2231062447208</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20237,7 +20237,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>95648.264897667585</v>
+        <v>93281.394132235553</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1207761428209515</v>
+        <v>0.1224682976008277</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20275,7 +20275,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30549.804482787389</v>
+        <v>30395.960175288274</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>95648.264897667585</v>
+        <v>93281.394132235553</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>126198.06938045498</v>
+        <v>123677.35430752383</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20320,7 +20320,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>119232.06938045498</v>
+        <v>116711.35430752381</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20338,7 +20338,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C24/C25</f>
-        <v>112.27125177067325</v>
+        <v>109.89769708806385</v>
       </c>
     </row>
   </sheetData>
@@ -20607,23 +20607,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>5630.0718779907465</v>
+        <v>5621.5843749942233</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>3362.5471291628237</v>
+        <v>3352.4164888166483</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>5240.7587790513708</v>
+        <v>5217.0926869734749</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7379.0394971529668</v>
+        <v>7334.6435182592077</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>8937.3871994294786</v>
+        <v>8870.2231062447208</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1207761428209515</v>
+        <v>0.1224682976008277</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>212521.19152379627</v>
+        <v>210924.10360618305</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>234133.60880715417</v>
+        <v>232449.84067522662</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21471,7 +21471,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>227167.60880715417</v>
+        <v>225483.84067522662</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21489,7 +21489,7 @@
       </c>
       <c r="C50" s="232">
         <f ca="1">C48/C49</f>
-        <v>213.90546968658586</v>
+        <v>212.32000063580659</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12690800000000002</v>
+        <v>0.12884700000000002</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="C58" s="232">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>193.35987095916772</v>
+        <v>191.70491241625226</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1207761428209515</v>
+        <v>0.1224682976008277</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>178747.74398858959</v>
+        <v>177404.46212489443</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21607,7 +21607,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>200360.16127194749</v>
+        <v>198930.199193938</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>193394.16127194749</v>
+        <v>191964.199193938</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="C71" s="232">
         <f ca="1">C69/C70</f>
-        <v>182.10373001125001</v>
+        <v>180.75724971180603</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1207761428209515</v>
+        <v>0.1224682976008277</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>203564.35969712288</v>
+        <v>202034.58199825964</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>225176.77698048079</v>
+        <v>223560.31906730321</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21738,7 +21738,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>218210.77698048079</v>
+        <v>216594.31906730321</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21756,22 +21756,22 @@
       </c>
       <c r="C84" s="232">
         <f ca="1">C82/C83</f>
-        <v>205.47154141288209</v>
+        <v>203.94945298239475</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21821,7 +21821,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>112.27125177067325</v>
+        <v>109.89769708806385</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>213.90546968658586</v>
+        <v>212.32000063580659</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21839,7 +21839,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>193.35987095916772</v>
+        <v>191.70491241625226</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>182.10373001125001</v>
+        <v>180.75724971180603</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>205.47154141288209</v>
+        <v>203.94945298239475</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="C10" s="232">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>181.42237276811179</v>
+        <v>179.72586256686469</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>184.1</v>
+        <v>180.79</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21884,7 +21884,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-1.4544417337795814E-2</v>
+        <v>-5.8860414466248168E-3</v>
       </c>
     </row>
   </sheetData>
@@ -22354,7 +22354,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12690800000000002</v>
+        <v>0.12884700000000002</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C23/(C24-C25)</f>
-        <v>34.504433718711411</v>
+        <v>33.889771881632015</v>
       </c>
     </row>
   </sheetData>
@@ -22608,7 +22608,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>242975.81151885833</v>
+        <v>238757.48934666064</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22662,23 +22662,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11993.839572545956</v>
+        <v>11975.758498002351</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12199.561170429646</v>
+        <v>12162.806483624838</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12408.811361102978</v>
+        <v>12352.775950081397</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12621.650667949027</v>
+        <v>12545.71252764298</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12838.140652464392</v>
+        <v>12741.662559274451</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22697,15 +22697,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>137394.27984040073</v>
+        <v>133994.38017008521</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="249" t="s">
+      <c r="B14" s="248" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="250"/>
+      <c r="C14" s="249"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22713,7 +22713,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>184.1</v>
+        <v>180.79</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>183.32407929989785</v>
+        <v>179.81628208448689</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22732,20 +22732,20 @@
       <c r="C17" s="156">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E17" s="248" t="s">
+      <c r="E17" s="250" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="250"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="249" t="s">
+      <c r="B19" s="248" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="250"/>
+      <c r="C19" s="249"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1207761428209515</v>
+        <v>0.1224682976008277</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22779,7 +22779,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>193305</v>
+        <v>189829.5</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22806,15 +22806,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>200271</v>
+        <v>196795.5</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="249" t="s">
+      <c r="B28" s="248" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="250"/>
+      <c r="C28" s="249"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>62062.003424491995</v>
+        <v>61778.716018626023</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22831,7 +22831,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>137394.27984040073</v>
+        <v>133994.38017008521</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>199456.28326489273</v>
+        <v>195773.09618871124</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22867,7 +22867,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>192490.28326489273</v>
+        <v>188807.09618871124</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22885,21 +22885,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>183.32407929989785</v>
+        <v>179.81628208448689</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29514,7 +29514,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>184.1</v>
+        <v>180.79</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>184.1</v>
+        <v>180.79</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31087,7 +31087,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>20.80615615812971</v>
+        <v>20.43207480623721</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31124,7 +31124,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.4888683398384313</v>
+        <v>4.4081613642552417</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31185,7 +31185,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.989117072817991</v>
+        <v>6.8634572275652612</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31246,7 +31246,7 @@
       </c>
       <c r="AC156" s="141">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>195514.19999999998</v>
+        <v>191998.97999999998</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31307,7 +31307,7 @@
       </c>
       <c r="AC157" s="141">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>202480.19999999998</v>
+        <v>198964.97999999998</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31344,7 +31344,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="179">
         <f ca="1">AC157/AC5</f>
-        <v>4.5947217935917211</v>
+        <v>4.5149537079059634</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31381,7 +31381,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="179">
         <f ca="1">AC157/AC12</f>
-        <v>19.814091398375574</v>
+        <v>19.470102749779819</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31478,8 +31478,8 @@
       <c r="Z161" s="49"/>
       <c r="AA161" s="49"/>
       <c r="AC161" s="64">
-        <f>AC108+AC53+AC109+AC55+AC57+AC58</f>
-        <v>9749.7648055654645</v>
+        <f>AC108+AC53+AC109+AC55+AC57+AC58+AC56</f>
+        <v>7780.7648055654645</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31516,7 +31516,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>27.253164204070252</v>
+        <v>26.763169779760243</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31553,7 +31553,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>20.767700968993434</v>
+        <v>25.571391112822653</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31590,7 +31590,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>3.6692987005547427E-2</v>
+        <v>3.7364781833736829E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31627,7 +31627,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>4.8062698001488574E-2</v>
+        <v>4.8942655578704829E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31664,7 +31664,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="152">
         <f ca="1">AC82/AC116</f>
-        <v>1.9500271591526345E-2</v>
+        <v>1.985729299186902E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31701,7 +31701,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="152">
         <f ca="1">-AC63/AC156</f>
-        <v>4.7311141594830457E-2</v>
+        <v>4.817733927544824E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31738,7 +31738,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="152">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>6.6874937984044133E-2</v>
+        <v>6.8099320110971431E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -31775,7 +31775,7 @@
       <c r="AA169" s="49"/>
       <c r="AC169" s="152">
         <f>AC161/AC5</f>
-        <v>0.22124364177102351</v>
+        <v>0.17656269414462794</v>
       </c>
     </row>
     <row r="170" spans="2:29" x14ac:dyDescent="0.2">
@@ -32241,7 +32241,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="152">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.562912565941502E-2</v>
+        <v>-3.6281442745164587E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33579,7 +33579,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>184.1</v>
+        <v>180.79</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33595,7 +33595,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>195514.19999999998</v>
+        <v>191998.97999999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33615,7 +33615,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>202480.19999999998</v>
+        <v>198964.97999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>20.80615615812971</v>
+        <v>20.43207480623721</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33655,7 +33655,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.4888683398384313</v>
+        <v>4.4081613642552417</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33675,7 +33675,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.989117072817991</v>
+        <v>6.8634572275652612</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33695,7 +33695,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.5947217935917211</v>
+        <v>4.5149537079059634</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33704,7 +33704,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>19.814091398375574</v>
+        <v>19.470102749779819</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33940,7 +33940,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>4.8062698001488574E-2</v>
+        <v>4.8942655578704829E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33956,7 +33956,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC164</f>
-        <v>3.6692987005547427E-2</v>
+        <v>3.7364781833736829E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33972,7 +33972,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>1.9500271591526345E-2</v>
+        <v>1.985729299186902E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.7311141594830457E-2</v>
+        <v>4.817733927544824E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33997,7 +33997,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>6.6874937984044133E-2</v>
+        <v>6.8099320110971431E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34041,7 +34041,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC179</f>
-        <v>-3.562912565941502E-2</v>
+        <v>-3.6281442745164587E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC115</f>
-        <v>184.1</v>
+        <v>180.79</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34250,7 +34250,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>195514.19999999998</v>
+        <v>191998.97999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34279,7 +34279,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>202480.19999999998</v>
+        <v>198964.97999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>20.80615615812971</v>
+        <v>20.43207480623721</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34337,7 +34337,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.4888683398384313</v>
+        <v>4.4081613642552417</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34366,7 +34366,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.989117072817991</v>
+        <v>6.8634572275652612</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34395,7 +34395,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.5947217935917211</v>
+        <v>4.5149537079059634</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34424,7 +34424,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>19.814091398375574</v>
+        <v>19.470102749779819</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>4.8062698001488574E-2</v>
+        <v>4.8942655578704829E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35226,7 +35226,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC164</f>
-        <v>3.6692987005547427E-2</v>
+        <v>3.7364781833736829E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35255,7 +35255,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>1.9500271591526345E-2</v>
+        <v>1.985729299186902E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35284,7 +35284,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.7311141594830457E-2</v>
+        <v>4.817733927544824E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35313,7 +35313,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>6.6874937984044133E-2</v>
+        <v>6.8099320110971431E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35549,7 +35549,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.562912565941502E-2</v>
+        <v>-3.6281442745164587E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36087,14 +36087,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="237" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="238"/>
+      <c r="F3" s="239" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="238"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36161,19 +36161,19 @@
       <c r="B7" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="237">
+      <c r="C7" s="240">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="F7" s="237">
+      <c r="D7" s="241"/>
+      <c r="F7" s="240">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="238"/>
+      <c r="G7" s="241"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36200,19 +36200,19 @@
       <c r="B9" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="237">
+      <c r="C9" s="240">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="F9" s="237">
+      <c r="D9" s="241"/>
+      <c r="F9" s="240">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="238"/>
+      <c r="G9" s="241"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36239,19 +36239,19 @@
       <c r="B11" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="237">
+      <c r="C11" s="240">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="F11" s="237">
+      <c r="D11" s="241"/>
+      <c r="F11" s="240">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="238"/>
+      <c r="G11" s="241"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36278,19 +36278,19 @@
       <c r="B13" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="237">
+      <c r="C13" s="240">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="F13" s="237">
+      <c r="D13" s="241"/>
+      <c r="F13" s="240">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="238"/>
+      <c r="G13" s="241"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36317,19 +36317,19 @@
       <c r="B15" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="237">
+      <c r="C15" s="240">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="F15" s="237">
+      <c r="D15" s="241"/>
+      <c r="F15" s="240">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="238"/>
+      <c r="G15" s="241"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36356,19 +36356,19 @@
       <c r="B17" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="237">
+      <c r="C17" s="240">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="238"/>
-      <c r="F17" s="237">
+      <c r="D17" s="241"/>
+      <c r="F17" s="240">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="238"/>
+      <c r="G17" s="241"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36395,22 +36395,22 @@
       <c r="B19" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="237">
+      <c r="C19" s="240">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="238"/>
-      <c r="F19" s="237">
+      <c r="D19" s="241"/>
+      <c r="F19" s="240">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="238"/>
+      <c r="G19" s="241"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36437,22 +36437,22 @@
       <c r="B21" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="237">
+      <c r="C21" s="240">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="F21" s="237">
+      <c r="D21" s="241"/>
+      <c r="F21" s="240">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="238"/>
+      <c r="G21" s="241"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36500,22 +36500,22 @@
       <c r="B25" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="237">
+      <c r="C25" s="240">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="F25" s="237">
+      <c r="D25" s="241"/>
+      <c r="F25" s="240">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="238"/>
+      <c r="G25" s="241"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="218" t="s">
@@ -36542,22 +36542,22 @@
       <c r="B27" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="237">
+      <c r="C27" s="240">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="238"/>
-      <c r="F27" s="237">
+      <c r="D27" s="241"/>
+      <c r="F27" s="240">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="238"/>
+      <c r="G27" s="241"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="218" t="s">
@@ -36584,22 +36584,22 @@
       <c r="B29" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="237">
+      <c r="C29" s="240">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="238"/>
-      <c r="F29" s="237">
+      <c r="D29" s="241"/>
+      <c r="F29" s="240">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="238"/>
+      <c r="G29" s="241"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36626,22 +36626,22 @@
       <c r="B31" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="237">
+      <c r="C31" s="240">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="F31" s="237">
+      <c r="D31" s="241"/>
+      <c r="F31" s="240">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="238"/>
+      <c r="G31" s="241"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36668,43 +36668,25 @@
       <c r="B33" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="237">
+      <c r="C33" s="240">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="F33" s="237">
+      <c r="D33" s="241"/>
+      <c r="F33" s="240">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="238"/>
+      <c r="G33" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36715,6 +36697,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6288DF1-C762-474E-83A9-C2E4BC6CF4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4EF581-00EE-3E4D-B6C6-9AFE394F7826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2365,6 +2365,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2372,12 +2378,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2398,14 +2398,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12764,11 +12764,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6906000000000001</v>
-    <v>-4.08</v>
-    <v>-2.2069999999999999E-2</v>
-    <v>0.68</v>
-    <v>3.761E-3</v>
+    <v>1.6831</v>
+    <v>-0.51</v>
+    <v>-2.898E-3</v>
+    <v>-0.11</v>
+    <v>-6.2679999999999995E-4</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12776,26 +12776,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>185.48</v>
+    <v>176.4</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46300.894140635937</v>
+    <v>46304.999839293749</v>
     <v>4</v>
-    <v>180.3</v>
-    <v>189829500000</v>
+    <v>171.79</v>
+    <v>184275000000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>185.07499999999999</v>
-    <v>21.396100000000001</v>
-    <v>184.87</v>
-    <v>180.79</v>
-    <v>181.47</v>
+    <v>176.4</v>
+    <v>20.370699999999999</v>
+    <v>176.01</v>
+    <v>175.5</v>
+    <v>175.39</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>12273142</v>
-    <v>13860225</v>
+    <v>7575243</v>
+    <v>13903112</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -12817,19 +12817,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>7</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13071,9 +13071,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC156</f>
-        <v>191998.97999999998</v>
+        <v>186381</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>109.89769708806385</v>
+        <v>111.00174930811593</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC157</f>
-        <v>198964.97999999998</v>
+        <v>193347</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>212.32000063580659</v>
+        <v>213.0628034773157</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>180.79</v>
+        <v>175.5</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>235</v>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>191.70491241625226</v>
+        <v>192.27270566264997</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -13751,14 +13751,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>181.47</v>
+        <v>175.39</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>20.43207480623721</v>
+        <v>19.834222736294212</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>180.75724971180603</v>
+        <v>181.38808888822939</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13775,14 +13775,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-4.08</v>
+        <v>-0.51</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>4.4081613642552417</v>
+        <v>4.279176499954616</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>203.94945298239475</v>
+        <v>204.66256268352114</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13799,14 +13799,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.68</v>
+        <v>-0.11</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC164</f>
-        <v>3.7364781833736829E-2</v>
+        <v>3.8491047907243767E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>179.72586256686469</v>
+        <v>180.47758200396643</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13823,14 +13823,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.2069999999999999E-2</v>
+        <v>-2.898E-3</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC165</f>
-        <v>4.8942655578704829E-2</v>
+        <v>5.0417907134325049E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-5.8860414466248168E-3</v>
+        <v>2.8362290620891354E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13847,14 +13847,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.761E-3</v>
+        <v>-6.2679999999999995E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC167</f>
-        <v>4.817733927544824E-2</v>
+        <v>4.962952232255434E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13870,14 +13870,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>1.985729299186902E-2</v>
+        <v>2.0455840455840455E-2</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>404</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>33.889771881632015</v>
+        <v>34.098881950831718</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6906000000000001</v>
+        <v>1.6831</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>96</v>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="I13" s="209">
         <f>'Reverse DCF'!C17</f>
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>13860225</v>
+        <v>13903112</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>97</v>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC179</f>
-        <v>-3.6281442745164587E-2</v>
+        <v>-3.7375054324206868E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18618,6 +18618,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18625,12 +18631,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19690,16 +19690,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>180.79</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19791,7 +19791,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>191998.97999999998</v>
+        <v>186381</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19809,7 +19809,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6906000000000001</v>
+        <v>1.6831</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.3672384550741751E-2</v>
+        <v>7.5724891024591998E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19870,7 +19870,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92632761544925823</v>
+        <v>0.92427510897540799</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19888,7 +19888,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.12884700000000002</v>
+        <v>0.1281795</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.1224682976008277</v>
+        <v>0.12167363385006769</v>
       </c>
     </row>
   </sheetData>
@@ -20148,7 +20148,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>166213.17578765977</v>
+        <v>167579.45923472667</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20202,23 +20202,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5621.5843749942233</v>
+        <v>5625.5670569347039</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3352.4164888166483</v>
+        <v>3357.1682944548088</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5217.0926869734749</v>
+        <v>5228.1888887014438</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7334.6435182592077</v>
+        <v>7355.4508977661635</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>8870.2231062447208</v>
+        <v>8901.688763072123</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20237,7 +20237,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>93281.394132235553</v>
+        <v>94381.793864289881</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1224682976008277</v>
+        <v>0.12167363385006769</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20275,7 +20275,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30395.960175288274</v>
+        <v>30468.063900929243</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>93281.394132235553</v>
+        <v>94381.793864289881</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>123677.35430752383</v>
+        <v>124849.85776521912</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20320,7 +20320,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>116711.35430752381</v>
+        <v>117883.85776521912</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20338,7 +20338,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C24/C25</f>
-        <v>109.89769708806385</v>
+        <v>111.00174930811593</v>
       </c>
     </row>
   </sheetData>
@@ -20607,23 +20607,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>5621.5843749942233</v>
+        <v>5625.5670569347039</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>3352.4164888166483</v>
+        <v>3357.1682944548088</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>5217.0926869734749</v>
+        <v>5228.1888887014438</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7334.6435182592077</v>
+        <v>7355.4508977661635</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>8870.2231062447208</v>
+        <v>8901.688763072123</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1224682976008277</v>
+        <v>0.12167363385006769</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>210924.10360618305</v>
+        <v>211672.32215505213</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>232449.84067522662</v>
+        <v>233238.69729290926</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21471,7 +21471,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>225483.84067522662</v>
+        <v>226272.69729290926</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21489,7 +21489,7 @@
       </c>
       <c r="C50" s="232">
         <f ca="1">C48/C49</f>
-        <v>212.32000063580659</v>
+        <v>213.0628034773157</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12884700000000002</v>
+        <v>0.1281795</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="C58" s="232">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>191.70491241625226</v>
+        <v>192.27270566264997</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1224682976008277</v>
+        <v>0.12167363385006769</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>177404.46212489443</v>
+        <v>178033.77526144247</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21607,7 +21607,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>198930.199193938</v>
+        <v>199600.1503992996</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>191964.199193938</v>
+        <v>192634.1503992996</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="C71" s="232">
         <f ca="1">C69/C70</f>
-        <v>180.75724971180603</v>
+        <v>181.38808888822939</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1224682976008277</v>
+        <v>0.12167363385006769</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>202034.58199825964</v>
+        <v>202751.26643204232</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>223560.31906730321</v>
+        <v>224317.64156989945</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21738,7 +21738,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>216594.31906730321</v>
+        <v>217351.64156989945</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21756,22 +21756,22 @@
       </c>
       <c r="C84" s="232">
         <f ca="1">C82/C83</f>
-        <v>203.94945298239475</v>
+        <v>204.66256268352114</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21821,7 +21821,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>109.89769708806385</v>
+        <v>111.00174930811593</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>212.32000063580659</v>
+        <v>213.0628034773157</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21839,7 +21839,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>191.70491241625226</v>
+        <v>192.27270566264997</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>180.75724971180603</v>
+        <v>181.38808888822939</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>203.94945298239475</v>
+        <v>204.66256268352114</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="C10" s="232">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>179.72586256686469</v>
+        <v>180.47758200396643</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>180.79</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21884,7 +21884,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-5.8860414466248168E-3</v>
+        <v>2.8362290620891354E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22354,7 +22354,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12884700000000002</v>
+        <v>0.1281795</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C23/(C24-C25)</f>
-        <v>33.889771881632015</v>
+        <v>34.098881950831718</v>
       </c>
     </row>
   </sheetData>
@@ -22560,23 +22560,23 @@
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>13442.409253731346</v>
+        <v>13324.493383084577</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>15324.346549253736</v>
+        <v>15056.677522885569</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>17469.755066149261</v>
+        <v>17014.045600860693</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>19915.520775410158</v>
+        <v>19225.871528972581</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>22703.693683967584</v>
+        <v>21725.234827739016</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22608,7 +22608,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>238757.48934666064</v>
+        <v>230345.80176192368</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22662,23 +22662,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11975.758498002351</v>
+        <v>11879.117936782706</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12162.806483624838</v>
+        <v>11967.298564814748</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12352.775950081397</v>
+        <v>12056.133772016849</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12545.71252764298</v>
+        <v>12145.62841743685</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12741.662559274451</v>
+        <v>12235.78739619209</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22697,15 +22697,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>133994.38017008521</v>
+        <v>129732.18841186768</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="248" t="s">
+      <c r="B14" s="249" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="249"/>
+      <c r="C14" s="250"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22713,7 +22713,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>180.79</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>179.81628208448689</v>
+        <v>174.33348047534375</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22730,22 +22730,22 @@
         <v>316</v>
       </c>
       <c r="C17" s="156">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E17" s="250" t="s">
+        <v>0.13</v>
+      </c>
+      <c r="E17" s="248" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="248" t="s">
+      <c r="B19" s="249" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="249"/>
+      <c r="C19" s="250"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.1224682976008277</v>
+        <v>0.12167363385006769</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22779,7 +22779,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>189829.5</v>
+        <v>184275</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22806,15 +22806,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>196795.5</v>
+        <v>191241</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="248" t="s">
+      <c r="B28" s="249" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="249"/>
+      <c r="C28" s="250"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>61778.716018626023</v>
+        <v>60283.966087243243</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22831,7 +22831,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>133994.38017008521</v>
+        <v>129732.18841186768</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>195773.09618871124</v>
+        <v>190016.15449911094</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22867,7 +22867,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>188807.09618871124</v>
+        <v>183050.15449911094</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22885,21 +22885,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>179.81628208448689</v>
+        <v>174.33348047534375</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29514,7 +29514,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>180.79</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>180.79</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31087,7 +31087,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>20.43207480623721</v>
+        <v>19.834222736294212</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31124,7 +31124,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.4081613642552417</v>
+        <v>4.279176499954616</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31185,7 +31185,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.8634572275652612</v>
+        <v>6.662629257357727</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31246,7 +31246,7 @@
       </c>
       <c r="AC156" s="141">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>191998.97999999998</v>
+        <v>186381</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31307,7 +31307,7 @@
       </c>
       <c r="AC157" s="141">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>198964.97999999998</v>
+        <v>193347</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31344,7 +31344,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="179">
         <f ca="1">AC157/AC5</f>
-        <v>4.5149537079059634</v>
+        <v>4.3874693655260053</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31381,7 +31381,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="179">
         <f ca="1">AC157/AC12</f>
-        <v>19.470102749779819</v>
+        <v>18.920344456404735</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31516,7 +31516,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>26.763169779760243</v>
+        <v>25.980066908279898</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31553,7 +31553,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>25.571391112822653</v>
+        <v>24.84935669327799</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31590,7 +31590,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>3.7364781833736829E-2</v>
+        <v>3.8491047907243767E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31627,7 +31627,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>4.8942655578704829E-2</v>
+        <v>5.0417907134325049E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31664,7 +31664,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="152">
         <f ca="1">AC82/AC116</f>
-        <v>1.985729299186902E-2</v>
+        <v>2.0455840455840455E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31701,7 +31701,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="152">
         <f ca="1">-AC63/AC156</f>
-        <v>4.817733927544824E-2</v>
+        <v>4.962952232255434E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31738,7 +31738,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="152">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>6.8099320110971431E-2</v>
+        <v>7.015200047215113E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32241,7 +32241,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="152">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.6281442745164587E-2</v>
+        <v>-3.7375054324206868E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33579,7 +33579,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>180.79</v>
+        <v>175.5</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33595,7 +33595,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>191998.97999999998</v>
+        <v>186381</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33615,7 +33615,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>198964.97999999998</v>
+        <v>193347</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>20.43207480623721</v>
+        <v>19.834222736294212</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33655,7 +33655,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.4081613642552417</v>
+        <v>4.279176499954616</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33675,7 +33675,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.8634572275652612</v>
+        <v>6.662629257357727</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33695,7 +33695,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.5149537079059634</v>
+        <v>4.3874693655260053</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33704,7 +33704,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>19.470102749779819</v>
+        <v>18.920344456404735</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33940,7 +33940,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>4.8942655578704829E-2</v>
+        <v>5.0417907134325049E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33956,7 +33956,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC164</f>
-        <v>3.7364781833736829E-2</v>
+        <v>3.8491047907243767E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33972,7 +33972,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>1.985729299186902E-2</v>
+        <v>2.0455840455840455E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.817733927544824E-2</v>
+        <v>4.962952232255434E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33997,7 +33997,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>6.8099320110971431E-2</v>
+        <v>7.015200047215113E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34041,7 +34041,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC179</f>
-        <v>-3.6281442745164587E-2</v>
+        <v>-3.7375054324206868E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC115</f>
-        <v>180.79</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34250,7 +34250,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>191998.97999999998</v>
+        <v>186381</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34279,7 +34279,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>198964.97999999998</v>
+        <v>193347</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>20.43207480623721</v>
+        <v>19.834222736294212</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34337,7 +34337,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.4081613642552417</v>
+        <v>4.279176499954616</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34366,7 +34366,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.8634572275652612</v>
+        <v>6.662629257357727</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34395,7 +34395,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.5149537079059634</v>
+        <v>4.3874693655260053</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34424,7 +34424,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>19.470102749779819</v>
+        <v>18.920344456404735</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>4.8942655578704829E-2</v>
+        <v>5.0417907134325049E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35226,7 +35226,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC164</f>
-        <v>3.7364781833736829E-2</v>
+        <v>3.8491047907243767E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35255,7 +35255,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>1.985729299186902E-2</v>
+        <v>2.0455840455840455E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35284,7 +35284,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.817733927544824E-2</v>
+        <v>4.962952232255434E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35313,7 +35313,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>6.8099320110971431E-2</v>
+        <v>7.015200047215113E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35549,7 +35549,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.6281442745164587E-2</v>
+        <v>-3.7375054324206868E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36087,14 +36087,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="239" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="F3" s="239" t="s">
+      <c r="D3" s="240"/>
+      <c r="F3" s="241" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="238"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36161,19 +36161,19 @@
       <c r="B7" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="240">
+      <c r="C7" s="237">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="241"/>
-      <c r="F7" s="240">
+      <c r="D7" s="238"/>
+      <c r="F7" s="237">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="241"/>
+      <c r="G7" s="238"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36200,19 +36200,19 @@
       <c r="B9" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="240">
+      <c r="C9" s="237">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="F9" s="240">
+      <c r="D9" s="238"/>
+      <c r="F9" s="237">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="241"/>
+      <c r="G9" s="238"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36239,19 +36239,19 @@
       <c r="B11" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="240">
+      <c r="C11" s="237">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="F11" s="240">
+      <c r="D11" s="238"/>
+      <c r="F11" s="237">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="241"/>
+      <c r="G11" s="238"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36278,19 +36278,19 @@
       <c r="B13" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="240">
+      <c r="C13" s="237">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="241"/>
-      <c r="F13" s="240">
+      <c r="D13" s="238"/>
+      <c r="F13" s="237">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="241"/>
+      <c r="G13" s="238"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36317,19 +36317,19 @@
       <c r="B15" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="240">
+      <c r="C15" s="237">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="241"/>
-      <c r="F15" s="240">
+      <c r="D15" s="238"/>
+      <c r="F15" s="237">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="241"/>
+      <c r="G15" s="238"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36356,19 +36356,19 @@
       <c r="B17" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="240">
+      <c r="C17" s="237">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="241"/>
-      <c r="F17" s="240">
+      <c r="D17" s="238"/>
+      <c r="F17" s="237">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="241"/>
+      <c r="G17" s="238"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36395,22 +36395,22 @@
       <c r="B19" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="240">
+      <c r="C19" s="237">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="241"/>
-      <c r="F19" s="240">
+      <c r="D19" s="238"/>
+      <c r="F19" s="237">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="241"/>
+      <c r="G19" s="238"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36437,22 +36437,22 @@
       <c r="B21" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="240">
+      <c r="C21" s="237">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="241"/>
-      <c r="F21" s="240">
+      <c r="D21" s="238"/>
+      <c r="F21" s="237">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="241"/>
+      <c r="G21" s="238"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36500,22 +36500,22 @@
       <c r="B25" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="240">
+      <c r="C25" s="237">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="241"/>
-      <c r="F25" s="240">
+      <c r="D25" s="238"/>
+      <c r="F25" s="237">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="241"/>
+      <c r="G25" s="238"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="218" t="s">
@@ -36542,22 +36542,22 @@
       <c r="B27" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="240">
+      <c r="C27" s="237">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="241"/>
-      <c r="F27" s="240">
+      <c r="D27" s="238"/>
+      <c r="F27" s="237">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="241"/>
+      <c r="G27" s="238"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="218" t="s">
@@ -36584,22 +36584,22 @@
       <c r="B29" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="240">
+      <c r="C29" s="237">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="241"/>
-      <c r="F29" s="240">
+      <c r="D29" s="238"/>
+      <c r="F29" s="237">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="241"/>
+      <c r="G29" s="238"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36626,22 +36626,22 @@
       <c r="B31" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="240">
+      <c r="C31" s="237">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="241"/>
-      <c r="F31" s="240">
+      <c r="D31" s="238"/>
+      <c r="F31" s="237">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="241"/>
+      <c r="G31" s="238"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36668,25 +36668,43 @@
       <c r="B33" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="240">
+      <c r="C33" s="237">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="241"/>
-      <c r="F33" s="240">
+      <c r="D33" s="238"/>
+      <c r="F33" s="237">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="241"/>
+      <c r="G33" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36697,24 +36715,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4EF581-00EE-3E4D-B6C6-9AFE394F7826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CAC794-62BA-714F-9C59-1CA23636227C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="437">
   <si>
     <t>Ticker</t>
   </si>
@@ -1438,6 +1438,30 @@
   </si>
   <si>
     <t>Reverse DCF rate</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1454,7 +1478,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1620,6 +1644,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2037,11 +2069,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2353,6 +2386,14 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2365,12 +2406,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2378,6 +2413,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2398,17 +2439,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -12765,10 +12807,10 @@
     <v>259.92</v>
     <v>121.99</v>
     <v>1.6831</v>
-    <v>-0.51</v>
-    <v>-2.898E-3</v>
-    <v>-0.11</v>
-    <v>-6.2679999999999995E-4</v>
+    <v>-1.07</v>
+    <v>-6.097E-3</v>
+    <v>-7.4999999999999997E-3</v>
+    <v>-4.3000000000000002E-5</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12776,26 +12818,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>176.4</v>
+    <v>175.23</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46304.999839293749</v>
+    <v>46307.863137082815</v>
     <v>4</v>
-    <v>171.79</v>
-    <v>184275000000</v>
+    <v>172.1601</v>
+    <v>183151500000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>176.4</v>
-    <v>20.370699999999999</v>
-    <v>176.01</v>
+    <v>175.185</v>
+    <v>20.311599999999999</v>
     <v>175.5</v>
-    <v>175.39</v>
+    <v>174.43</v>
+    <v>174.42250000000001</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>7575243</v>
-    <v>13903112</v>
+    <v>6451246</v>
+    <v>13926322</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -13071,9 +13113,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13643,7 +13685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I75"/>
+  <dimension ref="B1:K75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13655,25 +13697,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="238"/>
+      <c r="E2" s="237" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="238"/>
+      <c r="H2" s="237" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="234"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="238"/>
+      <c r="K2" s="132" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="181" t="s">
         <v>11</v>
       </c>
@@ -13686,7 +13733,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC156</f>
-        <v>186381</v>
+        <v>185244.66</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13694,10 +13741,13 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>111.00174930811593</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+        <v>111.05342524130505</v>
+      </c>
+      <c r="K3" s="235" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="181" t="s">
         <v>0</v>
       </c>
@@ -13710,7 +13760,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC157</f>
-        <v>193347</v>
+        <v>192210.66</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13718,16 +13768,19 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>213.0628034773157</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+        <v>213.09734232557355</v>
+      </c>
+      <c r="K4" s="235" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="181" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>175.5</v>
+        <v>174.43</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>235</v>
@@ -13744,21 +13797,24 @@
         <f ca="1">'AVG target price'!C7</f>
         <v>192.27270566264997</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="235" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>175.39</v>
+        <v>174.42250000000001</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>19.834222736294212</v>
+        <v>19.713296136135611</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13766,23 +13822,26 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>181.38808888822939</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+        <v>181.41742147090665</v>
+      </c>
+      <c r="K6" s="236" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="181" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.51</v>
+        <v>-1.07</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>4.279176499954616</v>
+        <v>4.2530869338295361</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13790,23 +13849,23 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>204.66256268352114</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+        <v>204.69572081264448</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.11</v>
+        <v>-7.4999999999999997E-3</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC164</f>
-        <v>3.8491047907243767E-2</v>
+        <v>3.8727162229669668E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13814,23 +13873,23 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>180.47758200396643</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+        <v>180.50732310261594</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="181" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.898E-3</v>
+        <v>-6.097E-3</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC165</f>
-        <v>5.0417907134325049E-2</v>
+        <v>5.0727183982537664E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13838,26 +13897,26 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>2.8362290620891354E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>3.4841042840199135E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-6.2679999999999995E-4</v>
+        <v>-4.3000000000000002E-5</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC167</f>
-        <v>4.962952232255434E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+        <v>4.9933963008704271E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="181" t="s">
         <v>7</v>
       </c>
@@ -13870,7 +13929,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>2.0455840455840455E-2</v>
+        <v>2.0581322020294671E-2</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>404</v>
@@ -13880,7 +13939,7 @@
         <v>34.098881950831718</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="181" t="s">
         <v>8</v>
       </c>
@@ -13896,7 +13955,7 @@
         <v>0.16596649641780117</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="181" t="s">
         <v>9</v>
       </c>
@@ -13919,13 +13978,13 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="182" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>13903112</v>
+        <v>13926322</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>97</v>
@@ -13935,16 +13994,16 @@
         <v>0.25062860459696928</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="181" t="s">
         <v>282</v>
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC179</f>
-        <v>-3.7375054324206868E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>-3.7604322845257727E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="182" t="s">
         <v>287</v>
       </c>
@@ -13952,12 +14011,16 @@
         <f>Statement!AC178</f>
         <v>-6.6342857142857143</v>
       </c>
+      <c r="H16" s="237" t="s">
+        <v>429</v>
+      </c>
+      <c r="I16" s="238"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="239" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="239"/>
       <c r="E17" s="180" t="s">
         <v>288</v>
       </c>
@@ -13965,6 +14028,13 @@
         <f>Statement!AC174</f>
         <v>9.4161958568738226E-4</v>
       </c>
+      <c r="H17" s="181" t="s">
+        <v>157</v>
+      </c>
+      <c r="I17" s="233">
+        <f ca="1">DCF!C15</f>
+        <v>0.12163676434665674</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="180" t="s">
@@ -13980,7 +14050,13 @@
         <f>Statement!AC147</f>
         <v>137.86178331838977</v>
       </c>
-      <c r="I18" s="50"/>
+      <c r="H18" s="182" t="s">
+        <v>430</v>
+      </c>
+      <c r="I18" s="234">
+        <f ca="1">Multiples!C54</f>
+        <v>0.1281795</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="180" t="s">
@@ -14030,14 +14106,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="239" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="239"/>
+      <c r="E25" s="237" t="s">
         <v>330</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="238"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -14378,13 +14454,14 @@
       <c r="H75" s="132"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14397,6 +14474,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{A7615854-1D09-9746-95EB-1A6F003C80AE}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{8D98D1EA-37AF-5C42-B65C-FF9794D53AFE}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{A5CDB327-BC87-4C42-A4CC-9A375364E5F6}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{9B0968EA-64F8-0248-ADB4-8F839DC9F0EF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14406,18 +14489,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="235" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="235" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="235" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="235" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="236" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>103</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{0B60C889-5E71-4040-9711-1E56BC33FBCA}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{A2661D6C-7355-7A4B-98B0-4B65804BC79C}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{CD1F50EC-B7ED-1E40-BD28-988C3B78B7D7}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{6EA355A0-DB8D-4246-B6DF-6448434F8A47}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{5650C899-7EB6-384E-82AF-650BFD0960D0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14454,36 +14576,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="236" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="236" t="s">
+      <c r="S2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="236"/>
-      <c r="U2" s="236"/>
-      <c r="V2" s="236"/>
-      <c r="W2" s="236"/>
-      <c r="X2" s="236"/>
-      <c r="Y2" s="236"/>
-      <c r="Z2" s="236"/>
-      <c r="AA2" s="236" t="s">
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
+      <c r="AA2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="236"/>
-      <c r="AC2" s="236"/>
+      <c r="AB2" s="240"/>
+      <c r="AC2" s="240"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14494,32 +14616,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="243" t="s">
+      <c r="S4" s="247" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
-      <c r="AA4" s="244"/>
-      <c r="AB4" s="244"/>
-      <c r="AC4" s="244"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
+      <c r="AA4" s="248"/>
+      <c r="AB4" s="248"/>
+      <c r="AC4" s="248"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15260,33 +15382,33 @@
       <c r="Q13" s="91"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="242" t="s">
+      <c r="C14" s="246" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="242"/>
-      <c r="E14" s="242"/>
-      <c r="F14" s="242"/>
-      <c r="G14" s="242"/>
-      <c r="H14" s="242"/>
-      <c r="I14" s="242"/>
-      <c r="J14" s="242"/>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="246"/>
+      <c r="G14" s="246"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="246"/>
+      <c r="L14" s="246"/>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
-      <c r="S14" s="243" t="s">
+      <c r="S14" s="247" t="s">
         <v>114</v>
       </c>
-      <c r="T14" s="244"/>
-      <c r="U14" s="244"/>
-      <c r="V14" s="244"/>
-      <c r="W14" s="244"/>
-      <c r="X14" s="244"/>
-      <c r="Y14" s="244"/>
-      <c r="Z14" s="244"/>
-      <c r="AA14" s="244"/>
-      <c r="AB14" s="244"/>
-      <c r="AC14" s="244"/>
+      <c r="T14" s="248"/>
+      <c r="U14" s="248"/>
+      <c r="V14" s="248"/>
+      <c r="W14" s="248"/>
+      <c r="X14" s="248"/>
+      <c r="Y14" s="248"/>
+      <c r="Z14" s="248"/>
+      <c r="AA14" s="248"/>
+      <c r="AB14" s="248"/>
+      <c r="AC14" s="248"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
@@ -15953,35 +16075,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="236" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="P2" s="236" t="s">
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="P2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="236"/>
-      <c r="U2" s="236"/>
-      <c r="V2" s="236"/>
-      <c r="W2" s="236"/>
-      <c r="X2" s="236" t="s">
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+      <c r="U2" s="240"/>
+      <c r="V2" s="240"/>
+      <c r="W2" s="240"/>
+      <c r="X2" s="240" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="236"/>
-      <c r="Z2" s="236"/>
+      <c r="Y2" s="240"/>
+      <c r="Z2" s="240"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -15990,31 +16112,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="P4" s="244" t="s">
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="P4" s="248" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="244"/>
-      <c r="S4" s="244"/>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
+      <c r="Q4" s="248"/>
+      <c r="R4" s="248"/>
+      <c r="S4" s="248"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="W4" s="248"/>
+      <c r="X4" s="248"/>
+      <c r="Y4" s="248"/>
+      <c r="Z4" s="248"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16209,32 +16331,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="242" t="s">
+      <c r="C9" s="246" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="242"/>
-      <c r="L9" s="242"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="244" t="s">
+      <c r="P9" s="248" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="244"/>
-      <c r="R9" s="244"/>
-      <c r="S9" s="244"/>
-      <c r="T9" s="244"/>
-      <c r="U9" s="244"/>
-      <c r="V9" s="244"/>
-      <c r="W9" s="244"/>
-      <c r="X9" s="244"/>
-      <c r="Y9" s="244"/>
-      <c r="Z9" s="244"/>
+      <c r="Q9" s="248"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16710,31 +16832,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="242" t="s">
+      <c r="C17" s="246" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="242"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="242"/>
-      <c r="K17" s="242"/>
-      <c r="L17" s="242"/>
-      <c r="P17" s="244" t="s">
+      <c r="D17" s="246"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="246"/>
+      <c r="G17" s="246"/>
+      <c r="H17" s="246"/>
+      <c r="I17" s="246"/>
+      <c r="J17" s="246"/>
+      <c r="K17" s="246"/>
+      <c r="L17" s="246"/>
+      <c r="P17" s="248" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="244"/>
-      <c r="R17" s="244"/>
-      <c r="S17" s="244"/>
-      <c r="T17" s="244"/>
-      <c r="U17" s="244"/>
-      <c r="V17" s="244"/>
-      <c r="W17" s="244"/>
-      <c r="X17" s="244"/>
-      <c r="Y17" s="244"/>
-      <c r="Z17" s="244"/>
+      <c r="Q17" s="248"/>
+      <c r="R17" s="248"/>
+      <c r="S17" s="248"/>
+      <c r="T17" s="248"/>
+      <c r="U17" s="248"/>
+      <c r="V17" s="248"/>
+      <c r="W17" s="248"/>
+      <c r="X17" s="248"/>
+      <c r="Y17" s="248"/>
+      <c r="Z17" s="248"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17212,60 +17334,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
-      <c r="F3" s="236"/>
-      <c r="G3" s="245"/>
-      <c r="H3" s="246" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="236"/>
-      <c r="J3" s="236"/>
-      <c r="K3" s="236"/>
-      <c r="L3" s="236"/>
-      <c r="P3" s="247"/>
-      <c r="Q3" s="247"/>
-      <c r="R3" s="247"/>
-      <c r="S3" s="247"/>
-      <c r="T3" s="247"/>
-      <c r="U3" s="247"/>
-      <c r="V3" s="247"/>
-      <c r="W3" s="247"/>
-      <c r="X3" s="247"/>
-      <c r="Y3" s="247"/>
-      <c r="Z3" s="247"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="246" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
-      <c r="P5" s="247"/>
-      <c r="Q5" s="247"/>
-      <c r="R5" s="247"/>
-      <c r="S5" s="247"/>
-      <c r="T5" s="247"/>
-      <c r="U5" s="247"/>
-      <c r="V5" s="247"/>
-      <c r="W5" s="247"/>
-      <c r="X5" s="247"/>
-      <c r="Y5" s="247"/>
-      <c r="Z5" s="247"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17451,30 +17573,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="242" t="s">
+      <c r="C11" s="246" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
-      <c r="F11" s="242"/>
-      <c r="G11" s="242"/>
-      <c r="H11" s="242"/>
-      <c r="I11" s="242"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="247"/>
-      <c r="Q11" s="247"/>
-      <c r="R11" s="247"/>
-      <c r="S11" s="247"/>
-      <c r="T11" s="247"/>
-      <c r="U11" s="247"/>
-      <c r="V11" s="247"/>
-      <c r="W11" s="247"/>
-      <c r="X11" s="247"/>
-      <c r="Y11" s="247"/>
-      <c r="Z11" s="247"/>
+      <c r="P11" s="251"/>
+      <c r="Q11" s="251"/>
+      <c r="R11" s="251"/>
+      <c r="S11" s="251"/>
+      <c r="T11" s="251"/>
+      <c r="U11" s="251"/>
+      <c r="V11" s="251"/>
+      <c r="W11" s="251"/>
+      <c r="X11" s="251"/>
+      <c r="Y11" s="251"/>
+      <c r="Z11" s="251"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17716,18 +17838,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="242" t="s">
+      <c r="C18" s="246" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="242"/>
-      <c r="I18" s="242"/>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17940,23 +18062,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="247"/>
-      <c r="C25" s="247"/>
+      <c r="B25" s="251"/>
+      <c r="C25" s="251"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="242" t="s">
+      <c r="C26" s="246" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="242"/>
-      <c r="E26" s="242"/>
-      <c r="F26" s="242"/>
-      <c r="G26" s="242"/>
-      <c r="H26" s="242"/>
-      <c r="I26" s="242"/>
-      <c r="J26" s="242"/>
-      <c r="K26" s="242"/>
-      <c r="L26" s="242"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18148,18 +18270,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="242" t="s">
+      <c r="C33" s="246" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="242"/>
-      <c r="E33" s="242"/>
-      <c r="F33" s="242"/>
-      <c r="G33" s="242"/>
-      <c r="H33" s="242"/>
-      <c r="I33" s="242"/>
-      <c r="J33" s="242"/>
-      <c r="K33" s="242"/>
-      <c r="L33" s="242"/>
+      <c r="D33" s="246"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246"/>
+      <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
+      <c r="I33" s="246"/>
+      <c r="J33" s="246"/>
+      <c r="K33" s="246"/>
+      <c r="L33" s="246"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18343,18 +18465,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="242" t="s">
+      <c r="C40" s="246" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="242"/>
-      <c r="E40" s="242"/>
-      <c r="F40" s="242"/>
-      <c r="G40" s="242"/>
-      <c r="H40" s="242"/>
-      <c r="I40" s="242"/>
-      <c r="J40" s="242"/>
-      <c r="K40" s="242"/>
-      <c r="L40" s="242"/>
+      <c r="D40" s="246"/>
+      <c r="E40" s="246"/>
+      <c r="F40" s="246"/>
+      <c r="G40" s="246"/>
+      <c r="H40" s="246"/>
+      <c r="I40" s="246"/>
+      <c r="J40" s="246"/>
+      <c r="K40" s="246"/>
+      <c r="L40" s="246"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18618,12 +18740,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18631,6 +18747,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18668,60 +18790,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="236" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
-      <c r="S2" s="247"/>
-      <c r="T2" s="247"/>
-      <c r="U2" s="247"/>
-      <c r="V2" s="247"/>
-      <c r="W2" s="247"/>
-      <c r="X2" s="247"/>
-      <c r="Y2" s="247"/>
-      <c r="Z2" s="247"/>
-      <c r="AA2" s="247"/>
-      <c r="AB2" s="247"/>
-      <c r="AC2" s="247"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
+      <c r="S2" s="251"/>
+      <c r="T2" s="251"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="251"/>
+      <c r="X2" s="251"/>
+      <c r="Y2" s="251"/>
+      <c r="Z2" s="251"/>
+      <c r="AA2" s="251"/>
+      <c r="AB2" s="251"/>
+      <c r="AC2" s="251"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="246" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="S4" s="247"/>
-      <c r="T4" s="247"/>
-      <c r="U4" s="247"/>
-      <c r="V4" s="247"/>
-      <c r="W4" s="247"/>
-      <c r="X4" s="247"/>
-      <c r="Y4" s="247"/>
-      <c r="Z4" s="247"/>
-      <c r="AA4" s="247"/>
-      <c r="AB4" s="247"/>
-      <c r="AC4" s="247"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="S4" s="251"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
+      <c r="AA4" s="251"/>
+      <c r="AB4" s="251"/>
+      <c r="AC4" s="251"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19084,18 +19206,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="242" t="s">
+      <c r="C13" s="246" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="E13" s="242"/>
-      <c r="F13" s="242"/>
-      <c r="G13" s="242"/>
-      <c r="H13" s="242"/>
-      <c r="I13" s="242"/>
-      <c r="J13" s="242"/>
-      <c r="K13" s="242"/>
-      <c r="L13" s="242"/>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="246"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="246"/>
+      <c r="I13" s="246"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
+      <c r="L13" s="246"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19188,18 +19310,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="242" t="s">
+      <c r="C18" s="246" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="242"/>
-      <c r="I18" s="242"/>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
+      <c r="G18" s="246"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19391,18 +19513,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="242" t="s">
+      <c r="C25" s="246" t="s">
         <v>254</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="E25" s="242"/>
-      <c r="F25" s="242"/>
-      <c r="G25" s="242"/>
-      <c r="H25" s="242"/>
-      <c r="I25" s="242"/>
-      <c r="J25" s="242"/>
-      <c r="K25" s="242"/>
-      <c r="L25" s="242"/>
+      <c r="D25" s="246"/>
+      <c r="E25" s="246"/>
+      <c r="F25" s="246"/>
+      <c r="G25" s="246"/>
+      <c r="H25" s="246"/>
+      <c r="I25" s="246"/>
+      <c r="J25" s="246"/>
+      <c r="K25" s="246"/>
+      <c r="L25" s="246"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19540,18 +19662,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="242" t="s">
+      <c r="C31" s="246" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="E31" s="242"/>
-      <c r="F31" s="242"/>
-      <c r="G31" s="242"/>
-      <c r="H31" s="242"/>
-      <c r="I31" s="242"/>
-      <c r="J31" s="242"/>
-      <c r="K31" s="242"/>
-      <c r="L31" s="242"/>
+      <c r="D31" s="246"/>
+      <c r="E31" s="246"/>
+      <c r="F31" s="246"/>
+      <c r="G31" s="246"/>
+      <c r="H31" s="246"/>
+      <c r="I31" s="246"/>
+      <c r="J31" s="246"/>
+      <c r="K31" s="246"/>
+      <c r="L31" s="246"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19690,16 +19812,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19713,18 +19835,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="235" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="235" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="235" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="235" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="236" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>156</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{6013F207-540F-1649-B587-D0A267965739}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{F21FBB04-AC52-A647-B388-217F84150366}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{58F574B5-5D83-0C4F-A190-CB17B6F437F0}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{23847DEB-9734-4F49-8199-B43CE4351C5D}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{475EE0E0-0A10-2346-A106-16E3CD679719}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19762,10 +19923,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="236" t="s">
+      <c r="B4" s="240" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="236"/>
+      <c r="C4" s="240"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19782,7 +19943,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>175.5</v>
+        <v>174.43</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19791,7 +19952,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>186381</v>
+        <v>185244.66</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19850,10 +20011,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="236" t="s">
+      <c r="B15" s="240" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="236"/>
+      <c r="C15" s="240"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19861,7 +20022,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.5724891024591998E-2</v>
+        <v>7.6154032827325441E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19870,7 +20031,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92427510897540799</v>
+        <v>0.92384596717267453</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19897,7 +20058,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.12167363385006769</v>
+        <v>0.12163676434665674</v>
       </c>
     </row>
   </sheetData>
@@ -19942,60 +20103,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
-      <c r="F3" s="236"/>
-      <c r="G3" s="245"/>
-      <c r="H3" s="246" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="236"/>
-      <c r="J3" s="236"/>
-      <c r="K3" s="236"/>
-      <c r="L3" s="236"/>
-      <c r="P3" s="247"/>
-      <c r="Q3" s="247"/>
-      <c r="R3" s="247"/>
-      <c r="S3" s="247"/>
-      <c r="T3" s="247"/>
-      <c r="U3" s="247"/>
-      <c r="V3" s="247"/>
-      <c r="W3" s="247"/>
-      <c r="X3" s="247"/>
-      <c r="Y3" s="247"/>
-      <c r="Z3" s="247"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="246" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
-      <c r="P5" s="247"/>
-      <c r="Q5" s="247"/>
-      <c r="R5" s="247"/>
-      <c r="S5" s="247"/>
-      <c r="T5" s="247"/>
-      <c r="U5" s="247"/>
-      <c r="V5" s="247"/>
-      <c r="W5" s="247"/>
-      <c r="X5" s="247"/>
-      <c r="Y5" s="247"/>
-      <c r="Z5" s="247"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20148,7 +20309,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>167579.45923472667</v>
+        <v>167643.39526865364</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20202,23 +20363,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5625.5670569347039</v>
+        <v>5625.7519758588933</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3357.1682944548088</v>
+        <v>3357.3890061257653</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5228.1888887014438</v>
+        <v>5228.7044755755487</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7355.4508977661635</v>
+        <v>7356.4180743155193</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>8901.688763072123</v>
+        <v>8903.1519035113542</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20237,14 +20398,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>94381.793864289881</v>
+        <v>94433.322170878877</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="236" t="s">
+      <c r="B13" s="240" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="236"/>
+      <c r="C13" s="240"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20260,14 +20421,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12167363385006769</v>
+        <v>0.12163676434665674</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="236" t="s">
+      <c r="B18" s="240" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="236"/>
+      <c r="C18" s="240"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20275,7 +20436,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30468.063900929243</v>
+        <v>30471.415435387084</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20284,7 +20445,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>94381.793864289881</v>
+        <v>94433.322170878877</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20293,7 +20454,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>124849.85776521912</v>
+        <v>124904.73760626596</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20320,7 +20481,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>117883.85776521912</v>
+        <v>117938.73760626596</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20338,7 +20499,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C24/C25</f>
-        <v>111.00174930811593</v>
+        <v>111.05342524130505</v>
       </c>
     </row>
   </sheetData>
@@ -20381,37 +20542,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="236" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="246" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20607,23 +20768,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>5625.5670569347039</v>
+        <v>5625.7519758588933</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>3357.1682944548088</v>
+        <v>3357.3890061257653</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>5228.1888887014438</v>
+        <v>5228.7044755755487</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7355.4508977661635</v>
+        <v>7356.4180743155193</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>8901.688763072123</v>
+        <v>8903.1519035113542</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20631,18 +20792,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="242" t="s">
+      <c r="C11" s="246" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
-      <c r="F11" s="242"/>
-      <c r="G11" s="242"/>
-      <c r="H11" s="242"/>
-      <c r="I11" s="242"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20836,18 +20997,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="242" t="s">
+      <c r="C17" s="246" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="242"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="242"/>
-      <c r="K17" s="242"/>
-      <c r="L17" s="242"/>
+      <c r="D17" s="246"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="246"/>
+      <c r="G17" s="246"/>
+      <c r="H17" s="246"/>
+      <c r="I17" s="246"/>
+      <c r="J17" s="246"/>
+      <c r="K17" s="246"/>
+      <c r="L17" s="246"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20981,18 +21142,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="242" t="s">
+      <c r="C22" s="246" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="242"/>
-      <c r="E22" s="242"/>
-      <c r="F22" s="242"/>
-      <c r="G22" s="242"/>
-      <c r="H22" s="242"/>
-      <c r="I22" s="242"/>
-      <c r="J22" s="242"/>
-      <c r="K22" s="242"/>
-      <c r="L22" s="242"/>
+      <c r="D22" s="246"/>
+      <c r="E22" s="246"/>
+      <c r="F22" s="246"/>
+      <c r="G22" s="246"/>
+      <c r="H22" s="246"/>
+      <c r="I22" s="246"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="246"/>
+      <c r="L22" s="246"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21076,18 +21237,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="242" t="s">
+      <c r="C27" s="246" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="E27" s="242"/>
-      <c r="F27" s="242"/>
-      <c r="G27" s="242"/>
-      <c r="H27" s="242"/>
-      <c r="I27" s="242"/>
-      <c r="J27" s="242"/>
-      <c r="K27" s="242"/>
-      <c r="L27" s="242"/>
+      <c r="D27" s="246"/>
+      <c r="E27" s="246"/>
+      <c r="F27" s="246"/>
+      <c r="G27" s="246"/>
+      <c r="H27" s="246"/>
+      <c r="I27" s="246"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="246"/>
+      <c r="L27" s="246"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21388,10 +21549,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="236" t="s">
+      <c r="B39" s="240" t="s">
         <v>197</v>
       </c>
-      <c r="C39" s="236"/>
+      <c r="C39" s="240"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21409,7 +21570,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12167363385006769</v>
+        <v>0.12163676434665674</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21435,7 +21596,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>211672.32215505213</v>
+        <v>211707.11401788337</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21444,7 +21605,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>233238.69729290926</v>
+        <v>233275.37754975911</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21471,7 +21632,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>226272.69729290926</v>
+        <v>226309.37754975911</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21489,14 +21650,14 @@
       </c>
       <c r="C50" s="232">
         <f ca="1">C48/C49</f>
-        <v>213.0628034773157</v>
+        <v>213.09734232557355</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="236" t="s">
+      <c r="B52" s="240" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="236"/>
+      <c r="C52" s="240"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21552,10 +21713,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="236" t="s">
+      <c r="B60" s="240" t="s">
         <v>314</v>
       </c>
-      <c r="C60" s="236"/>
+      <c r="C60" s="240"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21572,7 +21733,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12167363385006769</v>
+        <v>0.12163676434665674</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21598,7 +21759,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>178033.77526144247</v>
+        <v>178063.03807022711</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21607,7 +21768,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>199600.1503992996</v>
+        <v>199631.30160210285</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21634,7 +21795,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>192634.1503992996</v>
+        <v>192665.30160210285</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21652,14 +21813,14 @@
       </c>
       <c r="C71" s="232">
         <f ca="1">C69/C70</f>
-        <v>181.38808888822939</v>
+        <v>181.41742147090665</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="236" t="s">
+      <c r="B73" s="240" t="s">
         <v>425</v>
       </c>
-      <c r="C73" s="236"/>
+      <c r="C73" s="240"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21676,7 +21837,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12167363385006769</v>
+        <v>0.12163676434665674</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21702,7 +21863,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>202751.26643204232</v>
+        <v>202784.59197115269</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21711,7 +21872,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>224317.64156989945</v>
+        <v>224352.85550302843</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21738,7 +21899,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>217351.64156989945</v>
+        <v>217386.85550302843</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21756,22 +21917,22 @@
       </c>
       <c r="C84" s="232">
         <f ca="1">C82/C83</f>
-        <v>204.66256268352114</v>
+        <v>204.69572081264448</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21809,10 +21970,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="236" t="s">
+      <c r="B4" s="240" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="236"/>
+      <c r="C4" s="240"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21821,7 +21982,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>111.00174930811593</v>
+        <v>111.05342524130505</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21830,7 +21991,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>213.0628034773157</v>
+        <v>213.09734232557355</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21848,7 +22009,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>181.38808888822939</v>
+        <v>181.41742147090665</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21857,7 +22018,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>204.66256268352114</v>
+        <v>204.69572081264448</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21866,7 +22027,7 @@
       </c>
       <c r="C10" s="232">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>180.47758200396643</v>
+        <v>180.50732310261594</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21875,7 +22036,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>175.5</v>
+        <v>174.43</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21884,7 +22045,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>2.8362290620891354E-2</v>
+        <v>3.4841042840199135E-2</v>
       </c>
     </row>
   </sheetData>
@@ -21900,18 +22061,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="235" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="235" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="235" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="235" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="236" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{D8C6F701-2E1A-E545-95D1-2AD7393C3264}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{9E9045D6-501F-384A-9D9E-7B74D79E2D96}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{B98D5F18-FFFD-C142-9086-9E9FF795C5A7}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{47B06DF5-A147-CF48-8595-54FD84B437EC}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{0A8298A1-B259-BA46-AF50-A415354B561C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21940,37 +22140,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="236" t="s">
+      <c r="C2" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="240"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="236"/>
-      <c r="L2" s="236"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="240"/>
+      <c r="K2" s="240"/>
+      <c r="L2" s="240"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="246" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22083,18 +22283,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="242" t="s">
+      <c r="C9" s="246" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="242"/>
-      <c r="L9" s="242"/>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="246"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22215,18 +22415,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="242" t="s">
+      <c r="C14" s="246" t="s">
         <v>397</v>
       </c>
-      <c r="D14" s="242"/>
-      <c r="E14" s="242"/>
-      <c r="F14" s="242"/>
-      <c r="G14" s="242"/>
-      <c r="H14" s="242"/>
-      <c r="I14" s="242"/>
-      <c r="J14" s="242"/>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="246"/>
+      <c r="G14" s="246"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="246"/>
+      <c r="L14" s="246"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22316,10 +22516,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="236" t="s">
+      <c r="B20" s="240" t="s">
         <v>399</v>
       </c>
-      <c r="C20" s="236"/>
+      <c r="C20" s="240"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22420,60 +22620,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="240" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
-      <c r="F3" s="236"/>
-      <c r="G3" s="245"/>
-      <c r="H3" s="246" t="s">
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="236"/>
-      <c r="J3" s="236"/>
-      <c r="K3" s="236"/>
-      <c r="L3" s="236"/>
-      <c r="P3" s="247"/>
-      <c r="Q3" s="247"/>
-      <c r="R3" s="247"/>
-      <c r="S3" s="247"/>
-      <c r="T3" s="247"/>
-      <c r="U3" s="247"/>
-      <c r="V3" s="247"/>
-      <c r="W3" s="247"/>
-      <c r="X3" s="247"/>
-      <c r="Y3" s="247"/>
-      <c r="Z3" s="247"/>
+      <c r="I3" s="240"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="P3" s="251"/>
+      <c r="Q3" s="251"/>
+      <c r="R3" s="251"/>
+      <c r="S3" s="251"/>
+      <c r="T3" s="251"/>
+      <c r="U3" s="251"/>
+      <c r="V3" s="251"/>
+      <c r="W3" s="251"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="251"/>
+      <c r="Z3" s="251"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="246" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
-      <c r="P5" s="247"/>
-      <c r="Q5" s="247"/>
-      <c r="R5" s="247"/>
-      <c r="S5" s="247"/>
-      <c r="T5" s="247"/>
-      <c r="U5" s="247"/>
-      <c r="V5" s="247"/>
-      <c r="W5" s="247"/>
-      <c r="X5" s="247"/>
-      <c r="Y5" s="247"/>
-      <c r="Z5" s="247"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="P5" s="251"/>
+      <c r="Q5" s="251"/>
+      <c r="R5" s="251"/>
+      <c r="S5" s="251"/>
+      <c r="T5" s="251"/>
+      <c r="U5" s="251"/>
+      <c r="V5" s="251"/>
+      <c r="W5" s="251"/>
+      <c r="X5" s="251"/>
+      <c r="Y5" s="251"/>
+      <c r="Z5" s="251"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22608,7 +22808,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>230345.80176192368</v>
+        <v>230433.6848298345</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22662,23 +22862,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11879.117936782706</v>
+        <v>11879.508417188852</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>11967.298564814748</v>
+        <v>11968.085335757221</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12056.133772016849</v>
+        <v>12057.322708464562</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12145.62841743685</v>
+        <v>12147.225459840614</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12235.78739619209</v>
+        <v>12237.798551133777</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22697,15 +22897,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>129732.18841186768</v>
+        <v>129803.01647843908</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="249" t="s">
+      <c r="B14" s="252" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="250"/>
+      <c r="C14" s="253"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22713,7 +22913,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>175.5</v>
+        <v>174.43</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22722,7 +22922,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>174.33348047534375</v>
+        <v>174.40662566745152</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22732,20 +22932,20 @@
       <c r="C17" s="156">
         <v>0.13</v>
       </c>
-      <c r="E17" s="248" t="s">
+      <c r="E17" s="254" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="249" t="s">
+      <c r="B19" s="252" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="250"/>
+      <c r="C19" s="253"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22761,7 +22961,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12167363385006769</v>
+        <v>0.12163676434665674</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22779,7 +22979,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>184275</v>
+        <v>183151.5</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22806,15 +23006,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>191241</v>
+        <v>190117.5</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="249" t="s">
+      <c r="B28" s="252" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="250"/>
+      <c r="C28" s="253"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22822,7 +23022,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>60283.966087243243</v>
+        <v>60289.940472385024</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22831,7 +23031,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>129732.18841186768</v>
+        <v>129803.01647843908</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22840,7 +23040,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>190016.15449911094</v>
+        <v>190092.9569508241</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22867,7 +23067,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>183050.15449911094</v>
+        <v>183126.9569508241</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22885,21 +23085,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>174.33348047534375</v>
+        <v>174.40662566745152</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29514,7 +29714,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>175.5</v>
+        <v>174.43</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29585,7 +29785,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>175.5</v>
+        <v>174.43</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31087,7 +31287,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>19.834222736294212</v>
+        <v>19.713296136135611</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31124,7 +31324,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.279176499954616</v>
+        <v>4.2530869338295361</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31185,7 +31385,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.662629257357727</v>
+        <v>6.6220080989225547</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31246,7 +31446,7 @@
       </c>
       <c r="AC156" s="141">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>186381</v>
+        <v>185244.66</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31307,7 +31507,7 @@
       </c>
       <c r="AC157" s="141">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>193347</v>
+        <v>192210.66</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31344,7 +31544,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="179">
         <f ca="1">AC157/AC5</f>
-        <v>4.3874693655260053</v>
+        <v>4.361683307615503</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31381,7 +31581,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="179">
         <f ca="1">AC157/AC12</f>
-        <v>18.920344456404735</v>
+        <v>18.809145708973482</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31516,7 +31716,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>25.980066908279898</v>
+        <v>25.821669919152495</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31553,7 +31753,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>24.84935669327799</v>
+        <v>24.703311924107332</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31590,7 +31790,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>3.8491047907243767E-2</v>
+        <v>3.8727162229669668E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31627,7 +31827,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.0417907134325049E-2</v>
+        <v>5.0727183982537664E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31664,7 +31864,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="152">
         <f ca="1">AC82/AC116</f>
-        <v>2.0455840455840455E-2</v>
+        <v>2.0581322020294671E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31701,7 +31901,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="152">
         <f ca="1">-AC63/AC156</f>
-        <v>4.962952232255434E-2</v>
+        <v>4.9933963008704271E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31738,7 +31938,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="152">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>7.015200047215113E-2</v>
+        <v>7.0582331496087392E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32241,7 +32441,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="152">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.7375054324206868E-2</v>
+        <v>-3.7604322845257727E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33528,18 +33728,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="235" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="235" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="235" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="235" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="236" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>224</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{E411EA5B-4A5D-2140-BD20-77381ABB5A05}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{AAC82E31-33A4-924A-A4E3-C89D89A459B8}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{14C87523-0D9F-614F-B4ED-B1D1A71B3419}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{B0BCF9F6-882B-E44A-BD88-3E4DCC55A596}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{3873FC78-7731-A447-9EFD-0C47FAD2FC58}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -33563,15 +33802,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="236" t="s">
+      <c r="B4" s="240" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="236"/>
-      <c r="E4" s="236" t="s">
+      <c r="C4" s="240"/>
+      <c r="E4" s="240" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33579,7 +33818,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>175.5</v>
+        <v>174.43</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33595,7 +33834,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>186381</v>
+        <v>185244.66</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33615,7 +33854,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>193347</v>
+        <v>192210.66</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33635,7 +33874,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>19.834222736294212</v>
+        <v>19.713296136135611</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33655,7 +33894,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.279176499954616</v>
+        <v>4.2530869338295361</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33675,7 +33914,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.662629257357727</v>
+        <v>6.6220080989225547</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33695,7 +33934,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.3874693655260053</v>
+        <v>4.361683307615503</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33704,18 +33943,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>18.920344456404735</v>
+        <v>18.809145708973482</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="236" t="s">
+      <c r="B15" s="240" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="236"/>
-      <c r="E15" s="236" t="s">
+      <c r="C15" s="240"/>
+      <c r="E15" s="240" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="236"/>
+      <c r="F15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33766,14 +34005,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="236" t="s">
+      <c r="B21" s="240" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="236"/>
-      <c r="E21" s="236" t="s">
+      <c r="C21" s="240"/>
+      <c r="E21" s="240" t="s">
         <v>241</v>
       </c>
-      <c r="F21" s="236"/>
+      <c r="F21" s="240"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33842,14 +34081,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="236" t="s">
+      <c r="B29" s="240" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="236"/>
-      <c r="E29" s="236" t="s">
+      <c r="C29" s="240"/>
+      <c r="E29" s="240" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="236"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33925,14 +34164,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="236" t="s">
+      <c r="B37" s="240" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="236"/>
-      <c r="E37" s="236" t="s">
+      <c r="C37" s="240"/>
+      <c r="E37" s="240" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="236"/>
+      <c r="F37" s="240"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33940,7 +34179,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>5.0417907134325049E-2</v>
+        <v>5.0727183982537664E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -33956,7 +34195,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC164</f>
-        <v>3.8491047907243767E-2</v>
+        <v>3.8727162229669668E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -33972,7 +34211,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>2.0455840455840455E-2</v>
+        <v>2.0581322020294671E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -33988,7 +34227,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.962952232255434E-2</v>
+        <v>4.9933963008704271E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33997,18 +34236,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>7.015200047215113E-2</v>
+        <v>7.0582331496087392E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="236" t="s">
+      <c r="B45" s="240" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="236"/>
-      <c r="E45" s="236" t="s">
+      <c r="C45" s="240"/>
+      <c r="E45" s="240" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="236"/>
+      <c r="F45" s="240"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34041,18 +34280,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC179</f>
-        <v>-3.7375054324206868E-2</v>
+        <v>-3.7604322845257727E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="236" t="s">
+      <c r="B51" s="240" t="s">
         <v>274</v>
       </c>
-      <c r="C51" s="236"/>
-      <c r="E51" s="236" t="s">
+      <c r="C51" s="240"/>
+      <c r="E51" s="240" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="236"/>
+      <c r="F51" s="240"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34221,7 +34460,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC115</f>
-        <v>175.5</v>
+        <v>174.43</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34250,7 +34489,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>186381</v>
+        <v>185244.66</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34279,7 +34518,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>193347</v>
+        <v>192210.66</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34308,7 +34547,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>19.834222736294212</v>
+        <v>19.713296136135611</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34337,7 +34576,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.279176499954616</v>
+        <v>4.2530869338295361</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34366,7 +34605,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.662629257357727</v>
+        <v>6.6220080989225547</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34395,7 +34634,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.3874693655260053</v>
+        <v>4.361683307615503</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34424,7 +34663,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>18.920344456404735</v>
+        <v>18.809145708973482</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35197,7 +35436,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>5.0417907134325049E-2</v>
+        <v>5.0727183982537664E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35226,7 +35465,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC164</f>
-        <v>3.8491047907243767E-2</v>
+        <v>3.8727162229669668E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35255,7 +35494,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>2.0455840455840455E-2</v>
+        <v>2.0581322020294671E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35284,7 +35523,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.962952232255434E-2</v>
+        <v>4.9933963008704271E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35313,7 +35552,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>7.015200047215113E-2</v>
+        <v>7.0582331496087392E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35549,7 +35788,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.7375054324206868E-2</v>
+        <v>-3.7604322845257727E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36087,14 +36326,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="241" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="F3" s="241" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="240"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36161,19 +36400,19 @@
       <c r="B7" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="237">
+      <c r="C7" s="244">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="238"/>
-      <c r="F7" s="237">
+      <c r="D7" s="245"/>
+      <c r="F7" s="244">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="238"/>
+      <c r="G7" s="245"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36200,19 +36439,19 @@
       <c r="B9" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="237">
+      <c r="C9" s="244">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="238"/>
-      <c r="F9" s="237">
+      <c r="D9" s="245"/>
+      <c r="F9" s="244">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="238"/>
+      <c r="G9" s="245"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36239,19 +36478,19 @@
       <c r="B11" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="237">
+      <c r="C11" s="244">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="238"/>
-      <c r="F11" s="237">
+      <c r="D11" s="245"/>
+      <c r="F11" s="244">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="238"/>
+      <c r="G11" s="245"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36278,19 +36517,19 @@
       <c r="B13" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="237">
+      <c r="C13" s="244">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="238"/>
-      <c r="F13" s="237">
+      <c r="D13" s="245"/>
+      <c r="F13" s="244">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="238"/>
+      <c r="G13" s="245"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36317,19 +36556,19 @@
       <c r="B15" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="237">
+      <c r="C15" s="244">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="238"/>
-      <c r="F15" s="237">
+      <c r="D15" s="245"/>
+      <c r="F15" s="244">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="238"/>
+      <c r="G15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36356,19 +36595,19 @@
       <c r="B17" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="237">
+      <c r="C17" s="244">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="238"/>
-      <c r="F17" s="237">
+      <c r="D17" s="245"/>
+      <c r="F17" s="244">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="238"/>
+      <c r="G17" s="245"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36395,22 +36634,22 @@
       <c r="B19" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="237">
+      <c r="C19" s="244">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="238"/>
-      <c r="F19" s="237">
+      <c r="D19" s="245"/>
+      <c r="F19" s="244">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="238"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36437,22 +36676,22 @@
       <c r="B21" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="237">
+      <c r="C21" s="244">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="238"/>
-      <c r="F21" s="237">
+      <c r="D21" s="245"/>
+      <c r="F21" s="244">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="238"/>
+      <c r="G21" s="245"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36500,22 +36739,22 @@
       <c r="B25" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="237">
+      <c r="C25" s="244">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="F25" s="237">
+      <c r="D25" s="245"/>
+      <c r="F25" s="244">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="238"/>
+      <c r="G25" s="245"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="218" t="s">
@@ -36542,22 +36781,22 @@
       <c r="B27" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="237">
+      <c r="C27" s="244">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="238"/>
-      <c r="F27" s="237">
+      <c r="D27" s="245"/>
+      <c r="F27" s="244">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="238"/>
+      <c r="G27" s="245"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="218" t="s">
@@ -36584,22 +36823,22 @@
       <c r="B29" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="237">
+      <c r="C29" s="244">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="238"/>
-      <c r="F29" s="237">
+      <c r="D29" s="245"/>
+      <c r="F29" s="244">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="238"/>
+      <c r="G29" s="245"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36626,22 +36865,22 @@
       <c r="B31" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="237">
+      <c r="C31" s="244">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="238"/>
-      <c r="F31" s="237">
+      <c r="D31" s="245"/>
+      <c r="F31" s="244">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="238"/>
+      <c r="G31" s="245"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36668,43 +36907,25 @@
       <c r="B33" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="237">
+      <c r="C33" s="244">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="238"/>
-      <c r="F33" s="237">
+      <c r="D33" s="245"/>
+      <c r="F33" s="244">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="238"/>
+      <c r="G33" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36715,6 +36936,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CAC794-62BA-714F-9C59-1CA23636227C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207FDF5F-5718-E44C-9596-228E06FA92C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -12806,11 +12806,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6831</v>
-    <v>-1.07</v>
-    <v>-6.097E-3</v>
-    <v>-7.4999999999999997E-3</v>
-    <v>-4.3000000000000002E-5</v>
+    <v>1.6911</v>
+    <v>5.78</v>
+    <v>3.3484E-2</v>
+    <v>-0.95</v>
+    <v>-5.3249999999999999E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12818,26 +12818,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>175.23</v>
+    <v>179.208</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46307.863137082815</v>
+    <v>46310.908339305468</v>
     <v>4</v>
-    <v>172.1601</v>
-    <v>183151500000</v>
+    <v>168.84</v>
+    <v>187320000000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>175.185</v>
-    <v>20.311599999999999</v>
-    <v>175.5</v>
-    <v>174.43</v>
-    <v>174.42250000000001</v>
+    <v>169.31</v>
+    <v>20.647200000000002</v>
+    <v>172.62</v>
+    <v>178.4</v>
+    <v>177.45</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>6451246</v>
-    <v>13926322</v>
+    <v>11778660</v>
+    <v>13164456</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -12861,17 +12861,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>-0.27</v>
+    <v>-5.1749999999999999E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>53.29</v>
     <v>Index</v>
     <v>7</v>
-    <v>52.34</v>
+    <v>51.77</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.96</v>
+    <v>52.17</v>
+    <v>51.9</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13733,7 +13733,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC156</f>
-        <v>185244.66</v>
+        <v>189460.80000000002</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13741,7 +13741,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>111.05342524130505</v>
+        <v>111.09807910466851</v>
       </c>
       <c r="K3" s="235" t="s">
         <v>432</v>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC157</f>
-        <v>192210.66</v>
+        <v>196426.80000000002</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>213.09734232557355</v>
+        <v>213.12717145756969</v>
       </c>
       <c r="K4" s="235" t="s">
         <v>433</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>174.43</v>
+        <v>178.4</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>235</v>
@@ -13795,7 +13795,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>192.27270566264997</v>
+        <v>192.42616377251687</v>
       </c>
       <c r="K5" s="235" t="s">
         <v>434</v>
@@ -13807,14 +13807,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>174.42250000000001</v>
+        <v>177.45</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>19.713296136135611</v>
+        <v>20.161967727378276</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>181.41742147090665</v>
+        <v>181.44275425076793</v>
       </c>
       <c r="K6" s="236" t="s">
         <v>435</v>
@@ -13834,14 +13834,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.07</v>
+        <v>5.78</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>4.2530869338295361</v>
+        <v>4.3498865389852046</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13849,7 +13849,7 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>204.69572081264448</v>
+        <v>204.7243574969385</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13858,14 +13858,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-7.4999999999999997E-3</v>
+        <v>-0.95</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC164</f>
-        <v>3.8727162229669668E-2</v>
+        <v>3.7865352621756054E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13873,7 +13873,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>180.50732310261594</v>
+        <v>180.56370521649234</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13882,14 +13882,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-6.097E-3</v>
+        <v>3.3484E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC165</f>
-        <v>5.0727183982537664E-2</v>
+        <v>4.9598333531805185E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>3.4841042840199135E-2</v>
+        <v>1.2128392469127421E-2</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13906,14 +13906,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-4.3000000000000002E-5</v>
+        <v>-5.3249999999999999E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC167</f>
-        <v>4.9933963008704271E-2</v>
+        <v>4.8822764392423126E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13929,14 +13929,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>2.0581322020294671E-2</v>
+        <v>2.0123318385650221E-2</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>404</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>34.098881950831718</v>
+        <v>34.155713683859652</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6831</v>
+        <v>1.6911</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>96</v>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>13926322</v>
+        <v>13164456</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>97</v>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC179</f>
-        <v>-3.7604322845257727E-2</v>
+        <v>-3.6767500190012917E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="I17" s="233">
         <f ca="1">DCF!C15</f>
-        <v>0.12163676434665674</v>
+        <v>0.12160492812805888</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="I18" s="234">
         <f ca="1">Multiples!C54</f>
-        <v>0.1281795</v>
+        <v>0.12799949999999999</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>174.43</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19952,7 +19952,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>185244.66</v>
+        <v>189460.80000000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6831</v>
+        <v>1.6911</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.6154032827325441E-2</v>
+        <v>7.4585748700244411E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92384596717267453</v>
+        <v>0.92541425129975563</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1281795</v>
+        <v>0.12799949999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.12163676434665674</v>
+        <v>0.12160492812805888</v>
       </c>
     </row>
   </sheetData>
@@ -20309,7 +20309,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>167643.39526865364</v>
+        <v>167698.64226155225</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20363,23 +20363,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5625.7519758588933</v>
+        <v>5625.9116601338001</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3357.3890061257653</v>
+        <v>3357.5796045880193</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5228.7044755755487</v>
+        <v>5229.1497310291052</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7356.4180743155193</v>
+        <v>7357.2533434900042</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>8903.1519035113542</v>
+        <v>8904.4155337537304</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20398,7 +20398,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>94433.322170878877</v>
+        <v>94477.850136163295</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12163676434665674</v>
+        <v>0.12160492812805888</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20436,7 +20436,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30471.415435387084</v>
+        <v>30474.309872994658</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>94433.322170878877</v>
+        <v>94477.850136163295</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>124904.73760626596</v>
+        <v>124952.16000915796</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>117938.73760626596</v>
+        <v>117986.16000915796</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C24/C25</f>
-        <v>111.05342524130505</v>
+        <v>111.09807910466851</v>
       </c>
     </row>
   </sheetData>
@@ -20768,23 +20768,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>5625.7519758588933</v>
+        <v>5625.9116601338001</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>3357.3890061257653</v>
+        <v>3357.5796045880193</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>5228.7044755755487</v>
+        <v>5229.1497310291052</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7356.4180743155193</v>
+        <v>7357.2533434900042</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>8903.1519035113542</v>
+        <v>8904.4155337537304</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21570,7 +21570,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12163676434665674</v>
+        <v>0.12160492812805888</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>211707.11401788337</v>
+        <v>211737.16174869807</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21605,7 +21605,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>233275.37754975911</v>
+        <v>233307.05608793901</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21632,7 +21632,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>226309.37754975911</v>
+        <v>226341.05608793901</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C50" s="232">
         <f ca="1">C48/C49</f>
-        <v>213.09734232557355</v>
+        <v>213.12717145756969</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21674,7 +21674,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1281795</v>
+        <v>0.12799949999999999</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="C58" s="232">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>192.27270566264997</v>
+        <v>192.42616377251687</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21733,7 +21733,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12163676434665674</v>
+        <v>0.12160492812805888</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>178063.03807022711</v>
+        <v>178088.31067507464</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21768,7 +21768,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>199631.30160210285</v>
+        <v>199658.20501431555</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21795,7 +21795,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>192665.30160210285</v>
+        <v>192692.20501431555</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="C71" s="232">
         <f ca="1">C69/C70</f>
-        <v>181.41742147090665</v>
+        <v>181.44275425076793</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12163676434665674</v>
+        <v>0.12160492812805888</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>202784.59197115269</v>
+        <v>202813.37332250777</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21872,7 +21872,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>224352.85550302843</v>
+        <v>224383.26766174869</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>217386.85550302843</v>
+        <v>217417.26766174869</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21917,7 +21917,7 @@
       </c>
       <c r="C84" s="232">
         <f ca="1">C82/C83</f>
-        <v>204.69572081264448</v>
+        <v>204.7243574969385</v>
       </c>
     </row>
   </sheetData>
@@ -21982,7 +21982,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>111.05342524130505</v>
+        <v>111.09807910466851</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>213.09734232557355</v>
+        <v>213.12717145756969</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22000,7 +22000,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>192.27270566264997</v>
+        <v>192.42616377251687</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22009,7 +22009,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>181.41742147090665</v>
+        <v>181.44275425076793</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22018,7 +22018,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>204.69572081264448</v>
+        <v>204.7243574969385</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="C10" s="232">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>180.50732310261594</v>
+        <v>180.56370521649234</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>174.43</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22045,7 +22045,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>3.4841042840199135E-2</v>
+        <v>1.2128392469127421E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22554,7 +22554,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1281795</v>
+        <v>0.12799949999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22571,7 +22571,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C23/(C24-C25)</f>
-        <v>34.098881950831718</v>
+        <v>34.155713683859652</v>
       </c>
     </row>
   </sheetData>
@@ -22808,7 +22808,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>230433.6848298345</v>
+        <v>230509.62440460268</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22862,23 +22862,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11879.508417188852</v>
+        <v>11879.845611344583</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>11968.085335757221</v>
+        <v>11968.764762137947</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12057.322708464562</v>
+        <v>12058.349461595537</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12147.225459840614</v>
+        <v>12148.604691265422</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12237.798551133777</v>
+        <v>12239.535469981945</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22897,7 +22897,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>129803.01647843908</v>
+        <v>129864.22224859198</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>174.43</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22922,7 +22922,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>174.40662566745152</v>
+        <v>174.46983070944515</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22961,7 +22961,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12163676434665674</v>
+        <v>0.12160492812805888</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22979,7 +22979,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>183151.5</v>
+        <v>187320</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>190117.5</v>
+        <v>194286</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23022,7 +23022,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>60289.940472385024</v>
+        <v>60295.099996325429</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23031,7 +23031,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>129803.01647843908</v>
+        <v>129864.22224859198</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23040,7 +23040,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>190092.9569508241</v>
+        <v>190159.32224491739</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23067,7 +23067,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>183126.9569508241</v>
+        <v>183193.32224491739</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>174.40662566745152</v>
+        <v>174.46983070944515</v>
       </c>
     </row>
   </sheetData>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>174.43</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29785,7 +29785,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>174.43</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31287,7 +31287,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>19.713296136135611</v>
+        <v>20.161967727378276</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31324,7 +31324,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.2530869338295361</v>
+        <v>4.3498865389852046</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31385,7 +31385,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.6220080989225547</v>
+        <v>6.772723985826886</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31446,7 +31446,7 @@
       </c>
       <c r="AC156" s="141">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>185244.66</v>
+        <v>189460.80000000002</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31507,7 +31507,7 @@
       </c>
       <c r="AC157" s="141">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>192210.66</v>
+        <v>196426.80000000002</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31544,7 +31544,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="179">
         <f ca="1">AC157/AC5</f>
-        <v>4.361683307615503</v>
+        <v>4.457356812199329</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31581,7 +31581,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="179">
         <f ca="1">AC157/AC12</f>
-        <v>18.809145708973482</v>
+        <v>19.221724239162345</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31716,7 +31716,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>25.821669919152495</v>
+        <v>26.409367159185951</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31753,7 +31753,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>24.703311924107332</v>
+        <v>25.245178964862024</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31790,7 +31790,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>3.8727162229669668E-2</v>
+        <v>3.7865352621756054E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31827,7 +31827,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.0727183982537664E-2</v>
+        <v>4.9598333531805185E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31864,7 +31864,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="152">
         <f ca="1">AC82/AC116</f>
-        <v>2.0581322020294671E-2</v>
+        <v>2.0123318385650221E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31901,7 +31901,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="152">
         <f ca="1">-AC63/AC156</f>
-        <v>4.9933963008704271E-2</v>
+        <v>4.8822764392423126E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31938,7 +31938,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="152">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>7.0582331496087392E-2</v>
+        <v>6.9011637235776468E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32441,7 +32441,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="152">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.7604322845257727E-2</v>
+        <v>-3.6767500190012917E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33818,7 +33818,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>174.43</v>
+        <v>178.4</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33834,7 +33834,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>185244.66</v>
+        <v>189460.80000000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33854,7 +33854,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>192210.66</v>
+        <v>196426.80000000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>19.713296136135611</v>
+        <v>20.161967727378276</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33894,7 +33894,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.2530869338295361</v>
+        <v>4.3498865389852046</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33914,7 +33914,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.6220080989225547</v>
+        <v>6.772723985826886</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33934,7 +33934,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.361683307615503</v>
+        <v>4.457356812199329</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>18.809145708973482</v>
+        <v>19.221724239162345</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34179,7 +34179,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>5.0727183982537664E-2</v>
+        <v>4.9598333531805185E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -34195,7 +34195,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC164</f>
-        <v>3.8727162229669668E-2</v>
+        <v>3.7865352621756054E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -34211,7 +34211,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>2.0581322020294671E-2</v>
+        <v>2.0123318385650221E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -34227,7 +34227,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.9933963008704271E-2</v>
+        <v>4.8822764392423126E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34236,7 +34236,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>7.0582331496087392E-2</v>
+        <v>6.9011637235776468E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34280,7 +34280,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC179</f>
-        <v>-3.7604322845257727E-2</v>
+        <v>-3.6767500190012917E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34460,7 +34460,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC115</f>
-        <v>174.43</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34489,7 +34489,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>185244.66</v>
+        <v>189460.80000000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34518,7 +34518,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>192210.66</v>
+        <v>196426.80000000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34547,7 +34547,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>19.713296136135611</v>
+        <v>20.161967727378276</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34576,7 +34576,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.2530869338295361</v>
+        <v>4.3498865389852046</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34605,7 +34605,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.6220080989225547</v>
+        <v>6.772723985826886</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34634,7 +34634,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.361683307615503</v>
+        <v>4.457356812199329</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34663,7 +34663,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>18.809145708973482</v>
+        <v>19.221724239162345</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>5.0727183982537664E-2</v>
+        <v>4.9598333531805185E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35465,7 +35465,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC164</f>
-        <v>3.8727162229669668E-2</v>
+        <v>3.7865352621756054E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35494,7 +35494,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>2.0581322020294671E-2</v>
+        <v>2.0123318385650221E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35523,7 +35523,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.9933963008704271E-2</v>
+        <v>4.8822764392423126E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35552,7 +35552,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>7.0582331496087392E-2</v>
+        <v>6.9011637235776468E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35788,7 +35788,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.7604322845257727E-2</v>
+        <v>-3.6767500190012917E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207FDF5F-5718-E44C-9596-228E06FA92C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E93F3C-87CB-894D-9E92-247AD2773980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -118,7 +118,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -129,7 +129,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -139,19 +160,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="438">
   <si>
     <t>Ticker</t>
   </si>
@@ -1462,6 +1492,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2074,7 +2107,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2406,6 +2439,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2413,12 +2452,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2439,15 +2472,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12767,7 +12803,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12806,11 +12842,9 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6911</v>
-    <v>5.78</v>
-    <v>3.3484E-2</v>
-    <v>-0.95</v>
-    <v>-5.3249999999999999E-3</v>
+    <v>1.6930000000000001</v>
+    <v>1.87</v>
+    <v>1.0775999999999999E-2</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12818,36 +12852,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>179.208</v>
+    <v>176.41</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46310.908339305468</v>
+    <v>46315.727168217185</v>
     <v>4</v>
-    <v>168.84</v>
-    <v>187320000000</v>
+    <v>171.13</v>
+    <v>184170000000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>169.31</v>
-    <v>20.647200000000002</v>
-    <v>172.62</v>
-    <v>178.4</v>
-    <v>177.45</v>
+    <v>171.54</v>
+    <v>20.3</v>
+    <v>173.53</v>
+    <v>175.4</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>11778660</v>
-    <v>13164456</v>
+    <v>3141977</v>
+    <v>12922531</v>
     <v>1991</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12861,28 +12909,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-0.27</v>
-    <v>-5.1749999999999999E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>53.29</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>7</v>
-    <v>51.77</v>
+    <v>10</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.96</v>
-    <v>52.17</v>
-    <v>51.9</v>
+    <v>50.9</v>
+    <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12916,8 +12964,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12939,7 +12985,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12949,6 +12994,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12984,7 +13034,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12995,16 +13045,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13105,19 +13152,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13198,9 +13239,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13208,9 +13246,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13695,7 +13730,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -13733,7 +13768,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC156</f>
-        <v>189460.80000000002</v>
+        <v>186274.80000000002</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13741,7 +13776,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>111.09807910466851</v>
+        <v>111.8333625834032</v>
       </c>
       <c r="K3" s="235" t="s">
         <v>432</v>
@@ -13760,7 +13795,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC157</f>
-        <v>196426.80000000002</v>
+        <v>193240.80000000002</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13768,7 +13803,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>213.12717145756969</v>
+        <v>213.61617753938933</v>
       </c>
       <c r="K4" s="235" t="s">
         <v>433</v>
@@ -13780,7 +13815,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>178.4</v>
+        <v>175.4</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>235</v>
@@ -13795,7 +13830,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>192.42616377251687</v>
+        <v>192.81430006053344</v>
       </c>
       <c r="K5" s="235" t="s">
         <v>434</v>
@@ -13805,16 +13840,16 @@
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="204" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>177.45</v>
+      <c r="C6" s="204" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>20.161967727378276</v>
+        <v>19.822921184877522</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13822,7 +13857,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>181.44275425076793</v>
+        <v>181.85804736660177</v>
       </c>
       <c r="K6" s="236" t="s">
         <v>435</v>
@@ -13834,14 +13869,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>5.78</v>
+        <v>1.87</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>4.3498865389852046</v>
+        <v>4.2767382227466646</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13849,23 +13884,23 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>204.7243574969385</v>
+        <v>205.19381465236879</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.95</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC164</f>
-        <v>3.7865352621756054E-2</v>
+        <v>3.8512992632390421E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13873,7 +13908,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>180.56370521649234</v>
+        <v>181.06314044045934</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13882,14 +13917,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.3484E-2</v>
+        <v>1.0775999999999999E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC165</f>
-        <v>4.9598333531805185E-2</v>
+        <v>5.0446651665188399E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13897,23 +13932,23 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>1.2128392469127421E-2</v>
+        <v>3.2287003651421488E-2</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-5.3249999999999999E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC167</f>
-        <v>4.8822764392423126E-2</v>
+        <v>4.9657817375189768E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13929,14 +13964,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>2.0123318385650221E-2</v>
+        <v>2.0467502850627137E-2</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>404</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>34.155713683859652</v>
+        <v>34.300060439815887</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13961,7 +13996,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6911</v>
+        <v>1.6930000000000001</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>96</v>
@@ -13970,10 +14005,10 @@
         <f>Statement!AC124</f>
         <v>0.3442403644515149</v>
       </c>
-      <c r="H13" s="180" t="s">
+      <c r="H13" s="257" t="s">
         <v>428</v>
       </c>
-      <c r="I13" s="209">
+      <c r="I13" s="255">
         <f>'Reverse DCF'!C17</f>
         <v>0.13</v>
       </c>
@@ -13984,7 +14019,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>13164456</v>
+        <v>12922531</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>97</v>
@@ -13993,6 +14028,13 @@
         <f>Statement!AC143</f>
         <v>0.25062860459696928</v>
       </c>
+      <c r="H14" s="182" t="s">
+        <v>437</v>
+      </c>
+      <c r="I14" s="256">
+        <f ca="1">'Reverse DCF'!C16</f>
+        <v>175.51049119967018</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="181" t="s">
@@ -14000,7 +14042,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC179</f>
-        <v>-3.6767500190012917E-2</v>
+        <v>-3.73963627930348E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14033,7 +14075,7 @@
       </c>
       <c r="I17" s="233">
         <f ca="1">DCF!C15</f>
-        <v>0.12160492812805888</v>
+        <v>0.12108377847505866</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14055,7 +14097,7 @@
       </c>
       <c r="I18" s="234">
         <f ca="1">Multiples!C54</f>
-        <v>0.12799949999999999</v>
+        <v>0.12754500000000002</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14122,12 +14164,12 @@
       <c r="C26" s="166">
         <v>0.21</v>
       </c>
-      <c r="E26" s="181" t="e" vm="2">
+      <c r="E26" s="181" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.9</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14142,7 +14184,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18740,6 +18782,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18747,12 +18795,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19812,16 +19854,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19943,7 +19985,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>178.4</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19952,7 +19994,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>189460.80000000002</v>
+        <v>186274.80000000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19970,7 +20012,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19979,7 +20021,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6911</v>
+        <v>1.6930000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20022,7 +20064,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.4585748700244411E-2</v>
+        <v>7.5764792740869516E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20031,7 +20073,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92541425129975563</v>
+        <v>0.92423520725913044</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20049,7 +20091,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.12799949999999999</v>
+        <v>0.12754500000000002</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20058,7 +20100,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.12160492812805888</v>
+        <v>0.12108377847505866</v>
       </c>
     </row>
   </sheetData>
@@ -20309,7 +20351,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>167698.64226155225</v>
+        <v>168608.22440549239</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20363,23 +20405,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5625.9116601338001</v>
+        <v>5628.5269347152207</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3357.5796045880193</v>
+        <v>3360.7019549205675</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5229.1497310291052</v>
+        <v>5236.445626247345</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7357.2533434900042</v>
+        <v>7370.9433263910669</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>8904.4155337537304</v>
+        <v>8925.1314230528442</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20398,7 +20440,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>94477.850136163295</v>
+        <v>95211.281798247146</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20421,7 +20463,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12160492812805888</v>
+        <v>0.12108377847505866</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20436,7 +20478,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30474.309872994658</v>
+        <v>30521.749265327046</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20445,7 +20487,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>94477.850136163295</v>
+        <v>95211.281798247146</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20454,7 +20496,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>124952.16000915796</v>
+        <v>125733.03106357419</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20481,7 +20523,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>117986.16000915796</v>
+        <v>118767.03106357419</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20499,7 +20541,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C24/C25</f>
-        <v>111.09807910466851</v>
+        <v>111.8333625834032</v>
       </c>
     </row>
   </sheetData>
@@ -20768,23 +20810,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>5625.9116601338001</v>
+        <v>5628.5269347152207</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>3357.5796045880193</v>
+        <v>3360.7019549205675</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>5229.1497310291052</v>
+        <v>5236.445626247345</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7357.2533434900042</v>
+        <v>7370.9433263910669</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>8904.4155337537304</v>
+        <v>8925.1314230528442</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21570,7 +21612,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12160492812805888</v>
+        <v>0.12108377847505866</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21596,7 +21638,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>211737.16174869807</v>
+        <v>212229.76270455727</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21605,7 +21647,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>233307.05608793901</v>
+        <v>233826.38054683147</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21632,7 +21674,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>226341.05608793901</v>
+        <v>226860.38054683147</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21650,7 +21692,7 @@
       </c>
       <c r="C50" s="232">
         <f ca="1">C48/C49</f>
-        <v>213.12717145756969</v>
+        <v>213.61617753938933</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21674,7 +21716,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12799949999999999</v>
+        <v>0.12754500000000002</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21709,7 +21751,7 @@
       </c>
       <c r="C58" s="232">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>192.42616377251687</v>
+        <v>192.81430006053344</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21733,7 +21775,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12160492812805888</v>
+        <v>0.12108377847505866</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21759,7 +21801,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>178088.31067507464</v>
+        <v>178502.62846105688</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21768,7 +21810,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>199658.20501431555</v>
+        <v>200099.24630333108</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21795,7 +21837,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>192692.20501431555</v>
+        <v>193133.24630333108</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21813,7 +21855,7 @@
       </c>
       <c r="C71" s="232">
         <f ca="1">C69/C70</f>
-        <v>181.44275425076793</v>
+        <v>181.85804736660177</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21837,7 +21879,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12160492812805888</v>
+        <v>0.12108377847505866</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21863,7 +21905,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>202813.37332250777</v>
+        <v>203285.21331854147</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21872,7 +21914,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>224383.26766174869</v>
+        <v>224881.83116081567</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21899,7 +21941,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>217417.26766174869</v>
+        <v>217915.83116081567</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21917,22 +21959,22 @@
       </c>
       <c r="C84" s="232">
         <f ca="1">C82/C83</f>
-        <v>204.7243574969385</v>
+        <v>205.19381465236879</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21982,7 +22024,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>111.09807910466851</v>
+        <v>111.8333625834032</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21991,7 +22033,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>213.12717145756969</v>
+        <v>213.61617753938933</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22000,7 +22042,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>192.42616377251687</v>
+        <v>192.81430006053344</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22009,7 +22051,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>181.44275425076793</v>
+        <v>181.85804736660177</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22018,7 +22060,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>204.7243574969385</v>
+        <v>205.19381465236879</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22027,7 +22069,7 @@
       </c>
       <c r="C10" s="232">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>180.56370521649234</v>
+        <v>181.06314044045934</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22036,7 +22078,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>178.4</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22045,7 +22087,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>1.2128392469127421E-2</v>
+        <v>3.2287003651421488E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22554,7 +22596,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12799949999999999</v>
+        <v>0.12754500000000002</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22571,7 +22613,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C23/(C24-C25)</f>
-        <v>34.155713683859652</v>
+        <v>34.300060439815887</v>
       </c>
     </row>
   </sheetData>
@@ -22808,7 +22850,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>230509.62440460268</v>
+        <v>231759.88758823517</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22862,23 +22904,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11879.845611344583</v>
+        <v>11885.368104432895</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>11968.764762137947</v>
+        <v>11979.895005061804</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12058.349461595537</v>
+        <v>12075.173698556026</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12148.604691265422</v>
+        <v>12171.210164086657</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12239.535469981945</v>
+        <v>12268.010428378439</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22897,15 +22939,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>129864.22224859198</v>
+        <v>130872.35835913788</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="252" t="s">
+      <c r="B14" s="253" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="253"/>
+      <c r="C14" s="254"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22913,7 +22955,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>178.4</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22922,7 +22964,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>174.46983070944515</v>
+        <v>175.51049119967018</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22932,20 +22974,20 @@
       <c r="C17" s="156">
         <v>0.13</v>
       </c>
-      <c r="E17" s="254" t="s">
+      <c r="E17" s="252" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="254"/>
-      <c r="G17" s="254"/>
-      <c r="H17" s="254"/>
-      <c r="I17" s="254"/>
+      <c r="F17" s="252"/>
+      <c r="G17" s="252"/>
+      <c r="H17" s="252"/>
+      <c r="I17" s="252"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="252" t="s">
+      <c r="B19" s="253" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="253"/>
+      <c r="C19" s="254"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22961,7 +23003,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12160492812805888</v>
+        <v>0.12108377847505866</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22979,7 +23021,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>187320</v>
+        <v>184170</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23006,15 +23048,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>194286</v>
+        <v>191136</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="252" t="s">
+      <c r="B28" s="253" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="253"/>
+      <c r="C28" s="254"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -23022,7 +23064,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>60295.099996325429</v>
+        <v>60379.657400515825</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23031,7 +23073,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>129864.22224859198</v>
+        <v>130872.35835913788</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23040,7 +23082,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>190159.32224491739</v>
+        <v>191252.0157596537</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23067,7 +23109,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>183193.32224491739</v>
+        <v>184286.0157596537</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23085,21 +23127,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>174.46983070944515</v>
+        <v>175.51049119967018</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29714,7 +29756,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>178.4</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29785,7 +29827,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>178.4</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31287,7 +31329,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>20.161967727378276</v>
+        <v>19.822921184877522</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31324,7 +31366,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.3498865389852046</v>
+        <v>4.2767382227466646</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31385,7 +31427,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.772723985826886</v>
+        <v>6.6588328874105143</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31446,7 +31488,7 @@
       </c>
       <c r="AC156" s="141">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>189460.80000000002</v>
+        <v>186274.80000000002</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31507,7 +31549,7 @@
       </c>
       <c r="AC157" s="141">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>196426.80000000002</v>
+        <v>193240.80000000002</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31544,7 +31586,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="179">
         <f ca="1">AC157/AC5</f>
-        <v>4.457356812199329</v>
+        <v>4.3850594535717535</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31581,7 +31623,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="179">
         <f ca="1">AC157/AC12</f>
-        <v>19.221724239162345</v>
+        <v>18.909952050102753</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31716,7 +31758,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>26.409367159185951</v>
+        <v>25.965263451352108</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31753,7 +31795,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>25.245178964862024</v>
+        <v>24.835707649430269</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31790,7 +31832,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>3.7865352621756054E-2</v>
+        <v>3.8512992632390421E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31827,7 +31869,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>4.9598333531805185E-2</v>
+        <v>5.0446651665188399E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31864,7 +31906,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="152">
         <f ca="1">AC82/AC116</f>
-        <v>2.0123318385650221E-2</v>
+        <v>2.0467502850627137E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31901,7 +31943,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="152">
         <f ca="1">-AC63/AC156</f>
-        <v>4.8822764392423126E-2</v>
+        <v>4.9657817375189768E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31938,7 +31980,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="152">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>6.9011637235776468E-2</v>
+        <v>7.0191995911416893E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32441,7 +32483,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="152">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.6767500190012917E-2</v>
+        <v>-3.73963627930348E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33818,7 +33860,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>178.4</v>
+        <v>175.4</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33834,7 +33876,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>189460.80000000002</v>
+        <v>186274.80000000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33854,7 +33896,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>196426.80000000002</v>
+        <v>193240.80000000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33874,7 +33916,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>20.161967727378276</v>
+        <v>19.822921184877522</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33894,7 +33936,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.3498865389852046</v>
+        <v>4.2767382227466646</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33914,7 +33956,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.772723985826886</v>
+        <v>6.6588328874105143</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33934,7 +33976,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.457356812199329</v>
+        <v>4.3850594535717535</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33943,7 +33985,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>19.221724239162345</v>
+        <v>18.909952050102753</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34179,7 +34221,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>4.9598333531805185E-2</v>
+        <v>5.0446651665188399E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -34195,7 +34237,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC164</f>
-        <v>3.7865352621756054E-2</v>
+        <v>3.8512992632390421E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -34211,7 +34253,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>2.0123318385650221E-2</v>
+        <v>2.0467502850627137E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -34227,7 +34269,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.8822764392423126E-2</v>
+        <v>4.9657817375189768E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34236,7 +34278,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>6.9011637235776468E-2</v>
+        <v>7.0191995911416893E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34280,7 +34322,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC179</f>
-        <v>-3.6767500190012917E-2</v>
+        <v>-3.73963627930348E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34460,7 +34502,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC115</f>
-        <v>178.4</v>
+        <v>175.4</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34489,7 +34531,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>189460.80000000002</v>
+        <v>186274.80000000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34518,7 +34560,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>196426.80000000002</v>
+        <v>193240.80000000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34547,7 +34589,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>20.161967727378276</v>
+        <v>19.822921184877522</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34576,7 +34618,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.3498865389852046</v>
+        <v>4.2767382227466646</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34605,7 +34647,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.772723985826886</v>
+        <v>6.6588328874105143</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34634,7 +34676,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.457356812199329</v>
+        <v>4.3850594535717535</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34663,7 +34705,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>19.221724239162345</v>
+        <v>18.909952050102753</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35436,7 +35478,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>4.9598333531805185E-2</v>
+        <v>5.0446651665188399E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35465,7 +35507,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC164</f>
-        <v>3.7865352621756054E-2</v>
+        <v>3.8512992632390421E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35494,7 +35536,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>2.0123318385650221E-2</v>
+        <v>2.0467502850627137E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35523,7 +35565,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.8822764392423126E-2</v>
+        <v>4.9657817375189768E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35552,7 +35594,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>6.9011637235776468E-2</v>
+        <v>7.0191995911416893E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35788,7 +35830,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.6767500190012917E-2</v>
+        <v>-3.73963627930348E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36326,14 +36368,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="243" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="244"/>
+      <c r="F3" s="245" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36400,19 +36442,19 @@
       <c r="B7" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="241">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="242"/>
+      <c r="F7" s="241">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="242"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36439,19 +36481,19 @@
       <c r="B9" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="241">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="242"/>
+      <c r="F9" s="241">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="242"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36478,19 +36520,19 @@
       <c r="B11" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="241">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="242"/>
+      <c r="F11" s="241">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="242"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36517,19 +36559,19 @@
       <c r="B13" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="241">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="242"/>
+      <c r="F13" s="241">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="242"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36556,19 +36598,19 @@
       <c r="B15" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="241">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="242"/>
+      <c r="F15" s="241">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36595,19 +36637,19 @@
       <c r="B17" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="241">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="242"/>
+      <c r="F17" s="241">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="242"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36634,22 +36676,22 @@
       <c r="B19" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="241">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="242"/>
+      <c r="F19" s="241">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="242"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36676,22 +36718,22 @@
       <c r="B21" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="241">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="242"/>
+      <c r="F21" s="241">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="242"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36739,22 +36781,22 @@
       <c r="B25" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="241">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="242"/>
+      <c r="F25" s="241">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="242"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="218" t="s">
@@ -36781,22 +36823,22 @@
       <c r="B27" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="241">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="242"/>
+      <c r="F27" s="241">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="242"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="218" t="s">
@@ -36823,22 +36865,22 @@
       <c r="B29" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="241">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="242"/>
+      <c r="F29" s="241">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="242"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36865,22 +36907,22 @@
       <c r="B31" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="244">
+      <c r="C31" s="241">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="245"/>
-      <c r="F31" s="244">
+      <c r="D31" s="242"/>
+      <c r="F31" s="241">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="245"/>
+      <c r="G31" s="242"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36907,25 +36949,43 @@
       <c r="B33" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="244">
+      <c r="C33" s="241">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="245"/>
-      <c r="F33" s="244">
+      <c r="D33" s="242"/>
+      <c r="F33" s="241">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="245"/>
+      <c r="G33" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36936,24 +36996,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E93F3C-87CB-894D-9E92-247AD2773980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F17DE46-A926-544B-9D52-87621BCA2776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -118,7 +118,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -129,28 +129,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -160,21 +139,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2427,6 +2397,9 @@
     <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2481,9 +2454,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12803,7 +12773,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12842,9 +12812,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6930000000000001</v>
-    <v>1.87</v>
-    <v>1.0775999999999999E-2</v>
+    <v>1.6947000000000001</v>
+    <v>3.08</v>
+    <v>1.7821E-2</v>
+    <v>-1.1100000000000001</v>
+    <v>-6.3099999999999996E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12852,50 +12824,36 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>176.41</v>
+    <v>176.97499999999999</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46315.727168217185</v>
+    <v>46318.953474467191</v>
     <v>4</v>
-    <v>171.13</v>
-    <v>184170000000</v>
+    <v>171.47499999999999</v>
+    <v>184705500000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>171.54</v>
-    <v>20.3</v>
-    <v>173.53</v>
-    <v>175.4</v>
+    <v>172.07</v>
+    <v>20.359000000000002</v>
+    <v>172.83</v>
+    <v>175.91</v>
+    <v>174.8</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>3141977</v>
-    <v>12922531</v>
+    <v>7252454</v>
+    <v>12653239</v>
     <v>1991</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12909,28 +12867,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
-    <v>10</v>
-    <v>50.9</v>
+    <v>7</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>11</v>
+    <v>8</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12964,6 +12922,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12985,6 +12945,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12994,11 +12955,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13034,7 +12990,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13045,13 +13001,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13152,13 +13111,19 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
+      <v>1</v>
+      <v>1</v>
+      <v>6</v>
     </spb>
     <spb s="5">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13239,6 +13204,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13246,6 +13214,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13739,18 +13710,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="240" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="238"/>
-      <c r="E2" s="237" t="s">
+      <c r="C2" s="241"/>
+      <c r="E2" s="240" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="238"/>
-      <c r="H2" s="237" t="s">
+      <c r="F2" s="241"/>
+      <c r="H2" s="240" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="238"/>
+      <c r="I2" s="241"/>
       <c r="K2" s="132" t="s">
         <v>431</v>
       </c>
@@ -13768,7 +13739,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC156</f>
-        <v>186274.80000000002</v>
+        <v>186816.41999999998</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13776,7 +13747,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>111.8333625834032</v>
+        <v>114.14814457588841</v>
       </c>
       <c r="K3" s="235" t="s">
         <v>432</v>
@@ -13795,7 +13766,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC157</f>
-        <v>193240.80000000002</v>
+        <v>193782.41999999998</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13803,7 +13774,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>213.61617753938933</v>
+        <v>215.12940524485441</v>
       </c>
       <c r="K4" s="235" t="s">
         <v>433</v>
@@ -13815,7 +13786,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>175.4</v>
+        <v>175.91</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>235</v>
@@ -13830,7 +13801,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>192.81430006053344</v>
+        <v>194.32059472485892</v>
       </c>
       <c r="K5" s="235" t="s">
         <v>434</v>
@@ -13840,16 +13811,16 @@
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="204" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="204" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>174.8</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>19.822921184877522</v>
+        <v>19.880559097102648</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13857,7 +13828,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>181.85804736660177</v>
+        <v>183.14315051504727</v>
       </c>
       <c r="K6" s="236" t="s">
         <v>435</v>
@@ -13869,14 +13840,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.87</v>
+        <v>3.08</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>4.2767382227466646</v>
+        <v>4.2891734365072161</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13884,23 +13855,23 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>205.19381465236879</v>
+        <v>206.64654295839802</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC164</f>
-        <v>3.8512992632390421E-2</v>
+        <v>3.8401335385829578E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13908,7 +13879,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>181.06314044045934</v>
+        <v>182.67756760380939</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13917,14 +13888,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.0775999999999999E-2</v>
+        <v>1.7821E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC165</f>
-        <v>5.0446651665188399E-2</v>
+        <v>5.0300396237132887E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13932,23 +13903,23 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>3.2287003651421488E-2</v>
+        <v>3.8471761717977358E-2</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-6.3099999999999996E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC167</f>
-        <v>4.9657817375189768E-2</v>
+        <v>4.9513848943256708E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13964,14 +13935,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>2.0467502850627137E-2</v>
+        <v>2.0408163265306121E-2</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>404</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>34.300060439815887</v>
+        <v>34.868585850470033</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13996,7 +13967,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6930000000000001</v>
+        <v>1.6947000000000001</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>96</v>
@@ -14005,10 +13976,10 @@
         <f>Statement!AC124</f>
         <v>0.3442403644515149</v>
       </c>
-      <c r="H13" s="257" t="s">
+      <c r="H13" s="239" t="s">
         <v>428</v>
       </c>
-      <c r="I13" s="255">
+      <c r="I13" s="237">
         <f>'Reverse DCF'!C17</f>
         <v>0.13</v>
       </c>
@@ -14019,7 +13990,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>12922531</v>
+        <v>12653239</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>97</v>
@@ -14031,9 +14002,9 @@
       <c r="H14" s="182" t="s">
         <v>437</v>
       </c>
-      <c r="I14" s="256">
+      <c r="I14" s="238">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>175.51049119967018</v>
+        <v>178.78553447149005</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14042,7 +14013,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC179</f>
-        <v>-3.73963627930348E-2</v>
+        <v>-3.7287942890673102E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14053,16 +14024,16 @@
         <f>Statement!AC178</f>
         <v>-6.6342857142857143</v>
       </c>
-      <c r="H16" s="237" t="s">
+      <c r="H16" s="240" t="s">
         <v>429</v>
       </c>
-      <c r="I16" s="238"/>
+      <c r="I16" s="241"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="239" t="s">
+      <c r="B17" s="242" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="239"/>
+      <c r="C17" s="242"/>
       <c r="E17" s="180" t="s">
         <v>288</v>
       </c>
@@ -14075,7 +14046,7 @@
       </c>
       <c r="I17" s="233">
         <f ca="1">DCF!C15</f>
-        <v>0.12108377847505866</v>
+        <v>0.11948009295443998</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14097,7 +14068,7 @@
       </c>
       <c r="I18" s="234">
         <f ca="1">Multiples!C54</f>
-        <v>0.12754500000000002</v>
+        <v>0.1257915</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14148,14 +14119,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="239" t="s">
+      <c r="B25" s="242" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="239"/>
-      <c r="E25" s="237" t="s">
+      <c r="C25" s="242"/>
+      <c r="E25" s="240" t="s">
         <v>330</v>
       </c>
-      <c r="F25" s="238"/>
+      <c r="F25" s="241"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -14164,12 +14135,12 @@
       <c r="C26" s="166">
         <v>0.21</v>
       </c>
-      <c r="E26" s="181" t="e" vm="5">
+      <c r="E26" s="181" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14184,7 +14155,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14618,36 +14589,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="240" t="s">
+      <c r="S2" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240"/>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="240" t="s">
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
+      <c r="AA2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="AB2" s="240"/>
-      <c r="AC2" s="240"/>
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="243"/>
       <c r="AE2" s="85" t="s">
         <v>107</v>
       </c>
@@ -14658,32 +14629,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="249" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="247" t="s">
+      <c r="S4" s="250" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="248"/>
-      <c r="U4" s="248"/>
-      <c r="V4" s="248"/>
-      <c r="W4" s="248"/>
-      <c r="X4" s="248"/>
-      <c r="Y4" s="248"/>
-      <c r="Z4" s="248"/>
-      <c r="AA4" s="248"/>
-      <c r="AB4" s="248"/>
-      <c r="AC4" s="248"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
+      <c r="AA4" s="251"/>
+      <c r="AB4" s="251"/>
+      <c r="AC4" s="251"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15424,33 +15395,33 @@
       <c r="Q13" s="91"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C14" s="246" t="s">
+      <c r="C14" s="249" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="246"/>
-      <c r="E14" s="246"/>
-      <c r="F14" s="246"/>
-      <c r="G14" s="246"/>
-      <c r="H14" s="246"/>
-      <c r="I14" s="246"/>
-      <c r="J14" s="246"/>
-      <c r="K14" s="246"/>
-      <c r="L14" s="246"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="249"/>
+      <c r="K14" s="249"/>
+      <c r="L14" s="249"/>
       <c r="O14" s="5"/>
       <c r="Q14" s="91"/>
-      <c r="S14" s="247" t="s">
+      <c r="S14" s="250" t="s">
         <v>114</v>
       </c>
-      <c r="T14" s="248"/>
-      <c r="U14" s="248"/>
-      <c r="V14" s="248"/>
-      <c r="W14" s="248"/>
-      <c r="X14" s="248"/>
-      <c r="Y14" s="248"/>
-      <c r="Z14" s="248"/>
-      <c r="AA14" s="248"/>
-      <c r="AB14" s="248"/>
-      <c r="AC14" s="248"/>
+      <c r="T14" s="251"/>
+      <c r="U14" s="251"/>
+      <c r="V14" s="251"/>
+      <c r="W14" s="251"/>
+      <c r="X14" s="251"/>
+      <c r="Y14" s="251"/>
+      <c r="Z14" s="251"/>
+      <c r="AA14" s="251"/>
+      <c r="AB14" s="251"/>
+      <c r="AC14" s="251"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
@@ -16117,35 +16088,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
-      <c r="P2" s="240" t="s">
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="P2" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="240"/>
-      <c r="R2" s="240"/>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="240"/>
-      <c r="V2" s="240"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="240" t="s">
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243" t="s">
         <v>106</v>
       </c>
-      <c r="Y2" s="240"/>
-      <c r="Z2" s="240"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
       <c r="AB2" s="85" t="s">
         <v>107</v>
       </c>
@@ -16154,31 +16125,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="249" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="P4" s="248" t="s">
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
+      <c r="P4" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" s="248"/>
-      <c r="R4" s="248"/>
-      <c r="S4" s="248"/>
-      <c r="T4" s="248"/>
-      <c r="U4" s="248"/>
-      <c r="V4" s="248"/>
-      <c r="W4" s="248"/>
-      <c r="X4" s="248"/>
-      <c r="Y4" s="248"/>
-      <c r="Z4" s="248"/>
+      <c r="Q4" s="251"/>
+      <c r="R4" s="251"/>
+      <c r="S4" s="251"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16373,32 +16344,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="246" t="s">
+      <c r="C9" s="249" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="246"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="246"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="246"/>
-      <c r="K9" s="246"/>
-      <c r="L9" s="246"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="249"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="248" t="s">
+      <c r="P9" s="251" t="s">
         <v>118</v>
       </c>
-      <c r="Q9" s="248"/>
-      <c r="R9" s="248"/>
-      <c r="S9" s="248"/>
-      <c r="T9" s="248"/>
-      <c r="U9" s="248"/>
-      <c r="V9" s="248"/>
-      <c r="W9" s="248"/>
-      <c r="X9" s="248"/>
-      <c r="Y9" s="248"/>
-      <c r="Z9" s="248"/>
+      <c r="Q9" s="251"/>
+      <c r="R9" s="251"/>
+      <c r="S9" s="251"/>
+      <c r="T9" s="251"/>
+      <c r="U9" s="251"/>
+      <c r="V9" s="251"/>
+      <c r="W9" s="251"/>
+      <c r="X9" s="251"/>
+      <c r="Y9" s="251"/>
+      <c r="Z9" s="251"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16874,31 +16845,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="246" t="s">
+      <c r="C17" s="249" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="246"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="246"/>
-      <c r="G17" s="246"/>
-      <c r="H17" s="246"/>
-      <c r="I17" s="246"/>
-      <c r="J17" s="246"/>
-      <c r="K17" s="246"/>
-      <c r="L17" s="246"/>
-      <c r="P17" s="248" t="s">
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
+      <c r="J17" s="249"/>
+      <c r="K17" s="249"/>
+      <c r="L17" s="249"/>
+      <c r="P17" s="251" t="s">
         <v>120</v>
       </c>
-      <c r="Q17" s="248"/>
-      <c r="R17" s="248"/>
-      <c r="S17" s="248"/>
-      <c r="T17" s="248"/>
-      <c r="U17" s="248"/>
-      <c r="V17" s="248"/>
-      <c r="W17" s="248"/>
-      <c r="X17" s="248"/>
-      <c r="Y17" s="248"/>
-      <c r="Z17" s="248"/>
+      <c r="Q17" s="251"/>
+      <c r="R17" s="251"/>
+      <c r="S17" s="251"/>
+      <c r="T17" s="251"/>
+      <c r="U17" s="251"/>
+      <c r="V17" s="251"/>
+      <c r="W17" s="251"/>
+      <c r="X17" s="251"/>
+      <c r="Y17" s="251"/>
+      <c r="Z17" s="251"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17376,60 +17347,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="250" t="s">
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="252"/>
+      <c r="H3" s="253" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
-      <c r="P3" s="251"/>
-      <c r="Q3" s="251"/>
-      <c r="R3" s="251"/>
-      <c r="S3" s="251"/>
-      <c r="T3" s="251"/>
-      <c r="U3" s="251"/>
-      <c r="V3" s="251"/>
-      <c r="W3" s="251"/>
-      <c r="X3" s="251"/>
-      <c r="Y3" s="251"/>
-      <c r="Z3" s="251"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
+      <c r="P3" s="254"/>
+      <c r="Q3" s="254"/>
+      <c r="R3" s="254"/>
+      <c r="S3" s="254"/>
+      <c r="T3" s="254"/>
+      <c r="U3" s="254"/>
+      <c r="V3" s="254"/>
+      <c r="W3" s="254"/>
+      <c r="X3" s="254"/>
+      <c r="Y3" s="254"/>
+      <c r="Z3" s="254"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="249" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="P5" s="251"/>
-      <c r="Q5" s="251"/>
-      <c r="R5" s="251"/>
-      <c r="S5" s="251"/>
-      <c r="T5" s="251"/>
-      <c r="U5" s="251"/>
-      <c r="V5" s="251"/>
-      <c r="W5" s="251"/>
-      <c r="X5" s="251"/>
-      <c r="Y5" s="251"/>
-      <c r="Z5" s="251"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="249"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
+      <c r="P5" s="254"/>
+      <c r="Q5" s="254"/>
+      <c r="R5" s="254"/>
+      <c r="S5" s="254"/>
+      <c r="T5" s="254"/>
+      <c r="U5" s="254"/>
+      <c r="V5" s="254"/>
+      <c r="W5" s="254"/>
+      <c r="X5" s="254"/>
+      <c r="Y5" s="254"/>
+      <c r="Z5" s="254"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17615,30 +17586,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="246" t="s">
+      <c r="C11" s="249" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="246"/>
-      <c r="E11" s="246"/>
-      <c r="F11" s="246"/>
-      <c r="G11" s="246"/>
-      <c r="H11" s="246"/>
-      <c r="I11" s="246"/>
-      <c r="J11" s="246"/>
-      <c r="K11" s="246"/>
-      <c r="L11" s="246"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="249"/>
+      <c r="K11" s="249"/>
+      <c r="L11" s="249"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="251"/>
-      <c r="Q11" s="251"/>
-      <c r="R11" s="251"/>
-      <c r="S11" s="251"/>
-      <c r="T11" s="251"/>
-      <c r="U11" s="251"/>
-      <c r="V11" s="251"/>
-      <c r="W11" s="251"/>
-      <c r="X11" s="251"/>
-      <c r="Y11" s="251"/>
-      <c r="Z11" s="251"/>
+      <c r="P11" s="254"/>
+      <c r="Q11" s="254"/>
+      <c r="R11" s="254"/>
+      <c r="S11" s="254"/>
+      <c r="T11" s="254"/>
+      <c r="U11" s="254"/>
+      <c r="V11" s="254"/>
+      <c r="W11" s="254"/>
+      <c r="X11" s="254"/>
+      <c r="Y11" s="254"/>
+      <c r="Z11" s="254"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17880,18 +17851,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="246" t="s">
+      <c r="C18" s="249" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="246"/>
-      <c r="E18" s="246"/>
-      <c r="F18" s="246"/>
-      <c r="G18" s="246"/>
-      <c r="H18" s="246"/>
-      <c r="I18" s="246"/>
-      <c r="J18" s="246"/>
-      <c r="K18" s="246"/>
-      <c r="L18" s="246"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
+      <c r="K18" s="249"/>
+      <c r="L18" s="249"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18104,23 +18075,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="251"/>
-      <c r="C25" s="251"/>
+      <c r="B25" s="254"/>
+      <c r="C25" s="254"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="246" t="s">
+      <c r="C26" s="249" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="246"/>
-      <c r="E26" s="246"/>
-      <c r="F26" s="246"/>
-      <c r="G26" s="246"/>
-      <c r="H26" s="246"/>
-      <c r="I26" s="246"/>
-      <c r="J26" s="246"/>
-      <c r="K26" s="246"/>
-      <c r="L26" s="246"/>
+      <c r="D26" s="249"/>
+      <c r="E26" s="249"/>
+      <c r="F26" s="249"/>
+      <c r="G26" s="249"/>
+      <c r="H26" s="249"/>
+      <c r="I26" s="249"/>
+      <c r="J26" s="249"/>
+      <c r="K26" s="249"/>
+      <c r="L26" s="249"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18312,18 +18283,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="246" t="s">
+      <c r="C33" s="249" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="246"/>
-      <c r="E33" s="246"/>
-      <c r="F33" s="246"/>
-      <c r="G33" s="246"/>
-      <c r="H33" s="246"/>
-      <c r="I33" s="246"/>
-      <c r="J33" s="246"/>
-      <c r="K33" s="246"/>
-      <c r="L33" s="246"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="249"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="249"/>
+      <c r="I33" s="249"/>
+      <c r="J33" s="249"/>
+      <c r="K33" s="249"/>
+      <c r="L33" s="249"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18507,18 +18478,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="246" t="s">
+      <c r="C40" s="249" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="246"/>
-      <c r="E40" s="246"/>
-      <c r="F40" s="246"/>
-      <c r="G40" s="246"/>
-      <c r="H40" s="246"/>
-      <c r="I40" s="246"/>
-      <c r="J40" s="246"/>
-      <c r="K40" s="246"/>
-      <c r="L40" s="246"/>
+      <c r="D40" s="249"/>
+      <c r="E40" s="249"/>
+      <c r="F40" s="249"/>
+      <c r="G40" s="249"/>
+      <c r="H40" s="249"/>
+      <c r="I40" s="249"/>
+      <c r="J40" s="249"/>
+      <c r="K40" s="249"/>
+      <c r="L40" s="249"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18832,60 +18803,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
-      <c r="S2" s="251"/>
-      <c r="T2" s="251"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="251"/>
-      <c r="X2" s="251"/>
-      <c r="Y2" s="251"/>
-      <c r="Z2" s="251"/>
-      <c r="AA2" s="251"/>
-      <c r="AB2" s="251"/>
-      <c r="AC2" s="251"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
+      <c r="AA2" s="254"/>
+      <c r="AB2" s="254"/>
+      <c r="AC2" s="254"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="249" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="S4" s="251"/>
-      <c r="T4" s="251"/>
-      <c r="U4" s="251"/>
-      <c r="V4" s="251"/>
-      <c r="W4" s="251"/>
-      <c r="X4" s="251"/>
-      <c r="Y4" s="251"/>
-      <c r="Z4" s="251"/>
-      <c r="AA4" s="251"/>
-      <c r="AB4" s="251"/>
-      <c r="AC4" s="251"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
+      <c r="S4" s="254"/>
+      <c r="T4" s="254"/>
+      <c r="U4" s="254"/>
+      <c r="V4" s="254"/>
+      <c r="W4" s="254"/>
+      <c r="X4" s="254"/>
+      <c r="Y4" s="254"/>
+      <c r="Z4" s="254"/>
+      <c r="AA4" s="254"/>
+      <c r="AB4" s="254"/>
+      <c r="AC4" s="254"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19248,18 +19219,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="246" t="s">
+      <c r="C13" s="249" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="246"/>
-      <c r="E13" s="246"/>
-      <c r="F13" s="246"/>
-      <c r="G13" s="246"/>
-      <c r="H13" s="246"/>
-      <c r="I13" s="246"/>
-      <c r="J13" s="246"/>
-      <c r="K13" s="246"/>
-      <c r="L13" s="246"/>
+      <c r="D13" s="249"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="249"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="249"/>
+      <c r="I13" s="249"/>
+      <c r="J13" s="249"/>
+      <c r="K13" s="249"/>
+      <c r="L13" s="249"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19352,18 +19323,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="246" t="s">
+      <c r="C18" s="249" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="246"/>
-      <c r="E18" s="246"/>
-      <c r="F18" s="246"/>
-      <c r="G18" s="246"/>
-      <c r="H18" s="246"/>
-      <c r="I18" s="246"/>
-      <c r="J18" s="246"/>
-      <c r="K18" s="246"/>
-      <c r="L18" s="246"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
+      <c r="K18" s="249"/>
+      <c r="L18" s="249"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19555,18 +19526,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="246" t="s">
+      <c r="C25" s="249" t="s">
         <v>254</v>
       </c>
-      <c r="D25" s="246"/>
-      <c r="E25" s="246"/>
-      <c r="F25" s="246"/>
-      <c r="G25" s="246"/>
-      <c r="H25" s="246"/>
-      <c r="I25" s="246"/>
-      <c r="J25" s="246"/>
-      <c r="K25" s="246"/>
-      <c r="L25" s="246"/>
+      <c r="D25" s="249"/>
+      <c r="E25" s="249"/>
+      <c r="F25" s="249"/>
+      <c r="G25" s="249"/>
+      <c r="H25" s="249"/>
+      <c r="I25" s="249"/>
+      <c r="J25" s="249"/>
+      <c r="K25" s="249"/>
+      <c r="L25" s="249"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19704,18 +19675,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="246" t="s">
+      <c r="C31" s="249" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="246"/>
-      <c r="E31" s="246"/>
-      <c r="F31" s="246"/>
-      <c r="G31" s="246"/>
-      <c r="H31" s="246"/>
-      <c r="I31" s="246"/>
-      <c r="J31" s="246"/>
-      <c r="K31" s="246"/>
-      <c r="L31" s="246"/>
+      <c r="D31" s="249"/>
+      <c r="E31" s="249"/>
+      <c r="F31" s="249"/>
+      <c r="G31" s="249"/>
+      <c r="H31" s="249"/>
+      <c r="I31" s="249"/>
+      <c r="J31" s="249"/>
+      <c r="K31" s="249"/>
+      <c r="L31" s="249"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19965,10 +19936,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="243" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="243"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19985,7 +19956,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>175.4</v>
+        <v>175.91</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19994,7 +19965,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>186274.80000000002</v>
+        <v>186816.41999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20012,7 +19983,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20021,7 +19992,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6930000000000001</v>
+        <v>1.6947000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20053,10 +20024,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="243" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="240"/>
+      <c r="C15" s="243"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -20064,7 +20035,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.5764792740869516E-2</v>
+        <v>7.5561732450898977E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20073,7 +20044,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92423520725913044</v>
+        <v>0.92443826754910097</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20091,7 +20062,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.12754500000000002</v>
+        <v>0.1257915</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20100,7 +20071,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.12108377847505866</v>
+        <v>0.11948009295443998</v>
       </c>
     </row>
   </sheetData>
@@ -20145,60 +20116,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="250" t="s">
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="252"/>
+      <c r="H3" s="253" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
-      <c r="P3" s="251"/>
-      <c r="Q3" s="251"/>
-      <c r="R3" s="251"/>
-      <c r="S3" s="251"/>
-      <c r="T3" s="251"/>
-      <c r="U3" s="251"/>
-      <c r="V3" s="251"/>
-      <c r="W3" s="251"/>
-      <c r="X3" s="251"/>
-      <c r="Y3" s="251"/>
-      <c r="Z3" s="251"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
+      <c r="P3" s="254"/>
+      <c r="Q3" s="254"/>
+      <c r="R3" s="254"/>
+      <c r="S3" s="254"/>
+      <c r="T3" s="254"/>
+      <c r="U3" s="254"/>
+      <c r="V3" s="254"/>
+      <c r="W3" s="254"/>
+      <c r="X3" s="254"/>
+      <c r="Y3" s="254"/>
+      <c r="Z3" s="254"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="249" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="P5" s="251"/>
-      <c r="Q5" s="251"/>
-      <c r="R5" s="251"/>
-      <c r="S5" s="251"/>
-      <c r="T5" s="251"/>
-      <c r="U5" s="251"/>
-      <c r="V5" s="251"/>
-      <c r="W5" s="251"/>
-      <c r="X5" s="251"/>
-      <c r="Y5" s="251"/>
-      <c r="Z5" s="251"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="249"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
+      <c r="P5" s="254"/>
+      <c r="Q5" s="254"/>
+      <c r="R5" s="254"/>
+      <c r="S5" s="254"/>
+      <c r="T5" s="254"/>
+      <c r="U5" s="254"/>
+      <c r="V5" s="254"/>
+      <c r="W5" s="254"/>
+      <c r="X5" s="254"/>
+      <c r="Y5" s="254"/>
+      <c r="Z5" s="254"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20351,7 +20322,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>168608.22440549239</v>
+        <v>171470.14546929472</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20405,23 +20376,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5628.5269347152207</v>
+        <v>5636.5899518286324</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3360.7019549205675</v>
+        <v>3370.3374444785127</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5236.445626247345</v>
+        <v>5258.9819293956143</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7370.9433263910669</v>
+        <v>7413.2704730084488</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>8925.1314230528442</v>
+        <v>8989.2423024134478</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20440,14 +20411,14 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>95211.281798247146</v>
+        <v>97522.907438468843</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="240" t="s">
+      <c r="B13" s="243" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="240"/>
+      <c r="C13" s="243"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20463,14 +20434,14 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12108377847505866</v>
+        <v>0.11948009295443998</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="240" t="s">
+      <c r="B18" s="243" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="240"/>
+      <c r="C18" s="243"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20478,7 +20449,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30521.749265327046</v>
+        <v>30668.422101124655</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20487,7 +20458,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>95211.281798247146</v>
+        <v>97522.907438468843</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20496,7 +20467,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>125733.03106357419</v>
+        <v>128191.3295395935</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20523,7 +20494,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>118767.03106357419</v>
+        <v>121225.32953959348</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20541,7 +20512,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C24/C25</f>
-        <v>111.8333625834032</v>
+        <v>114.14814457588841</v>
       </c>
     </row>
   </sheetData>
@@ -20584,37 +20555,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="249" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20810,23 +20781,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>5628.5269347152207</v>
+        <v>5636.5899518286324</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>3360.7019549205675</v>
+        <v>3370.3374444785127</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>5236.445626247345</v>
+        <v>5258.9819293956143</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7370.9433263910669</v>
+        <v>7413.2704730084488</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>8925.1314230528442</v>
+        <v>8989.2423024134478</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -20834,18 +20805,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="246" t="s">
+      <c r="C11" s="249" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="246"/>
-      <c r="E11" s="246"/>
-      <c r="F11" s="246"/>
-      <c r="G11" s="246"/>
-      <c r="H11" s="246"/>
-      <c r="I11" s="246"/>
-      <c r="J11" s="246"/>
-      <c r="K11" s="246"/>
-      <c r="L11" s="246"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="249"/>
+      <c r="K11" s="249"/>
+      <c r="L11" s="249"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21039,18 +21010,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="246" t="s">
+      <c r="C17" s="249" t="s">
         <v>188</v>
       </c>
-      <c r="D17" s="246"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="246"/>
-      <c r="G17" s="246"/>
-      <c r="H17" s="246"/>
-      <c r="I17" s="246"/>
-      <c r="J17" s="246"/>
-      <c r="K17" s="246"/>
-      <c r="L17" s="246"/>
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
+      <c r="J17" s="249"/>
+      <c r="K17" s="249"/>
+      <c r="L17" s="249"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -21184,18 +21155,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="246" t="s">
+      <c r="C22" s="249" t="s">
         <v>191</v>
       </c>
-      <c r="D22" s="246"/>
-      <c r="E22" s="246"/>
-      <c r="F22" s="246"/>
-      <c r="G22" s="246"/>
-      <c r="H22" s="246"/>
-      <c r="I22" s="246"/>
-      <c r="J22" s="246"/>
-      <c r="K22" s="246"/>
-      <c r="L22" s="246"/>
+      <c r="D22" s="249"/>
+      <c r="E22" s="249"/>
+      <c r="F22" s="249"/>
+      <c r="G22" s="249"/>
+      <c r="H22" s="249"/>
+      <c r="I22" s="249"/>
+      <c r="J22" s="249"/>
+      <c r="K22" s="249"/>
+      <c r="L22" s="249"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21279,18 +21250,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="246" t="s">
+      <c r="C27" s="249" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="246"/>
-      <c r="E27" s="246"/>
-      <c r="F27" s="246"/>
-      <c r="G27" s="246"/>
-      <c r="H27" s="246"/>
-      <c r="I27" s="246"/>
-      <c r="J27" s="246"/>
-      <c r="K27" s="246"/>
-      <c r="L27" s="246"/>
+      <c r="D27" s="249"/>
+      <c r="E27" s="249"/>
+      <c r="F27" s="249"/>
+      <c r="G27" s="249"/>
+      <c r="H27" s="249"/>
+      <c r="I27" s="249"/>
+      <c r="J27" s="249"/>
+      <c r="K27" s="249"/>
+      <c r="L27" s="249"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21591,10 +21562,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="240" t="s">
+      <c r="B39" s="243" t="s">
         <v>197</v>
       </c>
-      <c r="C39" s="240"/>
+      <c r="C39" s="243"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21612,7 +21583,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12108377847505866</v>
+        <v>0.11948009295443998</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21638,7 +21609,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>212229.76270455727</v>
+        <v>213754.24857132419</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21647,7 +21618,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>233826.38054683147</v>
+        <v>235433.4283700354</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21674,7 +21645,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>226860.38054683147</v>
+        <v>228467.4283700354</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21692,14 +21663,14 @@
       </c>
       <c r="C50" s="232">
         <f ca="1">C48/C49</f>
-        <v>213.61617753938933</v>
+        <v>215.12940524485441</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="240" t="s">
+      <c r="B52" s="243" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="240"/>
+      <c r="C52" s="243"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21716,7 +21687,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12754500000000002</v>
+        <v>0.1257915</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21751,14 +21722,14 @@
       </c>
       <c r="C58" s="232">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>192.81430006053344</v>
+        <v>194.32059472485892</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="240" t="s">
+      <c r="B60" s="243" t="s">
         <v>314</v>
       </c>
-      <c r="C60" s="240"/>
+      <c r="C60" s="243"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21775,7 +21746,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12108377847505866</v>
+        <v>0.11948009295443998</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21801,7 +21772,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>178502.62846105688</v>
+        <v>179784.84604826898</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21810,7 +21781,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>200099.24630333108</v>
+        <v>201464.02584698019</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21837,7 +21808,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>193133.24630333108</v>
+        <v>194498.02584698019</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21855,14 +21826,14 @@
       </c>
       <c r="C71" s="232">
         <f ca="1">C69/C70</f>
-        <v>181.85804736660177</v>
+        <v>183.14315051504727</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="240" t="s">
+      <c r="B73" s="243" t="s">
         <v>425</v>
       </c>
-      <c r="C73" s="240"/>
+      <c r="C73" s="243"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21879,7 +21850,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12108377847505866</v>
+        <v>0.11948009295443998</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21905,7 +21876,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>203285.21331854147</v>
+        <v>204745.44882310749</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21914,7 +21885,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>224881.83116081567</v>
+        <v>226424.6286218187</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21941,7 +21912,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>217915.83116081567</v>
+        <v>219458.6286218187</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21959,7 +21930,7 @@
       </c>
       <c r="C84" s="232">
         <f ca="1">C82/C83</f>
-        <v>205.19381465236879</v>
+        <v>206.64654295839802</v>
       </c>
     </row>
   </sheetData>
@@ -22012,10 +21983,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="243" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="240"/>
+      <c r="C4" s="243"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -22024,7 +21995,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>111.8333625834032</v>
+        <v>114.14814457588841</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -22033,7 +22004,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>213.61617753938933</v>
+        <v>215.12940524485441</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22042,7 +22013,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>192.81430006053344</v>
+        <v>194.32059472485892</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22051,7 +22022,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>181.85804736660177</v>
+        <v>183.14315051504727</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22060,7 +22031,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>205.19381465236879</v>
+        <v>206.64654295839802</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22069,7 +22040,7 @@
       </c>
       <c r="C10" s="232">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>181.06314044045934</v>
+        <v>182.67756760380939</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22078,7 +22049,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>175.4</v>
+        <v>175.91</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22087,7 +22058,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>3.2287003651421488E-2</v>
+        <v>3.8471761717977358E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22182,37 +22153,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="246" t="s">
+      <c r="C4" s="249" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22325,18 +22296,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="246" t="s">
+      <c r="C9" s="249" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="246"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="246"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="246"/>
-      <c r="K9" s="246"/>
-      <c r="L9" s="246"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="249"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22457,18 +22428,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="246" t="s">
+      <c r="C14" s="249" t="s">
         <v>397</v>
       </c>
-      <c r="D14" s="246"/>
-      <c r="E14" s="246"/>
-      <c r="F14" s="246"/>
-      <c r="G14" s="246"/>
-      <c r="H14" s="246"/>
-      <c r="I14" s="246"/>
-      <c r="J14" s="246"/>
-      <c r="K14" s="246"/>
-      <c r="L14" s="246"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="249"/>
+      <c r="K14" s="249"/>
+      <c r="L14" s="249"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22558,10 +22529,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="240" t="s">
+      <c r="B20" s="243" t="s">
         <v>399</v>
       </c>
-      <c r="C20" s="240"/>
+      <c r="C20" s="243"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22596,7 +22567,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12754500000000002</v>
+        <v>0.1257915</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22613,7 +22584,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C23/(C24-C25)</f>
-        <v>34.300060439815887</v>
+        <v>34.868585850470033</v>
       </c>
     </row>
   </sheetData>
@@ -22662,60 +22633,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="240"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="250" t="s">
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="252"/>
+      <c r="H3" s="253" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="240"/>
-      <c r="J3" s="240"/>
-      <c r="K3" s="240"/>
-      <c r="L3" s="240"/>
-      <c r="P3" s="251"/>
-      <c r="Q3" s="251"/>
-      <c r="R3" s="251"/>
-      <c r="S3" s="251"/>
-      <c r="T3" s="251"/>
-      <c r="U3" s="251"/>
-      <c r="V3" s="251"/>
-      <c r="W3" s="251"/>
-      <c r="X3" s="251"/>
-      <c r="Y3" s="251"/>
-      <c r="Z3" s="251"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
+      <c r="P3" s="254"/>
+      <c r="Q3" s="254"/>
+      <c r="R3" s="254"/>
+      <c r="S3" s="254"/>
+      <c r="T3" s="254"/>
+      <c r="U3" s="254"/>
+      <c r="V3" s="254"/>
+      <c r="W3" s="254"/>
+      <c r="X3" s="254"/>
+      <c r="Y3" s="254"/>
+      <c r="Z3" s="254"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="249" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="P5" s="251"/>
-      <c r="Q5" s="251"/>
-      <c r="R5" s="251"/>
-      <c r="S5" s="251"/>
-      <c r="T5" s="251"/>
-      <c r="U5" s="251"/>
-      <c r="V5" s="251"/>
-      <c r="W5" s="251"/>
-      <c r="X5" s="251"/>
-      <c r="Y5" s="251"/>
-      <c r="Z5" s="251"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="249"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
+      <c r="P5" s="254"/>
+      <c r="Q5" s="254"/>
+      <c r="R5" s="254"/>
+      <c r="S5" s="254"/>
+      <c r="T5" s="254"/>
+      <c r="U5" s="254"/>
+      <c r="V5" s="254"/>
+      <c r="W5" s="254"/>
+      <c r="X5" s="254"/>
+      <c r="Y5" s="254"/>
+      <c r="Z5" s="254"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22850,7 +22821,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>231759.88758823517</v>
+        <v>235693.73189726536</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22904,23 +22875,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11885.368104432895</v>
+        <v>11902.394215800361</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>11979.895005061804</v>
+        <v>12014.242636828894</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12075.173698556026</v>
+        <v>12127.142112717464</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12171.210164086657</v>
+        <v>12241.102520371873</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12268.010428378439</v>
+        <v>12356.133829512557</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22939,15 +22910,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>130872.35835913788</v>
+        <v>134049.79587983343</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="253" t="s">
+      <c r="B14" s="256" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="254"/>
+      <c r="C14" s="257"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22955,7 +22926,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>175.4</v>
+        <v>175.91</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22964,7 +22935,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>175.51049119967018</v>
+        <v>178.78553447149005</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22974,20 +22945,20 @@
       <c r="C17" s="156">
         <v>0.13</v>
       </c>
-      <c r="E17" s="252" t="s">
+      <c r="E17" s="255" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="253" t="s">
+      <c r="B19" s="256" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="254"/>
+      <c r="C19" s="257"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -23003,7 +22974,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.12108377847505866</v>
+        <v>0.11948009295443998</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -23021,7 +22992,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>184170</v>
+        <v>184705.5</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23048,15 +23019,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>191136</v>
+        <v>191671.5</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="253" t="s">
+      <c r="B28" s="256" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="254"/>
+      <c r="C28" s="257"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -23064,7 +23035,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>60379.657400515825</v>
+        <v>60641.015315231154</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23073,7 +23044,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>130872.35835913788</v>
+        <v>134049.79587983343</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23082,7 +23053,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>191252.0157596537</v>
+        <v>194690.81119506457</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23109,7 +23080,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>184286.0157596537</v>
+        <v>187724.81119506457</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23127,7 +23098,7 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>175.51049119967018</v>
+        <v>178.78553447149005</v>
       </c>
     </row>
   </sheetData>
@@ -29756,7 +29727,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>175.4</v>
+        <v>175.91</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29827,7 +29798,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>175.4</v>
+        <v>175.91</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31329,7 +31300,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>19.822921184877522</v>
+        <v>19.880559097102648</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31366,7 +31337,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.2767382227466646</v>
+        <v>4.2891734365072161</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31427,7 +31398,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.6588328874105143</v>
+        <v>6.678194374141297</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31488,7 +31459,7 @@
       </c>
       <c r="AC156" s="141">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>186274.80000000002</v>
+        <v>186816.41999999998</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31549,7 +31520,7 @@
       </c>
       <c r="AC157" s="141">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>193240.80000000002</v>
+        <v>193782.41999999998</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31586,7 +31557,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="179">
         <f ca="1">AC157/AC5</f>
-        <v>4.3850594535717535</v>
+        <v>4.3973500045384402</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31623,7 +31594,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="179">
         <f ca="1">AC157/AC12</f>
-        <v>18.909952050102753</v>
+        <v>18.962953322242878</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31758,7 +31729,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>25.965263451352108</v>
+        <v>26.040761081683858</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31795,7 +31766,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>24.835707649430269</v>
+        <v>24.90531777305366</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31832,7 +31803,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>3.8512992632390421E-2</v>
+        <v>3.8401335385829578E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31869,7 +31840,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.0446651665188399E-2</v>
+        <v>5.0300396237132887E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31906,7 +31877,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="152">
         <f ca="1">AC82/AC116</f>
-        <v>2.0467502850627137E-2</v>
+        <v>2.0408163265306121E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31943,7 +31914,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="152">
         <f ca="1">-AC63/AC156</f>
-        <v>4.9657817375189768E-2</v>
+        <v>4.9513848943256708E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31980,7 +31951,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="152">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>7.0191995911416893E-2</v>
+        <v>6.9988494587360159E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32483,7 +32454,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="152">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.73963627930348E-2</v>
+        <v>-3.7287942890673102E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33844,15 +33815,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="243" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="240"/>
-      <c r="E4" s="240" t="s">
+      <c r="C4" s="243"/>
+      <c r="E4" s="243" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33860,7 +33831,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>175.4</v>
+        <v>175.91</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33876,7 +33847,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>186274.80000000002</v>
+        <v>186816.41999999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33896,7 +33867,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>193240.80000000002</v>
+        <v>193782.41999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33916,7 +33887,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>19.822921184877522</v>
+        <v>19.880559097102648</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33936,7 +33907,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.2767382227466646</v>
+        <v>4.2891734365072161</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33956,7 +33927,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.6588328874105143</v>
+        <v>6.678194374141297</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33976,7 +33947,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.3850594535717535</v>
+        <v>4.3973500045384402</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33985,18 +33956,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>18.909952050102753</v>
+        <v>18.962953322242878</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="240" t="s">
+      <c r="B15" s="243" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="240"/>
-      <c r="E15" s="240" t="s">
+      <c r="C15" s="243"/>
+      <c r="E15" s="243" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="240"/>
+      <c r="F15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34047,14 +34018,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="240" t="s">
+      <c r="B21" s="243" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="240"/>
-      <c r="E21" s="240" t="s">
+      <c r="C21" s="243"/>
+      <c r="E21" s="243" t="s">
         <v>241</v>
       </c>
-      <c r="F21" s="240"/>
+      <c r="F21" s="243"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34123,14 +34094,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="240" t="s">
+      <c r="B29" s="243" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="240"/>
-      <c r="E29" s="240" t="s">
+      <c r="C29" s="243"/>
+      <c r="E29" s="243" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="240"/>
+      <c r="F29" s="243"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34206,14 +34177,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="240" t="s">
+      <c r="B37" s="243" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="240"/>
-      <c r="E37" s="240" t="s">
+      <c r="C37" s="243"/>
+      <c r="E37" s="243" t="s">
         <v>263</v>
       </c>
-      <c r="F37" s="240"/>
+      <c r="F37" s="243"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34221,7 +34192,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>5.0446651665188399E-2</v>
+        <v>5.0300396237132887E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -34237,7 +34208,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC164</f>
-        <v>3.8512992632390421E-2</v>
+        <v>3.8401335385829578E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -34253,7 +34224,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>2.0467502850627137E-2</v>
+        <v>2.0408163265306121E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -34269,7 +34240,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.9657817375189768E-2</v>
+        <v>4.9513848943256708E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34278,18 +34249,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>7.0191995911416893E-2</v>
+        <v>6.9988494587360159E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="240" t="s">
+      <c r="B45" s="243" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="240"/>
-      <c r="E45" s="240" t="s">
+      <c r="C45" s="243"/>
+      <c r="E45" s="243" t="s">
         <v>277</v>
       </c>
-      <c r="F45" s="240"/>
+      <c r="F45" s="243"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34322,18 +34293,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC179</f>
-        <v>-3.73963627930348E-2</v>
+        <v>-3.7287942890673102E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="240" t="s">
+      <c r="B51" s="243" t="s">
         <v>274</v>
       </c>
-      <c r="C51" s="240"/>
-      <c r="E51" s="240" t="s">
+      <c r="C51" s="243"/>
+      <c r="E51" s="243" t="s">
         <v>295</v>
       </c>
-      <c r="F51" s="240"/>
+      <c r="F51" s="243"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34502,7 +34473,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC115</f>
-        <v>175.4</v>
+        <v>175.91</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34531,7 +34502,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>186274.80000000002</v>
+        <v>186816.41999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34560,7 +34531,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>193240.80000000002</v>
+        <v>193782.41999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34589,7 +34560,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>19.822921184877522</v>
+        <v>19.880559097102648</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34618,7 +34589,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.2767382227466646</v>
+        <v>4.2891734365072161</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34647,7 +34618,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.6588328874105143</v>
+        <v>6.678194374141297</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34676,7 +34647,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.3850594535717535</v>
+        <v>4.3973500045384402</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34705,7 +34676,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>18.909952050102753</v>
+        <v>18.962953322242878</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35478,7 +35449,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>5.0446651665188399E-2</v>
+        <v>5.0300396237132887E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35507,7 +35478,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC164</f>
-        <v>3.8512992632390421E-2</v>
+        <v>3.8401335385829578E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35536,7 +35507,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>2.0467502850627137E-2</v>
+        <v>2.0408163265306121E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35565,7 +35536,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.9657817375189768E-2</v>
+        <v>4.9513848943256708E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35594,7 +35565,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>7.0191995911416893E-2</v>
+        <v>6.9988494587360159E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35830,7 +35801,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.73963627930348E-2</v>
+        <v>-3.7287942890673102E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36368,14 +36339,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="246" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="244"/>
-      <c r="F3" s="245" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="244"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36442,19 +36413,19 @@
       <c r="B7" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="241">
+      <c r="C7" s="244">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="242"/>
-      <c r="F7" s="241">
+      <c r="D7" s="245"/>
+      <c r="F7" s="244">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="242"/>
+      <c r="G7" s="245"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36481,19 +36452,19 @@
       <c r="B9" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="241">
+      <c r="C9" s="244">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="F9" s="241">
+      <c r="D9" s="245"/>
+      <c r="F9" s="244">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="242"/>
+      <c r="G9" s="245"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36520,19 +36491,19 @@
       <c r="B11" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="241">
+      <c r="C11" s="244">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="F11" s="241">
+      <c r="D11" s="245"/>
+      <c r="F11" s="244">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="242"/>
+      <c r="G11" s="245"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36559,19 +36530,19 @@
       <c r="B13" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="241">
+      <c r="C13" s="244">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="F13" s="241">
+      <c r="D13" s="245"/>
+      <c r="F13" s="244">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="242"/>
+      <c r="G13" s="245"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36598,19 +36569,19 @@
       <c r="B15" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="241">
+      <c r="C15" s="244">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="242"/>
-      <c r="F15" s="241">
+      <c r="D15" s="245"/>
+      <c r="F15" s="244">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="242"/>
+      <c r="G15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36637,19 +36608,19 @@
       <c r="B17" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="241">
+      <c r="C17" s="244">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="F17" s="241">
+      <c r="D17" s="245"/>
+      <c r="F17" s="244">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="242"/>
+      <c r="G17" s="245"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36676,22 +36647,22 @@
       <c r="B19" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="241">
+      <c r="C19" s="244">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="242"/>
-      <c r="F19" s="241">
+      <c r="D19" s="245"/>
+      <c r="F19" s="244">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="242"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36718,22 +36689,22 @@
       <c r="B21" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="241">
+      <c r="C21" s="244">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="242"/>
-      <c r="F21" s="241">
+      <c r="D21" s="245"/>
+      <c r="F21" s="244">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="242"/>
+      <c r="G21" s="245"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36781,22 +36752,22 @@
       <c r="B25" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="241">
+      <c r="C25" s="244">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="F25" s="241">
+      <c r="D25" s="245"/>
+      <c r="F25" s="244">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="242"/>
+      <c r="G25" s="245"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="218" t="s">
@@ -36823,22 +36794,22 @@
       <c r="B27" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="241">
+      <c r="C27" s="244">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="F27" s="241">
+      <c r="D27" s="245"/>
+      <c r="F27" s="244">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="242"/>
+      <c r="G27" s="245"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="218" t="s">
@@ -36865,22 +36836,22 @@
       <c r="B29" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="241">
+      <c r="C29" s="244">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="242"/>
-      <c r="F29" s="241">
+      <c r="D29" s="245"/>
+      <c r="F29" s="244">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="242"/>
+      <c r="G29" s="245"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36907,22 +36878,22 @@
       <c r="B31" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="241">
+      <c r="C31" s="244">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="F31" s="241">
+      <c r="D31" s="245"/>
+      <c r="F31" s="244">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="242"/>
+      <c r="G31" s="245"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36949,22 +36920,22 @@
       <c r="B33" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="241">
+      <c r="C33" s="244">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="242"/>
-      <c r="F33" s="241">
+      <c r="D33" s="245"/>
+      <c r="F33" s="244">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="242"/>
+      <c r="G33" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/QCOM.xlsx
+++ b/QCOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F17DE46-A926-544B-9D52-87621BCA2776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE42468D-6B97-7542-866F-82A051EE1214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="442">
   <si>
     <t>Ticker</t>
   </si>
@@ -1465,6 +1465,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2412,12 +2424,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2425,6 +2431,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2445,14 +2457,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12812,11 +12824,11 @@
     <v>Powered by Refinitiv</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6947000000000001</v>
-    <v>3.08</v>
-    <v>1.7821E-2</v>
-    <v>-1.1100000000000001</v>
-    <v>-6.3099999999999996E-3</v>
+    <v>1.6919999999999999</v>
+    <v>4.57</v>
+    <v>2.5445000000000002E-2</v>
+    <v>-7.0000000000000007E-2</v>
+    <v>-3.8010000000000002E-4</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -12824,26 +12836,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>176.97499999999999</v>
+    <v>184.42</v>
     <v>3</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46318.953474467191</v>
+    <v>46322.887403517969</v>
     <v>4</v>
-    <v>171.47499999999999</v>
-    <v>184705500000</v>
+    <v>179.29</v>
+    <v>193378500000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>172.07</v>
-    <v>20.359000000000002</v>
-    <v>172.83</v>
-    <v>175.91</v>
-    <v>174.8</v>
+    <v>180.97</v>
+    <v>21.315000000000001</v>
+    <v>179.6</v>
+    <v>184.17</v>
+    <v>184.1</v>
     <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>7252454</v>
-    <v>12653239</v>
+    <v>12243695</v>
+    <v>10413207</v>
     <v>1991</v>
   </rv>
   <rv s="4">
@@ -12867,17 +12879,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
     <v>7</v>
-    <v>49.39</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
-    <v>49.53</v>
+    <v>50.03</v>
+    <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13739,7 +13751,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC156</f>
-        <v>186816.41999999998</v>
+        <v>195588.53999999998</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13747,7 +13759,7 @@
       </c>
       <c r="I3" s="207">
         <f ca="1">'AVG target price'!C5</f>
-        <v>114.14814457588841</v>
+        <v>113.48184256510474</v>
       </c>
       <c r="K3" s="235" t="s">
         <v>432</v>
@@ -13766,7 +13778,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC157</f>
-        <v>193782.41999999998</v>
+        <v>202554.53999999998</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13774,7 +13786,7 @@
       </c>
       <c r="I4" s="207">
         <f ca="1">'AVG target price'!C6</f>
-        <v>215.12940524485441</v>
+        <v>214.69785427877648</v>
       </c>
       <c r="K4" s="235" t="s">
         <v>433</v>
@@ -13786,7 +13798,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>175.91</v>
+        <v>184.17</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>235</v>
@@ -13801,7 +13813,7 @@
       </c>
       <c r="I5" s="207">
         <f ca="1">'AVG target price'!C7</f>
-        <v>194.32059472485892</v>
+        <v>194.14075084278639</v>
       </c>
       <c r="K5" s="235" t="s">
         <v>434</v>
@@ -13813,14 +13825,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>174.8</v>
+        <v>184.1</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>229</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>19.880559097102648</v>
+        <v>20.814067244121393</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13828,7 +13840,7 @@
       </c>
       <c r="I6" s="207">
         <f ca="1">'AVG target price'!C8</f>
-        <v>183.14315051504727</v>
+        <v>182.77666049477983</v>
       </c>
       <c r="K6" s="236" t="s">
         <v>435</v>
@@ -13840,14 +13852,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>3.08</v>
+        <v>4.57</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>193</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>4.2891734365072161</v>
+        <v>4.490575133883997</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13855,7 +13867,7 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>206.64654295839802</v>
+        <v>206.23224637387236</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13864,14 +13876,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.1100000000000001</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC164</f>
-        <v>3.8401335385829578E-2</v>
+        <v>3.66790406022766E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13879,7 +13891,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C10</f>
-        <v>182.67756760380939</v>
+        <v>182.26587091106398</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13888,14 +13900,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.7821E-2</v>
+        <v>2.5445000000000002E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>280</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC165</f>
-        <v>5.0300396237132887E-2</v>
+        <v>4.8044430157322293E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13903,7 +13915,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>3.8471761717977358E-2</v>
+        <v>-1.0338975343085208E-2</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13912,14 +13924,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-6.3099999999999996E-3</v>
+        <v>-3.8010000000000002E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>285</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC167</f>
-        <v>4.9513848943256708E-2</v>
+        <v>4.7293159404942643E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13935,14 +13947,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC166</f>
-        <v>2.0408163265306121E-2</v>
+        <v>1.9492859857740134E-2</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>404</v>
       </c>
       <c r="I11" s="208">
         <f ca="1">DDM!C26</f>
-        <v>34.868585850470033</v>
+        <v>34.800000000000004</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -13967,7 +13979,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.6947000000000001</v>
+        <v>1.6919999999999999</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>96</v>
@@ -13990,7 +14002,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>12653239</v>
+        <v>10413207</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>97</v>
@@ -14004,7 +14016,7 @@
       </c>
       <c r="I14" s="238">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>178.78553447149005</v>
+        <v>177.84299475553453</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14013,7 +14025,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC179</f>
-        <v>-3.7287942890673102E-2</v>
+        <v>-3.5615583612414105E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14046,7 +14058,7 @@
       </c>
       <c r="I17" s="233">
         <f ca="1">DCF!C15</f>
-        <v>0.11948009295443998</v>
+        <v>0.11993606040333961</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14068,7 +14080,7 @@
       </c>
       <c r="I18" s="234">
         <f ca="1">Multiples!C54</f>
-        <v>0.1257915</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14140,7 +14152,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14155,7 +14167,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18753,12 +18765,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18766,6 +18772,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19825,16 +19837,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19956,7 +19968,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>175.91</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19965,7 +19977,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>186816.41999999998</v>
+        <v>195588.53999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19983,7 +19995,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19992,7 +20004,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>1.6947000000000001</v>
+        <v>1.6919999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20035,7 +20047,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.5561732450898977E-2</v>
+        <v>7.2418219342692977E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20044,7 +20056,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92443826754910097</v>
+        <v>0.92758178065730701</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20062,7 +20074,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1257915</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20071,7 +20083,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.11948009295443998</v>
+        <v>0.11993606040333961</v>
       </c>
     </row>
   </sheetData>
@@ -20322,7 +20334,7 @@
       </c>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>171470.14546929472</v>
+        <v>170646.59323361202</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -20376,23 +20388,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>5636.5899518286324</v>
+        <v>5634.2950872986848</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>3370.3374444785127</v>
+        <v>3367.5936247480677</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>5258.9819293956143</v>
+        <v>5252.5611652801654</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>7413.2704730084488</v>
+        <v>7401.2049760850841</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="0"/>
-        <v>8989.2423024134478</v>
+        <v>8970.9579296022075</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -20411,7 +20423,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>97522.907438468843</v>
+        <v>96857.10402112703</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20434,7 +20446,7 @@
       </c>
       <c r="C15" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11948009295443998</v>
+        <v>0.11993606040333961</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20449,7 +20461,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>30668.422101124655</v>
+        <v>30626.612783014207</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20458,7 +20470,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>97522.907438468843</v>
+        <v>96857.10402112703</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20467,7 +20479,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>128191.3295395935</v>
+        <v>127483.71680414124</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20494,7 +20506,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>121225.32953959348</v>
+        <v>120517.71680414124</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20512,7 +20524,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C24/C25</f>
-        <v>114.14814457588841</v>
+        <v>113.48184256510474</v>
       </c>
     </row>
   </sheetData>
@@ -20781,23 +20793,23 @@
       <c r="G9" s="138"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>5636.5899518286324</v>
+        <v>5634.2950872986848</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>3370.3374444785127</v>
+        <v>3367.5936247480677</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>5258.9819293956143</v>
+        <v>5252.5611652801654</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>7413.2704730084488</v>
+        <v>7401.2049760850841</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>8989.2423024134478</v>
+        <v>8970.9579296022075</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -21583,7 +21595,7 @@
       </c>
       <c r="C41" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11948009295443998</v>
+        <v>0.11993606040333961</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21609,7 +21621,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>213754.24857132419</v>
+        <v>213319.46639064859</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21618,7 +21630,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>235433.4283700354</v>
+        <v>234975.1212440606</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21645,7 +21657,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>228467.4283700354</v>
+        <v>228009.1212440606</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21663,7 +21675,7 @@
       </c>
       <c r="C50" s="232">
         <f ca="1">C48/C49</f>
-        <v>215.12940524485441</v>
+        <v>214.69785427877648</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21687,7 +21699,7 @@
       </c>
       <c r="C54" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1257915</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21722,7 +21734,7 @@
       </c>
       <c r="C58" s="232">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>194.32059472485892</v>
+        <v>194.14075084278639</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21746,7 +21758,7 @@
       </c>
       <c r="C62" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11948009295443998</v>
+        <v>0.11993606040333961</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21772,7 +21784,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>179784.84604826898</v>
+        <v>179419.15859204417</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21781,7 +21793,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>201464.02584698019</v>
+        <v>201074.81344545618</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21808,7 +21820,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>194498.02584698019</v>
+        <v>194108.81344545618</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21826,7 +21838,7 @@
       </c>
       <c r="C71" s="232">
         <f ca="1">C69/C70</f>
-        <v>183.14315051504727</v>
+        <v>182.77666049477983</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21850,7 +21862,7 @@
       </c>
       <c r="C75" s="135">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11948009295443998</v>
+        <v>0.11993606040333961</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21876,7 +21888,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>204745.44882310749</v>
+        <v>204328.99079564045</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21885,7 +21897,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>226424.6286218187</v>
+        <v>225984.64564905246</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21912,7 +21924,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>219458.6286218187</v>
+        <v>219018.64564905246</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21930,22 +21942,22 @@
       </c>
       <c r="C84" s="232">
         <f ca="1">C82/C83</f>
-        <v>206.64654295839802</v>
+        <v>206.23224637387236</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21995,7 +22007,7 @@
       </c>
       <c r="C5" s="133">
         <f ca="1">DCF!C26</f>
-        <v>114.14814457588841</v>
+        <v>113.48184256510474</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -22004,7 +22016,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Multiples!C50</f>
-        <v>215.12940524485441</v>
+        <v>214.69785427877648</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22013,7 +22025,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">Multiples!C58</f>
-        <v>194.32059472485892</v>
+        <v>194.14075084278639</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22022,7 +22034,7 @@
       </c>
       <c r="C8" s="133">
         <f ca="1">Multiples!C71</f>
-        <v>183.14315051504727</v>
+        <v>182.77666049477983</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22031,7 +22043,7 @@
       </c>
       <c r="C9" s="133">
         <f ca="1">Multiples!C84</f>
-        <v>206.64654295839802</v>
+        <v>206.23224637387236</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22040,7 +22052,7 @@
       </c>
       <c r="C10" s="232">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>182.67756760380939</v>
+        <v>182.26587091106398</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22049,7 +22061,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>175.91</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22058,7 +22070,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>3.8471761717977358E-2</v>
+        <v>-1.0338975343085208E-2</v>
       </c>
     </row>
   </sheetData>
@@ -22567,7 +22579,7 @@
       </c>
       <c r="C24" s="135">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1257915</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22584,7 +22596,7 @@
       </c>
       <c r="C26" s="232">
         <f ca="1">C23/(C24-C25)</f>
-        <v>34.868585850470033</v>
+        <v>34.800000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -22821,7 +22833,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>235693.73189726536</v>
+        <v>234561.72084479235</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22875,23 +22887,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>11902.394215800361</v>
+        <v>11897.548310289985</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>12014.242636828894</v>
+        <v>12004.46174202642</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12127.142112717464</v>
+        <v>12112.335916395501</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12241.102520371873</v>
+        <v>12221.179466797086</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" ca="1" si="1"/>
-        <v>12356.133829512557</v>
+        <v>12331.001104212257</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22910,15 +22922,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>134049.79587983343</v>
+        <v>133134.61795359</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="256" t="s">
+      <c r="B14" s="255" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="257"/>
+      <c r="C14" s="256"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22926,7 +22938,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>175.91</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22935,7 +22947,7 @@
       </c>
       <c r="C16" s="154">
         <f ca="1">C36</f>
-        <v>178.78553447149005</v>
+        <v>177.84299475553453</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22945,20 +22957,20 @@
       <c r="C17" s="156">
         <v>0.13</v>
       </c>
-      <c r="E17" s="255" t="s">
+      <c r="E17" s="257" t="s">
         <v>217</v>
       </c>
-      <c r="F17" s="255"/>
-      <c r="G17" s="255"/>
-      <c r="H17" s="255"/>
-      <c r="I17" s="255"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="256" t="s">
+      <c r="B19" s="255" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="257"/>
+      <c r="C19" s="256"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22974,7 +22986,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.11948009295443998</v>
+        <v>0.11993606040333961</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22992,7 +23004,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>184705.5</v>
+        <v>193378.5</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23019,15 +23031,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>191671.5</v>
+        <v>200344.5</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="256" t="s">
+      <c r="B28" s="255" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="257"/>
+      <c r="C28" s="256"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -23035,7 +23047,7 @@
       </c>
       <c r="C29" s="159">
         <f ca="1">SUM(H10:L10)</f>
-        <v>60641.015315231154</v>
+        <v>60566.526539721257</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23044,7 +23056,7 @@
       </c>
       <c r="C30" s="159">
         <f ca="1">L11</f>
-        <v>134049.79587983343</v>
+        <v>133134.61795359</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23053,7 +23065,7 @@
       </c>
       <c r="C31" s="162">
         <f ca="1">C29+C30</f>
-        <v>194690.81119506457</v>
+        <v>193701.14449331127</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23080,7 +23092,7 @@
       </c>
       <c r="C34" s="162">
         <f ca="1">C31+C32-C33</f>
-        <v>187724.81119506457</v>
+        <v>186735.14449331127</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23098,21 +23110,21 @@
       </c>
       <c r="C36" s="165">
         <f ca="1">C34/C35</f>
-        <v>178.78553447149005</v>
+        <v>177.84299475553453</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29727,7 +29739,7 @@
       </c>
       <c r="AC115" s="63">
         <f ca="1">Overview!C5</f>
-        <v>175.91</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -29798,7 +29810,7 @@
       </c>
       <c r="AC116" s="65">
         <f ca="1">AC115/AC85</f>
-        <v>175.91</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -31300,7 +31312,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="72">
         <f ca="1">AC116/Statement!AC26</f>
-        <v>19.880559097102648</v>
+        <v>20.814067244121393</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31337,7 +31349,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="72">
         <f ca="1">AC116/(Statement!AC5/Statement!AC22)</f>
-        <v>4.2891734365072161</v>
+        <v>4.490575133883997</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31398,7 +31410,7 @@
       </c>
       <c r="AC155" s="72">
         <f ca="1">AC116/(Statement!AC49/Statement!AC75)</f>
-        <v>6.678194374141297</v>
+        <v>6.9917745317810391</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31459,7 +31471,7 @@
       </c>
       <c r="AC156" s="141">
         <f ca="1">Statement!AC116*Statement!AC78</f>
-        <v>186816.41999999998</v>
+        <v>195588.53999999998</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31520,7 +31532,7 @@
       </c>
       <c r="AC157" s="141">
         <f ca="1">AC156+AC107-AC106+AC48+AC45</f>
-        <v>193782.41999999998</v>
+        <v>202554.53999999998</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31557,7 +31569,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="179">
         <f ca="1">AC157/AC5</f>
-        <v>4.3973500045384402</v>
+        <v>4.5964087319596985</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31594,7 +31606,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="179">
         <f ca="1">AC157/AC12</f>
-        <v>18.962953322242878</v>
+        <v>19.821366082786962</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31729,7 +31741,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="72">
         <f t="shared" ref="AC162:AC163" ca="1" si="173">AC156/AC160</f>
-        <v>26.040761081683858</v>
+        <v>27.263526623919706</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31766,7 +31778,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="72">
         <f t="shared" ca="1" si="173"/>
-        <v>24.90531777305366</v>
+        <v>26.032728794875762</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31803,7 +31815,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="74">
         <f t="shared" ref="AC164" ca="1" si="176">AC160/AC156</f>
-        <v>3.8401335385829578E-2</v>
+        <v>3.66790406022766E-2</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31840,7 +31852,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="74">
         <f ca="1">AC26/AC116</f>
-        <v>5.0300396237132887E-2</v>
+        <v>4.8044430157322293E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31877,7 +31889,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="152">
         <f ca="1">AC82/AC116</f>
-        <v>2.0408163265306121E-2</v>
+        <v>1.9492859857740134E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -31914,7 +31926,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="152">
         <f ca="1">-AC63/AC156</f>
-        <v>4.9513848943256708E-2</v>
+        <v>4.7293159404942643E-2</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -31951,7 +31963,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="152">
         <f ca="1">-(AC63+AC64)/AC156</f>
-        <v>6.9988494587360159E-2</v>
+        <v>6.6849519915635147E-2</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32454,7 +32466,7 @@
       <c r="AA179" s="49"/>
       <c r="AC179" s="152">
         <f ca="1">(AC106-AC107)/AC156</f>
-        <v>-3.7287942890673102E-2</v>
+        <v>-3.5615583612414105E-2</v>
       </c>
     </row>
     <row r="180" spans="1:31" x14ac:dyDescent="0.2">
@@ -33798,7 +33810,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -33831,7 +33843,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>175.91</v>
+        <v>184.17</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33847,7 +33859,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>186816.41999999998</v>
+        <v>195588.53999999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33867,7 +33879,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>193782.41999999998</v>
+        <v>202554.53999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33887,7 +33899,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>19.880559097102648</v>
+        <v>20.814067244121393</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>235</v>
@@ -33907,7 +33919,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.2891734365072161</v>
+        <v>4.490575133883997</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>236</v>
@@ -33927,7 +33939,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.678194374141297</v>
+        <v>6.9917745317810391</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33947,7 +33959,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.3973500045384402</v>
+        <v>4.5964087319596985</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33956,7 +33968,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>18.962953322242878</v>
+        <v>19.821366082786962</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34192,7 +34204,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>5.0300396237132887E-2</v>
+        <v>4.8044430157322293E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>262</v>
@@ -34208,7 +34220,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC164</f>
-        <v>3.8401335385829578E-2</v>
+        <v>3.66790406022766E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>264</v>
@@ -34224,7 +34236,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>2.0408163265306121E-2</v>
+        <v>1.9492859857740134E-2</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>265</v>
@@ -34240,7 +34252,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.9513848943256708E-2</v>
+        <v>4.7293159404942643E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34249,7 +34261,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>6.9988494587360159E-2</v>
+        <v>6.6849519915635147E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34293,7 +34305,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC179</f>
-        <v>-3.7287942890673102E-2</v>
+        <v>-3.5615583612414105E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34347,8 +34359,51 @@
         <v>1.2619198982835347</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="243" t="s">
+        <v>438</v>
+      </c>
+      <c r="C57" s="243"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="C58" s="170">
+        <f ca="1">Statement!AC162</f>
+        <v>27.263526623919706</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="C59" s="170">
+        <f ca="1">Statement!AC163</f>
+        <v>26.032728794875762</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="C60" s="171">
+        <f>Statement!AC169</f>
+        <v>0.17656269414462794</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="C61" s="171">
+        <f>Statement!AC170</f>
+        <v>0.16279386402831986</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -34373,7 +34428,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I96"/>
+  <dimension ref="B1:I102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -34473,7 +34528,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC115</f>
-        <v>175.91</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34502,7 +34557,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>186816.41999999998</v>
+        <v>195588.53999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34531,7 +34586,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC157</f>
-        <v>193782.41999999998</v>
+        <v>202554.53999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34560,7 +34615,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>19.880559097102648</v>
+        <v>20.814067244121393</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34589,7 +34644,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>4.2891734365072161</v>
+        <v>4.490575133883997</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34618,7 +34673,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC155</f>
-        <v>6.678194374141297</v>
+        <v>6.9917745317810391</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34647,7 +34702,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>4.3973500045384402</v>
+        <v>4.5964087319596985</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34676,7 +34731,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC159</f>
-        <v>18.962953322242878</v>
+        <v>19.821366082786962</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35449,7 +35504,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC165</f>
-        <v>5.0300396237132887E-2</v>
+        <v>4.8044430157322293E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35478,7 +35533,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC164</f>
-        <v>3.8401335385829578E-2</v>
+        <v>3.66790406022766E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35507,7 +35562,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC166</f>
-        <v>2.0408163265306121E-2</v>
+        <v>1.9492859857740134E-2</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35536,7 +35591,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC167</f>
-        <v>4.9513848943256708E-2</v>
+        <v>4.7293159404942643E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35565,7 +35620,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC168</f>
-        <v>6.9988494587360159E-2</v>
+        <v>6.6849519915635147E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35801,7 +35856,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC179</f>
-        <v>-3.7287942890673102E-2</v>
+        <v>-3.5615583612414105E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36138,183 +36193,310 @@
       </c>
       <c r="I85" s="193"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="C88" s="170">
+        <f>Statement!M162</f>
+        <v>21.811802433786685</v>
+      </c>
+      <c r="D88" s="170">
+        <f>Statement!N162</f>
+        <v>28.638486362689985</v>
+      </c>
+      <c r="E88" s="170">
+        <f>Statement!O162</f>
+        <v>16.404203665987779</v>
+      </c>
+      <c r="F88" s="170">
+        <f>Statement!P162</f>
+        <v>22.482820392341125</v>
+      </c>
+      <c r="G88" s="170">
+        <f>Statement!Q162</f>
+        <v>18.206236923383482</v>
+      </c>
+      <c r="I88" s="170">
+        <f ca="1">Statement!AC162</f>
+        <v>27.263526623919706</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="C89" s="170">
+        <f>Statement!M163</f>
+        <v>19.834913152264804</v>
+      </c>
+      <c r="D89" s="170">
+        <f>Statement!N163</f>
+        <v>27.867839537332323</v>
+      </c>
+      <c r="E89" s="170">
+        <f>Statement!O163</f>
+        <v>11.081541471136106</v>
+      </c>
+      <c r="F89" s="170">
+        <f>Statement!P163</f>
+        <v>17.214522225380236</v>
+      </c>
+      <c r="G89" s="170">
+        <f>Statement!Q163</f>
+        <v>15.89200834223236</v>
+      </c>
+      <c r="I89" s="170">
+        <f ca="1">Statement!AC163</f>
+        <v>26.032728794875762</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="C90" s="171">
+        <f>Statement!M169</f>
+        <v>0.23384112648821215</v>
+      </c>
+      <c r="D90" s="171">
+        <f>Statement!N169</f>
+        <v>0.11905795584207608</v>
+      </c>
+      <c r="E90" s="171">
+        <f>Statement!O169</f>
+        <v>0.31463370639754373</v>
+      </c>
+      <c r="F90" s="171">
+        <f>Statement!P169</f>
+        <v>0.28735163264579622</v>
+      </c>
+      <c r="G90" s="171">
+        <f>Statement!Q169</f>
+        <v>0.26627195069724097</v>
+      </c>
+      <c r="I90" s="171">
+        <f>Statement!AC169</f>
+        <v>0.17656269414462794</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="C91" s="171">
+        <f>Statement!M170</f>
+        <v>0.20809747959244473</v>
+      </c>
+      <c r="D91" s="171">
+        <f>Statement!N170</f>
+        <v>0.10866515837104072</v>
+      </c>
+      <c r="E91" s="171">
+        <f>Statement!O170</f>
+        <v>0.20561139028475711</v>
+      </c>
+      <c r="F91" s="171">
+        <f>Statement!P170</f>
+        <v>0.21849494379138648</v>
+      </c>
+      <c r="G91" s="171">
+        <f>Statement!Q170</f>
+        <v>0.22665070905970552</v>
+      </c>
+      <c r="I91" s="171">
+        <f>Statement!AC170</f>
+        <v>0.16279386402831986</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C94" s="171">
+        <f>Statement!M206</f>
+        <v>-1</v>
+      </c>
+      <c r="D94" s="171">
+        <f>Statement!N206</f>
+        <v>6.7819148936170207E-2</v>
+      </c>
+      <c r="E94" s="171">
+        <f>Statement!O206</f>
+        <v>7.7833125778331264E-2</v>
+      </c>
+      <c r="F94" s="171">
+        <f>Statement!P206</f>
+        <v>6.4991334488734842E-2</v>
+      </c>
+      <c r="G94" s="171">
+        <f>Statement!Q206</f>
+        <v>3.2004339571467318E-2</v>
+      </c>
+      <c r="I94" s="193"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="218" t="s">
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="218" t="s">
         <v>376</v>
       </c>
-      <c r="C89" s="171">
+      <c r="C98" s="171">
         <f>Statement!M198</f>
         <v>1</v>
       </c>
-      <c r="D89" s="171">
+      <c r="D98" s="171">
         <f>Statement!N198</f>
         <v>0.48704693998811643</v>
       </c>
-      <c r="E89" s="171">
+      <c r="E98" s="171">
         <f>Statement!O198</f>
         <v>-9.8173972110121063E-2</v>
       </c>
-      <c r="F89" s="171">
+      <c r="F98" s="171">
         <f>Statement!P198</f>
         <v>0.10159503766061143</v>
       </c>
-      <c r="G89" s="171">
+      <c r="G98" s="171">
         <f>Statement!Q198</f>
         <v>0.11784579495636086</v>
       </c>
-      <c r="I89" s="193"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="218" t="s">
+      <c r="I98" s="193"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="218" t="s">
         <v>377</v>
       </c>
-      <c r="C90" s="171">
+      <c r="C99" s="171">
         <f>Statement!M199</f>
         <v>1</v>
       </c>
-      <c r="D90" s="171">
+      <c r="D99" s="171">
         <f>Statement!N199</f>
         <v>0.40717948717948715</v>
       </c>
-      <c r="E90" s="171">
+      <c r="E99" s="171">
         <f>Statement!O199</f>
         <v>0.36443148688046645</v>
       </c>
-      <c r="F90" s="171">
+      <c r="F99" s="171">
         <f>Statement!P199</f>
         <v>0.55448717948717952</v>
       </c>
-      <c r="G90" s="171">
+      <c r="G99" s="171">
         <f>Statement!Q199</f>
         <v>0.35979381443298969</v>
       </c>
-      <c r="I90" s="193"/>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B91" s="218" t="s">
+      <c r="I99" s="193"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="218" t="s">
         <v>378</v>
       </c>
-      <c r="C91" s="171">
+      <c r="C100" s="171">
         <f>Statement!M200</f>
         <v>1</v>
       </c>
-      <c r="D91" s="171">
+      <c r="D100" s="171">
         <f>Statement!N200</f>
         <v>0.37420886075949367</v>
       </c>
-      <c r="E91" s="171">
+      <c r="E100" s="171">
         <f>Statement!O200</f>
         <v>-0.14507772020725387</v>
       </c>
-      <c r="F91" s="171">
+      <c r="F100" s="171">
         <f>Statement!P200</f>
         <v>-8.7037037037037038E-2</v>
       </c>
-      <c r="G91" s="171">
+      <c r="G100" s="171">
         <f>Statement!Q200</f>
         <v>0.22017333579199705</v>
       </c>
-      <c r="I91" s="193"/>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B92" s="20" t="s">
+      <c r="I100" s="193"/>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B101" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="C92" s="171">
+      <c r="C101" s="171">
         <f>Statement!M201</f>
         <v>1</v>
       </c>
-      <c r="D92" s="171">
+      <c r="D101" s="171">
         <f>Statement!N201</f>
         <v>0.39446315555720046</v>
       </c>
-      <c r="E92" s="171">
+      <c r="E101" s="171">
         <f>Statement!O201</f>
         <v>-0.19361944953154445</v>
       </c>
-      <c r="F92" s="171">
+      <c r="F101" s="171">
         <f>Statement!P201</f>
         <v>9.2620630636561119E-2</v>
       </c>
-      <c r="G92" s="171">
+      <c r="G101" s="171">
         <f>Statement!Q201</f>
         <v>0.15577177973249789</v>
       </c>
-      <c r="I92" s="193"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B93" s="20" t="s">
+      <c r="I101" s="193"/>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B102" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="C93" s="171">
+      <c r="C102" s="171">
         <f>Statement!M202</f>
         <v>1</v>
       </c>
-      <c r="D93" s="171">
+      <c r="D102" s="171">
         <f>Statement!N202</f>
         <v>6.0126582278481012E-3</v>
       </c>
-      <c r="E93" s="171">
+      <c r="E102" s="171">
         <f>Statement!O202</f>
         <v>-0.16546083674111356</v>
       </c>
-      <c r="F93" s="171">
+      <c r="F102" s="171">
         <f>Statement!P202</f>
         <v>5.0131926121372031E-2</v>
       </c>
-      <c r="G93" s="171">
+      <c r="G102" s="171">
         <f>Statement!Q202</f>
         <v>1.7946877243359654E-3</v>
       </c>
-      <c r="I93" s="193"/>
-    </row>
-    <row r="95" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="C95" s="14"/>
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14"/>
-      <c r="I95" s="14"/>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B96" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C96" s="171">
-        <f>Statement!M205</f>
-        <v>0</v>
-      </c>
-      <c r="D96" s="171">
-        <f>Statement!N206</f>
-        <v>6.7819148936170207E-2</v>
-      </c>
-      <c r="E96" s="171">
-        <f>Statement!O206</f>
-        <v>7.7833125778331264E-2</v>
-      </c>
-      <c r="F96" s="171">
-        <f>Statement!P206</f>
-        <v>6.4991334488734842E-2</v>
-      </c>
-      <c r="G96" s="171">
-        <f>Statement!Q206</f>
-        <v>3.2004339571467318E-2</v>
-      </c>
-      <c r="I96" s="193"/>
+      <c r="I102" s="193"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36339,14 +36521,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="244" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="245"/>
+      <c r="F3" s="246" t="s">
         <v>306</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="245"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36413,19 +36595,19 @@
       <c r="B7" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="247">
         <f>Statement!AA89</f>
         <v>-6.1515237286536469E-2</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>-4.9498327759197325E-2</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36452,19 +36634,19 @@
       <c r="B9" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="247">
         <f>Statement!AA90</f>
         <v>-4.6938775510204082E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>1.3894919669995658E-2</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36491,19 +36673,19 @@
       <c r="B11" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="247">
         <f>Statement!AA91</f>
         <v>-7.4048078610282508E-2</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>-9.933435739887353E-2</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36530,19 +36712,19 @@
       <c r="B13" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="247">
         <f>Statement!AA94</f>
         <v>7.6991150442477882E-2</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.21821821821821821</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36569,19 +36751,19 @@
       <c r="B15" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="247">
         <f>Statement!AA95</f>
         <v>-0.29579904720658295</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>-0.41129616220130338</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36608,19 +36790,19 @@
       <c r="B17" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="247">
         <f>Statement!AA97</f>
         <v>3.6231884057971016E-2</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-0.24906226556639161</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36647,22 +36829,22 @@
       <c r="B19" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-2.798507462686567E-3</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-2.7297543221110099E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36689,22 +36871,22 @@
       <c r="B21" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>3.7598343685300246E-2</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-0.23360655737704911</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36752,22 +36934,22 @@
       <c r="B25" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>-0.15571049136786189</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>-0.19627054361567636</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="218" t="s">
@@ -36794,22 +36976,22 @@
       <c r="B27" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.1975867269984917</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.61382113821138207</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="218" t="s">
@@ -36836,22 +37018,22 @@
       <c r="B29" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>6.0254924681344149E-2</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>8.8637715645449131E-2</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="248"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36878,22 +37060,22 @@
       <c r="B31" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="244">
+      <c r="C31" s="247">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>-6.3023358307624511E-2</v>
       </c>
-      <c r="D31" s="245"/>
-      <c r="F31" s="244">
+      <c r="D31" s="248"/>
+      <c r="F31" s="247">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>-5.4375625486489491E-2</v>
       </c>
-      <c r="G31" s="245"/>
+      <c r="G31" s="248"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36920,43 +37102,25 @@
       <c r="B33" s="202" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="244">
+      <c r="C33" s="247">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>-7.5253256150506515E-2</v>
       </c>
-      <c r="D33" s="245"/>
-      <c r="F33" s="244">
+      <c r="D33" s="248"/>
+      <c r="F33" s="247">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-3.0349013657056147E-2</v>
       </c>
-      <c r="G33" s="245"/>
+      <c r="G33" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C31:D31"/>
@@ -36967,6 +37131,24 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
